--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3BFE18-D171-4349-B224-EF101203D4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E4982B-5E04-40E1-B836-90E1349E03AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="944">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="948">
   <si>
     <t>Jugador</t>
   </si>
@@ -1176,9 +1176,6 @@
     <t>PT Jan Oblak</t>
   </si>
   <si>
-    <t>PT Yann Sommer</t>
-  </si>
-  <si>
     <t>PT Yassine Bounou</t>
   </si>
   <si>
@@ -1194,9 +1191,6 @@
     <t>PT Alisson Becker</t>
   </si>
   <si>
-    <t>PT Christian Abbiati</t>
-  </si>
-  <si>
     <t>PT David Raya</t>
   </si>
   <si>
@@ -1221,9 +1215,6 @@
     <t>PT Andriy Lunin</t>
   </si>
   <si>
-    <t>PT Luis Malagon</t>
-  </si>
-  <si>
     <t>CT Alessandro Bastoni</t>
   </si>
   <si>
@@ -1260,9 +1251,6 @@
     <t>LI Paolo Maldini</t>
   </si>
   <si>
-    <t>LD Gabriele Zappa</t>
-  </si>
-  <si>
     <t>LD Trent Alexander-Arnold</t>
   </si>
   <si>
@@ -1314,9 +1302,6 @@
     <t>CT Jean-Clair Todibo</t>
   </si>
   <si>
-    <t>MCD Robert Andrich</t>
-  </si>
-  <si>
     <t>LI Andrew Robertson</t>
   </si>
   <si>
@@ -1338,9 +1323,6 @@
     <t>LI Álvaro Carreras</t>
   </si>
   <si>
-    <t>CT Dean Huijsen (P)</t>
-  </si>
-  <si>
     <t>LI Joško Gvardiol</t>
   </si>
   <si>
@@ -1356,9 +1338,6 @@
     <t>LI Ferdi Kadıoğlu</t>
   </si>
   <si>
-    <t>LI Maximiliano Araújo</t>
-  </si>
-  <si>
     <t>CT Ibrahima Konaté</t>
   </si>
   <si>
@@ -1368,9 +1347,6 @@
     <t>CT Dayot Upamecano</t>
   </si>
   <si>
-    <t>MCD Fabinho</t>
-  </si>
-  <si>
     <t>LD Marcos Llorente</t>
   </si>
   <si>
@@ -1419,18 +1395,12 @@
     <t>LI Alphonso Davies</t>
   </si>
   <si>
-    <t>CT John Stones</t>
-  </si>
-  <si>
     <t>LI Riccardo Calafiori</t>
   </si>
   <si>
     <t>CT Stefan de Vrij</t>
   </si>
   <si>
-    <t>MCD Martín Zubimendi</t>
-  </si>
-  <si>
     <t>MCD Thomas Partey</t>
   </si>
   <si>
@@ -1464,9 +1434,6 @@
     <t>MCD Youssouf Fofana</t>
   </si>
   <si>
-    <t>MCD James Garner</t>
-  </si>
-  <si>
     <t>MCD Manuel Ugarte</t>
   </si>
   <si>
@@ -1500,18 +1467,12 @@
     <t>LD Malo Gusto</t>
   </si>
   <si>
-    <t>MC Mikel Merino</t>
-  </si>
-  <si>
     <t>MC Pedri</t>
   </si>
   <si>
     <t>MC Alexis Mac Allister</t>
   </si>
   <si>
-    <t>MC Manuel Locatelli</t>
-  </si>
-  <si>
     <t>MCD Joshua Kimmich</t>
   </si>
   <si>
@@ -1530,9 +1491,6 @@
     <t>CT Rafael Márquez</t>
   </si>
   <si>
-    <t>MP Dominik Szoboszlai</t>
-  </si>
-  <si>
     <t>DC Kai Havertz</t>
   </si>
   <si>
@@ -1542,18 +1500,12 @@
     <t>II Rodrygo</t>
   </si>
   <si>
-    <t>MC Nico Paz (P)</t>
-  </si>
-  <si>
     <t>ED Dirk Kuyt</t>
   </si>
   <si>
     <t>DC Ademola Lookman</t>
   </si>
   <si>
-    <t>MP Antoine Griezmann</t>
-  </si>
-  <si>
     <t>EI Kingsley Coman</t>
   </si>
   <si>
@@ -1566,12 +1518,6 @@
     <t>MC Isco</t>
   </si>
   <si>
-    <t>MP Andreas Schjelderup</t>
-  </si>
-  <si>
-    <t>MC Petar Sučić</t>
-  </si>
-  <si>
     <t>MCD Jorginho</t>
   </si>
   <si>
@@ -1581,12 +1527,6 @@
     <t>CT Jesús Orozco</t>
   </si>
   <si>
-    <t>MP Rivaldo</t>
-  </si>
-  <si>
-    <t>ID Orkun Kökçü</t>
-  </si>
-  <si>
     <t>ED Lionel Messi</t>
   </si>
   <si>
@@ -1602,9 +1542,6 @@
     <t>DC Bryan Mbeumo</t>
   </si>
   <si>
-    <t>EI Mattia Zaccagni</t>
-  </si>
-  <si>
     <t>ID Mohammed Kudus</t>
   </si>
   <si>
@@ -1623,39 +1560,21 @@
     <t>MP Pablo Fornals</t>
   </si>
   <si>
-    <t>MCD Declan Rice</t>
-  </si>
-  <si>
     <t>DC Liam Delap</t>
   </si>
   <si>
-    <t>MCD Mateo Kovacic</t>
-  </si>
-  <si>
     <t>EI Raphinha</t>
   </si>
   <si>
-    <t>SD Ruud Gullit</t>
-  </si>
-  <si>
-    <t>DC Julián Álvarez (P)</t>
-  </si>
-  <si>
     <t>DC Erling Haaland</t>
   </si>
   <si>
     <t>ED Bernardo Silva</t>
   </si>
   <si>
-    <t>EI Federico Chiesa</t>
-  </si>
-  <si>
     <t>ED Leroy Sané</t>
   </si>
   <si>
-    <t>ED Iñaki Williams</t>
-  </si>
-  <si>
     <t>DC Victor Osimhen</t>
   </si>
   <si>
@@ -1677,9 +1596,6 @@
     <t>MP Bruno Fernandes</t>
   </si>
   <si>
-    <t>SD Lee Kang-in</t>
-  </si>
-  <si>
     <t>MP Calvin Stengs</t>
   </si>
   <si>
@@ -1689,9 +1605,6 @@
     <t>DC João Pedro</t>
   </si>
   <si>
-    <t>DC Gabriel Batistuta</t>
-  </si>
-  <si>
     <t>DC Cristiano Ronaldo</t>
   </si>
   <si>
@@ -1731,15 +1644,6 @@
     <t>DC Alexander Sørloth</t>
   </si>
   <si>
-    <t>ED Angel Correa</t>
-  </si>
-  <si>
-    <t>PT Anatolii Trubin</t>
-  </si>
-  <si>
-    <t>PT Antonio Sivera</t>
-  </si>
-  <si>
     <t>PT Mike Maignan</t>
   </si>
   <si>
@@ -1755,12 +1659,6 @@
     <t>MC Marc Bernal</t>
   </si>
   <si>
-    <t>CT Francesco Acerbi</t>
-  </si>
-  <si>
-    <t>PT Joan Garcia</t>
-  </si>
-  <si>
     <t>PT Gregor Kobel</t>
   </si>
   <si>
@@ -1770,9 +1668,6 @@
     <t>PT David Soria</t>
   </si>
   <si>
-    <t>PT Orlando Gil</t>
-  </si>
-  <si>
     <t>LD Nahuel Molina</t>
   </si>
   <si>
@@ -1785,9 +1680,6 @@
     <t>ED Roberto Alvarado</t>
   </si>
   <si>
-    <t>CT Bremer</t>
-  </si>
-  <si>
     <t>CT Tarik Muharemović</t>
   </si>
   <si>
@@ -1809,9 +1701,6 @@
     <t>LI Myles Lewis-Skelly</t>
   </si>
   <si>
-    <t>CT Jakud Kiwior</t>
-  </si>
-  <si>
     <t>CT Manuel Akanji</t>
   </si>
   <si>
@@ -1824,9 +1713,6 @@
     <t>CT Jhon Lucumí</t>
   </si>
   <si>
-    <t>CT Hans Vanaken</t>
-  </si>
-  <si>
     <t>DC Wayne Rooney</t>
   </si>
   <si>
@@ -1845,21 +1731,9 @@
     <t>CT Cristhian Mosquera</t>
   </si>
   <si>
-    <t>MC Tomoya Miki</t>
-  </si>
-  <si>
-    <t>LD João Neves</t>
-  </si>
-  <si>
-    <t>DC Joselu</t>
-  </si>
-  <si>
     <t>MCD Ryan Gravenberch</t>
   </si>
   <si>
-    <t>MC Nico González</t>
-  </si>
-  <si>
     <t>LD Pedro Porro</t>
   </si>
   <si>
@@ -1875,18 +1749,12 @@
     <t>MCD Raphael Onyedika</t>
   </si>
   <si>
-    <t>EI Facundo Pellistri</t>
-  </si>
-  <si>
     <t>EI Bradley Barcola</t>
   </si>
   <si>
     <t>CT Nehuén Pérez</t>
   </si>
   <si>
-    <t>ID Alex Zendejas</t>
-  </si>
-  <si>
     <t>CT Willian Pacho</t>
   </si>
   <si>
@@ -1902,15 +1770,9 @@
     <t>MCD Rúben Neves</t>
   </si>
   <si>
-    <t>ED Malcom</t>
-  </si>
-  <si>
     <t>DC Omar Marmoush</t>
   </si>
   <si>
-    <t>MC Pascal Groß</t>
-  </si>
-  <si>
     <t>ID Denzel Dumfries</t>
   </si>
   <si>
@@ -1929,9 +1791,6 @@
     <t>CT Jan Paul van Hecke</t>
   </si>
   <si>
-    <t>MP Morgan Rogers</t>
-  </si>
-  <si>
     <t>CT Piero Hincapié</t>
   </si>
   <si>
@@ -1941,24 +1800,15 @@
     <t>LI Milos Kerkez</t>
   </si>
   <si>
-    <t>CT Lucas Hernández</t>
-  </si>
-  <si>
     <t>LD Jules Koundé</t>
   </si>
   <si>
-    <t>MC Javi Guerra</t>
-  </si>
-  <si>
     <t>MCD Marcelo Brozović</t>
   </si>
   <si>
     <t>SD Paulo Dybala</t>
   </si>
   <si>
-    <t>EI Ousmane Dembélé</t>
-  </si>
-  <si>
     <t>MP Rodrigo Mora</t>
   </si>
   <si>
@@ -1968,15 +1818,6 @@
     <t>MC Sandro Tonali</t>
   </si>
   <si>
-    <t>MCD Pape Gueye</t>
-  </si>
-  <si>
-    <t>LD Nordi Mukiele</t>
-  </si>
-  <si>
-    <t>MC Qazim Laci</t>
-  </si>
-  <si>
     <t>MC Marcel Sabitzer</t>
   </si>
   <si>
@@ -1998,9 +1839,6 @@
     <t>MCD N'Golo Kanté</t>
   </si>
   <si>
-    <t>MP Malik Tillman</t>
-  </si>
-  <si>
     <t>MCD Hakan Çalhanoğlu</t>
   </si>
   <si>
@@ -2049,9 +1887,6 @@
     <t>MC Frenkie de Jong</t>
   </si>
   <si>
-    <t>MP Jude Bellingham</t>
-  </si>
-  <si>
     <t>MP Brahim Díaz</t>
   </si>
   <si>
@@ -2061,18 +1896,12 @@
     <t>II Conor Gallagher</t>
   </si>
   <si>
-    <t>ID Yéremy Pino</t>
-  </si>
-  <si>
     <t>MP Raheem Sterling</t>
   </si>
   <si>
     <t>MP Marco Asensio</t>
   </si>
   <si>
-    <t>MP Xavi Simons</t>
-  </si>
-  <si>
     <t>MCD Granit Xhaka</t>
   </si>
   <si>
@@ -2082,15 +1911,9 @@
     <t>DC Benjamin Šeško</t>
   </si>
   <si>
-    <t>DC Son Heung-min</t>
-  </si>
-  <si>
     <t>MC Fabián Ruiz</t>
   </si>
   <si>
-    <t>DC Álvaro Morata</t>
-  </si>
-  <si>
     <t>MP Rayan Cherki</t>
   </si>
   <si>
@@ -2100,9 +1923,6 @@
     <t>MC Vitinha</t>
   </si>
   <si>
-    <t>ID Arda Güler</t>
-  </si>
-  <si>
     <t>MP Christopher Nkunku</t>
   </si>
   <si>
@@ -2124,36 +1944,21 @@
     <t>MP Oihan Sancet</t>
   </si>
   <si>
-    <t>MP Ismael Saibari</t>
-  </si>
-  <si>
     <t>LI Antonee Robinson</t>
   </si>
   <si>
     <t>CT Strahinja Pavlović</t>
   </si>
   <si>
-    <t>EI João Félix</t>
-  </si>
-  <si>
     <t>MP Nicolò Zaniolo</t>
   </si>
   <si>
     <t>DC Tammy Abraham</t>
   </si>
   <si>
-    <t>II Nico Williams</t>
-  </si>
-  <si>
-    <t>ID Giuliano Simeone</t>
-  </si>
-  <si>
     <t>MP Jamal Musiala</t>
   </si>
   <si>
-    <t>EI Igor Paixão</t>
-  </si>
-  <si>
     <t>EI Jérémy Doku</t>
   </si>
   <si>
@@ -2181,42 +1986,15 @@
     <t>MP Bilal El Khannouss</t>
   </si>
   <si>
-    <t>ED Ismaïla Sarr</t>
-  </si>
-  <si>
     <t>CT José María Giménez</t>
   </si>
   <si>
     <t>MP Matheus Cunha</t>
   </si>
   <si>
-    <t>DC Pio Esposito</t>
-  </si>
-  <si>
-    <t>MP Talisca</t>
-  </si>
-  <si>
     <t>MP Fermín López</t>
   </si>
   <si>
-    <t>ED Franco Mastantuono</t>
-  </si>
-  <si>
-    <t>ED Phil Foden</t>
-  </si>
-  <si>
-    <t>CT Roger Ibañez</t>
-  </si>
-  <si>
-    <t>CT Rubén Dias</t>
-  </si>
-  <si>
-    <t>DC Samu Aghehowa</t>
-  </si>
-  <si>
-    <t>ED Estêvão</t>
-  </si>
-  <si>
     <t>EI Gabriel Martinelli</t>
   </si>
   <si>
@@ -2232,9 +2010,6 @@
     <t>CT Aymeric Laporte</t>
   </si>
   <si>
-    <t>ED Michael Olise</t>
-  </si>
-  <si>
     <t>ED Francisco Trincão</t>
   </si>
   <si>
@@ -2247,9 +2022,6 @@
     <t>DC Gonçalo Ramos</t>
   </si>
   <si>
-    <t>DC Rasmus Højlund</t>
-  </si>
-  <si>
     <t>DC Gabriel Jesus</t>
   </si>
   <si>
@@ -2259,9 +2031,6 @@
     <t>CT Lucas Beraldo</t>
   </si>
   <si>
-    <t>DC Julio Enciso</t>
-  </si>
-  <si>
     <t>DC Artem Dovbyk</t>
   </si>
   <si>
@@ -2301,12 +2070,6 @@
     <t>DC Hugo Ekitiké</t>
   </si>
   <si>
-    <t>LI Lee Tae-seok</t>
-  </si>
-  <si>
-    <t>LI Vanderson</t>
-  </si>
-  <si>
     <t>DC Mateo Retegui</t>
   </si>
   <si>
@@ -2319,24 +2082,12 @@
     <t>DC Serhou Guirassy</t>
   </si>
   <si>
-    <t>DC Pedro Neto</t>
-  </si>
-  <si>
-    <t>ED Dejan Kulusevski</t>
-  </si>
-  <si>
-    <t>PT Altay Bayındır</t>
-  </si>
-  <si>
     <t>DC Luis Suárez</t>
   </si>
   <si>
     <t>DC Jhon Durán</t>
   </si>
   <si>
-    <t>NO RENOVADOS</t>
-  </si>
-  <si>
     <t>Abreviatura</t>
   </si>
   <si>
@@ -2917,6 +2668,267 @@
   </si>
   <si>
     <t>Álex Baena</t>
+  </si>
+  <si>
+    <t>PT Emiliano Martínez</t>
+  </si>
+  <si>
+    <t>CT David Alaba</t>
+  </si>
+  <si>
+    <t>MC Steven Gerrard</t>
+  </si>
+  <si>
+    <t>SD Memphis Depay</t>
+  </si>
+  <si>
+    <t>ED Crysencio Summerville</t>
+  </si>
+  <si>
+    <t>EI Anthony Gordon</t>
+  </si>
+  <si>
+    <t>DC Ousmane Dembélé</t>
+  </si>
+  <si>
+    <t>CT Gleison Bremer</t>
+  </si>
+  <si>
+    <t>MC Martín Zubimendi</t>
+  </si>
+  <si>
+    <t>DC Francesco Pio Esposito</t>
+  </si>
+  <si>
+    <t>DC Barış Alper Yılmaz</t>
+  </si>
+  <si>
+    <t>CT Robert Andrich</t>
+  </si>
+  <si>
+    <t>MC Enzo Fernández</t>
+  </si>
+  <si>
+    <t>MP Petar Sučić</t>
+  </si>
+  <si>
+    <t>DC Giuliano Simeone</t>
+  </si>
+  <si>
+    <t>EI Nico Williams</t>
+  </si>
+  <si>
+    <t>MP Hans Vanaken</t>
+  </si>
+  <si>
+    <t>ID Ismaïla Sarr</t>
+  </si>
+  <si>
+    <t>ED Facundo Pellistri</t>
+  </si>
+  <si>
+    <t>ED Pedro Neto</t>
+  </si>
+  <si>
+    <t>Al-Nassr</t>
+  </si>
+  <si>
+    <t>PT Joan García</t>
+  </si>
+  <si>
+    <t>MC James Garner</t>
+  </si>
+  <si>
+    <t>EI Andreas Schjelderup</t>
+  </si>
+  <si>
+    <t>MC Qazim Laçi</t>
+  </si>
+  <si>
+    <t>CT Rúben Dias</t>
+  </si>
+  <si>
+    <t>DC Sergio Agüero</t>
+  </si>
+  <si>
+    <t>MC Jude Bellingham</t>
+  </si>
+  <si>
+    <t>MP Eberechi Eze</t>
+  </si>
+  <si>
+    <t>DC Andy Cole</t>
+  </si>
+  <si>
+    <t>MC João Neves</t>
+  </si>
+  <si>
+    <t>CT Nayef Aguerd</t>
+  </si>
+  <si>
+    <t>MCD Nico González</t>
+  </si>
+  <si>
+    <t>MC Paul Scholes</t>
+  </si>
+  <si>
+    <t>EI Son Heung-min</t>
+  </si>
+  <si>
+    <t>ED Antoine Semenyo</t>
+  </si>
+  <si>
+    <t>DC Semih Kılıçsoy</t>
+  </si>
+  <si>
+    <t>DC Samu Omorodion</t>
+  </si>
+  <si>
+    <t>SD Julio Enciso</t>
+  </si>
+  <si>
+    <t>ID Yeremy Pino</t>
+  </si>
+  <si>
+    <t>MP Mikel Merino</t>
+  </si>
+  <si>
+    <t>CT Fabinho</t>
+  </si>
+  <si>
+    <t>LD John Stones</t>
+  </si>
+  <si>
+    <t>MP Michael Olise</t>
+  </si>
+  <si>
+    <t>SD Antoine Griezmann</t>
+  </si>
+  <si>
+    <t>MC Declan Rice</t>
+  </si>
+  <si>
+    <t>SD João Félix</t>
+  </si>
+  <si>
+    <t>DC Morgan Rogers</t>
+  </si>
+  <si>
+    <t>CT Dean Huijsen</t>
+  </si>
+  <si>
+    <t>MC Orkun Kökçü</t>
+  </si>
+  <si>
+    <t>MP Estêvão</t>
+  </si>
+  <si>
+    <t>PT Vózinha</t>
+  </si>
+  <si>
+    <t>CT Illia Zabarnyi</t>
+  </si>
+  <si>
+    <t>MP Dejan Kulusevski</t>
+  </si>
+  <si>
+    <t>DC Pelé</t>
+  </si>
+  <si>
+    <t>CT Ramy Bensebaïni</t>
+  </si>
+  <si>
+    <t>MC Dominik Szoboszlai</t>
+  </si>
+  <si>
+    <t>II Gonçalo Guedes</t>
+  </si>
+  <si>
+    <t>MC Xavi Simons</t>
+  </si>
+  <si>
+    <t>ED Federico Chiesa</t>
+  </si>
+  <si>
+    <t>PT Luis Malagón</t>
+  </si>
+  <si>
+    <t>ED Ángel Correa</t>
+  </si>
+  <si>
+    <t>II Alejandro Zendejas</t>
+  </si>
+  <si>
+    <t>ED Lee Kang-in</t>
+  </si>
+  <si>
+    <t>CT Virgil van Dijk</t>
+  </si>
+  <si>
+    <t>MC Arda Güler</t>
+  </si>
+  <si>
+    <t>DC Julián Álvarez</t>
+  </si>
+  <si>
+    <t>AC Milan</t>
+  </si>
+  <si>
+    <t>MCD Frank Rijkaard</t>
+  </si>
+  <si>
+    <t>EI Marco Reus</t>
+  </si>
+  <si>
+    <t>PT Unai Simón</t>
+  </si>
+  <si>
+    <t>MCD Elliot Anderson</t>
+  </si>
+  <si>
+    <t>MC Ayyoub Bouaddi</t>
+  </si>
+  <si>
+    <t>ID Phil Foden</t>
+  </si>
+  <si>
+    <t>EI Yan Diomande</t>
+  </si>
+  <si>
+    <t>PT Gianluigi Buffon</t>
+  </si>
+  <si>
+    <t>CT Maxence Lacroix</t>
+  </si>
+  <si>
+    <t>MCD Manuel Locatelli</t>
+  </si>
+  <si>
+    <t>MP Johan Manzambi</t>
+  </si>
+  <si>
+    <t>EI Neymar Jr</t>
+  </si>
+  <si>
+    <t>PT Anatoliy Trubin</t>
+  </si>
+  <si>
+    <t>CT Jakub Kiwior</t>
+  </si>
+  <si>
+    <t>CT Nathan Collins</t>
+  </si>
+  <si>
+    <t>MP Maghnes Akliouche</t>
+  </si>
+  <si>
+    <t>ID Takefusa Kubo</t>
+  </si>
+  <si>
+    <t>ED Désiré Doué</t>
+  </si>
+  <si>
+    <t>DC Moise Kean</t>
   </si>
 </sst>
 </file>
@@ -6682,21 +6694,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>822</v>
+        <v>739</v>
       </c>
       <c r="B1" t="s">
-        <v>823</v>
+        <v>740</v>
       </c>
       <c r="C1" t="s">
-        <v>824</v>
+        <v>741</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>825</v>
+        <v>742</v>
       </c>
       <c r="B2" t="s">
-        <v>767</v>
+        <v>684</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6704,10 +6716,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>825</v>
+        <v>742</v>
       </c>
       <c r="B3" t="s">
-        <v>826</v>
+        <v>743</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6715,10 +6727,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>825</v>
+        <v>742</v>
       </c>
       <c r="B4" t="s">
-        <v>827</v>
+        <v>744</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6726,10 +6738,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>825</v>
+        <v>742</v>
       </c>
       <c r="B5" t="s">
-        <v>828</v>
+        <v>745</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6737,10 +6749,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>825</v>
+        <v>742</v>
       </c>
       <c r="B6" t="s">
-        <v>800</v>
+        <v>717</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6748,10 +6760,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>829</v>
+        <v>746</v>
       </c>
       <c r="B7" t="s">
-        <v>830</v>
+        <v>747</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6759,10 +6771,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>829</v>
+        <v>746</v>
       </c>
       <c r="B8" t="s">
-        <v>831</v>
+        <v>748</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6770,10 +6782,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>829</v>
+        <v>746</v>
       </c>
       <c r="B9" t="s">
-        <v>800</v>
+        <v>717</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6781,10 +6793,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>829</v>
+        <v>746</v>
       </c>
       <c r="B10" t="s">
-        <v>767</v>
+        <v>684</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6792,10 +6804,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>829</v>
+        <v>746</v>
       </c>
       <c r="B11" t="s">
-        <v>778</v>
+        <v>695</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6803,10 +6815,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>832</v>
+        <v>749</v>
       </c>
       <c r="B12" t="s">
-        <v>828</v>
+        <v>745</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6814,10 +6826,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>832</v>
+        <v>749</v>
       </c>
       <c r="B13" t="s">
-        <v>800</v>
+        <v>717</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6825,10 +6837,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>832</v>
+        <v>749</v>
       </c>
       <c r="B14" t="s">
-        <v>778</v>
+        <v>695</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -10334,7 +10346,7 @@
         <v>82</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>889</v>
+        <v>806</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>178</v>
@@ -10366,7 +10378,7 @@
         <v>189</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>853</v>
+        <v>770</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>184</v>
@@ -10378,7 +10390,7 @@
         <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>862</v>
+        <v>779</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>279</v>
@@ -10387,7 +10399,7 @@
         <v>183</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>890</v>
+        <v>807</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>190</v>
@@ -10458,7 +10470,7 @@
         <v>199</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>923</v>
+        <v>840</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>200</v>
@@ -10466,7 +10478,7 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>837</v>
+        <v>754</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>221</v>
@@ -10475,7 +10487,7 @@
         <v>292</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>854</v>
+        <v>771</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>203</v>
@@ -10484,16 +10496,16 @@
         <v>207</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>863</v>
+        <v>780</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>318</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>887</v>
+        <v>804</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>891</v>
+        <v>808</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>212</v>
@@ -10511,7 +10523,7 @@
         <v>104</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>924</v>
+        <v>841</v>
       </c>
       <c r="Q4" s="3" t="s">
         <v>209</v>
@@ -10534,25 +10546,25 @@
         <v>215</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>858</v>
+        <v>775</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>864</v>
+        <v>781</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>882</v>
+        <v>799</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>227</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>892</v>
+        <v>809</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>222</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>910</v>
+        <v>827</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>225</v>
@@ -10564,7 +10576,7 @@
         <v>306</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>925</v>
+        <v>842</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>219</v>
@@ -10590,7 +10602,7 @@
         <v>229</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>865</v>
+        <v>782</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>214</v>
@@ -10599,7 +10611,7 @@
         <v>216</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>893</v>
+        <v>810</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>235</v>
@@ -10608,7 +10620,7 @@
         <v>226</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>912</v>
+        <v>829</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>230</v>
@@ -10617,7 +10629,7 @@
         <v>32</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>926</v>
+        <v>843</v>
       </c>
       <c r="Q6" s="3" t="s">
         <v>232</v>
@@ -10625,7 +10637,7 @@
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>838</v>
+        <v>755</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>243</v>
@@ -10643,7 +10655,7 @@
         <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>866</v>
+        <v>783</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>236</v>
@@ -10652,10 +10664,10 @@
         <v>249</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>894</v>
+        <v>811</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>907</v>
+        <v>824</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>113</v>
@@ -10670,7 +10682,7 @@
         <v>241</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>927</v>
+        <v>844</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>168</v>
@@ -10681,7 +10693,7 @@
         <v>103</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>844</v>
+        <v>761</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>308</v>
@@ -10693,10 +10705,10 @@
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>859</v>
+        <v>776</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>867</v>
+        <v>784</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>87</v>
@@ -10705,10 +10717,10 @@
         <v>164</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>835</v>
+        <v>752</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>908</v>
+        <v>825</v>
       </c>
       <c r="L8" s="3" t="s">
         <v>172</v>
@@ -10720,10 +10732,10 @@
         <v>153</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>918</v>
+        <v>835</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>928</v>
+        <v>845</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>247</v>
@@ -10731,7 +10743,7 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>839</v>
+        <v>756</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>254</v>
@@ -10743,13 +10755,13 @@
         <v>173</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>856</v>
+        <v>773</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>860</v>
+        <v>777</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>868</v>
+        <v>785</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>57</v>
@@ -10758,7 +10770,7 @@
         <v>245</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>895</v>
+        <v>812</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>255</v>
@@ -10767,7 +10779,7 @@
         <v>115</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>913</v>
+        <v>830</v>
       </c>
       <c r="N9" s="3" t="s">
         <v>250</v>
@@ -10776,7 +10788,7 @@
         <v>252</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>929</v>
+        <v>846</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>174</v>
@@ -10784,10 +10796,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>840</v>
+        <v>757</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>845</v>
+        <v>762</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>253</v>
@@ -10811,7 +10823,7 @@
         <v>170</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>896</v>
+        <v>813</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>262</v>
@@ -10829,7 +10841,7 @@
         <v>97</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>930</v>
+        <v>847</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>157</v>
@@ -10837,7 +10849,7 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>841</v>
+        <v>758</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>27</v>
@@ -10882,7 +10894,7 @@
         <v>258</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>931</v>
+        <v>848</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>79</v>
@@ -10902,13 +10914,13 @@
         <v>268</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>857</v>
+        <v>774</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>861</v>
+        <v>778</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>869</v>
+        <v>786</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>149</v>
@@ -10935,7 +10947,7 @@
         <v>95</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>932</v>
+        <v>849</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>158</v>
@@ -10946,7 +10958,7 @@
         <v>179</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>846</v>
+        <v>763</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>188</v>
@@ -10961,10 +10973,10 @@
         <v>160</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>870</v>
+        <v>787</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>883</v>
+        <v>800</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>275</v>
@@ -10979,16 +10991,16 @@
         <v>274</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>914</v>
+        <v>831</v>
       </c>
       <c r="N13" s="3" t="s">
         <v>277</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>919</v>
+        <v>836</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>933</v>
+        <v>850</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>280</v>
@@ -10996,10 +11008,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>842</v>
+        <v>759</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>847</v>
+        <v>764</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>210</v>
@@ -11014,7 +11026,7 @@
         <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>871</v>
+        <v>788</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>202</v>
@@ -11023,7 +11035,7 @@
         <v>263</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>897</v>
+        <v>814</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>293</v>
@@ -11038,7 +11050,7 @@
         <v>289</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>920</v>
+        <v>837</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>13</v>
@@ -11067,7 +11079,7 @@
         <v>321</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>872</v>
+        <v>789</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>290</v>
@@ -11076,7 +11088,7 @@
         <v>126</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>898</v>
+        <v>815</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>300</v>
@@ -11094,7 +11106,7 @@
         <v>297</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>934</v>
+        <v>851</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>298</v>
@@ -11120,7 +11132,7 @@
         <v>128</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>873</v>
+        <v>790</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>282</v>
@@ -11129,7 +11141,7 @@
         <v>117</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>836</v>
+        <v>753</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>309</v>
@@ -11138,7 +11150,7 @@
         <v>110</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>915</v>
+        <v>832</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>305</v>
@@ -11147,7 +11159,7 @@
         <v>231</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>935</v>
+        <v>852</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>307</v>
@@ -11158,7 +11170,7 @@
         <v>310</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>848</v>
+        <v>765</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>314</v>
@@ -11173,16 +11185,16 @@
         <v>330</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>874</v>
+        <v>791</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>884</v>
+        <v>801</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>337</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>899</v>
+        <v>816</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>316</v>
@@ -11191,7 +11203,7 @@
         <v>166</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>916</v>
+        <v>833</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>313</v>
@@ -11203,7 +11215,7 @@
         <v>251</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>942</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -11211,7 +11223,7 @@
         <v>317</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>849</v>
+        <v>766</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>260</v>
@@ -11226,16 +11238,16 @@
         <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>875</v>
+        <v>792</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>302</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>888</v>
+        <v>805</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>900</v>
+        <v>817</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>326</v>
@@ -11253,7 +11265,7 @@
         <v>176</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>936</v>
+        <v>853</v>
       </c>
       <c r="Q18" s="3" t="s">
         <v>323</v>
@@ -11264,7 +11276,7 @@
         <v>152</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>850</v>
+        <v>767</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>333</v>
@@ -11279,7 +11291,7 @@
         <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>876</v>
+        <v>793</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>116</v>
@@ -11288,7 +11300,7 @@
         <v>61</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>901</v>
+        <v>818</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>334</v>
@@ -11303,10 +11315,10 @@
         <v>331</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>921</v>
+        <v>838</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>937</v>
+        <v>854</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>332</v>
@@ -11317,7 +11329,7 @@
         <v>327</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>851</v>
+        <v>768</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>233</v>
@@ -11332,7 +11344,7 @@
         <v>161</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>877</v>
+        <v>794</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>109</v>
@@ -11341,7 +11353,7 @@
         <v>111</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>902</v>
+        <v>819</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>341</v>
@@ -11359,7 +11371,7 @@
         <v>175</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>938</v>
+        <v>855</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>325</v>
@@ -11385,7 +11397,7 @@
         <v>312</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>878</v>
+        <v>795</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>336</v>
@@ -11394,7 +11406,7 @@
         <v>195</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>903</v>
+        <v>820</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>346</v>
@@ -11415,7 +11427,7 @@
         <v>59</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>943</v>
+        <v>860</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
@@ -11423,7 +11435,7 @@
         <v>347</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>852</v>
+        <v>769</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>151</v>
@@ -11438,34 +11450,34 @@
         <v>99</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>879</v>
+        <v>796</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>885</v>
+        <v>802</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>342</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>904</v>
+        <v>821</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>352</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>911</v>
+        <v>828</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>917</v>
+        <v>834</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>350</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>922</v>
+        <v>839</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>939</v>
+        <v>856</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>71</v>
@@ -11473,7 +11485,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>843</v>
+        <v>760</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>34</v>
@@ -11491,7 +11503,7 @@
         <v>288</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>880</v>
+        <v>797</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>353</v>
@@ -11500,10 +11512,10 @@
         <v>354</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>905</v>
+        <v>822</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>909</v>
+        <v>826</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>86</v>
@@ -11518,7 +11530,7 @@
         <v>121</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>940</v>
+        <v>857</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>357</v>
@@ -11535,7 +11547,7 @@
         <v>269</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>855</v>
+        <v>772</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>98</v>
@@ -11544,14 +11556,14 @@
         <v>217</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>881</v>
+        <v>798</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>886</v>
+        <v>803</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>906</v>
+        <v>823</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>361</v>
@@ -11569,7 +11581,7 @@
         <v>360</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>941</v>
+        <v>858</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>102</v>
@@ -11582,7 +11594,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.109375" style="1" bestFit="1" customWidth="1"/>
@@ -11610,1293 +11622,1294 @@
         <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
+      <c r="M1" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>362</v>
+        <v>861</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="M2" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="P2" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>371</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>378</v>
       </c>
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>380</v>
+        <v>435</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>381</v>
+        <v>549</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>382</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>395</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>396</v>
+        <v>862</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>398</v>
+        <v>541</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>401</v>
-      </c>
       <c r="G4" s="3" t="s">
-        <v>402</v>
+        <v>902</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>403</v>
+        <v>582</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>404</v>
+        <v>916</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>405</v>
+        <v>479</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>406</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>416</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>418</v>
+        <v>892</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>423</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>424</v>
+        <v>925</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>425</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>427</v>
+        <v>564</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>433</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>446</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="P7" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>448</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>465</v>
+        <v>873</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>474</v>
-      </c>
       <c r="L8" s="3" t="s">
-        <v>475</v>
+        <v>457</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>478</v>
+        <v>517</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>480</v>
+        <v>462</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>481</v>
+        <v>864</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>482</v>
+        <v>874</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>483</v>
+        <v>592</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>485</v>
+        <v>889</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>486</v>
+        <v>895</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>487</v>
+        <v>594</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>488</v>
+        <v>628</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>489</v>
+        <v>458</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>490</v>
+        <v>922</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>491</v>
+        <v>478</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>492</v>
+        <v>926</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>493</v>
+        <v>930</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>496</v>
+        <v>473</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>497</v>
+        <v>476</v>
       </c>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>511</v>
-      </c>
       <c r="O10" s="3" t="s">
-        <v>512</v>
+        <v>487</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>513</v>
+        <v>485</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>515</v>
+        <v>866</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>516</v>
+        <v>875</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>518</v>
+        <v>495</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>520</v>
+        <v>642</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>521</v>
+        <v>905</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>522</v>
+        <v>561</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>524</v>
+        <v>468</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>525</v>
+        <v>924</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>526</v>
+        <v>494</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>527</v>
+        <v>493</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>528</v>
+        <v>497</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>529</v>
+        <v>486</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>530</v>
+        <v>496</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>531</v>
+        <v>499</v>
       </c>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>532</v>
+        <v>867</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>533</v>
+        <v>876</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>534</v>
+        <v>607</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>536</v>
+        <v>890</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>537</v>
+        <v>897</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>539</v>
+        <v>911</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>540</v>
+        <v>483</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>541</v>
+        <v>492</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>542</v>
+        <v>518</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>543</v>
+        <v>507</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>544</v>
+        <v>506</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>545</v>
+        <v>512</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>546</v>
+        <v>513</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>547</v>
+        <v>511</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>548</v>
+        <v>514</v>
       </c>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>549</v>
+        <v>362</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>551</v>
+        <v>372</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>552</v>
+        <v>523</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>553</v>
+        <v>363</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>554</v>
+        <v>510</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>555</v>
+        <v>389</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>556</v>
+        <v>912</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>557</v>
+        <v>522</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>558</v>
+        <v>661</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>560</v>
+        <v>521</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>561</v>
+        <v>931</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>562</v>
+        <v>524</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>563</v>
+        <v>936</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>564</v>
+        <v>942</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>565</v>
+        <v>526</v>
       </c>
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>566</v>
+        <v>868</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>567</v>
+        <v>877</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>568</v>
+        <v>404</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>569</v>
+        <v>536</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>570</v>
+        <v>532</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>571</v>
+        <v>898</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>572</v>
+        <v>465</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>574</v>
+        <v>393</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>920</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>575</v>
+        <v>407</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>576</v>
+        <v>543</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>577</v>
+        <v>534</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>578</v>
+        <v>379</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>579</v>
+        <v>538</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>580</v>
+        <v>937</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>581</v>
+        <v>392</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>582</v>
+        <v>540</v>
       </c>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>583</v>
+        <v>545</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>584</v>
+        <v>620</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>591</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>592</v>
+        <v>452</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>593</v>
+        <v>555</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>595</v>
+        <v>520</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>596</v>
+        <v>550</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>597</v>
+        <v>551</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>598</v>
+        <v>943</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>599</v>
+        <v>552</v>
       </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>600</v>
+        <v>556</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>608</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>610</v>
+        <v>568</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>611</v>
+        <v>560</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>612</v>
+        <v>932</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>613</v>
+        <v>563</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>614</v>
+        <v>432</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>615</v>
+        <v>575</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>616</v>
+        <v>565</v>
       </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>617</v>
+        <v>570</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>618</v>
+        <v>878</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>619</v>
+        <v>885</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>620</v>
+        <v>504</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>621</v>
+        <v>558</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>622</v>
+        <v>900</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>623</v>
+        <v>906</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>624</v>
+        <v>546</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>625</v>
+        <v>613</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>626</v>
+        <v>503</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>627</v>
+        <v>579</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>628</v>
+        <v>572</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>629</v>
+        <v>933</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>630</v>
+        <v>576</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>631</v>
+        <v>938</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>632</v>
+        <v>588</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>633</v>
+        <v>533</v>
       </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>634</v>
+        <v>581</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>635</v>
+        <v>464</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>636</v>
+        <v>489</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>637</v>
+        <v>586</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>638</v>
+        <v>583</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>639</v>
+        <v>627</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>640</v>
+        <v>502</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>641</v>
+        <v>557</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>642</v>
+        <v>918</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>643</v>
+        <v>569</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>644</v>
+        <v>595</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>646</v>
+        <v>559</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>647</v>
+        <v>589</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>648</v>
+        <v>590</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>649</v>
+        <v>944</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>650</v>
+        <v>591</v>
       </c>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>651</v>
+        <v>869</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>652</v>
+        <v>516</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>653</v>
+        <v>606</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>654</v>
+        <v>602</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>655</v>
+        <v>599</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>656</v>
+        <v>615</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>657</v>
+        <v>578</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>658</v>
+        <v>423</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>659</v>
+        <v>919</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>660</v>
+        <v>580</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>661</v>
+        <v>608</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>663</v>
+        <v>470</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>664</v>
+        <v>604</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>665</v>
+        <v>939</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>666</v>
+        <v>603</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>668</v>
+        <v>597</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>669</v>
+        <v>879</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>670</v>
+        <v>434</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>671</v>
+        <v>614</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>672</v>
+        <v>891</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>673</v>
+        <v>901</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>674</v>
+        <v>554</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>675</v>
+        <v>598</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>676</v>
+        <v>573</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>677</v>
+        <v>544</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>678</v>
+        <v>621</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>679</v>
+        <v>612</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>680</v>
+        <v>481</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>681</v>
+        <v>617</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>682</v>
+        <v>650</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>683</v>
+        <v>945</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>684</v>
+        <v>593</v>
       </c>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>685</v>
+        <v>609</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>686</v>
+        <v>490</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>687</v>
+        <v>632</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>688</v>
+        <v>626</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>689</v>
+        <v>623</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>690</v>
+        <v>574</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>691</v>
+        <v>907</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>692</v>
+        <v>610</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>693</v>
+        <v>381</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>694</v>
+        <v>596</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>696</v>
+        <v>624</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>697</v>
+        <v>934</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>698</v>
+        <v>629</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>699</v>
+        <v>630</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="Q21" s="3"/>
+        <v>657</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>631</v>
+      </c>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>701</v>
+        <v>870</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>702</v>
+        <v>527</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>703</v>
+        <v>639</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>704</v>
+        <v>886</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>705</v>
+        <v>635</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>706</v>
+        <v>444</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>707</v>
+        <v>908</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>708</v>
+        <v>914</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>709</v>
+        <v>625</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>710</v>
+        <v>622</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>711</v>
+        <v>641</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>712</v>
+        <v>927</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>713</v>
+        <v>935</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>714</v>
+        <v>636</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>715</v>
+        <v>940</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="Q22" s="3"/>
+        <v>946</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>638</v>
+      </c>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>717</v>
+        <v>871</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>718</v>
+        <v>880</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>719</v>
+        <v>652</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>720</v>
+        <v>647</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>721</v>
+        <v>644</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>722</v>
+        <v>537</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>723</v>
+        <v>654</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>724</v>
+        <v>643</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>725</v>
+        <v>646</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>726</v>
+        <v>923</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>727</v>
+        <v>655</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>728</v>
+        <v>645</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>729</v>
+        <v>535</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>730</v>
+        <v>649</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>731</v>
+        <v>637</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q23" s="3"/>
+        <v>947</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>651</v>
+      </c>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>733</v>
+        <v>656</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>734</v>
+        <v>577</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>735</v>
+        <v>515</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>736</v>
+        <v>887</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>737</v>
+        <v>658</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>738</v>
+        <v>414</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>739</v>
+        <v>665</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>741</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>742</v>
+        <v>391</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>743</v>
+        <v>666</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>744</v>
+        <v>660</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>745</v>
+        <v>659</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>746</v>
+        <v>663</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>747</v>
+        <v>664</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="Q24" s="3"/>
+        <v>662</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>618</v>
+      </c>
       <c r="R24" s="3"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>749</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12922,25 +12935,25 @@
         <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>750</v>
+        <v>667</v>
       </c>
       <c r="C1" t="s">
-        <v>751</v>
+        <v>668</v>
       </c>
       <c r="D1" t="s">
-        <v>752</v>
+        <v>669</v>
       </c>
       <c r="E1" t="s">
-        <v>753</v>
+        <v>670</v>
       </c>
       <c r="F1" t="s">
-        <v>754</v>
+        <v>671</v>
       </c>
       <c r="G1" t="s">
-        <v>755</v>
+        <v>672</v>
       </c>
       <c r="H1" t="s">
-        <v>756</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -12948,13 +12961,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>757</v>
+        <v>674</v>
       </c>
       <c r="C2" t="s">
-        <v>758</v>
+        <v>675</v>
       </c>
       <c r="D2" t="s">
-        <v>759</v>
+        <v>676</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -12963,7 +12976,7 @@
         <v>1400000000</v>
       </c>
       <c r="G2" t="s">
-        <v>760</v>
+        <v>677</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -12974,13 +12987,13 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>761</v>
+        <v>678</v>
       </c>
       <c r="C3" t="s">
-        <v>762</v>
+        <v>679</v>
       </c>
       <c r="D3" t="s">
-        <v>763</v>
+        <v>680</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -12989,7 +13002,7 @@
         <v>68000000</v>
       </c>
       <c r="G3" t="s">
-        <v>764</v>
+        <v>681</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -13000,13 +13013,13 @@
         <v>137</v>
       </c>
       <c r="B4" t="s">
-        <v>765</v>
+        <v>682</v>
       </c>
       <c r="C4" t="s">
-        <v>766</v>
+        <v>683</v>
       </c>
       <c r="D4" t="s">
-        <v>767</v>
+        <v>684</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13015,7 +13028,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>768</v>
+        <v>685</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13026,13 +13039,13 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>769</v>
+        <v>686</v>
       </c>
       <c r="C5" t="s">
-        <v>770</v>
+        <v>687</v>
       </c>
       <c r="D5" t="s">
-        <v>771</v>
+        <v>688</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13041,7 +13054,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>772</v>
+        <v>689</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -13052,13 +13065,13 @@
         <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>773</v>
+        <v>690</v>
       </c>
       <c r="C6" t="s">
-        <v>758</v>
+        <v>675</v>
       </c>
       <c r="D6" t="s">
-        <v>774</v>
+        <v>691</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13067,7 +13080,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>775</v>
+        <v>692</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -13078,13 +13091,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>776</v>
+        <v>693</v>
       </c>
       <c r="C7" t="s">
-        <v>777</v>
+        <v>694</v>
       </c>
       <c r="D7" t="s">
-        <v>778</v>
+        <v>695</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13093,7 +13106,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>779</v>
+        <v>696</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -13104,13 +13117,13 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>780</v>
+        <v>697</v>
       </c>
       <c r="C8" t="s">
-        <v>781</v>
+        <v>698</v>
       </c>
       <c r="D8" t="s">
-        <v>782</v>
+        <v>699</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13119,7 +13132,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>783</v>
+        <v>700</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -13130,13 +13143,13 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>784</v>
+        <v>701</v>
       </c>
       <c r="C9" t="s">
-        <v>785</v>
+        <v>702</v>
       </c>
       <c r="D9" t="s">
-        <v>786</v>
+        <v>703</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13145,7 +13158,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>787</v>
+        <v>704</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -13156,13 +13169,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>788</v>
+        <v>705</v>
       </c>
       <c r="C10" t="s">
-        <v>789</v>
+        <v>706</v>
       </c>
       <c r="D10" t="s">
-        <v>790</v>
+        <v>707</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13171,7 +13184,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>791</v>
+        <v>708</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -13185,10 +13198,10 @@
         <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>792</v>
+        <v>709</v>
       </c>
       <c r="D11" t="s">
-        <v>793</v>
+        <v>710</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13197,7 +13210,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>794</v>
+        <v>711</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -13208,13 +13221,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>795</v>
+        <v>712</v>
       </c>
       <c r="C12" t="s">
-        <v>796</v>
+        <v>713</v>
       </c>
       <c r="D12" t="s">
-        <v>771</v>
+        <v>688</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13223,7 +13236,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>797</v>
+        <v>714</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -13234,13 +13247,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>798</v>
+        <v>715</v>
       </c>
       <c r="C13" t="s">
-        <v>799</v>
+        <v>716</v>
       </c>
       <c r="D13" t="s">
-        <v>800</v>
+        <v>717</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13249,7 +13262,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>801</v>
+        <v>718</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -13260,13 +13273,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>802</v>
+        <v>719</v>
       </c>
       <c r="C14" t="s">
-        <v>803</v>
+        <v>720</v>
       </c>
       <c r="D14" t="s">
-        <v>804</v>
+        <v>721</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13275,7 +13288,7 @@
         <v>893000000</v>
       </c>
       <c r="G14" t="s">
-        <v>805</v>
+        <v>722</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -13286,13 +13299,13 @@
         <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>806</v>
+        <v>723</v>
       </c>
       <c r="C15" t="s">
-        <v>807</v>
+        <v>724</v>
       </c>
       <c r="D15" t="s">
-        <v>808</v>
+        <v>725</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13301,7 +13314,7 @@
         <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>809</v>
+        <v>726</v>
       </c>
       <c r="H15">
         <v>15</v>
@@ -13312,13 +13325,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>810</v>
+        <v>727</v>
       </c>
       <c r="C16" t="s">
-        <v>811</v>
+        <v>728</v>
       </c>
       <c r="D16" t="s">
-        <v>812</v>
+        <v>729</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -13327,7 +13340,7 @@
         <v>300000000</v>
       </c>
       <c r="G16" t="s">
-        <v>813</v>
+        <v>730</v>
       </c>
       <c r="H16">
         <v>13</v>
@@ -13338,13 +13351,13 @@
         <v>178</v>
       </c>
       <c r="B17" t="s">
-        <v>814</v>
+        <v>731</v>
       </c>
       <c r="C17" t="s">
-        <v>815</v>
+        <v>732</v>
       </c>
       <c r="D17" t="s">
-        <v>816</v>
+        <v>733</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -13353,7 +13366,7 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>817</v>
+        <v>734</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -13364,13 +13377,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>818</v>
+        <v>735</v>
       </c>
       <c r="C18" t="s">
-        <v>819</v>
+        <v>736</v>
       </c>
       <c r="D18" t="s">
-        <v>820</v>
+        <v>737</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -13379,7 +13392,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>821</v>
+        <v>738</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14324,7 +14337,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>833</v>
+        <v>750</v>
       </c>
       <c r="B41" t="s">
         <v>62</v>
@@ -14407,7 +14420,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>834</v>
+        <v>751</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -14453,7 +14466,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>835</v>
+        <v>752</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -14499,7 +14512,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>836</v>
+        <v>753</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6E4982B-5E04-40E1-B836-90E1349E03AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3E32E-7E47-4AB5-BC98-6FDE9C2A9614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1306" uniqueCount="948">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="951">
   <si>
     <t>Jugador</t>
   </si>
@@ -420,9 +420,6 @@
     <t>Rúben Neves</t>
   </si>
   <si>
-    <t>Paulo Dybala</t>
-  </si>
-  <si>
     <t>Álvaro Carreras</t>
   </si>
   <si>
@@ -438,9 +435,6 @@
     <t>Bruno Guimarães</t>
   </si>
   <si>
-    <t>Amadou Onana</t>
-  </si>
-  <si>
     <t>Alejandro Garnacho</t>
   </si>
   <si>
@@ -465,9 +459,6 @@
     <t>Raphinha</t>
   </si>
   <si>
-    <t>Paul Pogba</t>
-  </si>
-  <si>
     <t>N'Golo Kanté</t>
   </si>
   <si>
@@ -564,9 +555,6 @@
     <t>Loïs Openda</t>
   </si>
   <si>
-    <t>Yoane Wissa</t>
-  </si>
-  <si>
     <t>Viktor Gyökeres</t>
   </si>
   <si>
@@ -579,9 +567,6 @@
     <t>Lamine Yamal</t>
   </si>
   <si>
-    <t>Manu Koné</t>
-  </si>
-  <si>
     <t>Manuel Locatelli</t>
   </si>
   <si>
@@ -597,9 +582,6 @@
     <t>Riyad Mahrez</t>
   </si>
   <si>
-    <t>Dirk Kuyt</t>
-  </si>
-  <si>
     <t>Gonçalo Ramos</t>
   </si>
   <si>
@@ -636,9 +618,6 @@
     <t>Gianluigi Donnarumma</t>
   </si>
   <si>
-    <t>Giorgi Mamardashvili</t>
-  </si>
-  <si>
     <t>Alisson Becker</t>
   </si>
   <si>
@@ -672,9 +651,6 @@
     <t>Pau Torres</t>
   </si>
   <si>
-    <t>Jonathan Tah</t>
-  </si>
-  <si>
     <t>Gabriel Magalhães</t>
   </si>
   <si>
@@ -705,9 +681,6 @@
     <t>Pepe</t>
   </si>
   <si>
-    <t>Murillo</t>
-  </si>
-  <si>
     <t>Marquinhos</t>
   </si>
   <si>
@@ -768,9 +741,6 @@
     <t>João Cancelo</t>
   </si>
   <si>
-    <t>Jeremie Frimpong</t>
-  </si>
-  <si>
     <t>Robin Le Normand</t>
   </si>
   <si>
@@ -876,9 +846,6 @@
     <t>Liam Delap</t>
   </si>
   <si>
-    <t>Federico Chiesa</t>
-  </si>
-  <si>
     <t>Leroy Sané</t>
   </si>
   <si>
@@ -912,9 +879,6 @@
     <t>David de Gea</t>
   </si>
   <si>
-    <t>Romelu Lukaku</t>
-  </si>
-  <si>
     <t>Marc Bernal</t>
   </si>
   <si>
@@ -1098,9 +1062,6 @@
     <t>Kevin De Bruyne</t>
   </si>
   <si>
-    <t>Marco Verratti</t>
-  </si>
-  <si>
     <t>Donyell Malen</t>
   </si>
   <si>
@@ -1113,9 +1074,6 @@
     <t>Nicolò Zaniolo</t>
   </si>
   <si>
-    <t>Kim Min-Jae</t>
-  </si>
-  <si>
     <t>Casemiro</t>
   </si>
   <si>
@@ -1185,9 +1143,6 @@
     <t>PT Gianluigi Donnarumma</t>
   </si>
   <si>
-    <t>PT Giorgi Mamardashvili</t>
-  </si>
-  <si>
     <t>PT Alisson Becker</t>
   </si>
   <si>
@@ -1230,9 +1185,6 @@
     <t>LI Nuno Mendes</t>
   </si>
   <si>
-    <t>CT Jonathan Tah</t>
-  </si>
-  <si>
     <t>CT Gabriel Magalhães</t>
   </si>
   <si>
@@ -1278,9 +1230,6 @@
     <t>CT Pepe</t>
   </si>
   <si>
-    <t>CT Murillo</t>
-  </si>
-  <si>
     <t>II Federico Dimarco</t>
   </si>
   <si>
@@ -1368,9 +1317,6 @@
     <t>LD João Cancelo</t>
   </si>
   <si>
-    <t>LD Jeremie Frimpong</t>
-  </si>
-  <si>
     <t>CT Robin Le Normand</t>
   </si>
   <si>
@@ -1413,9 +1359,6 @@
     <t>MCD Nicolò Barella</t>
   </si>
   <si>
-    <t>MC Manu Koné</t>
-  </si>
-  <si>
     <t>MCD Boubacar Kamara</t>
   </si>
   <si>
@@ -1500,9 +1443,6 @@
     <t>II Rodrygo</t>
   </si>
   <si>
-    <t>ED Dirk Kuyt</t>
-  </si>
-  <si>
     <t>DC Ademola Lookman</t>
   </si>
   <si>
@@ -1611,9 +1551,6 @@
     <t>DC Lautaro Martínez</t>
   </si>
   <si>
-    <t>DC Yoane Wissa</t>
-  </si>
-  <si>
     <t>MC Rodrigo De Paul</t>
   </si>
   <si>
@@ -1653,9 +1590,6 @@
     <t>PT David de Gea</t>
   </si>
   <si>
-    <t>DC Romelu Lukaku</t>
-  </si>
-  <si>
     <t>MC Marc Bernal</t>
   </si>
   <si>
@@ -1806,9 +1740,6 @@
     <t>MCD Marcelo Brozović</t>
   </si>
   <si>
-    <t>SD Paulo Dybala</t>
-  </si>
-  <si>
     <t>MP Rodrigo Mora</t>
   </si>
   <si>
@@ -1842,9 +1773,6 @@
     <t>MCD Hakan Çalhanoğlu</t>
   </si>
   <si>
-    <t>MC Paul Pogba</t>
-  </si>
-  <si>
     <t>LI Lewis Hall</t>
   </si>
   <si>
@@ -1890,9 +1818,6 @@
     <t>MP Brahim Díaz</t>
   </si>
   <si>
-    <t>MCD Amadou Onana</t>
-  </si>
-  <si>
     <t>II Conor Gallagher</t>
   </si>
   <si>
@@ -1926,9 +1851,6 @@
     <t>MP Christopher Nkunku</t>
   </si>
   <si>
-    <t>MC Marco Verratti</t>
-  </si>
-  <si>
     <t>ED Donyell Malen</t>
   </si>
   <si>
@@ -1962,9 +1884,6 @@
     <t>EI Jérémy Doku</t>
   </si>
   <si>
-    <t>CT Kim Min-jae</t>
-  </si>
-  <si>
     <t>MCD Casemiro</t>
   </si>
   <si>
@@ -2499,12 +2418,6 @@
     <t>Pelé</t>
   </si>
   <si>
-    <t>Ramy Bensebaïni</t>
-  </si>
-  <si>
-    <t>Gonçalo Guedes</t>
-  </si>
-  <si>
     <t>Atletico_de_Madrid</t>
   </si>
   <si>
@@ -2835,21 +2748,6 @@
     <t>DC Pelé</t>
   </si>
   <si>
-    <t>CT Ramy Bensebaïni</t>
-  </si>
-  <si>
-    <t>MC Dominik Szoboszlai</t>
-  </si>
-  <si>
-    <t>II Gonçalo Guedes</t>
-  </si>
-  <si>
-    <t>MC Xavi Simons</t>
-  </si>
-  <si>
-    <t>ED Federico Chiesa</t>
-  </si>
-  <si>
     <t>PT Luis Malagón</t>
   </si>
   <si>
@@ -2929,6 +2827,117 @@
   </si>
   <si>
     <t>DC Moise Kean</t>
+  </si>
+  <si>
+    <t>PT Wojciech Szczęsny</t>
+  </si>
+  <si>
+    <t>CT Nicolás Otamendi</t>
+  </si>
+  <si>
+    <t>LD Takehiro Tomiyasu</t>
+  </si>
+  <si>
+    <t>MC Piotr Zieliński</t>
+  </si>
+  <si>
+    <t>MP Nico O'Reilly</t>
+  </si>
+  <si>
+    <t>II Thiago Almada</t>
+  </si>
+  <si>
+    <t>ID Franco Mastantuono</t>
+  </si>
+  <si>
+    <t>LI Ian Maatsen</t>
+  </si>
+  <si>
+    <t>LD Sergiño Dest</t>
+  </si>
+  <si>
+    <t>CT Wesley Fofana</t>
+  </si>
+  <si>
+    <t>LD Lucas Vázquez</t>
+  </si>
+  <si>
+    <t>II Ben Chilwell</t>
+  </si>
+  <si>
+    <t>II Jack Grealish</t>
+  </si>
+  <si>
+    <t>II Kaoru Mitoma</t>
+  </si>
+  <si>
+    <t>ID Harry Wilson</t>
+  </si>
+  <si>
+    <t>MC Lucas Bergvall</t>
+  </si>
+  <si>
+    <t>MP Azzedine Ounahi</t>
+  </si>
+  <si>
+    <t>MP Dominik Szoboszlai</t>
+  </si>
+  <si>
+    <t>DC Ansu Fati</t>
+  </si>
+  <si>
+    <t>Wojciech Szczęsny</t>
+  </si>
+  <si>
+    <t>Nicolás Otamendi</t>
+  </si>
+  <si>
+    <t>Takehiro Tomiyasu</t>
+  </si>
+  <si>
+    <t>Piotr Zieliński</t>
+  </si>
+  <si>
+    <t>Nico O'Reilly</t>
+  </si>
+  <si>
+    <t>Thiago Almada</t>
+  </si>
+  <si>
+    <t>Franco Mastantuono</t>
+  </si>
+  <si>
+    <t>Ian Maatsen</t>
+  </si>
+  <si>
+    <t>Sergiño Dest</t>
+  </si>
+  <si>
+    <t>Wesley Fofana</t>
+  </si>
+  <si>
+    <t>Lucas Vázquez</t>
+  </si>
+  <si>
+    <t>Ben Chilwell</t>
+  </si>
+  <si>
+    <t>Jack Grealish</t>
+  </si>
+  <si>
+    <t>Kaoru Mitoma</t>
+  </si>
+  <si>
+    <t>Harry Wilson</t>
+  </si>
+  <si>
+    <t>Lucas Bergvall</t>
+  </si>
+  <si>
+    <t>Azzedine Ounahi</t>
+  </si>
+  <si>
+    <t>Ansu Fati</t>
   </si>
 </sst>
 </file>
@@ -6694,21 +6703,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="B1" t="s">
-        <v>740</v>
+        <v>713</v>
       </c>
       <c r="C1" t="s">
-        <v>741</v>
+        <v>714</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B2" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6716,10 +6725,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B3" t="s">
-        <v>743</v>
+        <v>716</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6727,10 +6736,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B4" t="s">
-        <v>744</v>
+        <v>717</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6738,10 +6747,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B5" t="s">
-        <v>745</v>
+        <v>718</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6749,10 +6758,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>742</v>
+        <v>715</v>
       </c>
       <c r="B6" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6760,10 +6769,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="B7" t="s">
-        <v>747</v>
+        <v>720</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6771,10 +6780,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="B8" t="s">
-        <v>748</v>
+        <v>721</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6782,10 +6791,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="B9" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6793,10 +6802,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="B10" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6804,10 +6813,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>746</v>
+        <v>719</v>
       </c>
       <c r="B11" t="s">
-        <v>695</v>
+        <v>668</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6815,10 +6824,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>749</v>
+        <v>722</v>
       </c>
       <c r="B12" t="s">
-        <v>745</v>
+        <v>718</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6826,10 +6835,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>749</v>
+        <v>722</v>
       </c>
       <c r="B13" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6837,10 +6846,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>749</v>
+        <v>722</v>
       </c>
       <c r="B14" t="s">
-        <v>695</v>
+        <v>668</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -6862,47 +6871,47 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
-      </c>
-      <c r="D1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
@@ -6917,12 +6926,12 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -6937,12 +6946,12 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -6957,12 +6966,12 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -6971,18 +6980,18 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
         <v>81</v>
@@ -6997,12 +7006,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -7017,7 +7026,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -7036,27 +7045,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>131</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>132</v>
-      </c>
-      <c r="D1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -7071,15 +7080,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7091,15 +7100,15 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -7111,12 +7120,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B5" t="s">
         <v>81</v>
@@ -7131,35 +7140,35 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7171,12 +7180,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
@@ -7191,7 +7200,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -10325,7 +10334,7 @@
         <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>80</v>
@@ -10337,7 +10346,7 @@
         <v>15</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>72</v>
@@ -10346,10 +10355,10 @@
         <v>82</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>806</v>
+        <v>777</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>75</v>
@@ -10372,320 +10381,320 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>770</v>
+        <v>743</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>779</v>
+        <v>752</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>807</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="L2" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>840</v>
+        <v>811</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>754</v>
+        <v>727</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>804</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>808</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>212</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>104</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>841</v>
+        <v>812</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>799</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>222</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>827</v>
+        <v>798</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>842</v>
+        <v>813</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>359</v>
+        <v>345</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>782</v>
+        <v>755</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>216</v>
+        <v>935</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>810</v>
+        <v>781</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>829</v>
+        <v>800</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>843</v>
+        <v>814</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>755</v>
+        <v>728</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>783</v>
+        <v>756</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>249</v>
+        <v>936</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>811</v>
+        <v>782</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>824</v>
+        <v>795</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>844</v>
+        <v>815</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -10693,140 +10702,140 @@
         <v>103</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>761</v>
+        <v>734</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>776</v>
+        <v>749</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>784</v>
+        <v>757</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>164</v>
+        <v>235</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>825</v>
+        <v>796</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>84</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>835</v>
+        <v>806</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>845</v>
+        <v>816</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>756</v>
+        <v>729</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>773</v>
+        <v>746</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>777</v>
+        <v>750</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>785</v>
+        <v>758</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>812</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>830</v>
+        <v>801</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>846</v>
+        <v>817</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>757</v>
+        <v>730</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>762</v>
+        <v>735</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>170</v>
+        <v>938</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>813</v>
+        <v>784</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>92</v>
@@ -10835,30 +10844,30 @@
         <v>50</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>97</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>847</v>
+        <v>818</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>758</v>
+        <v>731</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>106</v>
@@ -10873,13 +10882,13 @@
         <v>56</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>159</v>
+        <v>939</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>94</v>
@@ -10888,13 +10897,13 @@
         <v>78</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>848</v>
+        <v>819</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>79</v>
@@ -10902,7 +10911,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>16</v>
@@ -10911,31 +10920,31 @@
         <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>774</v>
+        <v>747</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>786</v>
+        <v>759</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>77</v>
@@ -10947,363 +10956,363 @@
         <v>95</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>849</v>
+        <v>820</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>763</v>
+        <v>736</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>787</v>
+        <v>760</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>800</v>
+        <v>773</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>275</v>
+        <v>940</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>831</v>
+        <v>802</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>836</v>
+        <v>807</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>850</v>
+        <v>821</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>759</v>
+        <v>732</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>764</v>
+        <v>737</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>788</v>
+        <v>761</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>263</v>
+        <v>941</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>814</v>
+        <v>785</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>837</v>
+        <v>808</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>789</v>
+        <v>762</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>126</v>
+        <v>942</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>815</v>
+        <v>786</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>851</v>
+        <v>822</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>351</v>
+        <v>337</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>790</v>
+        <v>763</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>117</v>
+        <v>943</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>753</v>
+        <v>726</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>110</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>832</v>
+        <v>803</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>852</v>
+        <v>823</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>765</v>
+        <v>738</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>791</v>
+        <v>764</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>801</v>
+        <v>774</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>337</v>
+        <v>944</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>816</v>
+        <v>787</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>833</v>
+        <v>804</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>859</v>
+        <v>830</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>766</v>
+        <v>739</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>792</v>
+        <v>765</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>805</v>
+        <v>945</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>817</v>
+        <v>788</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>853</v>
+        <v>824</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>767</v>
+        <v>740</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>793</v>
+        <v>766</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>61</v>
+        <v>946</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>818</v>
+        <v>789</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>76</v>
@@ -11312,51 +11321,51 @@
         <v>74</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>838</v>
+        <v>809</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>854</v>
+        <v>825</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>768</v>
+        <v>741</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>794</v>
+        <v>767</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>109</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>111</v>
+        <v>947</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>819</v>
+        <v>790</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>90</v>
@@ -11365,51 +11374,51 @@
         <v>100</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>855</v>
+        <v>826</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>345</v>
+        <v>331</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>343</v>
+        <v>329</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>795</v>
+        <v>768</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>195</v>
+        <v>948</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>820</v>
+        <v>791</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>346</v>
+        <v>332</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>88</v>
@@ -11418,66 +11427,66 @@
         <v>107</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>344</v>
+        <v>330</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>59</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>860</v>
+        <v>831</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>769</v>
+        <v>742</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>796</v>
+        <v>769</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>802</v>
+        <v>775</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>342</v>
+        <v>949</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>821</v>
+        <v>792</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>352</v>
+        <v>338</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>828</v>
+        <v>799</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>834</v>
+        <v>805</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>350</v>
+        <v>336</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>839</v>
+        <v>810</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>856</v>
+        <v>827</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>71</v>
@@ -11485,55 +11494,55 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>760</v>
+        <v>733</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>358</v>
+        <v>344</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>793</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>797</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>826</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>857</v>
+        <v>828</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -11541,47 +11550,49 @@
         <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>772</v>
+        <v>745</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>98</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>798</v>
+        <v>771</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>803</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>776</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>950</v>
+      </c>
       <c r="J24" s="3" t="s">
-        <v>823</v>
+        <v>794</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>858</v>
+        <v>829</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>102</v>
@@ -11625,13 +11636,13 @@
         <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>881</v>
+        <v>852</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>15</v>
@@ -11649,13 +11660,13 @@
         <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>928</v>
+        <v>894</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>81</v>
@@ -11673,1241 +11684,1243 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>861</v>
+        <v>832</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>882</v>
+        <v>853</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>519</v>
+        <v>498</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>366</v>
+        <v>914</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>921</v>
+        <v>887</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>941</v>
+        <v>907</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>435</v>
+        <v>417</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>390</v>
+        <v>374</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>862</v>
+        <v>833</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="M4" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>902</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>411</v>
-      </c>
       <c r="N4" s="3" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="N5" s="3" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>619</v>
+        <v>593</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>428</v>
+        <v>410</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>429</v>
+        <v>411</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>903</v>
+        <v>874</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="M6" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>430</v>
-      </c>
       <c r="Q6" s="3" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>863</v>
+        <v>834</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>883</v>
+        <v>854</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>439</v>
+        <v>421</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>893</v>
+        <v>864</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>438</v>
+        <v>420</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>917</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>441</v>
+        <v>423</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>440</v>
+        <v>422</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>873</v>
+        <v>844</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>888</v>
+        <v>859</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>894</v>
+        <v>865</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>904</v>
+        <v>875</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="N8" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>461</v>
-      </c>
       <c r="O8" s="3" t="s">
-        <v>517</v>
+        <v>496</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>864</v>
+        <v>835</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>874</v>
+        <v>845</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>592</v>
+        <v>568</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>889</v>
+        <v>860</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>895</v>
+        <v>866</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>594</v>
+        <v>570</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>628</v>
+        <v>601</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>478</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>926</v>
+        <v>892</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>930</v>
+        <v>896</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>865</v>
+        <v>836</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>884</v>
+        <v>855</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>896</v>
+        <v>867</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>910</v>
+        <v>881</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>491</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>482</v>
+        <v>462</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>866</v>
+        <v>837</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>875</v>
+        <v>846</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>642</v>
+        <v>615</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>905</v>
+        <v>876</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>508</v>
+        <v>920</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>924</v>
+        <v>890</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>867</v>
+        <v>838</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>876</v>
+        <v>847</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>607</v>
+        <v>582</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>890</v>
+        <v>861</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>897</v>
+        <v>868</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>911</v>
+        <v>882</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>483</v>
+        <v>463</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>513</v>
-      </c>
       <c r="P12" s="3" t="s">
-        <v>511</v>
+        <v>490</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>514</v>
+        <v>493</v>
       </c>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>510</v>
+        <v>489</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>912</v>
+        <v>883</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>522</v>
+        <v>921</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>521</v>
+        <v>500</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>931</v>
+        <v>897</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>936</v>
+        <v>902</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>942</v>
+        <v>908</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>868</v>
+        <v>839</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>877</v>
+        <v>848</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>898</v>
+        <v>869</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>393</v>
+        <v>377</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>937</v>
+        <v>903</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>620</v>
+        <v>594</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>587</v>
+        <v>563</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>913</v>
+        <v>884</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>585</v>
+        <v>923</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>555</v>
+        <v>533</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>611</v>
+        <v>586</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>520</v>
+        <v>499</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>943</v>
+        <v>909</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>640</v>
+        <v>613</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>899</v>
+        <v>870</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>633</v>
+        <v>606</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>601</v>
+        <v>924</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>932</v>
+        <v>898</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>432</v>
+        <v>414</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>878</v>
+        <v>849</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>885</v>
+        <v>856</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>900</v>
+        <v>871</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>906</v>
+        <v>877</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>613</v>
+        <v>925</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>579</v>
+        <v>556</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>933</v>
+        <v>899</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>576</v>
+        <v>553</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>938</v>
+        <v>904</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>583</v>
+        <v>560</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>627</v>
+        <v>600</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>584</v>
+        <v>561</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>590</v>
+        <v>566</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>944</v>
+        <v>910</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>869</v>
+        <v>840</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>516</v>
+        <v>495</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>606</v>
+        <v>581</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>602</v>
+        <v>577</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="J19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
         <v>580</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>605</v>
       </c>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>879</v>
+        <v>850</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>434</v>
+        <v>416</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>891</v>
+        <v>862</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>901</v>
+        <v>872</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>573</v>
+        <v>928</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>621</v>
+        <v>595</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>612</v>
+        <v>587</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>481</v>
+        <v>461</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>650</v>
+        <v>623</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>945</v>
+        <v>911</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>609</v>
+        <v>584</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>632</v>
+        <v>605</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>626</v>
+        <v>599</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>574</v>
+        <v>551</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>907</v>
+        <v>878</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>610</v>
+        <v>585</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>381</v>
+        <v>929</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>596</v>
+        <v>572</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>634</v>
+        <v>607</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>624</v>
+        <v>598</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>934</v>
+        <v>900</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>629</v>
+        <v>602</v>
       </c>
       <c r="O21" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="P21" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>657</v>
-      </c>
       <c r="Q21" s="3" t="s">
-        <v>631</v>
+        <v>604</v>
       </c>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>870</v>
+        <v>841</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>639</v>
+        <v>612</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>886</v>
+        <v>857</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>635</v>
+        <v>608</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>908</v>
+        <v>879</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>914</v>
+        <v>885</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>625</v>
+        <v>930</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>622</v>
+        <v>596</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>641</v>
+        <v>614</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>927</v>
+        <v>893</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>935</v>
+        <v>901</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>636</v>
+        <v>609</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>940</v>
+        <v>906</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>946</v>
+        <v>912</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>638</v>
+        <v>611</v>
       </c>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>871</v>
+        <v>842</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>880</v>
+        <v>851</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>652</v>
+        <v>625</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>647</v>
+        <v>620</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>644</v>
+        <v>617</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>646</v>
+        <v>931</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>923</v>
+        <v>889</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>655</v>
+        <v>628</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>645</v>
+        <v>618</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>649</v>
+        <v>622</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>637</v>
+        <v>610</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>947</v>
+        <v>913</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>651</v>
+        <v>624</v>
       </c>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>656</v>
+        <v>629</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>577</v>
+        <v>554</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>515</v>
+        <v>494</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>887</v>
+        <v>858</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>658</v>
+        <v>631</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>665</v>
+        <v>638</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="I24" s="3"/>
+        <v>886</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>932</v>
+      </c>
       <c r="J24" s="3" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>666</v>
+        <v>639</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>660</v>
+        <v>633</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>663</v>
+        <v>636</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>664</v>
+        <v>637</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>662</v>
+        <v>635</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>618</v>
+        <v>592</v>
       </c>
       <c r="R24" s="3"/>
     </row>
@@ -12935,25 +12948,25 @@
         <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>667</v>
+        <v>640</v>
       </c>
       <c r="C1" t="s">
-        <v>668</v>
+        <v>641</v>
       </c>
       <c r="D1" t="s">
-        <v>669</v>
+        <v>642</v>
       </c>
       <c r="E1" t="s">
-        <v>670</v>
+        <v>643</v>
       </c>
       <c r="F1" t="s">
-        <v>671</v>
+        <v>644</v>
       </c>
       <c r="G1" t="s">
-        <v>672</v>
+        <v>645</v>
       </c>
       <c r="H1" t="s">
-        <v>673</v>
+        <v>646</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -12961,13 +12974,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="C2" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="D2" t="s">
-        <v>676</v>
+        <v>649</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -12976,7 +12989,7 @@
         <v>1400000000</v>
       </c>
       <c r="G2" t="s">
-        <v>677</v>
+        <v>650</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -12987,13 +13000,13 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>678</v>
+        <v>651</v>
       </c>
       <c r="C3" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
       <c r="D3" t="s">
-        <v>680</v>
+        <v>653</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13002,7 +13015,7 @@
         <v>68000000</v>
       </c>
       <c r="G3" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -13010,16 +13023,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="C4" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="D4" t="s">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13028,7 +13041,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>685</v>
+        <v>658</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13039,13 +13052,13 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>686</v>
+        <v>659</v>
       </c>
       <c r="C5" t="s">
-        <v>687</v>
+        <v>660</v>
       </c>
       <c r="D5" t="s">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13054,7 +13067,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>689</v>
+        <v>662</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -13062,16 +13075,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B6" t="s">
-        <v>690</v>
+        <v>663</v>
       </c>
       <c r="C6" t="s">
-        <v>675</v>
+        <v>648</v>
       </c>
       <c r="D6" t="s">
-        <v>691</v>
+        <v>664</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13080,7 +13093,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>692</v>
+        <v>665</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -13091,13 +13104,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>693</v>
+        <v>666</v>
       </c>
       <c r="C7" t="s">
-        <v>694</v>
+        <v>667</v>
       </c>
       <c r="D7" t="s">
-        <v>695</v>
+        <v>668</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13106,7 +13119,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>696</v>
+        <v>669</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -13117,13 +13130,13 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>697</v>
+        <v>670</v>
       </c>
       <c r="C8" t="s">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="D8" t="s">
-        <v>699</v>
+        <v>672</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13132,7 +13145,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>700</v>
+        <v>673</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -13143,13 +13156,13 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>701</v>
+        <v>674</v>
       </c>
       <c r="C9" t="s">
-        <v>702</v>
+        <v>675</v>
       </c>
       <c r="D9" t="s">
-        <v>703</v>
+        <v>676</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13158,7 +13171,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>704</v>
+        <v>677</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -13169,13 +13182,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>705</v>
+        <v>678</v>
       </c>
       <c r="C10" t="s">
-        <v>706</v>
+        <v>679</v>
       </c>
       <c r="D10" t="s">
-        <v>707</v>
+        <v>680</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13184,7 +13197,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>708</v>
+        <v>681</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -13198,10 +13211,10 @@
         <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>709</v>
+        <v>682</v>
       </c>
       <c r="D11" t="s">
-        <v>710</v>
+        <v>683</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13210,7 +13223,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>711</v>
+        <v>684</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -13221,13 +13234,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>712</v>
+        <v>685</v>
       </c>
       <c r="C12" t="s">
-        <v>713</v>
+        <v>686</v>
       </c>
       <c r="D12" t="s">
-        <v>688</v>
+        <v>661</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13236,7 +13249,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>714</v>
+        <v>687</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -13247,13 +13260,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>715</v>
+        <v>688</v>
       </c>
       <c r="C13" t="s">
-        <v>716</v>
+        <v>689</v>
       </c>
       <c r="D13" t="s">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13262,7 +13275,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>718</v>
+        <v>691</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -13273,13 +13286,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>719</v>
+        <v>692</v>
       </c>
       <c r="C14" t="s">
-        <v>720</v>
+        <v>693</v>
       </c>
       <c r="D14" t="s">
-        <v>721</v>
+        <v>694</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13288,7 +13301,7 @@
         <v>893000000</v>
       </c>
       <c r="G14" t="s">
-        <v>722</v>
+        <v>695</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -13299,13 +13312,13 @@
         <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>723</v>
+        <v>696</v>
       </c>
       <c r="C15" t="s">
-        <v>724</v>
+        <v>697</v>
       </c>
       <c r="D15" t="s">
-        <v>725</v>
+        <v>698</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13314,7 +13327,7 @@
         <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="H15">
         <v>15</v>
@@ -13325,13 +13338,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>727</v>
+        <v>700</v>
       </c>
       <c r="C16" t="s">
-        <v>728</v>
+        <v>701</v>
       </c>
       <c r="D16" t="s">
-        <v>729</v>
+        <v>702</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -13340,7 +13353,7 @@
         <v>300000000</v>
       </c>
       <c r="G16" t="s">
-        <v>730</v>
+        <v>703</v>
       </c>
       <c r="H16">
         <v>13</v>
@@ -13348,16 +13361,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="B17" t="s">
-        <v>731</v>
+        <v>704</v>
       </c>
       <c r="C17" t="s">
-        <v>732</v>
+        <v>705</v>
       </c>
       <c r="D17" t="s">
-        <v>733</v>
+        <v>706</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -13366,7 +13379,7 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>734</v>
+        <v>707</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -13377,13 +13390,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>735</v>
+        <v>708</v>
       </c>
       <c r="C18" t="s">
-        <v>736</v>
+        <v>709</v>
       </c>
       <c r="D18" t="s">
-        <v>737</v>
+        <v>710</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -13392,7 +13405,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>738</v>
+        <v>711</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14294,7 +14307,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -14337,7 +14350,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>750</v>
+        <v>723</v>
       </c>
       <c r="B41" t="s">
         <v>62</v>
@@ -14357,7 +14370,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
@@ -14377,7 +14390,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
@@ -14420,7 +14433,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>751</v>
+        <v>724</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -14443,7 +14456,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -14466,7 +14479,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -14489,7 +14502,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -14512,7 +14525,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>753</v>
+        <v>726</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CC3E32E-7E47-4AB5-BC98-6FDE9C2A9614}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072265E3-A98F-4645-BB72-E369F9869AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="951">
   <si>
     <t>Jugador</t>
   </si>
@@ -528,9 +528,6 @@
     <t>Estêvão</t>
   </si>
   <si>
-    <t>Hellas_Verona</t>
-  </si>
-  <si>
     <t>Youssef En Nesyri</t>
   </si>
   <si>
@@ -2938,6 +2935,9 @@
   </si>
   <si>
     <t>Ansu Fati</t>
+  </si>
+  <si>
+    <t>Al_Nassr</t>
   </si>
 </sst>
 </file>
@@ -3379,304 +3379,624 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
       <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="A6" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="C6" s="3">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="A7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
+      <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>939</v>
+      </c>
       <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="A10" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
+      <c r="A11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>322</v>
+      </c>
       <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
+      <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
+      <c r="A13" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>817</v>
+      </c>
       <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
+      <c r="A14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
       <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>255</v>
+      </c>
       <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="A16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
       <c r="D17" s="3"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
+      <c r="A18" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+      <c r="A19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>333</v>
+      </c>
       <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
+      <c r="A20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C20" s="3">
+        <v>1</v>
+      </c>
       <c r="D20" s="3"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+      <c r="A21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="A22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="C22" s="3">
+        <v>1</v>
+      </c>
       <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
+      <c r="A23" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="3">
+        <v>8</v>
+      </c>
+      <c r="D24" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
+      <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
       <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="3"/>
+      <c r="A27" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="6">
+        <v>3</v>
+      </c>
+      <c r="D27" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C28" s="3">
+        <v>1</v>
+      </c>
       <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
+      <c r="A29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="3">
+        <v>1</v>
+      </c>
       <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+      <c r="A30" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>802</v>
+      </c>
       <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
+      <c r="D30" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
+      <c r="A31" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
       <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
+      <c r="A32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
+      <c r="A33" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
       <c r="D33" s="3"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
+      <c r="A34" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
       <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+      <c r="A35" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="A36" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
       <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+      <c r="A37" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>787</v>
+      </c>
       <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="A38" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="C38" s="3">
+        <v>2</v>
+      </c>
       <c r="D38" s="3"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
+      <c r="A39" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
       <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+      <c r="A40" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>786</v>
+      </c>
       <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
+      <c r="D40" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
+      <c r="A41" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1</v>
+      </c>
       <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+      <c r="A42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="3"/>
+      <c r="A43" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
       <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
+      <c r="A44" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="A45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+      <c r="A46" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
+      <c r="D46" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
+      <c r="A47" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>769</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1</v>
+      </c>
       <c r="D47" s="3"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="6"/>
+      <c r="A48" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C48" s="6">
+        <v>1</v>
+      </c>
       <c r="D48" s="3"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+      <c r="A49" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>745</v>
+      </c>
       <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="3"/>
+      <c r="A50" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
       <c r="D50" s="3"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+      <c r="A51" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>311</v>
+      </c>
       <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
@@ -4693,7 +5013,9 @@
       <c r="D220" s="6"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="3"/>
+      <c r="A221" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="B221" s="3"/>
       <c r="C221" s="6"/>
       <c r="D221" s="6"/>
@@ -6669,7 +6991,7 @@
       <c r="B694" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D220" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:D221" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D220">
       <sortCondition descending="1" ref="D1:D220"/>
     </sortState>
@@ -6682,7 +7004,7 @@
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A3:A260 A2</xm:sqref>
+          <xm:sqref>A2 A3:A49 A51:A260 A50</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0EE23BD-39F8-4DA0-B61E-6A00409D509E}">
           <x14:formula1>
@@ -6703,21 +7025,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B1" t="s">
         <v>712</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>713</v>
-      </c>
-      <c r="C1" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B2" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6725,10 +7047,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B3" t="s">
         <v>715</v>
-      </c>
-      <c r="B3" t="s">
-        <v>716</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6736,10 +7058,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6747,10 +7069,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6758,10 +7080,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B6" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6769,10 +7091,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>718</v>
+      </c>
+      <c r="B7" t="s">
         <v>719</v>
-      </c>
-      <c r="B7" t="s">
-        <v>720</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6780,10 +7102,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6791,10 +7113,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B9" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6802,10 +7124,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B10" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6813,10 +7135,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B11" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6824,10 +7146,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B12" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6835,10 +7157,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B13" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6846,10 +7168,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B14" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -10334,7 +10656,7 @@
         <v>83</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>147</v>
+        <v>950</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>80</v>
@@ -10346,7 +10668,7 @@
         <v>15</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>72</v>
@@ -10355,10 +10677,10 @@
         <v>82</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>75</v>
@@ -10381,320 +10703,320 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="N2" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>179</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>188</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>189</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>113</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N3" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>811</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>111</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>104</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>116</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>209</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>813</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>754</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>935</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>800</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>112</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N7" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>231</v>
-      </c>
       <c r="P7" s="3" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
@@ -10702,140 +11024,140 @@
         <v>103</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>87</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>84</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>114</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>92</v>
@@ -10844,30 +11166,30 @@
         <v>50</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>97</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>106</v>
@@ -10882,13 +11204,13 @@
         <v>56</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>94</v>
@@ -10897,13 +11219,13 @@
         <v>78</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>79</v>
@@ -10911,7 +11233,7 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>16</v>
@@ -10920,28 +11242,28 @@
         <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>146</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>123</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>118</v>
@@ -10956,289 +11278,289 @@
         <v>95</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>735</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>736</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>174</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>89</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>126</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>285</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>822</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="L16" s="3" t="s">
         <v>110</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>124</v>
@@ -11247,72 +11569,72 @@
         <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>824</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>105</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>115</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>76</v>
@@ -11321,51 +11643,51 @@
         <v>74</v>
       </c>
       <c r="N19" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>809</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>825</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>122</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>109</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>90</v>
@@ -11374,51 +11696,51 @@
         <v>100</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="I21" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>331</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>948</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>332</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>88</v>
@@ -11427,66 +11749,66 @@
         <v>107</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>59</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>333</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>742</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>334</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>99</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>71</v>
@@ -11494,55 +11816,55 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>86</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>119</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
@@ -11550,34 +11872,34 @@
         <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>98</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>117</v>
@@ -11589,10 +11911,10 @@
         <v>121</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>102</v>
@@ -11636,7 +11958,7 @@
         <v>17</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>24</v>
@@ -11660,13 +11982,13 @@
         <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>81</v>
@@ -11684,1243 +12006,1243 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>853</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="H2" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>914</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>887</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>355</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>356</v>
       </c>
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="P3" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="O3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>370</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>371</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="P4" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="O4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>385</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>386</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="N5" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>399</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>400</v>
       </c>
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D6" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="P6" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>874</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>895</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="Q6" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="M7" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>864</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>422</v>
-      </c>
       <c r="N7" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="Q7" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>844</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="I8" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>865</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="N8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>442</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>443</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>895</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="P9" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>860</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>888</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>892</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>896</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="O9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="P10" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>867</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>881</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="O10" s="3" t="s">
+      <c r="Q10" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>889</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="P11" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>476</v>
-      </c>
       <c r="Q11" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="N12" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="O12" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="P12" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="Q12" s="3" t="s">
         <v>492</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>493</v>
       </c>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="F13" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>896</v>
+      </c>
+      <c r="N13" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>897</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>502</v>
-      </c>
       <c r="O13" s="3" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="O15" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="Q15" s="3" t="s">
         <v>529</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>530</v>
       </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E18" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>561</v>
-      </c>
       <c r="M18" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N18" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>566</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>567</v>
       </c>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="P19" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="N19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="H20" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>850</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>862</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>872</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>574</v>
-      </c>
       <c r="I20" s="3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="E21" s="3" t="s">
+      <c r="I21" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>878</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>929</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>598</v>
-      </c>
       <c r="M21" s="3" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="N21" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="O21" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="Q21" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E22" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>878</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="N22" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>879</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>885</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>930</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>893</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>901</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>609</v>
-      </c>
       <c r="O22" s="3" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>930</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>888</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>931</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>889</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>618</v>
-      </c>
       <c r="M23" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>885</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>931</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="M24" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>886</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>932</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>632</v>
-      </c>
       <c r="N24" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>637</v>
-      </c>
       <c r="P24" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="R24" s="3"/>
     </row>
@@ -12948,25 +13270,25 @@
         <v>66</v>
       </c>
       <c r="B1" t="s">
+        <v>639</v>
+      </c>
+      <c r="C1" t="s">
         <v>640</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>641</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>642</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>643</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>644</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>645</v>
-      </c>
-      <c r="H1" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -12974,13 +13296,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
+        <v>646</v>
+      </c>
+      <c r="C2" t="s">
         <v>647</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>648</v>
-      </c>
-      <c r="D2" t="s">
-        <v>649</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -12989,7 +13311,7 @@
         <v>1400000000</v>
       </c>
       <c r="G2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -13000,13 +13322,13 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
+        <v>650</v>
+      </c>
+      <c r="C3" t="s">
         <v>651</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>652</v>
-      </c>
-      <c r="D3" t="s">
-        <v>653</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13015,7 +13337,7 @@
         <v>68000000</v>
       </c>
       <c r="G3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -13026,13 +13348,13 @@
         <v>134</v>
       </c>
       <c r="B4" t="s">
+        <v>654</v>
+      </c>
+      <c r="C4" t="s">
         <v>655</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>656</v>
-      </c>
-      <c r="D4" t="s">
-        <v>657</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13041,7 +13363,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13052,13 +13374,13 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
+        <v>658</v>
+      </c>
+      <c r="C5" t="s">
         <v>659</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>660</v>
-      </c>
-      <c r="D5" t="s">
-        <v>661</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13067,7 +13389,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -13078,13 +13400,13 @@
         <v>135</v>
       </c>
       <c r="B6" t="s">
+        <v>662</v>
+      </c>
+      <c r="C6" t="s">
+        <v>647</v>
+      </c>
+      <c r="D6" t="s">
         <v>663</v>
-      </c>
-      <c r="C6" t="s">
-        <v>648</v>
-      </c>
-      <c r="D6" t="s">
-        <v>664</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13093,7 +13415,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -13104,13 +13426,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
+        <v>665</v>
+      </c>
+      <c r="C7" t="s">
         <v>666</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>667</v>
-      </c>
-      <c r="D7" t="s">
-        <v>668</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13119,7 +13441,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -13130,13 +13452,13 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
+        <v>669</v>
+      </c>
+      <c r="C8" t="s">
         <v>670</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>671</v>
-      </c>
-      <c r="D8" t="s">
-        <v>672</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13145,7 +13467,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -13156,13 +13478,13 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
+        <v>673</v>
+      </c>
+      <c r="C9" t="s">
         <v>674</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>675</v>
-      </c>
-      <c r="D9" t="s">
-        <v>676</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13171,7 +13493,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -13182,13 +13504,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>677</v>
+      </c>
+      <c r="C10" t="s">
         <v>678</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>679</v>
-      </c>
-      <c r="D10" t="s">
-        <v>680</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13197,7 +13519,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -13211,10 +13533,10 @@
         <v>81</v>
       </c>
       <c r="C11" t="s">
+        <v>681</v>
+      </c>
+      <c r="D11" t="s">
         <v>682</v>
-      </c>
-      <c r="D11" t="s">
-        <v>683</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13223,7 +13545,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -13234,13 +13556,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>684</v>
+      </c>
+      <c r="C12" t="s">
         <v>685</v>
       </c>
-      <c r="C12" t="s">
-        <v>686</v>
-      </c>
       <c r="D12" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13249,7 +13571,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -13260,13 +13582,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
+        <v>687</v>
+      </c>
+      <c r="C13" t="s">
         <v>688</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>689</v>
-      </c>
-      <c r="D13" t="s">
-        <v>690</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13275,7 +13597,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -13286,13 +13608,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
+        <v>691</v>
+      </c>
+      <c r="C14" t="s">
         <v>692</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>693</v>
-      </c>
-      <c r="D14" t="s">
-        <v>694</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13301,7 +13623,7 @@
         <v>893000000</v>
       </c>
       <c r="G14" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -13312,13 +13634,13 @@
         <v>33</v>
       </c>
       <c r="B15" t="s">
+        <v>695</v>
+      </c>
+      <c r="C15" t="s">
         <v>696</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>697</v>
-      </c>
-      <c r="D15" t="s">
-        <v>698</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13327,7 +13649,7 @@
         <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H15">
         <v>15</v>
@@ -13338,13 +13660,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
+        <v>699</v>
+      </c>
+      <c r="C16" t="s">
         <v>700</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>701</v>
-      </c>
-      <c r="D16" t="s">
-        <v>702</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -13353,7 +13675,7 @@
         <v>300000000</v>
       </c>
       <c r="G16" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H16">
         <v>13</v>
@@ -13361,16 +13683,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
+        <v>703</v>
+      </c>
+      <c r="C17" t="s">
         <v>704</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>705</v>
-      </c>
-      <c r="D17" t="s">
-        <v>706</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -13379,7 +13701,7 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -13390,13 +13712,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
+        <v>707</v>
+      </c>
+      <c r="C18" t="s">
         <v>708</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>709</v>
-      </c>
-      <c r="D18" t="s">
-        <v>710</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -13405,7 +13727,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14307,7 +14629,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -14350,7 +14672,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B41" t="s">
         <v>62</v>
@@ -14370,7 +14692,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
@@ -14390,7 +14712,7 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
@@ -14433,7 +14755,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -14456,7 +14778,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -14479,7 +14801,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -14525,7 +14847,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072265E3-A98F-4645-BB72-E369F9869AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB26832F-5537-414A-8BE3-CCE7DADCAAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$223</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="951">
   <si>
     <t>Jugador</t>
   </si>
@@ -3453,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -3464,7 +3464,7 @@
         <v>938</v>
       </c>
       <c r="C8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="3"/>
     </row>
@@ -3549,9 +3549,11 @@
       <c r="B15" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="C15" s="3"/>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -3562,7 +3564,7 @@
         <v>796</v>
       </c>
       <c r="C16" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -3636,7 +3638,7 @@
         <v>798</v>
       </c>
       <c r="C22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="3"/>
     </row>
@@ -3712,7 +3714,7 @@
         <v>238</v>
       </c>
       <c r="C28" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" s="3"/>
     </row>
@@ -3786,7 +3788,7 @@
         <v>744</v>
       </c>
       <c r="C34" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="3"/>
     </row>
@@ -3834,7 +3836,7 @@
         <v>819</v>
       </c>
       <c r="C38" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D38" s="3"/>
     </row>
@@ -3848,7 +3850,9 @@
       <c r="C39" s="3">
         <v>1</v>
       </c>
-      <c r="D39" s="3"/>
+      <c r="D39" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
@@ -3883,7 +3887,7 @@
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -3999,106 +4003,218 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
-      <c r="C52" s="3"/>
-      <c r="D52" s="3"/>
+      <c r="A52" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="A53" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53" s="3">
+        <v>4</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
-      <c r="C54" s="3"/>
-      <c r="D54" s="3"/>
+      <c r="A54" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C54" s="3">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
+      <c r="A55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C55" s="3">
+        <v>2</v>
+      </c>
       <c r="D55" s="3"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="A56" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C56" s="3">
+        <v>4</v>
+      </c>
       <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+      <c r="A57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>230</v>
+      </c>
       <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
+      <c r="D57" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
+      <c r="A58" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
+      <c r="A59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+      <c r="A60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
+      <c r="D60" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+      <c r="A61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="D61" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+      <c r="A62" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>810</v>
+      </c>
       <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+      <c r="A63" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>795</v>
+      </c>
       <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
+      <c r="D63" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="A64" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
       <c r="D64" s="3"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+      <c r="A65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>324</v>
+      </c>
       <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
+      <c r="D65" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+      <c r="A66" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>86</v>
+      </c>
       <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
+      <c r="A67" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
       <c r="D67" s="3"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+      <c r="A68" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
@@ -5021,16 +5137,28 @@
       <c r="D221" s="6"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="3"/>
-      <c r="B222" s="3"/>
-      <c r="C222" s="6"/>
+      <c r="A222" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B222" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C222" s="6">
+        <v>1</v>
+      </c>
       <c r="D222" s="6"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="3"/>
-      <c r="B223" s="3"/>
+      <c r="A223" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B223" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="C223" s="6"/>
-      <c r="D223" s="6"/>
+      <c r="D223" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
@@ -6991,7 +7119,7 @@
       <c r="B694" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D221" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:D223" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D220">
       <sortCondition descending="1" ref="D1:D220"/>
     </sortState>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB26832F-5537-414A-8BE3-CCE7DADCAAC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2385C79-4BAA-49FF-BFF4-CC59BF7FE490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="951">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="943">
   <si>
     <t>Jugador</t>
   </si>
@@ -294,15 +294,9 @@
     <t>Asistencias</t>
   </si>
   <si>
-    <t>Tottenham_Hotspur</t>
-  </si>
-  <si>
     <t>FC_Barcelona</t>
   </si>
   <si>
-    <t>Ángel Di María</t>
-  </si>
-  <si>
     <t>Real_Madrid</t>
   </si>
   <si>
@@ -324,9 +318,6 @@
     <t>Erling Haaland</t>
   </si>
   <si>
-    <t>Darwin Núñez</t>
-  </si>
-  <si>
     <t>Boca_Juniors</t>
   </si>
   <si>
@@ -336,9 +327,6 @@
     <t>RB_Leipzig</t>
   </si>
   <si>
-    <t>Manchester_United</t>
-  </si>
-  <si>
     <t>Joelinton</t>
   </si>
   <si>
@@ -546,12 +534,6 @@
     <t>Harry Kane</t>
   </si>
   <si>
-    <t>Jonathan David</t>
-  </si>
-  <si>
-    <t>Loïs Openda</t>
-  </si>
-  <si>
     <t>Viktor Gyökeres</t>
   </si>
   <si>
@@ -573,9 +555,6 @@
     <t>Tijjani Reijnders</t>
   </si>
   <si>
-    <t>Youssouf Fofana</t>
-  </si>
-  <si>
     <t>Riyad Mahrez</t>
   </si>
   <si>
@@ -624,9 +603,6 @@
     <t>Diogo Costa</t>
   </si>
   <si>
-    <t>Manuel Neuer</t>
-  </si>
-  <si>
     <t>Marco Carnesecchi</t>
   </si>
   <si>
@@ -660,9 +636,6 @@
     <t>Ronald Araújo</t>
   </si>
   <si>
-    <t>Paolo Maldini</t>
-  </si>
-  <si>
     <t>Victor Nelsson</t>
   </si>
   <si>
@@ -684,15 +657,9 @@
     <t>Ezri Konsa</t>
   </si>
   <si>
-    <t>Micky van de Ven</t>
-  </si>
-  <si>
     <t>Jean-Clair Todibo</t>
   </si>
   <si>
-    <t>Robert Andrich</t>
-  </si>
-  <si>
     <t>Mario Gila</t>
   </si>
   <si>
@@ -720,9 +687,6 @@
     <t>Edmond Tapsoba</t>
   </si>
   <si>
-    <t>Dayot Upamecano</t>
-  </si>
-  <si>
     <t>Marcos Llorente</t>
   </si>
   <si>
@@ -756,9 +720,6 @@
     <t>Aaron Martin</t>
   </si>
   <si>
-    <t>Alphonso Davies</t>
-  </si>
-  <si>
     <t>Riccardo Calafiori</t>
   </si>
   <si>
@@ -783,9 +744,6 @@
     <t>James Garner</t>
   </si>
   <si>
-    <t>Manuel Ugarte</t>
-  </si>
-  <si>
     <t>Dani Olmo</t>
   </si>
   <si>
@@ -795,9 +753,6 @@
     <t>Malo Gusto</t>
   </si>
   <si>
-    <t>Joshua Kimmich</t>
-  </si>
-  <si>
     <t>Michel Aebischer</t>
   </si>
   <si>
@@ -816,9 +771,6 @@
     <t>Andreas Schjelderup</t>
   </si>
   <si>
-    <t>Petar Sučić</t>
-  </si>
-  <si>
     <t>İlkay Gündoğan</t>
   </si>
   <si>
@@ -837,9 +789,6 @@
     <t>Julian Quiñones</t>
   </si>
   <si>
-    <t>Pablo Fornals</t>
-  </si>
-  <si>
     <t>Liam Delap</t>
   </si>
   <si>
@@ -888,9 +837,6 @@
     <t>Thibaut Courtois</t>
   </si>
   <si>
-    <t>David Soria</t>
-  </si>
-  <si>
     <t>Aaron Ramsdale</t>
   </si>
   <si>
@@ -921,9 +867,6 @@
     <t>Illia Zabarnyi</t>
   </si>
   <si>
-    <t>Rayan Aït-Nouri</t>
-  </si>
-  <si>
     <t>Jhon Lucumi</t>
   </si>
   <si>
@@ -942,9 +885,6 @@
     <t>Andrea Cambiaso</t>
   </si>
   <si>
-    <t>Éder Militão</t>
-  </si>
-  <si>
     <t>Raphael Onyedika</t>
   </si>
   <si>
@@ -969,9 +909,6 @@
     <t>Sergi Cardona</t>
   </si>
   <si>
-    <t>Lewis Dunk</t>
-  </si>
-  <si>
     <t>Yangel Herrera</t>
   </si>
   <si>
@@ -993,9 +930,6 @@
     <t>Qazim Laci</t>
   </si>
   <si>
-    <t>Marcel Sabitzer</t>
-  </si>
-  <si>
     <t>Alex Freeman</t>
   </si>
   <si>
@@ -1017,9 +951,6 @@
     <t>Matteo Guendouzi</t>
   </si>
   <si>
-    <t>Morten Hjulmand</t>
-  </si>
-  <si>
     <t>James Ward Prowse</t>
   </si>
   <si>
@@ -1044,9 +975,6 @@
     <t>Marco Asensio</t>
   </si>
   <si>
-    <t>Granit Xhaka</t>
-  </si>
-  <si>
     <t>Josip Stanisić</t>
   </si>
   <si>
@@ -1065,9 +993,6 @@
     <t>Antonee Robinson</t>
   </si>
   <si>
-    <t>Strahinja Pavlović</t>
-  </si>
-  <si>
     <t>Nicolò Zaniolo</t>
   </si>
   <si>
@@ -1095,9 +1020,6 @@
     <t>Gabriel Martinelli</t>
   </si>
   <si>
-    <t>Aymeric Laporte</t>
-  </si>
-  <si>
     <t>Francisco Trincão</t>
   </si>
   <si>
@@ -1113,15 +1035,9 @@
     <t>Christian Pulišić</t>
   </si>
   <si>
-    <t>Edinson Cavani</t>
-  </si>
-  <si>
     <t>Václav Černy</t>
   </si>
   <si>
-    <t>Danilo</t>
-  </si>
-  <si>
     <t>Serhou Guirassy</t>
   </si>
   <si>
@@ -1152,9 +1068,6 @@
     <t>PT Diogo Costa</t>
   </si>
   <si>
-    <t>PT Manuel Neuer</t>
-  </si>
-  <si>
     <t>PT Marco Carnesecchi</t>
   </si>
   <si>
@@ -1197,9 +1110,6 @@
     <t>CT Ronald Araújo</t>
   </si>
   <si>
-    <t>LI Paolo Maldini</t>
-  </si>
-  <si>
     <t>LD Trent Alexander-Arnold</t>
   </si>
   <si>
@@ -1242,9 +1152,6 @@
     <t>CT Nico Schlotterbeck</t>
   </si>
   <si>
-    <t>CT Micky van de Ven</t>
-  </si>
-  <si>
     <t>CT Jean-Clair Todibo</t>
   </si>
   <si>
@@ -1290,9 +1197,6 @@
     <t>CT Edmond Tapsoba</t>
   </si>
   <si>
-    <t>CT Dayot Upamecano</t>
-  </si>
-  <si>
     <t>LD Marcos Llorente</t>
   </si>
   <si>
@@ -1329,15 +1233,9 @@
     <t>LD Kyle Walker</t>
   </si>
   <si>
-    <t>LD Achraf Hakimi</t>
-  </si>
-  <si>
     <t>LI Aarón Martín</t>
   </si>
   <si>
-    <t>LI Alphonso Davies</t>
-  </si>
-  <si>
     <t>LI Riccardo Calafiori</t>
   </si>
   <si>
@@ -1371,12 +1269,6 @@
     <t>MCD Felix Nmecha</t>
   </si>
   <si>
-    <t>MCD Youssouf Fofana</t>
-  </si>
-  <si>
-    <t>MCD Manuel Ugarte</t>
-  </si>
-  <si>
     <t>CT Sergio Ramos</t>
   </si>
   <si>
@@ -1413,15 +1305,9 @@
     <t>MC Alexis Mac Allister</t>
   </si>
   <si>
-    <t>MCD Joshua Kimmich</t>
-  </si>
-  <si>
     <t>MC Michel Aebischer</t>
   </si>
   <si>
-    <t>MC Nadiem Amiri</t>
-  </si>
-  <si>
     <t>CT Lisandro Martínez</t>
   </si>
   <si>
@@ -1452,9 +1338,6 @@
     <t>MP Florian Wirtz</t>
   </si>
   <si>
-    <t>MC Isco</t>
-  </si>
-  <si>
     <t>MCD Jorginho</t>
   </si>
   <si>
@@ -1488,15 +1371,9 @@
     <t>EI Kenan Yıldız</t>
   </si>
   <si>
-    <t>SD Jonathan David</t>
-  </si>
-  <si>
     <t>EI Julián Quiñones</t>
   </si>
   <si>
-    <t>MP Pablo Fornals</t>
-  </si>
-  <si>
     <t>DC Liam Delap</t>
   </si>
   <si>
@@ -1521,15 +1398,9 @@
     <t>ED Lamine Yamal</t>
   </si>
   <si>
-    <t>DC Darwin Núñez</t>
-  </si>
-  <si>
     <t>ED Antonio Nusa</t>
   </si>
   <si>
-    <t>SD Roberto Baggio</t>
-  </si>
-  <si>
     <t>MP Bruno Fernandes</t>
   </si>
   <si>
@@ -1563,15 +1434,9 @@
     <t>DC Jamie Vardy</t>
   </si>
   <si>
-    <t>DC Loïs Openda</t>
-  </si>
-  <si>
     <t>DC Raúl Jiménez</t>
   </si>
   <si>
-    <t>DC Marko Arnautović</t>
-  </si>
-  <si>
     <t>MC Luka Modrić</t>
   </si>
   <si>
@@ -1596,12 +1461,6 @@
     <t>PT Thibaut Courtois</t>
   </si>
   <si>
-    <t>PT David Soria</t>
-  </si>
-  <si>
-    <t>LD Nahuel Molina</t>
-  </si>
-  <si>
     <t>ED Bukayo Saka</t>
   </si>
   <si>
@@ -1617,9 +1476,6 @@
     <t>CT Eric García</t>
   </si>
   <si>
-    <t>LD Dani Carvajal</t>
-  </si>
-  <si>
     <t>CT Matthijs de Ligt</t>
   </si>
   <si>
@@ -1638,9 +1494,6 @@
     <t>CT Cristian Romero</t>
   </si>
   <si>
-    <t>LI Rayan Aït-Nouri</t>
-  </si>
-  <si>
     <t>CT Jhon Lucumí</t>
   </si>
   <si>
@@ -1674,9 +1527,6 @@
     <t>II Andrea Cambiaso</t>
   </si>
   <si>
-    <t>CT Éder Militão</t>
-  </si>
-  <si>
     <t>MCD Raphael Onyedika</t>
   </si>
   <si>
@@ -1713,15 +1563,9 @@
     <t>LI Sergi Cardona</t>
   </si>
   <si>
-    <t>CT Lewis Dunk</t>
-  </si>
-  <si>
     <t>MCD Yangel Herrera</t>
   </si>
   <si>
-    <t>CT Jan Paul van Hecke</t>
-  </si>
-  <si>
     <t>CT Piero Hincapié</t>
   </si>
   <si>
@@ -1746,9 +1590,6 @@
     <t>MC Sandro Tonali</t>
   </si>
   <si>
-    <t>MC Marcel Sabitzer</t>
-  </si>
-  <si>
     <t>EI Rafael Leão</t>
   </si>
   <si>
@@ -1785,9 +1626,6 @@
     <t>MC Rodri</t>
   </si>
   <si>
-    <t>MCD Morten Hjulmand</t>
-  </si>
-  <si>
     <t>MP James Ward-Prowse</t>
   </si>
   <si>
@@ -1824,9 +1662,6 @@
     <t>MP Marco Asensio</t>
   </si>
   <si>
-    <t>MCD Granit Xhaka</t>
-  </si>
-  <si>
     <t>LD Josip Stanišić</t>
   </si>
   <si>
@@ -1860,15 +1695,9 @@
     <t>MP Tijjani Reijnders</t>
   </si>
   <si>
-    <t>MP Oihan Sancet</t>
-  </si>
-  <si>
     <t>LI Antonee Robinson</t>
   </si>
   <si>
-    <t>CT Strahinja Pavlović</t>
-  </si>
-  <si>
     <t>MP Nicolò Zaniolo</t>
   </si>
   <si>
@@ -1896,9 +1725,6 @@
     <t>ED Riyad Mahrez</t>
   </si>
   <si>
-    <t>MP Álex Baena</t>
-  </si>
-  <si>
     <t>MP Bilal El Khannouss</t>
   </si>
   <si>
@@ -1917,15 +1743,9 @@
     <t>EI Cody Gakpo</t>
   </si>
   <si>
-    <t>SD Ángel Di María</t>
-  </si>
-  <si>
     <t>DC Youssef En-Nesyri</t>
   </si>
   <si>
-    <t>CT Aymeric Laporte</t>
-  </si>
-  <si>
     <t>ED Francisco Trincão</t>
   </si>
   <si>
@@ -1956,15 +1776,9 @@
     <t>MP Karim Adeyemi</t>
   </si>
   <si>
-    <t>DC Edinson Cavani</t>
-  </si>
-  <si>
     <t>ED Václav Černý</t>
   </si>
   <si>
-    <t>LD Danilo</t>
-  </si>
-  <si>
     <t>DC Robert Lewandowski</t>
   </si>
   <si>
@@ -2289,30 +2103,9 @@
     <t>Enzo Fernández</t>
   </si>
   <si>
-    <t>Roberto Baggio</t>
-  </si>
-  <si>
-    <t>Jan Paul Van Hecke</t>
-  </si>
-  <si>
-    <t>Hans Vanaken</t>
-  </si>
-  <si>
-    <t>Ismaïla Sarr</t>
-  </si>
-  <si>
-    <t>Nadiem Amiri</t>
-  </si>
-  <si>
-    <t>Marco Arnautovic</t>
-  </si>
-  <si>
     <t>Facundo Pellistri</t>
   </si>
   <si>
-    <t>Nahuel Molina</t>
-  </si>
-  <si>
     <t>Joan García</t>
   </si>
   <si>
@@ -2574,12 +2367,6 @@
     <t>Gonzalo García</t>
   </si>
   <si>
-    <t>Daniel Carvajal</t>
-  </si>
-  <si>
-    <t>Álex Baena</t>
-  </si>
-  <si>
     <t>PT Emiliano Martínez</t>
   </si>
   <si>
@@ -2613,27 +2400,12 @@
     <t>DC Barış Alper Yılmaz</t>
   </si>
   <si>
-    <t>CT Robert Andrich</t>
-  </si>
-  <si>
     <t>MC Enzo Fernández</t>
   </si>
   <si>
-    <t>MP Petar Sučić</t>
-  </si>
-  <si>
-    <t>DC Giuliano Simeone</t>
-  </si>
-  <si>
     <t>EI Nico Williams</t>
   </si>
   <si>
-    <t>MP Hans Vanaken</t>
-  </si>
-  <si>
-    <t>ID Ismaïla Sarr</t>
-  </si>
-  <si>
     <t>ED Facundo Pellistri</t>
   </si>
   <si>
@@ -2938,6 +2710,210 @@
   </si>
   <si>
     <t>Al_Nassr</t>
+  </si>
+  <si>
+    <t>Borussia_Dortmund</t>
+  </si>
+  <si>
+    <t>DC Romelu Lukaku</t>
+  </si>
+  <si>
+    <t>ED Diego Maradona</t>
+  </si>
+  <si>
+    <t>MP Isco</t>
+  </si>
+  <si>
+    <t>MCD Khéphren Thuram</t>
+  </si>
+  <si>
+    <t>LI Achraf Hakimi</t>
+  </si>
+  <si>
+    <t>LD Óscar Mingueza</t>
+  </si>
+  <si>
+    <t>PT Senne Lammens</t>
+  </si>
+  <si>
+    <t>SD Paulo Dybala</t>
+  </si>
+  <si>
+    <t>DC Ivan Toney</t>
+  </si>
+  <si>
+    <t>EI Ansu Fati</t>
+  </si>
+  <si>
+    <t>ED Rodrygo</t>
+  </si>
+  <si>
+    <t>MP Ismael Saibari</t>
+  </si>
+  <si>
+    <t>MC Leon Goretzka</t>
+  </si>
+  <si>
+    <t>MC Adrien Rabiot</t>
+  </si>
+  <si>
+    <t>ID Diogo Dalot</t>
+  </si>
+  <si>
+    <t>CT Raúl Asencio</t>
+  </si>
+  <si>
+    <t>PT Zion Suzuki</t>
+  </si>
+  <si>
+    <t>EI Christos Tzolis</t>
+  </si>
+  <si>
+    <t>MC Christian Nørgaard</t>
+  </si>
+  <si>
+    <t>CT Youri Baas</t>
+  </si>
+  <si>
+    <t>CT Malang Sarr</t>
+  </si>
+  <si>
+    <t>Borussia Dortmund</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>MP Raphael Veiga</t>
+  </si>
+  <si>
+    <t>PT Ronwen Williams</t>
+  </si>
+  <si>
+    <t>CT Sebastián Cáceres</t>
+  </si>
+  <si>
+    <t>CT Marcos Senesi</t>
+  </si>
+  <si>
+    <t>CT Gonçalo Inácio</t>
+  </si>
+  <si>
+    <t>CT Israel Reyes</t>
+  </si>
+  <si>
+    <t>LI Carlos Augusto</t>
+  </si>
+  <si>
+    <t>LI Luke Shaw</t>
+  </si>
+  <si>
+    <t>LD Matty Cash</t>
+  </si>
+  <si>
+    <t>MCD Máximo Perrone</t>
+  </si>
+  <si>
+    <t>ED Florian Thauvin</t>
+  </si>
+  <si>
+    <t>DC Mauro Icardi</t>
+  </si>
+  <si>
+    <t>DC Andriy Shevchenko</t>
+  </si>
+  <si>
+    <t>Romelu Lukaku</t>
+  </si>
+  <si>
+    <t>Diego Maradona</t>
+  </si>
+  <si>
+    <t>Khéphren Thuram</t>
+  </si>
+  <si>
+    <t>Óscar Mingueza</t>
+  </si>
+  <si>
+    <t>Senne Lammens</t>
+  </si>
+  <si>
+    <t>Paulo Dybala</t>
+  </si>
+  <si>
+    <t>Ivan Toney</t>
+  </si>
+  <si>
+    <t>Ismael Saibari</t>
+  </si>
+  <si>
+    <t>Raphael Veiga</t>
+  </si>
+  <si>
+    <t>Leon Goretzka</t>
+  </si>
+  <si>
+    <t>Adrien Rabiot</t>
+  </si>
+  <si>
+    <t>Diogo Dalot</t>
+  </si>
+  <si>
+    <t>Raúl Asencio</t>
+  </si>
+  <si>
+    <t>Zion Suzuki</t>
+  </si>
+  <si>
+    <t>Christos Tzolis</t>
+  </si>
+  <si>
+    <t>Christian Nørgaard</t>
+  </si>
+  <si>
+    <t>Youri Baas</t>
+  </si>
+  <si>
+    <t>Malang Sarr</t>
+  </si>
+  <si>
+    <t>Ronwen Williams</t>
+  </si>
+  <si>
+    <t>Sebastián Cáceres</t>
+  </si>
+  <si>
+    <t>Marcos Senesi</t>
+  </si>
+  <si>
+    <t>Gonçalo Inácio</t>
+  </si>
+  <si>
+    <t>Israel Reyes</t>
+  </si>
+  <si>
+    <t>Carlos Augusto</t>
+  </si>
+  <si>
+    <t>Luke Shaw</t>
+  </si>
+  <si>
+    <t>Matty Cash</t>
+  </si>
+  <si>
+    <t>Máximo Perrone</t>
+  </si>
+  <si>
+    <t>Florian Thauvin</t>
+  </si>
+  <si>
+    <t>Mauro Icardi</t>
+  </si>
+  <si>
+    <t>Andriy Shevchenko</t>
+  </si>
+  <si>
+    <t>River_Plate</t>
   </si>
 </sst>
 </file>
@@ -3383,7 +3359,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>816</v>
+        <v>747</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -3394,10 +3370,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -3406,10 +3382,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
@@ -3418,10 +3394,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
@@ -3430,10 +3406,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>948</v>
+        <v>872</v>
       </c>
       <c r="C6" s="3">
         <v>2</v>
@@ -3444,10 +3420,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -3458,10 +3434,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>938</v>
+        <v>862</v>
       </c>
       <c r="C8" s="3">
         <v>2</v>
@@ -3470,10 +3446,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>939</v>
+        <v>863</v>
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="3">
@@ -3482,10 +3458,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -3494,10 +3470,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>322</v>
+        <v>298</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3">
@@ -3509,7 +3485,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>827</v>
+        <v>758</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -3523,7 +3499,7 @@
         <v>10</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>817</v>
+        <v>748</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3">
@@ -3532,10 +3508,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -3544,10 +3520,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -3558,10 +3534,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="C16" s="3">
         <v>5</v>
@@ -3573,7 +3549,7 @@
         <v>10</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>813</v>
+        <v>744</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -3582,10 +3558,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>746</v>
+        <v>677</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -3596,10 +3572,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3">
@@ -3608,10 +3584,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -3620,10 +3596,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C21" s="3"/>
       <c r="D21" s="3">
@@ -3632,10 +3608,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>798</v>
+        <v>729</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
@@ -3644,10 +3620,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C23" s="3"/>
       <c r="D23" s="3">
@@ -3656,7 +3632,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>56</v>
@@ -3670,10 +3646,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3">
@@ -3682,10 +3658,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="C26" s="3">
         <v>2</v>
@@ -3694,10 +3670,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C27" s="6">
         <v>3</v>
@@ -3708,10 +3684,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C28" s="3">
         <v>2</v>
@@ -3720,10 +3696,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
@@ -3732,10 +3708,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>802</v>
+        <v>733</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3">
@@ -3744,10 +3720,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -3756,10 +3732,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
@@ -3770,10 +3746,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C33" s="3">
         <v>1</v>
@@ -3782,10 +3758,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>744</v>
+        <v>675</v>
       </c>
       <c r="C34" s="3">
         <v>2</v>
@@ -3794,7 +3770,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>40</v>
@@ -3806,10 +3782,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
@@ -3818,10 +3794,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>787</v>
+        <v>718</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3">
@@ -3833,7 +3809,7 @@
         <v>10</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>819</v>
+        <v>750</v>
       </c>
       <c r="C38" s="3">
         <v>4</v>
@@ -3842,7 +3818,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>58</v>
@@ -3856,10 +3832,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>786</v>
+        <v>717</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3">
@@ -3871,7 +3847,7 @@
         <v>10</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>828</v>
+        <v>759</v>
       </c>
       <c r="C41" s="3">
         <v>1</v>
@@ -3892,10 +3868,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="C43" s="3">
         <v>1</v>
@@ -3904,10 +3880,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C44" s="3">
         <v>2</v>
@@ -3918,10 +3894,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>770</v>
+        <v>701</v>
       </c>
       <c r="C45" s="3">
         <v>1</v>
@@ -3932,7 +3908,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>55</v>
@@ -3944,10 +3920,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>769</v>
+        <v>700</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -3956,10 +3932,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -3968,10 +3944,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>745</v>
+        <v>676</v>
       </c>
       <c r="C49" s="3"/>
       <c r="D49" s="3">
@@ -3980,10 +3956,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>950</v>
+        <v>874</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
@@ -3992,10 +3968,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>950</v>
+        <v>874</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="C51" s="3"/>
       <c r="D51" s="3">
@@ -4007,7 +3983,7 @@
         <v>31</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>808</v>
+        <v>739</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
@@ -4021,7 +3997,7 @@
         <v>31</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C53" s="3">
         <v>4</v>
@@ -4035,7 +4011,7 @@
         <v>31</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>805</v>
+        <v>736</v>
       </c>
       <c r="C54" s="3">
         <v>2</v>
@@ -4049,7 +4025,7 @@
         <v>31</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="C55" s="3">
         <v>2</v>
@@ -4058,7 +4034,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>52</v>
@@ -4073,7 +4049,7 @@
         <v>31</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C57" s="3"/>
       <c r="D57" s="3">
@@ -4082,10 +4058,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -4099,7 +4075,7 @@
         <v>31</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C59" s="3">
         <v>1</v>
@@ -4113,7 +4089,7 @@
         <v>31</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C60" s="3"/>
       <c r="D60" s="3">
@@ -4125,7 +4101,7 @@
         <v>31</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C61" s="6"/>
       <c r="D61" s="6">
@@ -4137,7 +4113,7 @@
         <v>10</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>810</v>
+        <v>741</v>
       </c>
       <c r="C62" s="3"/>
       <c r="D62" s="3">
@@ -4146,10 +4122,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>795</v>
+        <v>726</v>
       </c>
       <c r="C63" s="3"/>
       <c r="D63" s="3">
@@ -4158,10 +4134,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -4170,10 +4146,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="C65" s="3"/>
       <c r="D65" s="3">
@@ -4182,10 +4158,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C66" s="3"/>
       <c r="D66" s="3">
@@ -4194,10 +4170,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="C67" s="3">
         <v>1</v>
@@ -4206,10 +4182,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="C68" s="3"/>
       <c r="D68" s="3">
@@ -5130,7 +5106,7 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B221" s="3"/>
       <c r="C221" s="6"/>
@@ -5141,7 +5117,7 @@
         <v>31</v>
       </c>
       <c r="B222" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -7153,21 +7129,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>711</v>
+        <v>649</v>
       </c>
       <c r="B1" t="s">
-        <v>712</v>
+        <v>650</v>
       </c>
       <c r="C1" t="s">
-        <v>713</v>
+        <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="B2" t="s">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7175,10 +7151,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="B3" t="s">
-        <v>715</v>
+        <v>653</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7186,10 +7162,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="B4" t="s">
-        <v>716</v>
+        <v>654</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7197,10 +7173,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="B5" t="s">
-        <v>717</v>
+        <v>655</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7208,10 +7184,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>714</v>
+        <v>652</v>
       </c>
       <c r="B6" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7219,10 +7195,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="B7" t="s">
-        <v>719</v>
+        <v>657</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7230,10 +7206,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="B8" t="s">
-        <v>720</v>
+        <v>658</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7241,10 +7217,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="B9" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7252,10 +7228,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="B10" t="s">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7263,10 +7239,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>718</v>
+        <v>656</v>
       </c>
       <c r="B11" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -7274,10 +7250,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>721</v>
+        <v>659</v>
       </c>
       <c r="B12" t="s">
-        <v>717</v>
+        <v>655</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -7285,10 +7261,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>721</v>
+        <v>659</v>
       </c>
       <c r="B13" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7296,10 +7272,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>721</v>
+        <v>659</v>
       </c>
       <c r="B14" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7321,47 +7297,47 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>128</v>
-      </c>
-      <c r="C1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
         <v>33</v>
@@ -7376,12 +7352,12 @@
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
         <v>35</v>
@@ -7390,18 +7366,18 @@
         <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E4">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
         <v>9</v>
@@ -7416,12 +7392,12 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
@@ -7430,21 +7406,21 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7456,12 +7432,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -7476,7 +7452,7 @@
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -7495,27 +7471,27 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E1" t="s">
         <v>127</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>128</v>
-      </c>
-      <c r="C1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -7530,15 +7506,15 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7550,15 +7526,15 @@
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -7570,15 +7546,15 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -7590,35 +7566,35 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
       </c>
       <c r="E6" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -7630,12 +7606,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
@@ -7650,7 +7626,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -10778,46 +10754,46 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>83</v>
+        <v>942</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>950</v>
+        <v>874</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>776</v>
+        <v>707</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>31</v>
@@ -10826,501 +10802,501 @@
         <v>10</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>69</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>181</v>
+        <v>930</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>742</v>
+        <v>673</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>51</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>751</v>
+        <v>682</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>932</v>
+        <v>856</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>777</v>
+        <v>708</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>179</v>
+        <v>912</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>223</v>
+        <v>173</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>810</v>
+        <v>741</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>191</v>
+        <v>913</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>726</v>
+        <v>664</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>211</v>
+        <v>931</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>743</v>
+        <v>674</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>752</v>
+        <v>683</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>933</v>
+        <v>857</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>778</v>
+        <v>709</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>811</v>
+        <v>742</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>199</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>797</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>215</v>
-      </c>
       <c r="N5" s="3" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>812</v>
+        <v>743</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>209</v>
+        <v>914</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>344</v>
+        <v>933</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>325</v>
+        <v>301</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>754</v>
+        <v>685</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>858</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>934</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="M6" s="3" t="s">
-        <v>799</v>
+        <v>730</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>813</v>
+        <v>744</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>727</v>
+        <v>665</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>232</v>
+        <v>934</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>226</v>
+        <v>213</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>755</v>
+        <v>686</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>935</v>
+        <v>859</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>781</v>
+        <v>712</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>794</v>
+        <v>725</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>814</v>
+        <v>745</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>733</v>
+        <v>935</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>295</v>
+        <v>274</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>748</v>
+        <v>679</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>756</v>
+        <v>687</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>724</v>
+        <v>662</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>795</v>
+        <v>726</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>805</v>
+        <v>736</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>815</v>
+        <v>746</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>236</v>
+        <v>915</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>728</v>
+        <v>666</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>243</v>
+        <v>936</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>745</v>
+        <v>676</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>749</v>
+        <v>680</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>757</v>
+        <v>688</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>57</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>936</v>
+        <v>860</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>782</v>
+        <v>713</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>800</v>
+        <v>731</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>816</v>
+        <v>747</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>167</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>729</v>
+        <v>667</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>734</v>
+        <v>937</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>246</v>
+        <v>230</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>245</v>
+        <v>229</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>937</v>
+        <v>861</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>783</v>
+        <v>714</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>50</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>817</v>
+        <v>748</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>153</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
-        <v>730</v>
+        <v>668</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>27</v>
+        <v>671</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>14</v>
@@ -11332,720 +11308,710 @@
         <v>56</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>938</v>
+        <v>862</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>58</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>818</v>
+        <v>749</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>79</v>
+        <v>918</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>298</v>
+        <v>277</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>16</v>
+        <v>938</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>746</v>
+        <v>677</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="P12" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>819</v>
-      </c>
       <c r="Q12" s="3" t="s">
-        <v>154</v>
+        <v>873</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>735</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>759</v>
+        <v>690</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>772</v>
+        <v>703</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>939</v>
+        <v>863</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>52</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>801</v>
+        <v>732</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>806</v>
+        <v>737</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>820</v>
+        <v>751</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>267</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>731</v>
+        <v>669</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>736</v>
+        <v>16</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>274</v>
+        <v>256</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>270</v>
+        <v>252</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>760</v>
+        <v>691</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>940</v>
+        <v>864</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>784</v>
+        <v>715</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>272</v>
+        <v>254</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>807</v>
+        <v>738</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>278</v>
+        <v>919</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>326</v>
+        <v>672</v>
       </c>
       <c r="C15" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>308</v>
-      </c>
       <c r="G15" s="3" t="s">
-        <v>761</v>
+        <v>692</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>941</v>
+        <v>865</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>785</v>
+        <v>716</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>47</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>821</v>
+        <v>752</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>285</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>40</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>762</v>
+        <v>693</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>269</v>
+        <v>251</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>942</v>
+        <v>866</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>296</v>
+        <v>275</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>802</v>
+        <v>733</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>822</v>
+        <v>753</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>294</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
-        <v>297</v>
+        <v>276</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>737</v>
+        <v>939</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>317</v>
+        <v>294</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>763</v>
+        <v>694</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>773</v>
+        <v>704</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>943</v>
+        <v>867</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>786</v>
+        <v>717</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>803</v>
+        <v>734</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>829</v>
+        <v>922</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>738</v>
+        <v>940</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>249</v>
+        <v>233</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>764</v>
+        <v>695</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>944</v>
+        <v>868</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>787</v>
+        <v>718</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>313</v>
+        <v>290</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>823</v>
+        <v>754</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>310</v>
+        <v>923</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B19" s="5" t="s">
+        <v>941</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>869</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>315</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>945</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>808</v>
-      </c>
       <c r="P19" s="3" t="s">
-        <v>824</v>
+        <v>755</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>319</v>
+        <v>924</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>314</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>740</v>
-      </c>
+        <v>291</v>
+      </c>
+      <c r="B20" s="5"/>
       <c r="C20" s="5" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>324</v>
+        <v>300</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>766</v>
+        <v>697</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>946</v>
+        <v>870</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>789</v>
+        <v>720</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="N20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="P20" s="3" t="s">
-        <v>825</v>
+        <v>756</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>312</v>
+        <v>925</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>250</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="B21" s="5"/>
       <c r="C21" s="5" t="s">
-        <v>330</v>
+        <v>305</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>328</v>
+        <v>303</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>323</v>
-      </c>
       <c r="I21" s="3" t="s">
-        <v>947</v>
+        <v>871</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>790</v>
+        <v>721</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>329</v>
+        <v>304</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="P21" s="3" t="s">
         <v>59</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>830</v>
+        <v>926</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>741</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="B22" s="5"/>
       <c r="C22" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>334</v>
+        <v>309</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>333</v>
+        <v>308</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>768</v>
+        <v>699</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>774</v>
+        <v>705</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>948</v>
+        <v>872</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>791</v>
+        <v>722</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>798</v>
+        <v>729</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>804</v>
+        <v>735</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>809</v>
+        <v>740</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>826</v>
+        <v>757</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>71</v>
+        <v>927</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>732</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>34</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>340</v>
+        <v>314</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>275</v>
+        <v>257</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>769</v>
+        <v>700</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>338</v>
+        <v>312</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>792</v>
+        <v>723</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>796</v>
+        <v>727</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>341</v>
+        <v>315</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>827</v>
+        <v>758</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>342</v>
+        <v>928</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>302</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="B24" s="5"/>
       <c r="C24" s="5" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>744</v>
+        <v>675</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>770</v>
+        <v>701</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>775</v>
+        <v>706</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>949</v>
+        <v>873</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>793</v>
+        <v>724</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>346</v>
+        <v>318</v>
       </c>
       <c r="L24" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="O24" s="3" t="s">
-        <v>345</v>
+        <v>317</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>828</v>
+        <v>759</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>102</v>
+        <v>929</v>
       </c>
     </row>
   </sheetData>
@@ -12068,7 +12034,7 @@
     <col min="9" max="9" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="22.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="23.109375" style="1" bestFit="1" customWidth="1"/>
@@ -12083,16 +12049,16 @@
         <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>898</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>851</v>
+        <v>775</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>15</v>
@@ -12110,16 +12076,16 @@
         <v>19</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L1" s="3" t="s">
         <v>46</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>893</v>
+        <v>817</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="O1" s="3" t="s">
         <v>31</v>
@@ -12128,1249 +12094,1239 @@
         <v>10</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>35</v>
+        <v>897</v>
       </c>
       <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>831</v>
+        <v>760</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>357</v>
+        <v>900</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>852</v>
+        <v>776</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>351</v>
+        <v>323</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>497</v>
+        <v>452</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>352</v>
+        <v>324</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>502</v>
+        <v>457</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>913</v>
+        <v>837</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>886</v>
+        <v>810</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>350</v>
+        <v>322</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>353</v>
+        <v>325</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>354</v>
+        <v>326</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>906</v>
+        <v>830</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>355</v>
+        <v>876</v>
       </c>
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>526</v>
+        <v>477</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>516</v>
+        <v>468</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>394</v>
+        <v>363</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>539</v>
+        <v>489</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>378</v>
+        <v>348</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>370</v>
+        <v>877</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>832</v>
+        <v>761</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>401</v>
+        <v>901</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>518</v>
+        <v>469</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>548</v>
+        <v>496</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>377</v>
+        <v>347</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>381</v>
+        <v>351</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>872</v>
+        <v>796</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>558</v>
+        <v>505</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>914</v>
+        <v>838</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>458</v>
+        <v>419</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>388</v>
+        <v>357</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>393</v>
+        <v>362</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>383</v>
+        <v>353</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>384</v>
+        <v>354</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>382</v>
+        <v>352</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>385</v>
+        <v>878</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>842</v>
+        <v>902</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>400</v>
+        <v>369</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>395</v>
+        <v>364</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>392</v>
+        <v>361</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>862</v>
+        <v>786</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>803</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q5" s="3" t="s">
         <v>879</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>890</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>399</v>
       </c>
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>404</v>
+        <v>372</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>625</v>
+        <v>903</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>592</v>
+        <v>536</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>409</v>
+        <v>377</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>839</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="N6" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>873</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>894</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>412</v>
-      </c>
       <c r="O6" s="3" t="s">
-        <v>371</v>
+        <v>341</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>411</v>
+        <v>379</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>414</v>
+        <v>880</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>833</v>
+        <v>762</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>429</v>
+        <v>904</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>853</v>
+        <v>777</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>423</v>
+        <v>389</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>420</v>
+        <v>386</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>863</v>
+        <v>787</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>456</v>
+        <v>417</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>419</v>
+        <v>385</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>916</v>
+        <v>840</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>431</v>
+        <v>395</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>422</v>
+        <v>388</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>421</v>
+        <v>387</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>426</v>
+        <v>392</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>427</v>
+        <v>393</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>428</v>
+        <v>368</v>
       </c>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>843</v>
+        <v>905</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>439</v>
+        <v>403</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>858</v>
+        <v>782</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>864</v>
+        <v>788</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>874</v>
+        <v>798</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>438</v>
+        <v>402</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>589</v>
+        <v>534</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>437</v>
+        <v>401</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>436</v>
+        <v>400</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>495</v>
+        <v>450</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>440</v>
+        <v>404</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>442</v>
+        <v>881</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>834</v>
+        <v>763</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>844</v>
+        <v>906</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>567</v>
+        <v>513</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>451</v>
+        <v>413</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>859</v>
+        <v>783</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>865</v>
+        <v>789</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>569</v>
+        <v>515</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>600</v>
+        <v>543</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>917</v>
+        <v>841</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>887</v>
+        <v>811</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>457</v>
+        <v>418</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>891</v>
+        <v>815</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>895</v>
+        <v>819</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>453</v>
+        <v>415</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>454</v>
+        <v>416</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>452</v>
+        <v>414</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>455</v>
+        <v>882</v>
       </c>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>835</v>
+        <v>764</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>480</v>
+        <v>907</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>854</v>
+        <v>778</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>463</v>
+        <v>424</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>435</v>
+        <v>399</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>866</v>
+        <v>790</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>505</v>
+        <v>458</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>880</v>
+        <v>804</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>918</v>
+        <v>842</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>507</v>
+        <v>460</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>470</v>
+        <v>429</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>461</v>
+        <v>422</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>459</v>
+        <v>420</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>477</v>
+        <v>436</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>466</v>
+        <v>427</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>464</v>
+        <v>425</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>467</v>
+        <v>883</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>836</v>
+        <v>765</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>845</v>
+        <v>771</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>479</v>
+        <v>437</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>474</v>
+        <v>433</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>484</v>
+        <v>441</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>614</v>
+        <v>554</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>875</v>
+        <v>799</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>538</v>
+        <v>488</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>919</v>
+        <v>843</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>448</v>
+        <v>410</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>889</v>
+        <v>813</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>473</v>
+        <v>432</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>472</v>
+        <v>431</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>476</v>
+        <v>435</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>465</v>
+        <v>426</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>475</v>
+        <v>434</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>478</v>
+        <v>884</v>
       </c>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>837</v>
+        <v>766</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>846</v>
+        <v>908</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>581</v>
+        <v>526</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>487</v>
+        <v>444</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>860</v>
+        <v>784</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>867</v>
+        <v>791</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>519</v>
+        <v>470</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>881</v>
+        <v>805</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>462</v>
+        <v>423</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>471</v>
+        <v>430</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>496</v>
+        <v>451</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>486</v>
+        <v>443</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>485</v>
+        <v>442</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>490</v>
+        <v>447</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>491</v>
+        <v>448</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>489</v>
+        <v>446</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>492</v>
+        <v>885</v>
       </c>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>544</v>
+        <v>514</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>500</v>
+        <v>455</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>488</v>
+        <v>445</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>372</v>
+        <v>342</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>882</v>
+        <v>806</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>920</v>
+        <v>844</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>633</v>
+        <v>571</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>506</v>
+        <v>459</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>499</v>
+        <v>454</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>896</v>
+        <v>820</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>501</v>
+        <v>456</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>901</v>
+        <v>825</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>907</v>
+        <v>831</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>503</v>
+        <v>886</v>
       </c>
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>838</v>
+        <v>767</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>847</v>
+        <v>772</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>513</v>
+        <v>465</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>509</v>
+        <v>462</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>868</v>
+        <v>792</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>445</v>
+        <v>407</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>921</v>
+        <v>845</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>389</v>
+        <v>358</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>520</v>
+        <v>471</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>511</v>
+        <v>463</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>515</v>
+        <v>467</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>902</v>
+        <v>826</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>517</v>
+        <v>887</v>
       </c>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>522</v>
+        <v>473</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>593</v>
+        <v>773</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>883</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>585</v>
-      </c>
       <c r="M15" s="3" t="s">
-        <v>498</v>
+        <v>453</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>527</v>
+        <v>478</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>528</v>
+        <v>479</v>
       </c>
       <c r="P15" s="3" t="s">
-        <v>908</v>
+        <v>832</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>529</v>
+        <v>899</v>
       </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>533</v>
+        <v>483</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>612</v>
+        <v>774</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>443</v>
+        <v>406</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>449</v>
+        <v>411</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>406</v>
+        <v>374</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>869</v>
+        <v>793</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>508</v>
+        <v>461</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>923</v>
+        <v>847</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>620</v>
+        <v>560</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>545</v>
+        <v>493</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>537</v>
+        <v>487</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>897</v>
+        <v>821</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>540</v>
+        <v>490</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>551</v>
+        <v>499</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>542</v>
+        <v>888</v>
       </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>547</v>
+        <v>495</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>779</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>848</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>855</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>870</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>876</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>924</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>482</v>
+        <v>439</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>555</v>
+        <v>502</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>549</v>
+        <v>497</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>898</v>
+        <v>822</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>552</v>
+        <v>500</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>903</v>
+        <v>827</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>563</v>
+        <v>510</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>510</v>
+        <v>889</v>
       </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>557</v>
+        <v>504</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>444</v>
+        <v>910</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>561</v>
+        <v>508</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>559</v>
+        <v>506</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>599</v>
+        <v>542</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>481</v>
+        <v>438</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>534</v>
+        <v>484</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>925</v>
+        <v>849</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>546</v>
+        <v>494</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>570</v>
+        <v>516</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>560</v>
+        <v>507</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>536</v>
+        <v>486</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>564</v>
+        <v>511</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>565</v>
+        <v>512</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>909</v>
+        <v>833</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>566</v>
+        <v>890</v>
       </c>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>839</v>
+        <v>768</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>494</v>
+        <v>911</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>580</v>
+        <v>525</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>576</v>
+        <v>522</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>574</v>
+        <v>520</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>588</v>
+        <v>533</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>554</v>
+        <v>501</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>405</v>
+        <v>373</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>926</v>
+        <v>850</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>556</v>
+        <v>503</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>582</v>
+        <v>527</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>575</v>
+        <v>521</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>450</v>
+        <v>412</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>578</v>
+        <v>524</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>904</v>
+        <v>828</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>577</v>
+        <v>523</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>579</v>
+        <v>891</v>
       </c>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>849</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="B20" s="3"/>
       <c r="C20" s="3" t="s">
-        <v>415</v>
+        <v>382</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>587</v>
+        <v>532</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>861</v>
+        <v>785</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>871</v>
+        <v>795</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="M20" s="3" t="s">
-        <v>460</v>
+        <v>421</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>590</v>
+        <v>535</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>622</v>
+        <v>562</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>910</v>
+        <v>834</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>568</v>
+        <v>892</v>
       </c>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>469</v>
-      </c>
+        <v>528</v>
+      </c>
+      <c r="B21" s="3"/>
       <c r="C21" s="3" t="s">
-        <v>604</v>
+        <v>546</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>598</v>
+        <v>541</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>596</v>
+        <v>539</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>550</v>
+        <v>498</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>877</v>
+        <v>801</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>584</v>
+        <v>529</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>928</v>
+        <v>852</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>571</v>
+        <v>517</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>606</v>
+        <v>548</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>597</v>
+        <v>540</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>899</v>
+        <v>823</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>601</v>
+        <v>544</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>602</v>
+        <v>545</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>629</v>
+        <v>567</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>603</v>
+        <v>893</v>
       </c>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>840</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>504</v>
-      </c>
+        <v>769</v>
+      </c>
+      <c r="B22" s="3"/>
       <c r="C22" s="3" t="s">
-        <v>611</v>
+        <v>552</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>856</v>
+        <v>780</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>607</v>
+        <v>549</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>424</v>
+        <v>390</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>878</v>
+        <v>802</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>884</v>
+        <v>808</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>929</v>
+        <v>853</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>595</v>
+        <v>538</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>613</v>
+        <v>553</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>892</v>
+        <v>816</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>900</v>
+        <v>824</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>608</v>
+        <v>550</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>905</v>
+        <v>829</v>
       </c>
       <c r="P22" s="3" t="s">
-        <v>911</v>
+        <v>835</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>610</v>
+        <v>894</v>
       </c>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>841</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>850</v>
-      </c>
+        <v>770</v>
+      </c>
+      <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>624</v>
+        <v>563</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>619</v>
+        <v>559</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>616</v>
+        <v>556</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>514</v>
+        <v>466</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>626</v>
+        <v>564</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>615</v>
+        <v>555</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>930</v>
+        <v>854</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>888</v>
+        <v>812</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>627</v>
+        <v>565</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>617</v>
+        <v>557</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>512</v>
+        <v>464</v>
       </c>
       <c r="N23" s="3" t="s">
-        <v>621</v>
+        <v>561</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>609</v>
+        <v>551</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>912</v>
+        <v>836</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>623</v>
+        <v>895</v>
       </c>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>553</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="B24" s="3"/>
       <c r="C24" s="3" t="s">
-        <v>493</v>
+        <v>449</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>857</v>
+        <v>781</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>630</v>
+        <v>568</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>396</v>
+        <v>365</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>637</v>
+        <v>575</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>885</v>
+        <v>809</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>931</v>
+        <v>855</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>374</v>
+        <v>344</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>638</v>
+        <v>576</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>632</v>
+        <v>570</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>631</v>
+        <v>569</v>
       </c>
       <c r="N24" s="3" t="s">
-        <v>635</v>
+        <v>573</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>634</v>
+        <v>572</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>591</v>
+        <v>896</v>
       </c>
       <c r="R24" s="3"/>
     </row>
@@ -13398,25 +13354,25 @@
         <v>66</v>
       </c>
       <c r="B1" t="s">
-        <v>639</v>
+        <v>577</v>
       </c>
       <c r="C1" t="s">
-        <v>640</v>
+        <v>578</v>
       </c>
       <c r="D1" t="s">
-        <v>641</v>
+        <v>579</v>
       </c>
       <c r="E1" t="s">
-        <v>642</v>
+        <v>580</v>
       </c>
       <c r="F1" t="s">
-        <v>643</v>
+        <v>581</v>
       </c>
       <c r="G1" t="s">
-        <v>644</v>
+        <v>582</v>
       </c>
       <c r="H1" t="s">
-        <v>645</v>
+        <v>583</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -13424,13 +13380,13 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>646</v>
+        <v>584</v>
       </c>
       <c r="C2" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D2" t="s">
-        <v>648</v>
+        <v>586</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -13439,7 +13395,7 @@
         <v>1400000000</v>
       </c>
       <c r="G2" t="s">
-        <v>649</v>
+        <v>587</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -13450,13 +13406,13 @@
         <v>29</v>
       </c>
       <c r="B3" t="s">
-        <v>650</v>
+        <v>588</v>
       </c>
       <c r="C3" t="s">
-        <v>651</v>
+        <v>589</v>
       </c>
       <c r="D3" t="s">
-        <v>652</v>
+        <v>590</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13465,7 +13421,7 @@
         <v>68000000</v>
       </c>
       <c r="G3" t="s">
-        <v>653</v>
+        <v>591</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -13473,16 +13429,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>654</v>
+        <v>592</v>
       </c>
       <c r="C4" t="s">
-        <v>655</v>
+        <v>593</v>
       </c>
       <c r="D4" t="s">
-        <v>656</v>
+        <v>594</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13491,7 +13447,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>657</v>
+        <v>595</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13502,13 +13458,13 @@
         <v>54</v>
       </c>
       <c r="B5" t="s">
-        <v>658</v>
+        <v>596</v>
       </c>
       <c r="C5" t="s">
-        <v>659</v>
+        <v>597</v>
       </c>
       <c r="D5" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13517,7 +13473,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>661</v>
+        <v>599</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -13525,16 +13481,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>662</v>
+        <v>600</v>
       </c>
       <c r="C6" t="s">
-        <v>647</v>
+        <v>585</v>
       </c>
       <c r="D6" t="s">
-        <v>663</v>
+        <v>601</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13543,7 +13499,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>664</v>
+        <v>602</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -13554,13 +13510,13 @@
         <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>665</v>
+        <v>603</v>
       </c>
       <c r="C7" t="s">
-        <v>666</v>
+        <v>604</v>
       </c>
       <c r="D7" t="s">
-        <v>667</v>
+        <v>605</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13569,7 +13525,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>668</v>
+        <v>606</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -13580,13 +13536,13 @@
         <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>669</v>
+        <v>607</v>
       </c>
       <c r="C8" t="s">
-        <v>670</v>
+        <v>608</v>
       </c>
       <c r="D8" t="s">
-        <v>671</v>
+        <v>609</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13595,7 +13551,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>672</v>
+        <v>610</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -13606,13 +13562,13 @@
         <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>673</v>
+        <v>611</v>
       </c>
       <c r="C9" t="s">
-        <v>674</v>
+        <v>612</v>
       </c>
       <c r="D9" t="s">
-        <v>675</v>
+        <v>613</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13621,7 +13577,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>676</v>
+        <v>614</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -13632,13 +13588,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>677</v>
+        <v>615</v>
       </c>
       <c r="C10" t="s">
-        <v>678</v>
+        <v>616</v>
       </c>
       <c r="D10" t="s">
-        <v>679</v>
+        <v>617</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13647,7 +13603,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>680</v>
+        <v>618</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -13655,16 +13611,16 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>681</v>
+        <v>619</v>
       </c>
       <c r="D11" t="s">
-        <v>682</v>
+        <v>620</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13673,7 +13629,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>683</v>
+        <v>621</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -13684,13 +13640,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>684</v>
+        <v>622</v>
       </c>
       <c r="C12" t="s">
-        <v>685</v>
+        <v>623</v>
       </c>
       <c r="D12" t="s">
-        <v>660</v>
+        <v>598</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13699,7 +13655,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>686</v>
+        <v>624</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -13710,13 +13666,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>687</v>
+        <v>625</v>
       </c>
       <c r="C13" t="s">
-        <v>688</v>
+        <v>626</v>
       </c>
       <c r="D13" t="s">
-        <v>689</v>
+        <v>627</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13725,7 +13681,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>690</v>
+        <v>628</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -13736,13 +13692,13 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>691</v>
+        <v>629</v>
       </c>
       <c r="C14" t="s">
-        <v>692</v>
+        <v>630</v>
       </c>
       <c r="D14" t="s">
-        <v>693</v>
+        <v>631</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13751,7 +13707,7 @@
         <v>893000000</v>
       </c>
       <c r="G14" t="s">
-        <v>694</v>
+        <v>632</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -13762,13 +13718,13 @@
         <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>695</v>
+        <v>633</v>
       </c>
       <c r="C15" t="s">
-        <v>696</v>
+        <v>634</v>
       </c>
       <c r="D15" t="s">
-        <v>697</v>
+        <v>635</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13777,7 +13733,7 @@
         <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>698</v>
+        <v>636</v>
       </c>
       <c r="H15">
         <v>15</v>
@@ -13788,13 +13744,13 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>699</v>
+        <v>637</v>
       </c>
       <c r="C16" t="s">
-        <v>700</v>
+        <v>638</v>
       </c>
       <c r="D16" t="s">
-        <v>701</v>
+        <v>639</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -13803,7 +13759,7 @@
         <v>300000000</v>
       </c>
       <c r="G16" t="s">
-        <v>702</v>
+        <v>640</v>
       </c>
       <c r="H16">
         <v>13</v>
@@ -13811,16 +13767,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B17" t="s">
-        <v>703</v>
+        <v>641</v>
       </c>
       <c r="C17" t="s">
-        <v>704</v>
+        <v>642</v>
       </c>
       <c r="D17" t="s">
-        <v>705</v>
+        <v>643</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -13829,7 +13785,7 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>706</v>
+        <v>644</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -13840,13 +13796,13 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>707</v>
+        <v>645</v>
       </c>
       <c r="C18" t="s">
-        <v>708</v>
+        <v>646</v>
       </c>
       <c r="D18" t="s">
-        <v>709</v>
+        <v>647</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -13855,7 +13811,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>710</v>
+        <v>648</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14757,7 +14713,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="B39" t="s">
         <v>8</v>
@@ -14780,7 +14736,7 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
         <v>62</v>
@@ -14800,7 +14756,7 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>722</v>
+        <v>660</v>
       </c>
       <c r="B41" t="s">
         <v>62</v>
@@ -14820,7 +14776,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
@@ -14829,7 +14785,7 @@
         <v>31</v>
       </c>
       <c r="D42" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -14840,13 +14796,13 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s">
         <v>62</v>
       </c>
       <c r="C43" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D43" t="s">
         <v>31</v>
@@ -14860,7 +14816,7 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
@@ -14883,7 +14839,7 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>723</v>
+        <v>661</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
@@ -14906,7 +14862,7 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="B46" t="s">
         <v>62</v>
@@ -14929,7 +14885,7 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>724</v>
+        <v>662</v>
       </c>
       <c r="B47" t="s">
         <v>8</v>
@@ -14952,7 +14908,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B48" t="s">
         <v>8</v>
@@ -14975,7 +14931,7 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
       <c r="B49" t="s">
         <v>8</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2385C79-4BAA-49FF-BFF4-CC59BF7FE490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D836891-7C9C-4066-BB40-47BF9F2C7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="943">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -2742,12 +2742,6 @@
     <t>DC Ivan Toney</t>
   </si>
   <si>
-    <t>EI Ansu Fati</t>
-  </si>
-  <si>
-    <t>ED Rodrygo</t>
-  </si>
-  <si>
     <t>MP Ismael Saibari</t>
   </si>
   <si>
@@ -2914,6 +2908,48 @@
   </si>
   <si>
     <t>River_Plate</t>
+  </si>
+  <si>
+    <t>Thorgan Hazard</t>
+  </si>
+  <si>
+    <t>Amadou Onana</t>
+  </si>
+  <si>
+    <t>Ryan Christie</t>
+  </si>
+  <si>
+    <t>Rodrigo Salazar</t>
+  </si>
+  <si>
+    <t>Emanuel Emegha</t>
+  </si>
+  <si>
+    <t>Nahuel Molina</t>
+  </si>
+  <si>
+    <t>Lukas Provod</t>
+  </si>
+  <si>
+    <t>MC Ryan Christie</t>
+  </si>
+  <si>
+    <t>MP Rodrigo Zalazar</t>
+  </si>
+  <si>
+    <t>DC Emanuel Emegha</t>
+  </si>
+  <si>
+    <t>LD Nahuel Molina</t>
+  </si>
+  <si>
+    <t>II Lukáš Provod</t>
+  </si>
+  <si>
+    <t>EI Thorgan Hazard</t>
+  </si>
+  <si>
+    <t>MCD Amadou Onana</t>
   </si>
 </sst>
 </file>
@@ -10757,7 +10793,7 @@
         <v>87</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>874</v>
@@ -10810,7 +10846,7 @@
         <v>248</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>673</v>
@@ -10855,7 +10891,7 @@
         <v>242</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
@@ -10908,7 +10944,7 @@
         <v>741</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
@@ -10916,7 +10952,7 @@
         <v>664</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>260</v>
@@ -10969,7 +11005,7 @@
         <v>192</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>199</v>
@@ -11014,7 +11050,7 @@
         <v>743</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
@@ -11022,7 +11058,7 @@
         <v>201</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>301</v>
@@ -11075,7 +11111,7 @@
         <v>665</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>218</v>
@@ -11128,7 +11164,7 @@
         <v>99</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>274</v>
@@ -11173,7 +11209,7 @@
         <v>746</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
@@ -11181,7 +11217,7 @@
         <v>666</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>288</v>
@@ -11226,7 +11262,7 @@
         <v>747</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
@@ -11234,7 +11270,7 @@
         <v>667</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>227</v>
@@ -11279,7 +11315,7 @@
         <v>748</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
@@ -11332,7 +11368,7 @@
         <v>749</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
@@ -11340,7 +11376,7 @@
         <v>277</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>30</v>
@@ -11385,7 +11421,7 @@
         <v>750</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>873</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
@@ -11438,7 +11474,7 @@
         <v>751</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>72</v>
+        <v>942</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
@@ -11491,7 +11527,7 @@
         <v>13</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
@@ -11544,7 +11580,7 @@
         <v>752</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
@@ -11597,7 +11633,7 @@
         <v>753</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
@@ -11605,7 +11641,7 @@
         <v>276</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>280</v>
@@ -11650,7 +11686,7 @@
         <v>225</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
@@ -11658,7 +11694,7 @@
         <v>282</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>233</v>
@@ -11703,7 +11739,7 @@
         <v>754</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
@@ -11711,7 +11747,7 @@
         <v>144</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>296</v>
@@ -11756,14 +11792,16 @@
         <v>755</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>943</v>
+      </c>
       <c r="C20" s="5" t="s">
         <v>210</v>
       </c>
@@ -11807,14 +11845,16 @@
         <v>756</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>944</v>
+      </c>
       <c r="C21" s="5" t="s">
         <v>305</v>
       </c>
@@ -11858,14 +11898,16 @@
         <v>59</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>945</v>
+      </c>
       <c r="C22" s="5" t="s">
         <v>143</v>
       </c>
@@ -11909,14 +11951,16 @@
         <v>757</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>670</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>946</v>
+      </c>
       <c r="C23" s="5" t="s">
         <v>316</v>
       </c>
@@ -11960,14 +12004,16 @@
         <v>758</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>947</v>
+      </c>
       <c r="C24" s="5" t="s">
         <v>240</v>
       </c>
@@ -12011,7 +12057,7 @@
         <v>759</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
   </sheetData>
@@ -12049,7 +12095,7 @@
         <v>9</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>775</v>
@@ -12094,7 +12140,7 @@
         <v>10</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="R1" s="3"/>
     </row>
@@ -12103,7 +12149,7 @@
         <v>760</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>776</v>
@@ -12211,7 +12257,7 @@
         <v>761</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>469</v>
@@ -12265,7 +12311,7 @@
         <v>359</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>369</v>
@@ -12319,7 +12365,7 @@
         <v>372</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>536</v>
@@ -12373,7 +12419,7 @@
         <v>762</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>777</v>
@@ -12427,7 +12473,7 @@
         <v>397</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>492</v>
@@ -12481,7 +12527,7 @@
         <v>763</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>513</v>
@@ -12535,7 +12581,7 @@
         <v>764</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>778</v>
@@ -12643,7 +12689,7 @@
         <v>766</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>526</v>
@@ -12688,7 +12734,7 @@
         <v>446</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>885</v>
+        <v>953</v>
       </c>
       <c r="R12" s="3"/>
     </row>
@@ -12742,7 +12788,7 @@
         <v>831</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>886</v>
+        <v>954</v>
       </c>
       <c r="R13" s="3"/>
     </row>
@@ -12796,7 +12842,7 @@
         <v>345</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="R14" s="3"/>
     </row>
@@ -12850,7 +12896,7 @@
         <v>832</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="R15" s="3"/>
     </row>
@@ -12904,7 +12950,7 @@
         <v>499</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="R16" s="3"/>
     </row>
@@ -12913,7 +12959,7 @@
         <v>495</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>779</v>
@@ -12958,7 +13004,7 @@
         <v>510</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="R17" s="3"/>
     </row>
@@ -12967,7 +13013,7 @@
         <v>504</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>428</v>
@@ -13012,7 +13058,7 @@
         <v>833</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="R18" s="3"/>
     </row>
@@ -13021,7 +13067,7 @@
         <v>768</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>525</v>
@@ -13066,7 +13112,7 @@
         <v>523</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="R19" s="3"/>
     </row>
@@ -13074,7 +13120,9 @@
       <c r="A20" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>948</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>382</v>
       </c>
@@ -13118,7 +13166,7 @@
         <v>834</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="R20" s="3"/>
     </row>
@@ -13126,7 +13174,9 @@
       <c r="A21" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>949</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>546</v>
       </c>
@@ -13170,7 +13220,7 @@
         <v>567</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="R21" s="3"/>
     </row>
@@ -13178,7 +13228,9 @@
       <c r="A22" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>950</v>
+      </c>
       <c r="C22" s="3" t="s">
         <v>552</v>
       </c>
@@ -13222,7 +13274,7 @@
         <v>835</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="R22" s="3"/>
     </row>
@@ -13230,7 +13282,9 @@
       <c r="A23" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>951</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>563</v>
       </c>
@@ -13274,7 +13328,7 @@
         <v>836</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="R23" s="3"/>
     </row>
@@ -13282,7 +13336,9 @@
       <c r="A24" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>952</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>449</v>
       </c>
@@ -13326,7 +13382,7 @@
         <v>572</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="R24" s="3"/>
     </row>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D836891-7C9C-4066-BB40-47BF9F2C7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90EDE15-A0C8-4209-86DF-B8BE6D38505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$223</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$233</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -3367,6 +3367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D694"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3390,7 +3391,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -3404,7 +3405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>78</v>
       </c>
@@ -3416,7 +3417,7 @@
       </c>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>78</v>
       </c>
@@ -3425,10 +3426,10 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>78</v>
       </c>
@@ -3436,11 +3437,11 @@
         <v>152</v>
       </c>
       <c r="C5" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>79</v>
       </c>
@@ -3448,13 +3449,13 @@
         <v>872</v>
       </c>
       <c r="C6" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>79</v>
       </c>
@@ -3462,13 +3463,13 @@
         <v>148</v>
       </c>
       <c r="C7" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>79</v>
       </c>
@@ -3480,7 +3481,7 @@
       </c>
       <c r="D8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>79</v>
       </c>
@@ -3492,7 +3493,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>87</v>
       </c>
@@ -3504,7 +3505,7 @@
       </c>
       <c r="D10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>87</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>10</v>
       </c>
@@ -3530,7 +3531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>10</v>
       </c>
@@ -3542,7 +3543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>164</v>
       </c>
@@ -3550,11 +3551,13 @@
         <v>306</v>
       </c>
       <c r="C14" s="3">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3">
         <v>1</v>
       </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>164</v>
       </c>
@@ -3565,10 +3568,10 @@
         <v>1</v>
       </c>
       <c r="D15" s="3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>164</v>
       </c>
@@ -3576,11 +3579,11 @@
         <v>727</v>
       </c>
       <c r="C16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>10</v>
       </c>
@@ -3592,7 +3595,7 @@
       </c>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
@@ -3606,7 +3609,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -3618,7 +3621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>69</v>
       </c>
@@ -3630,7 +3633,7 @@
       </c>
       <c r="D20" s="3"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>69</v>
       </c>
@@ -3642,7 +3645,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>73</v>
       </c>
@@ -3654,7 +3657,7 @@
       </c>
       <c r="D22" s="3"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>73</v>
       </c>
@@ -3666,7 +3669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>70</v>
       </c>
@@ -3680,7 +3683,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>70</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>70</v>
       </c>
@@ -3704,7 +3707,7 @@
       </c>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>70</v>
       </c>
@@ -3718,7 +3721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>79</v>
       </c>
@@ -3726,11 +3729,11 @@
         <v>223</v>
       </c>
       <c r="C28" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>71</v>
       </c>
@@ -3742,7 +3745,7 @@
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>71</v>
       </c>
@@ -3754,7 +3757,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>71</v>
       </c>
@@ -3766,7 +3769,7 @@
       </c>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>70</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>78</v>
       </c>
@@ -3788,11 +3791,13 @@
         <v>117</v>
       </c>
       <c r="C33" s="3">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3">
         <v>1</v>
       </c>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>77</v>
       </c>
@@ -3804,7 +3809,7 @@
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>77</v>
       </c>
@@ -3816,7 +3821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>707</v>
       </c>
@@ -3828,7 +3833,7 @@
       </c>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>707</v>
       </c>
@@ -3840,7 +3845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>10</v>
       </c>
@@ -3852,7 +3857,7 @@
       </c>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>707</v>
       </c>
@@ -3866,7 +3871,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>707</v>
       </c>
@@ -3878,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>10</v>
       </c>
@@ -3890,7 +3895,7 @@
       </c>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>10</v>
       </c>
@@ -3902,7 +3907,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>69</v>
       </c>
@@ -3912,9 +3917,11 @@
       <c r="C43" s="3">
         <v>1</v>
       </c>
-      <c r="D43" s="3"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D43" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>69</v>
       </c>
@@ -3922,13 +3929,13 @@
         <v>157</v>
       </c>
       <c r="C44" s="3">
+        <v>4</v>
+      </c>
+      <c r="D44" s="3">
         <v>2</v>
       </c>
-      <c r="D44" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>163</v>
       </c>
@@ -3942,7 +3949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>163</v>
       </c>
@@ -3954,7 +3961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>163</v>
       </c>
@@ -3966,7 +3973,7 @@
       </c>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>69</v>
       </c>
@@ -3978,7 +3985,7 @@
       </c>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>69</v>
       </c>
@@ -3990,7 +3997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>874</v>
       </c>
@@ -4002,7 +4009,7 @@
       </c>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>874</v>
       </c>
@@ -4025,7 +4032,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -4036,7 +4043,7 @@
         <v>91</v>
       </c>
       <c r="C53" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D53" s="3">
         <v>1</v>
@@ -4068,7 +4075,7 @@
       </c>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>707</v>
       </c>
@@ -4092,7 +4099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>707</v>
       </c>
@@ -4117,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -4127,7 +4134,9 @@
       <c r="B60" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C60" s="3"/>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
       <c r="D60" s="3">
         <v>1</v>
       </c>
@@ -4144,7 +4153,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>10</v>
       </c>
@@ -4156,7 +4165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>164</v>
       </c>
@@ -4168,7 +4177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>164</v>
       </c>
@@ -4180,7 +4189,7 @@
       </c>
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>77</v>
       </c>
@@ -4192,7 +4201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>73</v>
       </c>
@@ -4204,7 +4213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>78</v>
       </c>
@@ -4216,931 +4225,933 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C68" s="3"/>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
       <c r="D68" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="6"/>
       <c r="D69" s="6"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="6"/>
       <c r="D75" s="3"/>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="6"/>
       <c r="D79" s="6"/>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="6"/>
       <c r="D80" s="6"/>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="6"/>
       <c r="D81" s="6"/>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="6"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="6"/>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="6"/>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="6"/>
       <c r="D130" s="6"/>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="6"/>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="6"/>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="6"/>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="6"/>
       <c r="D162" s="3"/>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="6"/>
       <c r="D163" s="6"/>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="6"/>
       <c r="D164" s="6"/>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="6"/>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="6"/>
       <c r="D167" s="6"/>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="6"/>
       <c r="D168" s="6"/>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="6"/>
       <c r="D169" s="6"/>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="6"/>
       <c r="D172" s="6"/>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="6"/>
       <c r="D185" s="6"/>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="6"/>
       <c r="D196" s="6"/>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="6"/>
       <c r="D201" s="6"/>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="6"/>
       <c r="D202" s="6"/>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="6"/>
       <c r="D203" s="6"/>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="6"/>
       <c r="D204" s="6"/>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="6"/>
       <c r="D205" s="6"/>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="6"/>
       <c r="D206" s="6"/>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="6"/>
       <c r="D207" s="6"/>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="6"/>
       <c r="D208" s="6"/>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="6"/>
       <c r="D209" s="6"/>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="6"/>
       <c r="D210" s="6"/>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="6"/>
       <c r="D212" s="6"/>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="6"/>
       <c r="D213" s="6"/>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="6"/>
       <c r="D218" s="6"/>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="6"/>
       <c r="D219" s="6"/>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="6"/>
       <c r="D220" s="6"/>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="3" t="s">
         <v>87</v>
       </c>
@@ -5172,65 +5183,127 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="3"/>
-      <c r="B224" s="3"/>
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A224" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B224" s="3" t="s">
+        <v>858</v>
+      </c>
       <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A225" s="3"/>
-      <c r="B225" s="3"/>
+      <c r="D224" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A225" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B225" s="3" t="s">
+        <v>860</v>
+      </c>
       <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A226" s="3"/>
-      <c r="B226" s="3"/>
-      <c r="C226" s="6"/>
+      <c r="D225" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A226" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B226" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C226" s="6">
+        <v>1</v>
+      </c>
       <c r="D226" s="6"/>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="3"/>
-      <c r="B227" s="3"/>
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A227" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B227" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="C227" s="6"/>
-      <c r="D227" s="6"/>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="3"/>
-      <c r="B228" s="3"/>
-      <c r="C228" s="6"/>
+      <c r="D227" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B228" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C228" s="6">
+        <v>1</v>
+      </c>
       <c r="D228" s="6"/>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="3"/>
-      <c r="B229" s="3"/>
-      <c r="C229" s="6"/>
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B229" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C229" s="6">
+        <v>1</v>
+      </c>
       <c r="D229" s="6"/>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="3"/>
-      <c r="B230" s="3"/>
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B230" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="C230" s="6"/>
-      <c r="D230" s="6"/>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="3"/>
-      <c r="B231" s="3"/>
-      <c r="C231" s="6"/>
-      <c r="D231" s="6"/>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="3"/>
-      <c r="B232" s="3"/>
-      <c r="C232" s="6"/>
+      <c r="D230" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B231" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C231" s="6">
+        <v>1</v>
+      </c>
+      <c r="D231" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A232" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B232" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="C232" s="6">
+        <v>1</v>
+      </c>
       <c r="D232" s="6"/>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="3"/>
-      <c r="B233" s="3"/>
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A233" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B233" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="C233" s="6"/>
-      <c r="D233" s="6"/>
+      <c r="D233" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
@@ -7131,7 +7204,12 @@
       <c r="B694" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D223" xr:uid="{00000000-0009-0000-0000-000000000000}">
+  <autoFilter ref="A1:D233" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Como 1907"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D220">
       <sortCondition descending="1" ref="D1:D220"/>
     </sortState>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90EDE15-A0C8-4209-86DF-B8BE6D38505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80EDDA4-181C-47DD-B000-15058B4ED9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$233</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -3367,7 +3367,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:D694"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3391,45 +3390,47 @@
         <v>68</v>
       </c>
     </row>
-    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="3">
         <v>10</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="C2" s="3">
+      <c r="D2" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="3">
+        <v>6</v>
+      </c>
+      <c r="D4" s="3">
         <v>1</v>
       </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1</v>
-      </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>78</v>
       </c>
@@ -3441,428 +3442,444 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>872</v>
+        <v>758</v>
       </c>
       <c r="C6" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>750</v>
       </c>
       <c r="C7" s="3">
-        <v>3</v>
-      </c>
-      <c r="D7" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>862</v>
+        <v>872</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="C9" s="3"/>
+        <v>677</v>
+      </c>
+      <c r="C9" s="3">
+        <v>4</v>
+      </c>
       <c r="D9" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C10" s="3">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="C10" s="6">
+        <v>4</v>
+      </c>
+      <c r="D10" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C11" s="3"/>
+        <v>117</v>
+      </c>
+      <c r="C11" s="3">
+        <v>4</v>
+      </c>
       <c r="D11" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>758</v>
+        <v>157</v>
       </c>
       <c r="C12" s="3">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3">
         <v>3</v>
       </c>
-      <c r="D12" s="3">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="3">
+        <v>4</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>729</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>736</v>
+      </c>
+      <c r="C17" s="3">
+        <v>3</v>
+      </c>
+      <c r="D17" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="C16" s="3">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="C17" s="3">
-        <v>1</v>
-      </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="C18" s="3">
+        <v>94</v>
+      </c>
+      <c r="C18" s="6">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6">
         <v>1</v>
       </c>
-      <c r="D18" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3">
+        <v>151</v>
+      </c>
+      <c r="C19" s="6">
+        <v>3</v>
+      </c>
+      <c r="D19" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>747</v>
       </c>
       <c r="C20" s="3">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3">
         <v>1</v>
       </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>862</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>729</v>
+        <v>306</v>
       </c>
       <c r="C22" s="3">
         <v>2</v>
       </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>56</v>
+        <v>675</v>
       </c>
       <c r="C24" s="3">
-        <v>8</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>70</v>
+        <v>707</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="3"/>
+        <v>58</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2</v>
+      </c>
       <c r="D25" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C26" s="3">
         <v>2</v>
       </c>
-      <c r="D26" s="3"/>
-    </row>
-    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>83</v>
+        <v>681</v>
       </c>
       <c r="C27" s="6">
-        <v>3</v>
-      </c>
-      <c r="D27" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D27" s="6"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C28" s="3">
-        <v>3</v>
-      </c>
-      <c r="D28" s="3"/>
-    </row>
-    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>749</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2</v>
+      </c>
+      <c r="D28" s="6"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>277</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>71</v>
+        <v>164</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>76</v>
+        <v>238</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
       </c>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D31" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>142</v>
+        <v>744</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
       </c>
-      <c r="D32" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D32" s="3"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="C33" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>675</v>
+        <v>75</v>
       </c>
       <c r="C34" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6">
+        <v>76</v>
+      </c>
+      <c r="C35" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="3"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>707</v>
+        <v>70</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>663</v>
+        <v>142</v>
       </c>
       <c r="C36" s="3">
         <v>1</v>
       </c>
-      <c r="D36" s="3"/>
-    </row>
-    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D36" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>707</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3">
+        <v>663</v>
+      </c>
+      <c r="C37" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D37" s="3"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>750</v>
+        <v>759</v>
       </c>
       <c r="C38" s="3">
-        <v>4</v>
-      </c>
-      <c r="D38" s="3"/>
-    </row>
-    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>707</v>
+        <v>69</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="C39" s="3">
         <v>1</v>
@@ -3871,1439 +3888,1527 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>707</v>
+        <v>163</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="C40" s="3"/>
+        <v>701</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
       <c r="D40" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>10</v>
+        <v>163</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>759</v>
+        <v>700</v>
       </c>
       <c r="C41" s="3">
         <v>1</v>
       </c>
       <c r="D41" s="3"/>
     </row>
-    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>69</v>
+        <v>874</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>219</v>
+        <v>305</v>
       </c>
       <c r="C43" s="3">
         <v>1</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="C44" s="3">
         <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C44" s="3">
-        <v>4</v>
       </c>
       <c r="D44" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>163</v>
+        <v>707</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>701</v>
+        <v>119</v>
       </c>
       <c r="C45" s="3">
         <v>1</v>
       </c>
       <c r="D45" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C46" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C46" s="3"/>
       <c r="D46" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>700</v>
+        <v>115</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
       </c>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D47" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C48" s="6">
+        <v>302</v>
+      </c>
+      <c r="C48" s="3">
         <v>1</v>
       </c>
-      <c r="D48" s="3"/>
-    </row>
-    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D48" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C49" s="3"/>
+        <v>82</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>874</v>
+        <v>78</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
       </c>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>874</v>
+        <v>78</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C51" s="3"/>
+        <v>304</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
       <c r="D51" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>739</v>
+        <v>149</v>
       </c>
       <c r="C52" s="3">
         <v>1</v>
       </c>
-      <c r="D52" s="3">
-        <v>2</v>
-      </c>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="C53" s="3">
-        <v>5</v>
-      </c>
-      <c r="D53" s="3">
         <v>1</v>
       </c>
+      <c r="D53" s="3"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>736</v>
+        <v>114</v>
       </c>
       <c r="C54" s="3">
-        <v>2</v>
-      </c>
-      <c r="D54" s="3">
         <v>1</v>
       </c>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>31</v>
+        <v>78</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>231</v>
+        <v>181</v>
       </c>
       <c r="C55" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>707</v>
+        <v>78</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>31</v>
+        <v>707</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3">
+        <v>721</v>
+      </c>
+      <c r="C57" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="6"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>707</v>
+        <v>87</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C58" s="3">
+        <v>670</v>
+      </c>
+      <c r="C58" s="6">
         <v>1</v>
       </c>
-      <c r="D58" s="3">
-        <v>2</v>
-      </c>
+      <c r="D58" s="6"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C59" s="3">
+        <v>182</v>
+      </c>
+      <c r="C59" s="6">
         <v>1</v>
       </c>
-      <c r="D59" s="3">
-        <v>3</v>
-      </c>
+      <c r="D59" s="6"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" s="3">
+        <v>159</v>
+      </c>
+      <c r="C60" s="6">
         <v>1</v>
       </c>
-      <c r="D60" s="3">
-        <v>1</v>
-      </c>
+      <c r="D60" s="6"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" s="6">
+        <v>1</v>
+      </c>
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C62" s="6">
+        <v>1</v>
+      </c>
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="C63" s="6">
+        <v>1</v>
+      </c>
+      <c r="D63" s="6"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="6">
+        <v>1</v>
+      </c>
+      <c r="D64" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>746</v>
+      </c>
+      <c r="C65" s="6">
+        <v>1</v>
+      </c>
+      <c r="D65" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="C66" s="6">
+        <v>1</v>
+      </c>
+      <c r="D66" s="6"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="6">
+        <v>1</v>
+      </c>
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C68" s="6">
+        <v>1</v>
+      </c>
+      <c r="D68" s="6"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="C69" s="6">
+        <v>1</v>
+      </c>
+      <c r="D69" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" s="6"/>
+      <c r="D79" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B86" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6">
+      <c r="C87" s="6"/>
+      <c r="D87" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B88" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3">
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>726</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C64" s="3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3">
         <v>1</v>
       </c>
-      <c r="D64" s="3"/>
-    </row>
-    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3">
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" s="6"/>
+      <c r="D93" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="C67" s="3">
-        <v>1</v>
-      </c>
-      <c r="D67" s="3"/>
-    </row>
-    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C68" s="3">
-        <v>1</v>
-      </c>
-      <c r="D68" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
-    </row>
-    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3"/>
-    </row>
-    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3"/>
-    </row>
-    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3"/>
-    </row>
-    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-    </row>
-    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3"/>
-    </row>
-    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="3"/>
-    </row>
-    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3"/>
-    </row>
-    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-    </row>
-    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="3"/>
-      <c r="D78" s="3"/>
-    </row>
-    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
-    </row>
-    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
-    </row>
-    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
-    </row>
-    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="3"/>
-      <c r="D82" s="3"/>
-    </row>
-    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-    </row>
-    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-    </row>
-    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3"/>
-    </row>
-    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-    </row>
-    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="3"/>
-      <c r="D87" s="3"/>
-    </row>
-    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3"/>
-    </row>
-    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3"/>
-    </row>
-    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="3"/>
-      <c r="D90" s="3"/>
-    </row>
-    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3"/>
-    </row>
-    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="3"/>
-      <c r="D93" s="3"/>
-    </row>
-    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3"/>
-    </row>
-    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="3"/>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
-      <c r="C96" s="3"/>
-      <c r="D96" s="3"/>
-    </row>
-    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C96" s="6"/>
+      <c r="D96" s="6"/>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
     </row>
-    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
     </row>
-    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
     </row>
-    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
     </row>
-    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
     </row>
-    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
     </row>
-    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
-      <c r="C104" s="6"/>
+      <c r="C104" s="3"/>
       <c r="D104" s="3"/>
     </row>
-    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
     </row>
-    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
     </row>
-    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
     </row>
-    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
     </row>
-    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
     </row>
-    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
     </row>
-    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
     </row>
-    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
     </row>
-    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
     </row>
-    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
     </row>
-    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
     </row>
-    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
     </row>
-    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
+      <c r="C119" s="6"/>
       <c r="D119" s="3"/>
     </row>
-    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
     </row>
-    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
     </row>
-    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
     </row>
-    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
     </row>
-    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
     </row>
-    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
     </row>
-    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
     </row>
-    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
     </row>
-    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
-      <c r="C128" s="6"/>
+      <c r="C128" s="3"/>
       <c r="D128" s="3"/>
     </row>
-    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
-      <c r="C129" s="6"/>
+      <c r="C129" s="3"/>
       <c r="D129" s="3"/>
     </row>
-    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
-    </row>
-    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
     </row>
-    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
     </row>
-    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
     </row>
-    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
     </row>
-    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
     </row>
-    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
     </row>
-    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
     </row>
-    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
     </row>
-    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
     </row>
-    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
     </row>
-    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
     </row>
-    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
     </row>
-    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
+      <c r="C143" s="6"/>
       <c r="D143" s="3"/>
     </row>
-    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
-      <c r="C144" s="3"/>
+      <c r="C144" s="6"/>
       <c r="D144" s="3"/>
     </row>
-    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
-      <c r="C145" s="3"/>
-      <c r="D145" s="3"/>
-    </row>
-    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C145" s="6"/>
+      <c r="D145" s="6"/>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
     </row>
-    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
-      <c r="D147" s="6"/>
-    </row>
-    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D147" s="3"/>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
     </row>
-    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
     </row>
-    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
     </row>
-    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
     </row>
-    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
     </row>
-    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
     </row>
-    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
     </row>
-    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
     </row>
-    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
     </row>
-    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
     </row>
-    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
     </row>
-    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
     </row>
-    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
-      <c r="D160" s="6"/>
-    </row>
-    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D160" s="3"/>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
-      <c r="D161" s="6"/>
-    </row>
-    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D161" s="3"/>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="3"/>
-    </row>
-    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C162" s="3"/>
+      <c r="D162" s="6"/>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
-    </row>
-    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
-    </row>
-    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
-      <c r="D165" s="6"/>
-    </row>
-    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D165" s="3"/>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
     </row>
-    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
-    </row>
-    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
-    </row>
-    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
-    </row>
-    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
     </row>
-    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
     </row>
-    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
-    </row>
-    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
     </row>
-    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
     </row>
-    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="3"/>
-    </row>
-    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D175" s="6"/>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
-    </row>
-    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D176" s="6"/>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
-      <c r="C177" s="3"/>
+      <c r="C177" s="6"/>
       <c r="D177" s="3"/>
     </row>
-    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
-      <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
-    </row>
-    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C178" s="6"/>
+      <c r="D178" s="6"/>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
-      <c r="D179" s="3"/>
-    </row>
-    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C179" s="6"/>
+      <c r="D179" s="6"/>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
-    </row>
-    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="D180" s="6"/>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
     </row>
-    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="6"/>
       <c r="D182" s="6"/>
     </row>
-    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="6"/>
       <c r="D183" s="6"/>
     </row>
-    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="6"/>
       <c r="D184" s="6"/>
     </row>
-    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
-    </row>
-    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
     </row>
-    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
-      <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
-    </row>
-    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C187" s="6"/>
+      <c r="D187" s="6"/>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
     </row>
-    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
     </row>
-    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
     </row>
-    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
     </row>
-    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
     </row>
-    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
     </row>
-    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
     </row>
-    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
     </row>
-    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
-    </row>
-    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="6"/>
       <c r="D197" s="6"/>
     </row>
-    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="6"/>
       <c r="D198" s="6"/>
     </row>
-    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="6"/>
       <c r="D199" s="6"/>
     </row>
-    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="6"/>
       <c r="D200" s="6"/>
     </row>
-    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
-    </row>
-    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
-    </row>
-    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
-    </row>
-    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
-    </row>
-    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
-    </row>
-    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
-    </row>
-    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
-    </row>
-    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
-    </row>
-    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
-    </row>
-    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
-    </row>
-    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="6"/>
       <c r="D211" s="6"/>
     </row>
-    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="6"/>
       <c r="D212" s="6"/>
     </row>
-    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="6"/>
       <c r="D213" s="6"/>
     </row>
-    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="6"/>
       <c r="D214" s="6"/>
     </row>
-    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="6"/>
       <c r="D215" s="6"/>
     </row>
-    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="6"/>
       <c r="D216" s="6"/>
     </row>
-    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="6"/>
       <c r="D217" s="6"/>
     </row>
-    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="6"/>
       <c r="D218" s="6"/>
     </row>
-    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="6"/>
       <c r="D219" s="6"/>
     </row>
-    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="6"/>
       <c r="D220" s="6"/>
     </row>
-    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="3" t="s">
-        <v>87</v>
-      </c>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="6"/>
       <c r="D221" s="6"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B222" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C222" s="6">
-        <v>1</v>
-      </c>
+      <c r="A222" s="3"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="6"/>
       <c r="D222" s="6"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B223" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A223" s="3"/>
+      <c r="B223" s="3"/>
       <c r="C223" s="6"/>
-      <c r="D223" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B224" s="3" t="s">
-        <v>858</v>
-      </c>
+      <c r="D223" s="6"/>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224" s="3"/>
+      <c r="B224" s="3"/>
       <c r="C224" s="6"/>
-      <c r="D224" s="6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B225" s="3" t="s">
-        <v>860</v>
-      </c>
+      <c r="D224" s="6"/>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225" s="3"/>
+      <c r="B225" s="3"/>
       <c r="C225" s="6"/>
-      <c r="D225" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B226" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C226" s="6">
-        <v>1</v>
-      </c>
+      <c r="D225" s="6"/>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="6"/>
       <c r="D226" s="6"/>
     </row>
-    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="B227" s="3" t="s">
-        <v>293</v>
-      </c>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227" s="3"/>
+      <c r="B227" s="3"/>
       <c r="C227" s="6"/>
-      <c r="D227" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B228" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C228" s="6">
-        <v>1</v>
-      </c>
+      <c r="D227" s="6"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228" s="3"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="6"/>
       <c r="D228" s="6"/>
     </row>
-    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B229" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C229" s="6">
-        <v>1</v>
-      </c>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229" s="3"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="6"/>
       <c r="D229" s="6"/>
     </row>
-    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B230" s="3" t="s">
-        <v>287</v>
-      </c>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230" s="3"/>
+      <c r="B230" s="3"/>
       <c r="C230" s="6"/>
-      <c r="D230" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B231" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C231" s="6">
-        <v>1</v>
-      </c>
-      <c r="D231" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="B232" s="3" t="s">
-        <v>938</v>
-      </c>
-      <c r="C232" s="6">
-        <v>1</v>
-      </c>
+      <c r="D230" s="6"/>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231" s="3"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="6"/>
+      <c r="D231" s="6"/>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232" s="3"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="6"/>
       <c r="D232" s="6"/>
     </row>
-    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="B233" s="3" t="s">
-        <v>289</v>
-      </c>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
       <c r="C233" s="6"/>
-      <c r="D233" s="6">
-        <v>1</v>
-      </c>
+      <c r="D233" s="6"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
@@ -5318,70 +5423,136 @@
       <c r="D235" s="6"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="3"/>
-      <c r="B236" s="3"/>
+      <c r="A236" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B236" s="3" t="s">
+        <v>32</v>
+      </c>
       <c r="C236" s="6"/>
-      <c r="D236" s="6"/>
+      <c r="D236" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="3"/>
-      <c r="B237" s="3"/>
+      <c r="A237" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B237" s="3" t="s">
+        <v>858</v>
+      </c>
       <c r="C237" s="6"/>
-      <c r="D237" s="6"/>
+      <c r="D237" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="3"/>
-      <c r="B238" s="3"/>
+      <c r="A238" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B238" s="3" t="s">
+        <v>860</v>
+      </c>
       <c r="C238" s="6"/>
-      <c r="D238" s="6"/>
+      <c r="D238" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="3"/>
-      <c r="B239" s="3"/>
+      <c r="A239" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B239" s="3" t="s">
+        <v>293</v>
+      </c>
       <c r="C239" s="6"/>
-      <c r="D239" s="6"/>
+      <c r="D239" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="3"/>
-      <c r="B240" s="3"/>
+      <c r="A240" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B240" s="3" t="s">
+        <v>287</v>
+      </c>
       <c r="C240" s="6"/>
-      <c r="D240" s="6"/>
+      <c r="D240" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="3"/>
-      <c r="B241" s="3"/>
+      <c r="A241" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B241" s="3" t="s">
+        <v>289</v>
+      </c>
       <c r="C241" s="6"/>
-      <c r="D241" s="6"/>
+      <c r="D241" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="3"/>
-      <c r="B242" s="3"/>
+      <c r="A242" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B242" s="3" t="s">
+        <v>754</v>
+      </c>
       <c r="C242" s="6"/>
-      <c r="D242" s="6"/>
+      <c r="D242" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="3"/>
-      <c r="B243" s="3"/>
+      <c r="A243" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B243" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="C243" s="6"/>
-      <c r="D243" s="6"/>
+      <c r="D243" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="3"/>
-      <c r="B244" s="3"/>
+      <c r="A244" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B244" s="3" t="s">
+        <v>723</v>
+      </c>
       <c r="C244" s="6"/>
-      <c r="D244" s="6"/>
+      <c r="D244" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="3"/>
-      <c r="B245" s="3"/>
+      <c r="A245" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B245" s="3" t="s">
+        <v>748</v>
+      </c>
       <c r="C245" s="6"/>
-      <c r="D245" s="6"/>
+      <c r="D245" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="3"/>
-      <c r="B246" s="3"/>
+      <c r="A246" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B246" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="C246" s="6"/>
-      <c r="D246" s="6"/>
+      <c r="D246" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
@@ -7204,14 +7375,9 @@
       <c r="B694" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D233" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Como 1907"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D220">
-      <sortCondition descending="1" ref="D1:D220"/>
+  <autoFilter ref="A1:D246" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D246">
+      <sortCondition descending="1" ref="C1:C246"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80EDDA4-181C-47DD-B000-15058B4ED9A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3738FFB7-C4F6-44B4-8479-7A89CE9BE54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -3398,10 +3398,10 @@
         <v>56</v>
       </c>
       <c r="C2" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3412,9 +3412,11 @@
         <v>727</v>
       </c>
       <c r="C3" s="3">
-        <v>6</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>10</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -3450,7 +3452,7 @@
         <v>758</v>
       </c>
       <c r="C6" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -3466,7 +3468,9 @@
       <c r="C7" s="3">
         <v>5</v>
       </c>
-      <c r="D7" s="3"/>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -3490,7 +3494,7 @@
         <v>677</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3">
         <v>2</v>
@@ -3507,7 +3511,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -3532,7 +3536,7 @@
         <v>157</v>
       </c>
       <c r="C12" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3">
         <v>3</v>
@@ -3546,9 +3550,11 @@
         <v>52</v>
       </c>
       <c r="C13" s="3">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -3574,7 +3580,9 @@
       <c r="C15" s="3">
         <v>3</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -3596,7 +3604,7 @@
         <v>736</v>
       </c>
       <c r="C17" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -3613,7 +3621,7 @@
         <v>3</v>
       </c>
       <c r="D18" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -3627,7 +3635,7 @@
         <v>3</v>
       </c>
       <c r="D19" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -3638,7 +3646,7 @@
         <v>747</v>
       </c>
       <c r="C20" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="3">
         <v>1</v>
@@ -3664,7 +3672,7 @@
         <v>306</v>
       </c>
       <c r="C22" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -3690,9 +3698,11 @@
         <v>675</v>
       </c>
       <c r="C24" s="3">
+        <v>4</v>
+      </c>
+      <c r="D24" s="3">
         <v>2</v>
       </c>
-      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
@@ -3702,7 +3712,7 @@
         <v>58</v>
       </c>
       <c r="C25" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -3716,7 +3726,7 @@
         <v>231</v>
       </c>
       <c r="C26" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" s="3">
         <v>1</v>
@@ -3730,7 +3740,7 @@
         <v>681</v>
       </c>
       <c r="C27" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6"/>
     </row>
@@ -3744,7 +3754,9 @@
       <c r="C28" s="6">
         <v>2</v>
       </c>
-      <c r="D28" s="6"/>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
@@ -3766,9 +3778,11 @@
         <v>277</v>
       </c>
       <c r="C30" s="3">
+        <v>4</v>
+      </c>
+      <c r="D30" s="3">
         <v>1</v>
       </c>
-      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
@@ -3781,7 +3795,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -3842,7 +3856,7 @@
         <v>142</v>
       </c>
       <c r="C36" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="3">
         <v>3</v>
@@ -3974,7 +3988,7 @@
         <v>226</v>
       </c>
       <c r="C46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
@@ -4005,7 +4019,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -4056,9 +4070,11 @@
         <v>149</v>
       </c>
       <c r="C52" s="3">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3">
         <v>1</v>
       </c>
-      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
@@ -4080,9 +4096,11 @@
         <v>114</v>
       </c>
       <c r="C54" s="3">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3">
         <v>1</v>
       </c>
-      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
@@ -4118,7 +4136,9 @@
       <c r="C57" s="6">
         <v>1</v>
       </c>
-      <c r="D57" s="6"/>
+      <c r="D57" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
@@ -4166,7 +4186,9 @@
       <c r="C61" s="6">
         <v>1</v>
       </c>
-      <c r="D61" s="6"/>
+      <c r="D61" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
@@ -4303,7 +4325,7 @@
       </c>
       <c r="C72" s="3"/>
       <c r="D72" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -4327,7 +4349,7 @@
       </c>
       <c r="C74" s="3"/>
       <c r="D74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -4339,7 +4361,7 @@
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -4351,7 +4373,7 @@
       </c>
       <c r="C76" s="3"/>
       <c r="D76" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -4363,7 +4385,7 @@
       </c>
       <c r="C77" s="3"/>
       <c r="D77" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -4399,7 +4421,7 @@
       </c>
       <c r="C80" s="3"/>
       <c r="D80" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -4421,7 +4443,9 @@
       <c r="B82" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C82" s="3"/>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
       <c r="D82" s="3">
         <v>2</v>
       </c>
@@ -4531,7 +4555,7 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -4583,129 +4607,265 @@
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="6"/>
+      <c r="A96" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C96" s="6">
+        <v>5</v>
+      </c>
       <c r="D96" s="6"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
+      <c r="A97" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>285</v>
+      </c>
       <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
+      <c r="A98" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
       <c r="D98" s="3"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="A99" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1</v>
+      </c>
       <c r="D99" s="3"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
+      <c r="A100" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
       <c r="D100" s="3"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
+      <c r="A101" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="C101" s="3">
+        <v>2</v>
+      </c>
+      <c r="D101" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
+      <c r="A102" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="C102" s="3">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
+      <c r="A103" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="A104" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
       <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="A105" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C105" s="3">
+        <v>1</v>
+      </c>
       <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
+      <c r="A106" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>317</v>
+      </c>
       <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
+      <c r="D106" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C107" s="3">
+        <v>1</v>
+      </c>
       <c r="D107" s="3"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
+      <c r="A108" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
       <c r="D108" s="3"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
+      <c r="A109" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1</v>
+      </c>
       <c r="D109" s="3"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
+      <c r="A110" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
+      <c r="A111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
+      <c r="D111" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
+      <c r="A112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
+      <c r="A113" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>246</v>
+      </c>
       <c r="C113" s="3"/>
-      <c r="D113" s="3"/>
+      <c r="D113" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
-      <c r="C114" s="3"/>
+      <c r="A114" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1</v>
+      </c>
       <c r="D114" s="3"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
+      <c r="A115" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>717</v>
+      </c>
       <c r="C115" s="3"/>
-      <c r="D115" s="3"/>
+      <c r="D115" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
+      <c r="A116" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1</v>
+      </c>
       <c r="D116" s="3"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
@@ -5455,7 +5615,7 @@
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
@@ -5501,7 +5661,9 @@
       <c r="B242" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="C242" s="6"/>
+      <c r="C242" s="6">
+        <v>1</v>
+      </c>
       <c r="D242" s="6">
         <v>1</v>
       </c>
@@ -5539,7 +5701,7 @@
       </c>
       <c r="C245" s="6"/>
       <c r="D245" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3738FFB7-C4F6-44B4-8479-7A89CE9BE54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001DAA8-A995-4472-A84F-D0A9EB27D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -3426,7 +3426,7 @@
         <v>91</v>
       </c>
       <c r="C4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -3442,7 +3442,9 @@
       <c r="C5" s="3">
         <v>5</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -3452,10 +3454,10 @@
         <v>758</v>
       </c>
       <c r="C6" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -3522,7 +3524,7 @@
         <v>117</v>
       </c>
       <c r="C11" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -3550,7 +3552,7 @@
         <v>52</v>
       </c>
       <c r="C13" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -3592,7 +3594,7 @@
         <v>223</v>
       </c>
       <c r="C16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3"/>
     </row>
@@ -3701,7 +3703,7 @@
         <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -3740,9 +3742,11 @@
         <v>681</v>
       </c>
       <c r="C27" s="6">
-        <v>3</v>
-      </c>
-      <c r="D27" s="6"/>
+        <v>7</v>
+      </c>
+      <c r="D27" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
@@ -3766,7 +3770,7 @@
         <v>92</v>
       </c>
       <c r="C29" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D29" s="3"/>
     </row>
@@ -3882,7 +3886,7 @@
         <v>759</v>
       </c>
       <c r="C38" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D38" s="3">
         <v>1</v>
@@ -3974,7 +3978,7 @@
         <v>119</v>
       </c>
       <c r="C45" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="3">
         <v>2</v>
@@ -3988,7 +3992,7 @@
         <v>226</v>
       </c>
       <c r="C46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="3">
         <v>3</v>
@@ -4046,7 +4050,9 @@
       <c r="C50" s="3">
         <v>1</v>
       </c>
-      <c r="D50" s="3"/>
+      <c r="D50" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
@@ -4056,7 +4062,7 @@
         <v>304</v>
       </c>
       <c r="C51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D51" s="3">
         <v>1</v>
@@ -4073,7 +4079,7 @@
         <v>2</v>
       </c>
       <c r="D52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -4122,9 +4128,11 @@
         <v>236</v>
       </c>
       <c r="C56" s="3">
+        <v>4</v>
+      </c>
+      <c r="D56" s="3">
         <v>1</v>
       </c>
-      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
@@ -4236,7 +4244,7 @@
         <v>746</v>
       </c>
       <c r="C65" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="6">
         <v>1</v>
@@ -4301,7 +4309,7 @@
       </c>
       <c r="C70" s="3"/>
       <c r="D70" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -4337,7 +4345,7 @@
       </c>
       <c r="C73" s="3"/>
       <c r="D73" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -4433,7 +4441,7 @@
       </c>
       <c r="C81" s="3"/>
       <c r="D81" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -4447,7 +4455,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -4505,7 +4513,9 @@
       <c r="B87" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C87" s="6"/>
+      <c r="C87" s="6">
+        <v>1</v>
+      </c>
       <c r="D87" s="6">
         <v>1</v>
       </c>
@@ -4555,7 +4565,7 @@
       </c>
       <c r="C91" s="3"/>
       <c r="D91" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -4601,7 +4611,9 @@
       <c r="B95" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C95" s="6"/>
+      <c r="C95" s="6">
+        <v>1</v>
+      </c>
       <c r="D95" s="6">
         <v>1</v>
       </c>
@@ -4614,7 +4626,7 @@
         <v>147</v>
       </c>
       <c r="C96" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D96" s="6"/>
     </row>
@@ -4640,7 +4652,9 @@
       <c r="C98" s="3">
         <v>1</v>
       </c>
-      <c r="D98" s="3"/>
+      <c r="D98" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
@@ -4650,7 +4664,7 @@
         <v>235</v>
       </c>
       <c r="C99" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99" s="3"/>
     </row>
@@ -4788,10 +4802,10 @@
         <v>14</v>
       </c>
       <c r="C110" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
@@ -4864,69 +4878,131 @@
         <v>85</v>
       </c>
       <c r="C116" s="3">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3"/>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B117" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3">
         <v>1</v>
       </c>
-      <c r="D116" s="3"/>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
+      <c r="A118" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B118" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="C118" s="3">
+        <v>2</v>
+      </c>
+      <c r="D118" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
-      <c r="C119" s="6"/>
+      <c r="A119" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="C119" s="6">
+        <v>2</v>
+      </c>
       <c r="D119" s="3"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
+      <c r="A120" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B120" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
+      <c r="D120" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
-      <c r="C121" s="3"/>
+      <c r="A121" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B121" s="3" t="s">
+        <v>944</v>
+      </c>
+      <c r="C121" s="3">
+        <v>1</v>
+      </c>
       <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
-      <c r="C122" s="3"/>
+      <c r="A122" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B122" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C122" s="3">
+        <v>1</v>
+      </c>
       <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
-      <c r="C123" s="3"/>
+      <c r="A123" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B123" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C123" s="3">
+        <v>1</v>
+      </c>
       <c r="D123" s="3"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
-      <c r="C124" s="3"/>
+      <c r="A124" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B124" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C124" s="3">
+        <v>1</v>
+      </c>
       <c r="D124" s="3"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
+      <c r="A125" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B125" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="C125" s="3"/>
-      <c r="D125" s="3"/>
+      <c r="D125" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
+      <c r="A126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="C126" s="3"/>
-      <c r="D126" s="3"/>
+      <c r="D126" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
@@ -5649,9 +5725,11 @@
       <c r="B241" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C241" s="6"/>
+      <c r="C241" s="6">
+        <v>1</v>
+      </c>
       <c r="D241" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F001DAA8-A995-4472-A84F-D0A9EB27D2DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B48962-6FF5-47CE-AB07-76708D5EE602}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="955">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="955">
   <si>
     <t>Jugador</t>
   </si>
@@ -3420,13 +3420,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>707</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="C4" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -3434,94 +3434,94 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>152</v>
+        <v>758</v>
       </c>
       <c r="C5" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>758</v>
+        <v>91</v>
       </c>
       <c r="C6" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="C7" s="3">
-        <v>5</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
+        <v>681</v>
+      </c>
+      <c r="C7" s="6">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>872</v>
+        <v>677</v>
       </c>
       <c r="C8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>677</v>
+        <v>117</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="6">
-        <v>4</v>
+        <v>157</v>
+      </c>
+      <c r="C10" s="3">
+        <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>707</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="C11" s="3">
         <v>6</v>
@@ -3532,27 +3532,25 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="3">
+        <v>147</v>
+      </c>
+      <c r="C12" s="6">
         <v>6</v>
       </c>
-      <c r="D12" s="3">
-        <v>3</v>
-      </c>
+      <c r="D12" s="6"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>707</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="C13" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -3560,27 +3558,27 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>148</v>
+        <v>750</v>
       </c>
       <c r="C14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>729</v>
+        <v>872</v>
       </c>
       <c r="C15" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -3588,93 +3586,93 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>223</v>
+        <v>92</v>
       </c>
       <c r="C16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="C17" s="3">
+        <v>83</v>
+      </c>
+      <c r="C17" s="6">
         <v>4</v>
       </c>
       <c r="D17" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="6">
-        <v>3</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4</v>
+      </c>
+      <c r="D18" s="3"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>69</v>
+        <v>31</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="C19" s="6">
-        <v>3</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2</v>
+        <v>736</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>747</v>
+        <v>675</v>
       </c>
       <c r="C20" s="3">
+        <v>4</v>
+      </c>
+      <c r="D20" s="3">
         <v>3</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>862</v>
+        <v>277</v>
       </c>
       <c r="C21" s="3">
-        <v>2</v>
-      </c>
-      <c r="D21" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>164</v>
+        <v>10</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>306</v>
+        <v>759</v>
       </c>
       <c r="C22" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -3682,39 +3680,41 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C23" s="3">
-        <v>2</v>
-      </c>
-      <c r="D23" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>675</v>
+        <v>148</v>
       </c>
       <c r="C24" s="3">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3">
         <v>4</v>
-      </c>
-      <c r="D24" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>707</v>
+        <v>73</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>58</v>
+        <v>729</v>
       </c>
       <c r="C25" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="3">
         <v>1</v>
@@ -3722,27 +3722,27 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="C26" s="3">
+        <v>94</v>
+      </c>
+      <c r="C26" s="6">
         <v>3</v>
       </c>
-      <c r="D26" s="3">
-        <v>1</v>
+      <c r="D26" s="6">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>681</v>
+        <v>151</v>
       </c>
       <c r="C27" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D27" s="6">
         <v>2</v>
@@ -3753,36 +3753,38 @@
         <v>10</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="C28" s="6">
-        <v>2</v>
-      </c>
-      <c r="D28" s="6">
+        <v>747</v>
+      </c>
+      <c r="C28" s="3">
+        <v>3</v>
+      </c>
+      <c r="D28" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
+        <v>306</v>
       </c>
       <c r="C29" s="3">
         <v>3</v>
       </c>
-      <c r="D29" s="3"/>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>277</v>
+        <v>231</v>
       </c>
       <c r="C30" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -3790,65 +3792,67 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="C31" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>744</v>
+        <v>304</v>
       </c>
       <c r="C32" s="3">
+        <v>3</v>
+      </c>
+      <c r="D32" s="3">
         <v>1</v>
       </c>
-      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="C33" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>71</v>
+        <v>15</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C34" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>76</v>
+        <v>862</v>
       </c>
       <c r="C35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="3"/>
     </row>
@@ -3857,184 +3861,184 @@
         <v>70</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>142</v>
+        <v>229</v>
       </c>
       <c r="C36" s="3">
         <v>2</v>
       </c>
-      <c r="D36" s="3">
-        <v>3</v>
-      </c>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>707</v>
+        <v>10</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="C37" s="3">
+        <v>749</v>
+      </c>
+      <c r="C37" s="6">
+        <v>2</v>
+      </c>
+      <c r="D37" s="6">
         <v>1</v>
       </c>
-      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>759</v>
+        <v>142</v>
       </c>
       <c r="C38" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D38" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>69</v>
+        <v>707</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>219</v>
+        <v>119</v>
       </c>
       <c r="C39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>701</v>
+        <v>149</v>
       </c>
       <c r="C40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>700</v>
+        <v>114</v>
       </c>
       <c r="C41" s="3">
+        <v>2</v>
+      </c>
+      <c r="D41" s="3">
         <v>1</v>
       </c>
-      <c r="D41" s="3"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1</v>
+        <v>181</v>
+      </c>
+      <c r="C42" s="3">
+        <v>2</v>
       </c>
       <c r="D42" s="3"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>874</v>
+        <v>940</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C43" s="3">
-        <v>1</v>
-      </c>
-      <c r="D43" s="3"/>
+        <v>938</v>
+      </c>
+      <c r="C43" s="6">
+        <v>2</v>
+      </c>
+      <c r="D43" s="6"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="C44" s="3">
+        <v>746</v>
+      </c>
+      <c r="C44" s="6">
+        <v>2</v>
+      </c>
+      <c r="D44" s="6">
         <v>1</v>
-      </c>
-      <c r="D44" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>707</v>
+        <v>77</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="C45" s="3">
         <v>2</v>
       </c>
-      <c r="D45" s="3">
-        <v>2</v>
-      </c>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>226</v>
+        <v>705</v>
       </c>
       <c r="C46" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D46" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>115</v>
+        <v>667</v>
       </c>
       <c r="C47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>164</v>
+        <v>940</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>302</v>
+        <v>939</v>
       </c>
       <c r="C48" s="3">
+        <v>2</v>
+      </c>
+      <c r="D48" s="3">
         <v>1</v>
-      </c>
-      <c r="D48" s="3">
-        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>73</v>
+        <v>15</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C49" s="3">
-        <v>1</v>
+        <v>680</v>
+      </c>
+      <c r="C49" s="6">
+        <v>2</v>
       </c>
       <c r="D49" s="3">
         <v>1</v>
@@ -4042,52 +4046,50 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>78</v>
+        <v>164</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>310</v>
+        <v>238</v>
       </c>
       <c r="C50" s="3">
         <v>1</v>
       </c>
       <c r="D50" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>78</v>
+        <v>10</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>304</v>
+        <v>744</v>
       </c>
       <c r="C51" s="3">
-        <v>3</v>
-      </c>
-      <c r="D51" s="3">
         <v>1</v>
       </c>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="C52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="C53" s="3">
         <v>1</v>
@@ -4096,24 +4098,22 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C54" s="3">
-        <v>2</v>
-      </c>
-      <c r="D54" s="3">
         <v>1</v>
       </c>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>78</v>
+        <v>707</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>181</v>
+        <v>663</v>
       </c>
       <c r="C55" s="3">
         <v>1</v>
@@ -4122,13 +4122,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C56" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -4136,150 +4136,156 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>707</v>
+        <v>163</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="C57" s="6">
+        <v>701</v>
+      </c>
+      <c r="C57" s="3">
         <v>1</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>87</v>
+        <v>163</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="C58" s="6">
+        <v>700</v>
+      </c>
+      <c r="C58" s="3">
         <v>1</v>
       </c>
-      <c r="D58" s="6"/>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C59" s="6">
         <v>1</v>
       </c>
-      <c r="D59" s="6"/>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>77</v>
+        <v>874</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C60" s="6">
+        <v>305</v>
+      </c>
+      <c r="C60" s="3">
         <v>1</v>
       </c>
-      <c r="D60" s="6"/>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>70</v>
+        <v>31</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="C61" s="6">
+        <v>739</v>
+      </c>
+      <c r="C61" s="3">
         <v>1</v>
       </c>
-      <c r="D61" s="6">
-        <v>1</v>
+      <c r="D61" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C62" s="6">
+        <v>115</v>
+      </c>
+      <c r="C62" s="3">
         <v>1</v>
       </c>
-      <c r="D62" s="6"/>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>940</v>
+        <v>164</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>938</v>
-      </c>
-      <c r="C63" s="6">
+        <v>302</v>
+      </c>
+      <c r="C63" s="3">
         <v>1</v>
       </c>
-      <c r="D63" s="6"/>
+      <c r="D63" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C64" s="6">
+        <v>82</v>
+      </c>
+      <c r="C64" s="3">
         <v>1</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="C65" s="6">
-        <v>2</v>
-      </c>
-      <c r="D65" s="6">
+        <v>310</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>164</v>
+        <v>15</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="C66" s="6">
+        <v>146</v>
+      </c>
+      <c r="C66" s="3">
         <v>1</v>
       </c>
-      <c r="D66" s="6"/>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>71</v>
+        <v>707</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>80</v>
+        <v>721</v>
       </c>
       <c r="C67" s="6">
         <v>1</v>
       </c>
-      <c r="D67" s="6"/>
+      <c r="D67" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>202</v>
+        <v>670</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -4288,532 +4294,538 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>707</v>
+        <v>31</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>713</v>
+        <v>182</v>
       </c>
       <c r="C69" s="6">
         <v>1</v>
       </c>
-      <c r="D69" s="6">
-        <v>1</v>
-      </c>
+      <c r="D69" s="6"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="C70" s="3"/>
-      <c r="D70" s="3">
-        <v>4</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="C70" s="6">
+        <v>1</v>
+      </c>
+      <c r="D70" s="6"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>863</v>
-      </c>
-      <c r="C71" s="3"/>
-      <c r="D71" s="3">
-        <v>2</v>
+        <v>193</v>
+      </c>
+      <c r="C71" s="6">
+        <v>1</v>
+      </c>
+      <c r="D71" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C72" s="3"/>
-      <c r="D72" s="3">
-        <v>4</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="C72" s="6">
+        <v>1</v>
+      </c>
+      <c r="D72" s="6"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="C73" s="6">
+        <v>1</v>
+      </c>
+      <c r="D73" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C74" s="3"/>
-      <c r="D74" s="3">
-        <v>3</v>
-      </c>
+        <v>725</v>
+      </c>
+      <c r="C74" s="6">
+        <v>1</v>
+      </c>
+      <c r="D74" s="6"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C75" s="3"/>
-      <c r="D75" s="3">
-        <v>2</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C75" s="6">
+        <v>1</v>
+      </c>
+      <c r="D75" s="6"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C76" s="3"/>
-      <c r="D76" s="3">
-        <v>2</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C76" s="6">
+        <v>1</v>
+      </c>
+      <c r="D76" s="6"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>70</v>
+        <v>707</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3">
-        <v>2</v>
+        <v>713</v>
+      </c>
+      <c r="C77" s="6">
+        <v>1</v>
+      </c>
+      <c r="D77" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>71</v>
+        <v>10</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="C78" s="3"/>
+        <v>59</v>
+      </c>
+      <c r="C78" s="3">
+        <v>1</v>
+      </c>
       <c r="D78" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C79" s="6"/>
+        <v>93</v>
+      </c>
+      <c r="C79" s="6">
+        <v>1</v>
+      </c>
       <c r="D79" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>707</v>
+        <v>78</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="C80" s="3"/>
+        <v>155</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
       <c r="D80" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>707</v>
+        <v>78</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="C81" s="3"/>
-      <c r="D81" s="3">
-        <v>2</v>
+        <v>224</v>
+      </c>
+      <c r="C81" s="6">
+        <v>1</v>
+      </c>
+      <c r="D81" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>59</v>
+        <v>859</v>
       </c>
       <c r="C82" s="3">
         <v>1</v>
       </c>
       <c r="D82" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>163</v>
+        <v>77</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3">
+        <v>303</v>
+      </c>
+      <c r="C83" s="3">
         <v>1</v>
       </c>
+      <c r="D83" s="3"/>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="C84" s="3"/>
+        <v>666</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
       <c r="D84" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>874</v>
+        <v>87</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C85" s="3"/>
-      <c r="D85" s="3">
+        <v>668</v>
+      </c>
+      <c r="C85" s="3">
         <v>1</v>
       </c>
+      <c r="D85" s="3"/>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3">
+        <v>74</v>
+      </c>
+      <c r="C86" s="3">
         <v>1</v>
       </c>
+      <c r="D86" s="3"/>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C87" s="6">
+        <v>291</v>
+      </c>
+      <c r="C87" s="3">
         <v>1</v>
       </c>
-      <c r="D87" s="6">
-        <v>1</v>
-      </c>
+      <c r="D87" s="3"/>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>10</v>
+        <v>164</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="C88" s="3"/>
-      <c r="D88" s="3">
-        <v>3</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3"/>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="C89" s="3"/>
-      <c r="D89" s="3">
+        <v>90</v>
+      </c>
+      <c r="C89" s="3">
         <v>1</v>
       </c>
+      <c r="D89" s="3"/>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C90" s="3"/>
+        <v>121</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
       <c r="D90" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>15</v>
+        <v>73</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="C91" s="3"/>
-      <c r="D91" s="3">
-        <v>4</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3"/>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>15</v>
+        <v>940</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3">
+        <v>944</v>
+      </c>
+      <c r="C92" s="3">
         <v>1</v>
       </c>
+      <c r="D92" s="3"/>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C93" s="6"/>
-      <c r="D93" s="3">
-        <v>2</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C93" s="3">
+        <v>1</v>
+      </c>
+      <c r="D93" s="3"/>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C94" s="3"/>
-      <c r="D94" s="3">
-        <v>2</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3"/>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C95" s="6">
+        <v>230</v>
+      </c>
+      <c r="C95" s="3">
         <v>1</v>
       </c>
-      <c r="D95" s="6">
-        <v>1</v>
-      </c>
+      <c r="D95" s="3"/>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>77</v>
+        <v>940</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C96" s="6">
-        <v>6</v>
-      </c>
-      <c r="D96" s="6"/>
+        <v>946</v>
+      </c>
+      <c r="C96" s="3">
+        <v>1</v>
+      </c>
+      <c r="D96" s="3"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>77</v>
+        <v>940</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3">
+        <v>289</v>
+      </c>
+      <c r="C97" s="6">
         <v>1</v>
+      </c>
+      <c r="D97" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>79</v>
+        <v>10</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>859</v>
-      </c>
-      <c r="C98" s="3">
+        <v>754</v>
+      </c>
+      <c r="C98" s="6">
         <v>1</v>
       </c>
-      <c r="D98" s="3">
+      <c r="D98" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C99" s="3">
-        <v>2</v>
-      </c>
-      <c r="D99" s="3"/>
+        <v>145</v>
+      </c>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C100" s="3">
-        <v>1</v>
-      </c>
-      <c r="D100" s="3"/>
+        <v>863</v>
+      </c>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="C101" s="3">
-        <v>2</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="C101" s="3"/>
       <c r="D101" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>87</v>
+        <v>10</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="C102" s="3">
-        <v>2</v>
-      </c>
+        <v>748</v>
+      </c>
+      <c r="C102" s="3"/>
       <c r="D102" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="C103" s="3">
-        <v>1</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C103" s="3"/>
       <c r="D103" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="C104" s="3">
-        <v>1</v>
-      </c>
-      <c r="D104" s="3"/>
+        <v>94</v>
+      </c>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
         <v>73</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C105" s="3">
-        <v>1</v>
-      </c>
-      <c r="D105" s="3"/>
+        <v>86</v>
+      </c>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>317</v>
+        <v>105</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C107" s="3">
-        <v>1</v>
-      </c>
-      <c r="D107" s="3"/>
+        <v>733</v>
+      </c>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="C108" s="3">
+        <v>40</v>
+      </c>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6">
         <v>1</v>
       </c>
-      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>73</v>
+        <v>707</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C109" s="3">
-        <v>1</v>
-      </c>
-      <c r="D109" s="3"/>
+        <v>718</v>
+      </c>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>15</v>
+        <v>707</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C110" s="3">
+        <v>717</v>
+      </c>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3">
         <v>2</v>
-      </c>
-      <c r="D110" s="3">
-        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>15</v>
+        <v>163</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>206</v>
+        <v>55</v>
       </c>
       <c r="C111" s="3"/>
       <c r="D111" s="3">
@@ -4822,24 +4834,22 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C112" s="3">
-        <v>1</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="C112" s="3"/>
       <c r="D112" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>77</v>
+        <v>874</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>246</v>
+        <v>288</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3">
@@ -4848,46 +4858,46 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C114" s="3">
+        <v>217</v>
+      </c>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3">
         <v>1</v>
       </c>
-      <c r="D114" s="3"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>707</v>
+        <v>10</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>717</v>
+        <v>741</v>
       </c>
       <c r="C115" s="3"/>
       <c r="D115" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C116" s="3">
-        <v>2</v>
-      </c>
-      <c r="D116" s="3"/>
+        <v>726</v>
+      </c>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>197</v>
+        <v>300</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3">
@@ -4896,16 +4906,14 @@
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>940</v>
+        <v>15</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>939</v>
-      </c>
-      <c r="C118" s="3">
-        <v>2</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="C118" s="3"/>
       <c r="D118" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
@@ -4913,91 +4921,91 @@
         <v>15</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="C119" s="6">
-        <v>2</v>
-      </c>
-      <c r="D119" s="3"/>
+        <v>101</v>
+      </c>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>940</v>
+        <v>73</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="C120" s="6"/>
       <c r="D120" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>940</v>
+        <v>77</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>944</v>
-      </c>
-      <c r="C121" s="3">
+        <v>285</v>
+      </c>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3">
         <v>1</v>
       </c>
-      <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C122" s="3">
+        <v>317</v>
+      </c>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3">
         <v>1</v>
       </c>
-      <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="C123" s="3">
+        <v>206</v>
+      </c>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3">
         <v>1</v>
       </c>
-      <c r="D123" s="3"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C124" s="3">
+        <v>246</v>
+      </c>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3">
         <v>1</v>
       </c>
-      <c r="D124" s="3"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
         <v>707</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3">
@@ -5005,28 +5013,52 @@
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
+      <c r="A127" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="B127" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="C127" s="3"/>
-      <c r="D127" s="3"/>
+      <c r="D127" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
+      <c r="A128" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B128" s="3" t="s">
+        <v>711</v>
+      </c>
       <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
+      <c r="D128" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
+      <c r="A129" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="3" t="s">
+        <v>81</v>
+      </c>
       <c r="C129" s="3"/>
-      <c r="D129" s="3"/>
+      <c r="D129" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
+      <c r="A130" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" s="3" t="s">
+        <v>97</v>
+      </c>
       <c r="C130" s="3"/>
-      <c r="D130" s="3"/>
+      <c r="D130" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
@@ -5103,32 +5135,32 @@
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
-      <c r="C143" s="6"/>
+      <c r="C143" s="3"/>
       <c r="D143" s="3"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
-      <c r="C144" s="6"/>
+      <c r="C144" s="3"/>
       <c r="D144" s="3"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
+      <c r="D145" s="3"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
-      <c r="C146" s="3"/>
+      <c r="C146" s="6"/>
       <c r="D146" s="3"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
-      <c r="C147" s="3"/>
-      <c r="D147" s="3"/>
+      <c r="C147" s="6"/>
+      <c r="D147" s="6"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
@@ -5218,7 +5250,7 @@
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
-      <c r="D162" s="6"/>
+      <c r="D162" s="3"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
@@ -5230,7 +5262,7 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
+      <c r="D164" s="6"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
@@ -5296,55 +5328,55 @@
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
-      <c r="D175" s="6"/>
+      <c r="D175" s="3"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="6"/>
+      <c r="D176" s="3"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="6"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
-      <c r="C178" s="6"/>
+      <c r="C178" s="3"/>
       <c r="D178" s="6"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
+      <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
+      <c r="C180" s="6"/>
       <c r="D180" s="6"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
+      <c r="C181" s="6"/>
+      <c r="D181" s="6"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
-      <c r="C182" s="6"/>
+      <c r="C182" s="3"/>
       <c r="D182" s="6"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
@@ -5355,20 +5387,20 @@
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
-      <c r="D185" s="3"/>
+      <c r="C185" s="6"/>
+      <c r="D185" s="6"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
-      <c r="C186" s="3"/>
-      <c r="D186" s="3"/>
+      <c r="C186" s="6"/>
+      <c r="D186" s="6"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
@@ -5379,8 +5411,8 @@
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
+      <c r="C189" s="6"/>
+      <c r="D189" s="6"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
@@ -5427,14 +5459,14 @@
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
@@ -5451,14 +5483,14 @@
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
-      <c r="C201" s="3"/>
-      <c r="D201" s="3"/>
+      <c r="C201" s="6"/>
+      <c r="D201" s="6"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
-      <c r="C202" s="3"/>
-      <c r="D202" s="3"/>
+      <c r="C202" s="6"/>
+      <c r="D202" s="6"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
@@ -5511,14 +5543,14 @@
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
@@ -5659,89 +5691,73 @@
       <c r="D235" s="6"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B236" s="3" t="s">
-        <v>32</v>
-      </c>
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
       <c r="C236" s="6"/>
-      <c r="D236" s="6">
-        <v>1</v>
-      </c>
+      <c r="D236" s="6"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B237" s="3" t="s">
-        <v>858</v>
-      </c>
+      <c r="A237" s="3"/>
+      <c r="B237" s="3"/>
       <c r="C237" s="6"/>
-      <c r="D237" s="6">
-        <v>2</v>
-      </c>
+      <c r="D237" s="6"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="B238" s="3" t="s">
-        <v>860</v>
+        <v>32</v>
       </c>
       <c r="C238" s="6"/>
       <c r="D238" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B239" s="3" t="s">
-        <v>293</v>
+        <v>858</v>
       </c>
       <c r="C239" s="6"/>
       <c r="D239" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B240" s="3" t="s">
-        <v>287</v>
+        <v>860</v>
       </c>
       <c r="C240" s="6"/>
       <c r="D240" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A241" s="3" t="s">
-        <v>940</v>
+        <v>77</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C241" s="6">
+        <v>293</v>
+      </c>
+      <c r="C241" s="6"/>
+      <c r="D241" s="6">
         <v>1</v>
-      </c>
-      <c r="D241" s="6">
-        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" s="3" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B242" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="C242" s="6">
-        <v>1</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="C242" s="6"/>
       <c r="D242" s="6">
         <v>1</v>
       </c>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57033F9B-1375-41E9-8BA7-13A61C5E7916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DFE5B2-0843-495A-A331-EBFE16A334DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -85,7 +85,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="965">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -2511,9 +2511,6 @@
     <t>Logos Equipos/realmadrid.webp</t>
   </si>
   <si>
-    <t xml:space="preserve">FC </t>
-  </si>
-  <si>
     <t>Spotify Camp Nou</t>
   </si>
   <si>
@@ -2535,9 +2532,6 @@
     <t>Logos Equipos/manchestercity.png</t>
   </si>
   <si>
-    <t xml:space="preserve">AC </t>
-  </si>
-  <si>
     <t>Daniel Ugarte</t>
   </si>
   <si>
@@ -2556,9 +2550,6 @@
     <t>Logos Equipos/bayernleverkusen.png</t>
   </si>
   <si>
-    <t xml:space="preserve">RB </t>
-  </si>
-  <si>
     <t>Red Bull Arena</t>
   </si>
   <si>
@@ -2622,27 +2613,9 @@
     <t>Logos Equipos/como.webp</t>
   </si>
   <si>
-    <t>TOT</t>
-  </si>
-  <si>
-    <t>Tottenham Hotspur Stadium</t>
-  </si>
-  <si>
-    <t>Jose Mendez</t>
-  </si>
-  <si>
-    <t>Logos Equipos/tottenham.png</t>
-  </si>
-  <si>
     <t>CPI</t>
   </si>
   <si>
-    <t>Stadio Marcantonio Bentegodi</t>
-  </si>
-  <si>
-    <t>Aldo Perez</t>
-  </si>
-  <si>
     <t>Logos Equipos/casapia.webp</t>
   </si>
   <si>
@@ -2827,6 +2800,186 @@
   </si>
   <si>
     <t>II Álex Baena</t>
+  </si>
+  <si>
+    <t>SD Sebastian Szymański</t>
+  </si>
+  <si>
+    <t>PT Guglielmo Vicario</t>
+  </si>
+  <si>
+    <t>LI Alex Sandro</t>
+  </si>
+  <si>
+    <t>LI Ferland Mendy</t>
+  </si>
+  <si>
+    <t>LD Dani Carvajal</t>
+  </si>
+  <si>
+    <t>CT Dayot Upamecano</t>
+  </si>
+  <si>
+    <t>ID Juan Cuadrado</t>
+  </si>
+  <si>
+    <t>MP Takumi Minamino</t>
+  </si>
+  <si>
+    <t>ED Ismaïla Sarr</t>
+  </si>
+  <si>
+    <t>DC Randal Kolo Muani</t>
+  </si>
+  <si>
+    <t>MC Teboho Mokoena</t>
+  </si>
+  <si>
+    <t>MC Kodai Sano</t>
+  </si>
+  <si>
+    <t>DC Darwin Núñez</t>
+  </si>
+  <si>
+    <t>EI Eden Hazard</t>
+  </si>
+  <si>
+    <t>ED Jhon Arias</t>
+  </si>
+  <si>
+    <t>MP Lucas Paquetá</t>
+  </si>
+  <si>
+    <t>CT Gianluca Mancini</t>
+  </si>
+  <si>
+    <t>MCD Bryan Cristante</t>
+  </si>
+  <si>
+    <t>MCD Samuele Ricci</t>
+  </si>
+  <si>
+    <t>LI David Møller Wolfe</t>
+  </si>
+  <si>
+    <t>CT Renato Veiga</t>
+  </si>
+  <si>
+    <t>LD Nahuel Molina</t>
+  </si>
+  <si>
+    <t>PT Rui Silva</t>
+  </si>
+  <si>
+    <t>Urawa Red Diamonds</t>
+  </si>
+  <si>
+    <t>Urawa_Red_Diamonds</t>
+  </si>
+  <si>
+    <t>Sebastian Szymański</t>
+  </si>
+  <si>
+    <t>Guglielmo Vicario</t>
+  </si>
+  <si>
+    <t>Alex Sandro</t>
+  </si>
+  <si>
+    <t>Ferland Mendy</t>
+  </si>
+  <si>
+    <t>Dayot Upamecano</t>
+  </si>
+  <si>
+    <t>Juan Cuadrado</t>
+  </si>
+  <si>
+    <t>Takumi Minamino</t>
+  </si>
+  <si>
+    <t>Ismaïla Sarr</t>
+  </si>
+  <si>
+    <t>Randal Kolo Muani</t>
+  </si>
+  <si>
+    <t>Teboho Mokoena</t>
+  </si>
+  <si>
+    <t>Kodai Sano</t>
+  </si>
+  <si>
+    <t>Darwin Núñez</t>
+  </si>
+  <si>
+    <t>Eden Hazard</t>
+  </si>
+  <si>
+    <t>Jhon Arias</t>
+  </si>
+  <si>
+    <t>Lucas Paquetá</t>
+  </si>
+  <si>
+    <t>Gianluca Mancini</t>
+  </si>
+  <si>
+    <t>Bryan Cristante</t>
+  </si>
+  <si>
+    <t>Samuele Ricci</t>
+  </si>
+  <si>
+    <t>David Møller Wolfe</t>
+  </si>
+  <si>
+    <t>Renato Veiga</t>
+  </si>
+  <si>
+    <t>Rui Silva</t>
+  </si>
+  <si>
+    <t>URD</t>
+  </si>
+  <si>
+    <t>BVB</t>
+  </si>
+  <si>
+    <t>FC</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>RB</t>
+  </si>
+  <si>
+    <t>Estádio Nacional do Jamor</t>
+  </si>
+  <si>
+    <t>Saitama Stadium 2002</t>
+  </si>
+  <si>
+    <t>Signal Iduna Park</t>
+  </si>
+  <si>
+    <t>Duvan Ardila</t>
+  </si>
+  <si>
+    <t>Daniel</t>
+  </si>
+  <si>
+    <t>Padilla</t>
+  </si>
+  <si>
+    <t>Eseba</t>
+  </si>
+  <si>
+    <t>Logos Equipos/urawareds.png</t>
+  </si>
+  <si>
+    <t>Logos Equipos/borussia.webp</t>
   </si>
 </sst>
 </file>
@@ -7524,21 +7677,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="B1" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="C1" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7546,10 +7699,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B3" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7557,10 +7710,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B4" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7568,10 +7721,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B5" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7579,10 +7732,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B6" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7590,10 +7743,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B7" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7601,10 +7754,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B8" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7612,10 +7765,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B9" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7623,10 +7776,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B10" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7634,10 +7787,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B11" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -7645,10 +7798,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B12" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -7656,10 +7809,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7667,10 +7820,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B14" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -11115,7 +11268,9 @@
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" t="s">
+        <v>929</v>
+      </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
@@ -11166,7 +11321,9 @@
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="5" t="s">
+        <v>930</v>
+      </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
@@ -11217,7 +11374,9 @@
       <c r="A3" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="5" t="s">
+        <v>931</v>
+      </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
       </c>
@@ -11268,7 +11427,9 @@
       <c r="A4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="5" t="s">
+        <v>932</v>
+      </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
       </c>
@@ -11319,7 +11480,9 @@
       <c r="A5" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="5" t="s">
+        <v>933</v>
+      </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
       </c>
@@ -11370,7 +11533,9 @@
       <c r="A6" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="5" t="s">
+        <v>888</v>
+      </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
       </c>
@@ -11421,7 +11586,9 @@
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="5"/>
+      <c r="B7" s="5" t="s">
+        <v>934</v>
+      </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
       </c>
@@ -11472,7 +11639,9 @@
       <c r="A8" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="5" t="s">
+        <v>935</v>
+      </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
       </c>
@@ -11523,7 +11692,9 @@
       <c r="A9" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="5" t="s">
+        <v>936</v>
+      </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
       </c>
@@ -11574,9 +11745,11 @@
       <c r="A10" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>937</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -11625,7 +11798,9 @@
       <c r="A11" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>938</v>
+      </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
       </c>
@@ -11676,7 +11851,9 @@
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="B12" s="5"/>
+      <c r="B12" s="5" t="s">
+        <v>939</v>
+      </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
       </c>
@@ -11727,7 +11904,9 @@
       <c r="A13" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="5" t="s">
+        <v>940</v>
+      </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
       </c>
@@ -11778,7 +11957,9 @@
       <c r="A14" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="5" t="s">
+        <v>941</v>
+      </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
       </c>
@@ -11829,7 +12010,9 @@
       <c r="A15" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="5" t="s">
+        <v>942</v>
+      </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
       </c>
@@ -11880,7 +12063,9 @@
       <c r="A16" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="B16" s="5"/>
+      <c r="B16" s="5" t="s">
+        <v>943</v>
+      </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
       </c>
@@ -11931,7 +12116,9 @@
       <c r="A17" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="B17" s="5"/>
+      <c r="B17" s="5" t="s">
+        <v>944</v>
+      </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
       </c>
@@ -11982,7 +12169,9 @@
       <c r="A18" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5" t="s">
+        <v>945</v>
+      </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
       </c>
@@ -12033,7 +12222,9 @@
       <c r="A19" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5" t="s">
+        <v>946</v>
+      </c>
       <c r="C19" s="5" t="s">
         <v>288</v>
       </c>
@@ -12084,7 +12275,9 @@
       <c r="A20" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="5"/>
+      <c r="B20" s="5" t="s">
+        <v>947</v>
+      </c>
       <c r="C20" s="5" t="s">
         <v>304</v>
       </c>
@@ -12135,7 +12328,9 @@
       <c r="A21" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5" t="s">
+        <v>948</v>
+      </c>
       <c r="C21" s="5" t="s">
         <v>320</v>
       </c>
@@ -12186,7 +12381,9 @@
       <c r="A22" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>949</v>
+      </c>
       <c r="C22" s="5" t="s">
         <v>336</v>
       </c>
@@ -12237,7 +12434,9 @@
       <c r="A23" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>392</v>
+      </c>
       <c r="C23" s="5" t="s">
         <v>352</v>
       </c>
@@ -12288,7 +12487,9 @@
       <c r="A24" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B24" s="5"/>
+      <c r="B24" s="5" t="s">
+        <v>950</v>
+      </c>
       <c r="C24" s="5" t="s">
         <v>368</v>
       </c>
@@ -12369,7 +12570,9 @@
       <c r="A1" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B1" s="3"/>
+      <c r="B1" t="s">
+        <v>928</v>
+      </c>
       <c r="C1" s="3" t="s">
         <v>420</v>
       </c>
@@ -12421,7 +12624,9 @@
       <c r="A2" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B2" s="3"/>
+      <c r="B2" s="3" t="s">
+        <v>905</v>
+      </c>
       <c r="C2" s="3" t="s">
         <v>428</v>
       </c>
@@ -12473,7 +12678,9 @@
       <c r="A3" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="3"/>
+      <c r="B3" s="3" t="s">
+        <v>906</v>
+      </c>
       <c r="C3" s="3" t="s">
         <v>444</v>
       </c>
@@ -12525,7 +12732,9 @@
       <c r="A4" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B4" s="3"/>
+      <c r="B4" s="3" t="s">
+        <v>907</v>
+      </c>
       <c r="C4" s="3" t="s">
         <v>460</v>
       </c>
@@ -12577,7 +12786,9 @@
       <c r="A5" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>908</v>
+      </c>
       <c r="C5" s="3" t="s">
         <v>476</v>
       </c>
@@ -12629,7 +12840,9 @@
       <c r="A6" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B6" s="3"/>
+      <c r="B6" s="3" t="s">
+        <v>909</v>
+      </c>
       <c r="C6" s="3" t="s">
         <v>492</v>
       </c>
@@ -12681,7 +12894,9 @@
       <c r="A7" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B7" s="3"/>
+      <c r="B7" s="3" t="s">
+        <v>910</v>
+      </c>
       <c r="C7" s="3" t="s">
         <v>508</v>
       </c>
@@ -12733,7 +12948,9 @@
       <c r="A8" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B8" s="3"/>
+      <c r="B8" s="3" t="s">
+        <v>911</v>
+      </c>
       <c r="C8" s="3" t="s">
         <v>524</v>
       </c>
@@ -12785,7 +13002,9 @@
       <c r="A9" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B9" s="3"/>
+      <c r="B9" s="3" t="s">
+        <v>912</v>
+      </c>
       <c r="C9" s="3" t="s">
         <v>540</v>
       </c>
@@ -12837,9 +13056,11 @@
       <c r="A10" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="B10" s="3"/>
+      <c r="B10" s="3" t="s">
+        <v>913</v>
+      </c>
       <c r="C10" s="3" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>557</v>
@@ -12889,7 +13110,9 @@
       <c r="A11" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B11" s="3"/>
+      <c r="B11" s="3" t="s">
+        <v>914</v>
+      </c>
       <c r="C11" s="3" t="s">
         <v>571</v>
       </c>
@@ -12941,7 +13164,9 @@
       <c r="A12" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>915</v>
+      </c>
       <c r="C12" s="3" t="s">
         <v>587</v>
       </c>
@@ -12993,7 +13218,9 @@
       <c r="A13" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B13" s="3"/>
+      <c r="B13" s="3" t="s">
+        <v>916</v>
+      </c>
       <c r="C13" s="3" t="s">
         <v>603</v>
       </c>
@@ -13045,7 +13272,9 @@
       <c r="A14" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B14" s="3"/>
+      <c r="B14" s="3" t="s">
+        <v>917</v>
+      </c>
       <c r="C14" s="3" t="s">
         <v>619</v>
       </c>
@@ -13097,7 +13326,9 @@
       <c r="A15" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B15" s="3" t="s">
+        <v>918</v>
+      </c>
       <c r="C15" s="3" t="s">
         <v>635</v>
       </c>
@@ -13149,7 +13380,9 @@
       <c r="A16" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B16" s="3"/>
+      <c r="B16" s="3" t="s">
+        <v>919</v>
+      </c>
       <c r="C16" s="3" t="s">
         <v>651</v>
       </c>
@@ -13201,7 +13434,9 @@
       <c r="A17" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B17" s="3"/>
+      <c r="B17" s="3" t="s">
+        <v>920</v>
+      </c>
       <c r="C17" s="3" t="s">
         <v>667</v>
       </c>
@@ -13253,7 +13488,9 @@
       <c r="A18" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B18" s="3"/>
+      <c r="B18" s="3" t="s">
+        <v>921</v>
+      </c>
       <c r="C18" s="3" t="s">
         <v>683</v>
       </c>
@@ -13305,7 +13542,9 @@
       <c r="A19" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B19" s="3"/>
+      <c r="B19" s="3" t="s">
+        <v>922</v>
+      </c>
       <c r="C19" s="3" t="s">
         <v>653</v>
       </c>
@@ -13357,7 +13596,9 @@
       <c r="A20" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B20" s="3"/>
+      <c r="B20" s="3" t="s">
+        <v>923</v>
+      </c>
       <c r="C20" s="3" t="s">
         <v>714</v>
       </c>
@@ -13409,7 +13650,9 @@
       <c r="A21" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B21" s="3"/>
+      <c r="B21" s="3" t="s">
+        <v>924</v>
+      </c>
       <c r="C21" s="3" t="s">
         <v>730</v>
       </c>
@@ -13461,7 +13704,9 @@
       <c r="A22" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B22" s="3"/>
+      <c r="B22" s="3" t="s">
+        <v>925</v>
+      </c>
       <c r="C22" s="3" t="s">
         <v>746</v>
       </c>
@@ -13513,7 +13758,9 @@
       <c r="A23" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>926</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>762</v>
       </c>
@@ -13565,7 +13812,9 @@
       <c r="A24" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B24" s="3"/>
+      <c r="B24" s="3" t="s">
+        <v>927</v>
+      </c>
       <c r="C24" s="3" t="s">
         <v>778</v>
       </c>
@@ -13623,7 +13872,7 @@
   <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -13715,13 +13964,13 @@
         <v>403</v>
       </c>
       <c r="B4" t="s">
+        <v>953</v>
+      </c>
+      <c r="C4" t="s">
         <v>808</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>809</v>
-      </c>
-      <c r="D4" t="s">
-        <v>810</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13730,7 +13979,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13741,13 +13990,13 @@
         <v>422</v>
       </c>
       <c r="B5" t="s">
+        <v>811</v>
+      </c>
+      <c r="C5" t="s">
         <v>812</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>813</v>
-      </c>
-      <c r="D5" t="s">
-        <v>814</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13756,7 +14005,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -13767,13 +14016,13 @@
         <v>404</v>
       </c>
       <c r="B6" t="s">
-        <v>816</v>
+        <v>954</v>
       </c>
       <c r="C6" t="s">
         <v>801</v>
       </c>
       <c r="D6" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13782,7 +14031,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -13793,13 +14042,13 @@
         <v>408</v>
       </c>
       <c r="B7" t="s">
+        <v>817</v>
+      </c>
+      <c r="C7" t="s">
+        <v>818</v>
+      </c>
+      <c r="D7" t="s">
         <v>819</v>
-      </c>
-      <c r="C7" t="s">
-        <v>820</v>
-      </c>
-      <c r="D7" t="s">
-        <v>821</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13808,7 +14057,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -13819,13 +14068,13 @@
         <v>416</v>
       </c>
       <c r="B8" t="s">
-        <v>823</v>
+        <v>955</v>
       </c>
       <c r="C8" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D8" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13834,7 +14083,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -13845,13 +14094,13 @@
         <v>421</v>
       </c>
       <c r="B9" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C9" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D9" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13860,7 +14109,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -13871,13 +14120,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C10" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D10" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13886,7 +14135,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -13900,10 +14149,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D11" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13912,7 +14161,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -13923,13 +14172,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C12" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D12" t="s">
-        <v>814</v>
+        <v>959</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13938,7 +14187,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -13949,13 +14198,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C13" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D13" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13964,7 +14213,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -13972,74 +14221,94 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B14" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C14" t="s">
-        <v>846</v>
+        <v>956</v>
       </c>
       <c r="D14" t="s">
-        <v>847</v>
+        <v>960</v>
       </c>
       <c r="E14">
         <v>100000000</v>
       </c>
       <c r="F14" s="7">
-        <v>893000000</v>
+        <v>450000000</v>
       </c>
       <c r="G14" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="H14">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>420</v>
+        <v>928</v>
       </c>
       <c r="B15" t="s">
-        <v>849</v>
+        <v>951</v>
       </c>
       <c r="C15" t="s">
-        <v>850</v>
+        <v>957</v>
       </c>
       <c r="D15" t="s">
-        <v>851</v>
+        <v>961</v>
       </c>
       <c r="E15">
         <v>100000000</v>
       </c>
       <c r="F15" s="7">
-        <v>450000000</v>
+        <v>300000000</v>
       </c>
       <c r="G15" t="s">
-        <v>852</v>
+        <v>963</v>
       </c>
       <c r="H15">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F16" s="7"/>
+      <c r="A16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" t="s">
+        <v>844</v>
+      </c>
+      <c r="C16" t="s">
+        <v>845</v>
+      </c>
+      <c r="D16" t="s">
+        <v>846</v>
+      </c>
+      <c r="E16">
+        <v>100000000</v>
+      </c>
+      <c r="F16" s="7">
+        <v>300000000</v>
+      </c>
+      <c r="G16" t="s">
+        <v>847</v>
+      </c>
       <c r="H16">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>424</v>
       </c>
       <c r="B17" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C17" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="D17" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -14048,24 +14317,24 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="H17">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B18" t="s">
-        <v>857</v>
+        <v>952</v>
       </c>
       <c r="C18" t="s">
-        <v>858</v>
+        <v>958</v>
       </c>
       <c r="D18" t="s">
-        <v>859</v>
+        <v>962</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14074,10 +14343,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>860</v>
-      </c>
-      <c r="H18">
-        <v>17</v>
+        <v>964</v>
       </c>
     </row>
   </sheetData>
@@ -14105,30 +14371,30 @@
         <v>384</v>
       </c>
       <c r="B1" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="C1" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="D1" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="E1" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="F1" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="G1" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B2" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C2" t="s">
         <v>412</v>
@@ -14140,10 +14406,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G2" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -14151,7 +14417,7 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C3" t="s">
         <v>412</v>
@@ -14163,10 +14429,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G3" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -14174,7 +14440,7 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C4" t="s">
         <v>412</v>
@@ -14186,10 +14452,10 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G4" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -14197,30 +14463,30 @@
         <v>395</v>
       </c>
       <c r="B5" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C5" t="s">
         <v>412</v>
       </c>
       <c r="D5" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G5" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="B6" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C6" t="s">
         <v>412</v>
@@ -14232,18 +14498,18 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G6" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B7" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C7" t="s">
         <v>412</v>
@@ -14255,18 +14521,18 @@
         <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G7" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B8" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C8" t="s">
         <v>421</v>
@@ -14278,18 +14544,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G8" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="B9" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C9" t="s">
         <v>412</v>
@@ -14301,33 +14567,33 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G9" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B10" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C10" t="s">
         <v>423</v>
       </c>
       <c r="D10" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E10">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G10" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -14335,33 +14601,33 @@
         <v>395</v>
       </c>
       <c r="B11" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C11" t="s">
         <v>412</v>
       </c>
       <c r="D11" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G11" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="B12" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C12" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -14370,10 +14636,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G12" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -14381,10 +14647,10 @@
         <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C13" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D13" t="s">
         <v>407</v>
@@ -14393,21 +14659,21 @@
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G13" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B14" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C14" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D14" t="s">
         <v>410</v>
@@ -14416,41 +14682,41 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G14" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B15" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C15" t="s">
         <v>410</v>
       </c>
       <c r="D15" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G15" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="B16" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -14462,18 +14728,18 @@
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G16" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="B17" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -14485,18 +14751,18 @@
         <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G17" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B18" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C18" t="s">
         <v>407</v>
@@ -14508,10 +14774,10 @@
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G18" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -14519,10 +14785,10 @@
         <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C19" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D19" t="s">
         <v>421</v>
@@ -14531,21 +14797,21 @@
         <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G19" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="B20" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C20" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D20" t="s">
         <v>421</v>
@@ -14554,10 +14820,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G20" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -14565,68 +14831,68 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C21" t="s">
         <v>421</v>
       </c>
       <c r="D21" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G21" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="B22" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C22" t="s">
         <v>423</v>
       </c>
       <c r="D22" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="E22">
         <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G22" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="B23" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C23" t="s">
         <v>408</v>
       </c>
       <c r="D23" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G23" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -14634,10 +14900,10 @@
         <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C24" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D24" t="s">
         <v>408</v>
@@ -14646,10 +14912,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G24" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -14657,22 +14923,22 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C25" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="D25" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G25" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -14680,22 +14946,22 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C26" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D26" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G26" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -14703,7 +14969,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -14715,10 +14981,10 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G27" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -14726,7 +14992,7 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -14738,18 +15004,18 @@
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G28" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B29" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C29" t="s">
         <v>422</v>
@@ -14761,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G29" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -14772,7 +15038,7 @@
         <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -14784,10 +15050,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G30" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -14795,7 +15061,7 @@
         <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C31" t="s">
         <v>421</v>
@@ -14807,10 +15073,10 @@
         <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G31" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -14818,7 +15084,7 @@
         <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -14830,10 +15096,10 @@
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G32" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -14841,7 +15107,7 @@
         <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C33" t="s">
         <v>423</v>
@@ -14853,10 +15119,10 @@
         <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G33" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -14864,7 +15130,7 @@
         <v>333</v>
       </c>
       <c r="B34" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C34" t="s">
         <v>423</v>
@@ -14876,18 +15142,18 @@
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G34" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="B35" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -14899,18 +15165,18 @@
         <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G35" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="B36" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -14925,7 +15191,7 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -14933,7 +15199,7 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -14945,18 +15211,18 @@
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G37" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="B38" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="C38" t="s">
         <v>422</v>
@@ -14968,33 +15234,33 @@
         <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G38" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="B39" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C39" t="s">
         <v>410</v>
       </c>
       <c r="D39" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="E39">
         <v>5</v>
       </c>
       <c r="F39" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G39" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -15002,30 +15268,30 @@
         <v>330</v>
       </c>
       <c r="B40" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C40" t="s">
         <v>408</v>
       </c>
       <c r="D40" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="B41" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C41" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="D41" t="s">
         <v>408</v>
@@ -15034,7 +15300,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -15042,7 +15308,7 @@
         <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -15054,7 +15320,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -15062,7 +15328,7 @@
         <v>172</v>
       </c>
       <c r="B43" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -15074,15 +15340,15 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B44" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -15094,18 +15360,18 @@
         <v>30</v>
       </c>
       <c r="F44" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G44" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B45" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C45" t="s">
         <v>423</v>
@@ -15120,7 +15386,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -15128,7 +15394,7 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="C46" t="s">
         <v>423</v>
@@ -15143,7 +15409,7 @@
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -15151,7 +15417,7 @@
         <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -15163,10 +15429,10 @@
         <v>42</v>
       </c>
       <c r="F47" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G47" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -15174,7 +15440,7 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -15186,10 +15452,10 @@
         <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G48" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -15197,7 +15463,7 @@
         <v>247</v>
       </c>
       <c r="B49" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
@@ -15209,10 +15475,10 @@
         <v>31</v>
       </c>
       <c r="F49" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G49" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DFE5B2-0843-495A-A331-EBFE16A334DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F92B88D-B526-48E1-89A8-5AC569A2098D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -951,9 +951,6 @@
     <t>Martín Zubimendi</t>
   </si>
   <si>
-    <t xml:space="preserve">Reece James </t>
-  </si>
-  <si>
     <t>Conor Gallagher</t>
   </si>
   <si>
@@ -2980,6 +2977,9 @@
   </si>
   <si>
     <t>Logos Equipos/borussia.webp</t>
+  </si>
+  <si>
+    <t>PT Joan Garcia</t>
   </si>
 </sst>
 </file>
@@ -3408,16 +3408,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -3439,7 +3439,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C3" s="3">
         <v>10</v>
@@ -3467,7 +3467,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C5" s="3">
         <v>8</v>
@@ -3523,7 +3523,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C9" s="3">
         <v>6</v>
@@ -3537,7 +3537,7 @@
         <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C10" s="3">
         <v>6</v>
@@ -3605,7 +3605,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C15" s="3">
         <v>5</v>
@@ -3645,7 +3645,7 @@
         <v>7</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C18" s="3">
         <v>4</v>
@@ -3671,7 +3671,7 @@
         <v>2</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C20" s="3">
         <v>4</v>
@@ -3699,7 +3699,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C22" s="3">
         <v>4</v>
@@ -3741,7 +3741,7 @@
         <v>10</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C25" s="3">
         <v>3</v>
@@ -3755,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C26" s="6">
         <v>3</v>
@@ -3769,7 +3769,7 @@
         <v>3</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C27" s="6">
         <v>3</v>
@@ -3797,7 +3797,7 @@
         <v>9</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C29" s="3">
         <v>3</v>
@@ -3839,7 +3839,7 @@
         <v>12</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C32" s="3">
         <v>3</v>
@@ -3982,10 +3982,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="C43" s="6">
         <v>2</v>
@@ -4023,7 +4023,7 @@
         <v>6</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C46" s="3">
         <v>2</v>
@@ -4048,10 +4048,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C48" s="3">
         <v>2</v>
@@ -4169,7 +4169,7 @@
         <v>5</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C57" s="3">
         <v>1</v>
@@ -4183,7 +4183,7 @@
         <v>5</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C58" s="3">
         <v>1</v>
@@ -4207,7 +4207,7 @@
         <v>1</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -4219,7 +4219,7 @@
         <v>13</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C61" s="3">
         <v>1</v>
@@ -4233,7 +4233,7 @@
         <v>13</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C62" s="3">
         <v>1</v>
@@ -4247,7 +4247,7 @@
         <v>9</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C63" s="3">
         <v>1</v>
@@ -4261,7 +4261,7 @@
         <v>10</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C64" s="3">
         <v>1</v>
@@ -4275,7 +4275,7 @@
         <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C65" s="3">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>8</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C67" s="6">
         <v>1</v>
@@ -4315,7 +4315,7 @@
         <v>0</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C68" s="6">
         <v>1</v>
@@ -4441,7 +4441,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C78" s="3">
         <v>1</v>
@@ -4469,7 +4469,7 @@
         <v>12</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C80" s="3">
         <v>1</v>
@@ -4511,7 +4511,7 @@
         <v>2</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C83" s="3">
         <v>1</v>
@@ -4549,7 +4549,7 @@
         <v>10</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C86" s="3">
         <v>1</v>
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C87" s="3">
         <v>1</v>
@@ -4573,7 +4573,7 @@
         <v>9</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C88" s="3">
         <v>1</v>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C92" s="3">
         <v>1</v>
@@ -4635,7 +4635,7 @@
         <v>13</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C93" s="3">
         <v>1</v>
@@ -4668,10 +4668,10 @@
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -4680,10 +4680,10 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C97" s="6">
         <v>1</v>
@@ -4735,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C101" s="3"/>
       <c r="D101" s="3">
@@ -4759,7 +4759,7 @@
         <v>3</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C103" s="3"/>
       <c r="D103" s="3">
@@ -4771,7 +4771,7 @@
         <v>3</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C104" s="3"/>
       <c r="D104" s="3">
@@ -4783,7 +4783,7 @@
         <v>10</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C105" s="3"/>
       <c r="D105" s="3">
@@ -4795,7 +4795,7 @@
         <v>6</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C106" s="3"/>
       <c r="D106" s="3">
@@ -4879,7 +4879,7 @@
         <v>1</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C113" s="3"/>
       <c r="D113" s="3">
@@ -4927,7 +4927,7 @@
         <v>2</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3">
@@ -4951,7 +4951,7 @@
         <v>4</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3">
@@ -4963,7 +4963,7 @@
         <v>10</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="3">
@@ -4987,7 +4987,7 @@
         <v>13</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3">
@@ -5044,10 +5044,10 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3">
@@ -5773,7 +5773,7 @@
         <v>2</v>
       </c>
       <c r="B241" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C241" s="6"/>
       <c r="D241" s="6">
@@ -5809,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="B244" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C244" s="6"/>
       <c r="D244" s="6">
@@ -7677,21 +7677,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B1" t="s">
         <v>892</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>893</v>
-      </c>
-      <c r="C1" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>894</v>
+      </c>
+      <c r="B3" t="s">
         <v>895</v>
-      </c>
-      <c r="B3" t="s">
-        <v>896</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7710,10 +7710,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -7721,10 +7721,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B5" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7732,10 +7732,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B6" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -7743,10 +7743,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>898</v>
+      </c>
+      <c r="B7" t="s">
         <v>899</v>
-      </c>
-      <c r="B7" t="s">
-        <v>900</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -7754,10 +7754,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B8" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -7765,10 +7765,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B9" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -7776,10 +7776,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B10" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -7787,10 +7787,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -7798,10 +7798,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B12" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -7809,10 +7809,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B13" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B14" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7845,70 +7845,70 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1" t="s">
         <v>396</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>397</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>398</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>399</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>400</v>
-      </c>
-      <c r="F1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B2" t="s">
         <v>402</v>
-      </c>
-      <c r="B2" t="s">
-        <v>403</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" t="s">
         <v>406</v>
-      </c>
-      <c r="B3" t="s">
-        <v>407</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E3">
         <v>3</v>
       </c>
       <c r="F3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" t="s">
         <v>409</v>
-      </c>
-      <c r="B4" t="s">
-        <v>410</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -7920,15 +7920,15 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" t="s">
         <v>411</v>
-      </c>
-      <c r="B5" t="s">
-        <v>412</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7940,32 +7940,32 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -7980,12 +7980,12 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
@@ -7994,13 +7994,13 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E8">
         <v>4</v>
       </c>
       <c r="F8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -8019,70 +8019,70 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1" t="s">
         <v>396</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>397</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>398</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>399</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>400</v>
-      </c>
-      <c r="F1" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E3">
         <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -8094,12 +8094,12 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -8114,35 +8114,35 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B6" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C6" t="s">
+        <v>417</v>
+      </c>
+      <c r="D6" t="s">
+        <v>409</v>
+      </c>
+      <c r="E6" t="s">
         <v>418</v>
       </c>
-      <c r="D6" t="s">
-        <v>410</v>
-      </c>
-      <c r="E6" t="s">
-        <v>419</v>
-      </c>
       <c r="F6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -8154,15 +8154,15 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -8174,7 +8174,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -8195,16 +8195,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -9724,16 +9724,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -11269,7 +11269,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -11322,7 +11322,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -11375,7 +11375,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -11428,7 +11428,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -11481,7 +11481,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -11534,7 +11534,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -11587,7 +11587,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -11640,7 +11640,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -11693,7 +11693,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -11746,10 +11746,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -11799,7 +11799,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -11852,7 +11852,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -11905,7 +11905,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -11958,7 +11958,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -12011,7 +12011,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -12064,7 +12064,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -12117,7 +12117,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -12170,7 +12170,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -12223,317 +12223,317 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>873</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="O19" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="O19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>947</v>
-      </c>
-      <c r="C20" s="5" t="s">
+      <c r="D20" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="E20" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="F20" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="P20" s="3" t="s">
+      <c r="Q20" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>947</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>948</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>321</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>948</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>949</v>
-      </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="F22" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>349</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="N23" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="O23" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>949</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>950</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
         <v>368</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="F24" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="P24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>381</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>382</v>
       </c>
     </row>
   </sheetData>
@@ -12568,43 +12568,43 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>421</v>
-      </c>
       <c r="E1" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>423</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>424</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="N1" s="3" t="s">
         <v>12</v>
@@ -12616,1249 +12616,1249 @@
         <v>14</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="R1" s="3"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>457</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>458</v>
       </c>
       <c r="R3" s="3"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>473</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>474</v>
       </c>
       <c r="R4" s="3"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>490</v>
       </c>
       <c r="R5" s="3"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="O6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="P6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>505</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>506</v>
       </c>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>537</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>538</v>
       </c>
       <c r="R8" s="3"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>553</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>554</v>
       </c>
       <c r="R9" s="3"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="Q10" s="3" t="s">
         <v>555</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>913</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>556</v>
       </c>
       <c r="R10" s="3"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>914</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="Q11" s="3" t="s">
         <v>584</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>585</v>
       </c>
       <c r="R11" s="3"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>915</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="Q12" s="3" t="s">
         <v>600</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>601</v>
       </c>
       <c r="R12" s="3"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>916</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="N13" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="N13" s="3" t="s">
+      <c r="O13" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="Q13" s="3" t="s">
         <v>616</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>617</v>
       </c>
       <c r="R13" s="3"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>618</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>917</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>621</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>624</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="L14" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>632</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>633</v>
       </c>
       <c r="R14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>917</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>634</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>918</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>642</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="N15" s="3" t="s">
         <v>645</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="O15" s="3" t="s">
         <v>646</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>648</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>649</v>
       </c>
       <c r="R15" s="3"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>918</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>650</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>919</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>653</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>660</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="O16" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="P16" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="Q16" s="3" t="s">
         <v>664</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>665</v>
       </c>
       <c r="R16" s="3"/>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>919</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>920</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>667</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>674</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>675</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="N17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="O17" s="3" t="s">
+      <c r="P17" s="3" t="s">
         <v>679</v>
       </c>
-      <c r="P17" s="3" t="s">
+      <c r="Q17" s="3" t="s">
         <v>680</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>681</v>
       </c>
       <c r="R17" s="3"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>920</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>683</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>684</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>687</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>691</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="N18" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="N18" s="3" t="s">
+      <c r="O18" s="3" t="s">
         <v>694</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="Q18" s="3" t="s">
         <v>696</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>697</v>
       </c>
       <c r="R18" s="3"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>921</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>922</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="3" t="s">
         <v>708</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="O19" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="O19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="Q19" s="3" t="s">
         <v>711</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>712</v>
       </c>
       <c r="R19" s="3"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>922</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>923</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>715</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="O20" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="Q20" s="3" t="s">
         <v>727</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>728</v>
       </c>
       <c r="R20" s="3"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>923</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>924</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>731</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>733</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>735</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>736</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>737</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>740</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="O21" s="3" t="s">
         <v>741</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>742</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>743</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>744</v>
       </c>
       <c r="R21" s="3"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>744</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>925</v>
-      </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>747</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>749</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>750</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>752</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>754</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="O22" s="3" t="s">
         <v>757</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>758</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>760</v>
       </c>
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>761</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>926</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>762</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>763</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>764</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>765</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>766</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>767</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>768</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>769</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>770</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>771</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="N23" s="3" t="s">
         <v>772</v>
       </c>
-      <c r="N23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>773</v>
       </c>
-      <c r="O23" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>775</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>776</v>
       </c>
       <c r="R23" s="3"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>927</v>
-      </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>778</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>780</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>781</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>783</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>784</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>785</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>786</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>787</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3" t="s">
         <v>788</v>
       </c>
-      <c r="N24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>789</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>790</v>
       </c>
-      <c r="P24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>791</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>792</v>
       </c>
       <c r="R24" s="3"/>
     </row>
@@ -13883,42 +13883,42 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B1" t="s">
+        <v>792</v>
+      </c>
+      <c r="C1" t="s">
         <v>793</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>794</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>795</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>796</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>797</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>798</v>
-      </c>
-      <c r="H1" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B2" t="s">
+        <v>799</v>
+      </c>
+      <c r="C2" t="s">
         <v>800</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>801</v>
-      </c>
-      <c r="D2" t="s">
-        <v>802</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -13927,7 +13927,7 @@
         <v>1400000000</v>
       </c>
       <c r="G2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2">
         <v>9</v>
@@ -13935,16 +13935,16 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B3" t="s">
+        <v>803</v>
+      </c>
+      <c r="C3" t="s">
         <v>804</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>805</v>
-      </c>
-      <c r="D3" t="s">
-        <v>806</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13953,7 +13953,7 @@
         <v>68000000</v>
       </c>
       <c r="G3" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H3">
         <v>12</v>
@@ -13961,16 +13961,16 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C4" t="s">
+        <v>807</v>
+      </c>
+      <c r="D4" t="s">
         <v>808</v>
-      </c>
-      <c r="D4" t="s">
-        <v>809</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13979,7 +13979,7 @@
         <v>2575000000</v>
       </c>
       <c r="G4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H4">
         <v>6</v>
@@ -13987,16 +13987,16 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B5" t="s">
+        <v>810</v>
+      </c>
+      <c r="C5" t="s">
         <v>811</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>812</v>
-      </c>
-      <c r="D5" t="s">
-        <v>813</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -14005,7 +14005,7 @@
         <v>300000000</v>
       </c>
       <c r="G5" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H5">
         <v>14</v>
@@ -14013,16 +14013,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B6" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="C6" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D6" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -14031,7 +14031,7 @@
         <v>566000000</v>
       </c>
       <c r="G6" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -14039,16 +14039,16 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B7" t="s">
+        <v>816</v>
+      </c>
+      <c r="C7" t="s">
         <v>817</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>818</v>
-      </c>
-      <c r="D7" t="s">
-        <v>819</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -14057,7 +14057,7 @@
         <v>2152000000</v>
       </c>
       <c r="G7" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H7">
         <v>4</v>
@@ -14065,16 +14065,16 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="C8" t="s">
+        <v>820</v>
+      </c>
+      <c r="D8" t="s">
         <v>821</v>
-      </c>
-      <c r="D8" t="s">
-        <v>822</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -14083,7 +14083,7 @@
         <v>299000000</v>
       </c>
       <c r="G8" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H8">
         <v>11</v>
@@ -14091,16 +14091,16 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B9" t="s">
+        <v>823</v>
+      </c>
+      <c r="C9" t="s">
         <v>824</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>825</v>
-      </c>
-      <c r="D9" t="s">
-        <v>826</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -14109,7 +14109,7 @@
         <v>815000000</v>
       </c>
       <c r="G9" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H9">
         <v>10</v>
@@ -14120,13 +14120,13 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
+        <v>827</v>
+      </c>
+      <c r="C10" t="s">
         <v>828</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>829</v>
-      </c>
-      <c r="D10" t="s">
-        <v>830</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -14135,7 +14135,7 @@
         <v>358000000</v>
       </c>
       <c r="G10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H10">
         <v>7</v>
@@ -14149,10 +14149,10 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
+        <v>831</v>
+      </c>
+      <c r="D11" t="s">
         <v>832</v>
-      </c>
-      <c r="D11" t="s">
-        <v>833</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -14161,7 +14161,7 @@
         <v>1000000000</v>
       </c>
       <c r="G11" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H11">
         <v>3</v>
@@ -14172,13 +14172,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
+        <v>834</v>
+      </c>
+      <c r="C12" t="s">
         <v>835</v>
       </c>
-      <c r="C12" t="s">
-        <v>836</v>
-      </c>
       <c r="D12" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -14187,7 +14187,7 @@
         <v>300000000</v>
       </c>
       <c r="G12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -14198,13 +14198,13 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
+        <v>837</v>
+      </c>
+      <c r="C13" t="s">
         <v>838</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>839</v>
-      </c>
-      <c r="D13" t="s">
-        <v>840</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -14213,7 +14213,7 @@
         <v>2690000000</v>
       </c>
       <c r="G13" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -14221,16 +14221,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B14" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C14" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D14" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -14239,7 +14239,7 @@
         <v>450000000</v>
       </c>
       <c r="G14" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H14">
         <v>15</v>
@@ -14247,16 +14247,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B15" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C15" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="D15" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -14265,7 +14265,7 @@
         <v>300000000</v>
       </c>
       <c r="G15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H15">
         <v>13</v>
@@ -14276,13 +14276,13 @@
         <v>9</v>
       </c>
       <c r="B16" t="s">
+        <v>843</v>
+      </c>
+      <c r="C16" t="s">
         <v>844</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>845</v>
-      </c>
-      <c r="D16" t="s">
-        <v>846</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -14291,7 +14291,7 @@
         <v>300000000</v>
       </c>
       <c r="G16" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H16">
         <v>16</v>
@@ -14299,16 +14299,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B17" t="s">
+        <v>847</v>
+      </c>
+      <c r="C17" t="s">
         <v>848</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>849</v>
-      </c>
-      <c r="D17" t="s">
-        <v>850</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -14317,7 +14317,7 @@
         <v>300000000</v>
       </c>
       <c r="G17" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H17">
         <v>17</v>
@@ -14325,16 +14325,16 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="C18" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="D18" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14343,7 +14343,7 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
   </sheetData>
@@ -14368,36 +14368,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B1" t="s">
+        <v>851</v>
+      </c>
+      <c r="C1" t="s">
         <v>852</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>853</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>854</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>855</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>856</v>
-      </c>
-      <c r="G1" t="s">
-        <v>857</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B2" t="s">
         <v>858</v>
       </c>
-      <c r="B2" t="s">
-        <v>859</v>
-      </c>
       <c r="C2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D2" t="s">
         <v>14</v>
@@ -14406,10 +14406,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
+        <v>859</v>
+      </c>
+      <c r="G2" t="s">
         <v>860</v>
-      </c>
-      <c r="G2" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -14417,10 +14417,10 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
@@ -14429,10 +14429,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
+        <v>859</v>
+      </c>
+      <c r="G3" t="s">
         <v>860</v>
-      </c>
-      <c r="G3" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -14440,10 +14440,10 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -14452,182 +14452,182 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
+        <v>859</v>
+      </c>
+      <c r="G4" t="s">
         <v>860</v>
-      </c>
-      <c r="G4" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D5" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
+        <v>859</v>
+      </c>
+      <c r="G5" t="s">
         <v>860</v>
-      </c>
-      <c r="G5" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B6" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E6">
         <v>90</v>
       </c>
       <c r="F6" t="s">
+        <v>859</v>
+      </c>
+      <c r="G6" t="s">
         <v>860</v>
-      </c>
-      <c r="G6" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B7" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E7">
         <v>170</v>
       </c>
       <c r="F7" t="s">
+        <v>859</v>
+      </c>
+      <c r="G7" t="s">
         <v>860</v>
-      </c>
-      <c r="G7" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>864</v>
+      </c>
+      <c r="B8" t="s">
         <v>865</v>
       </c>
-      <c r="B8" t="s">
-        <v>866</v>
-      </c>
       <c r="C8" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D8" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B9" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D9" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>868</v>
+      </c>
+      <c r="B10" t="s">
         <v>869</v>
       </c>
-      <c r="B10" t="s">
-        <v>870</v>
-      </c>
       <c r="C10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E10">
         <v>68</v>
       </c>
       <c r="F10" t="s">
+        <v>859</v>
+      </c>
+      <c r="G10" t="s">
         <v>860</v>
-      </c>
-      <c r="G10" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D11" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
+        <v>859</v>
+      </c>
+      <c r="G11" t="s">
         <v>860</v>
-      </c>
-      <c r="G11" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="B12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -14636,10 +14636,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="s">
+        <v>859</v>
+      </c>
+      <c r="G12" t="s">
         <v>860</v>
-      </c>
-      <c r="G12" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -14647,137 +14647,137 @@
         <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C13" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D13" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E13">
         <v>90</v>
       </c>
       <c r="F13" t="s">
+        <v>859</v>
+      </c>
+      <c r="G13" t="s">
         <v>860</v>
-      </c>
-      <c r="G13" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B14" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C14" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="D14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E14">
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G14" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B15" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G15" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B16" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E16">
         <v>75</v>
       </c>
       <c r="F16" t="s">
+        <v>859</v>
+      </c>
+      <c r="G16" t="s">
         <v>860</v>
-      </c>
-      <c r="G16" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="B17" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E17">
         <v>60</v>
       </c>
       <c r="F17" t="s">
+        <v>859</v>
+      </c>
+      <c r="G17" t="s">
         <v>860</v>
-      </c>
-      <c r="G17" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C18" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D18" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E18">
         <v>20</v>
       </c>
       <c r="F18" t="s">
+        <v>859</v>
+      </c>
+      <c r="G18" t="s">
         <v>860</v>
-      </c>
-      <c r="G18" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -14785,45 +14785,45 @@
         <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C19" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D19" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E19">
         <v>130</v>
       </c>
       <c r="F19" t="s">
+        <v>859</v>
+      </c>
+      <c r="G19" t="s">
         <v>860</v>
-      </c>
-      <c r="G19" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B20" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C20" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D20" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E20">
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G20" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -14831,68 +14831,68 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C21" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G21" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B22" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C22" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E22">
         <v>136</v>
       </c>
       <c r="F22" t="s">
+        <v>859</v>
+      </c>
+      <c r="G22" t="s">
         <v>860</v>
-      </c>
-      <c r="G22" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B23" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C23" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D23" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G23" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -14900,22 +14900,22 @@
         <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C24" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D24" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G24" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -14923,22 +14923,22 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C25" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D25" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G25" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -14946,22 +14946,22 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C26" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="D26" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G26" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -14969,7 +14969,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -14981,10 +14981,10 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
+        <v>859</v>
+      </c>
+      <c r="G27" t="s">
         <v>860</v>
-      </c>
-      <c r="G27" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -14992,33 +14992,33 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
       </c>
       <c r="D28" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E28">
         <v>25</v>
       </c>
       <c r="F28" t="s">
+        <v>859</v>
+      </c>
+      <c r="G28" t="s">
         <v>860</v>
-      </c>
-      <c r="G28" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B29" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C29" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G29" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -15038,22 +15038,22 @@
         <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
       </c>
       <c r="D30" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E30">
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G30" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -15061,22 +15061,22 @@
         <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C31" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D31" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E31">
         <v>80</v>
       </c>
       <c r="F31" t="s">
+        <v>859</v>
+      </c>
+      <c r="G31" t="s">
         <v>860</v>
-      </c>
-      <c r="G31" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -15084,22 +15084,22 @@
         <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E32">
         <v>20</v>
       </c>
       <c r="F32" t="s">
+        <v>859</v>
+      </c>
+      <c r="G32" t="s">
         <v>860</v>
-      </c>
-      <c r="G32" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -15107,33 +15107,33 @@
         <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C33" t="s">
+        <v>422</v>
+      </c>
+      <c r="D33" t="s">
         <v>423</v>
-      </c>
-      <c r="D33" t="s">
-        <v>424</v>
       </c>
       <c r="E33">
         <v>20</v>
       </c>
       <c r="F33" t="s">
+        <v>859</v>
+      </c>
+      <c r="G33" t="s">
         <v>860</v>
-      </c>
-      <c r="G33" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C34" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D34" t="s">
         <v>14</v>
@@ -15142,47 +15142,47 @@
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G34" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B35" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E35">
         <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G35" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>883</v>
+      </c>
+      <c r="B36" t="s">
         <v>884</v>
-      </c>
-      <c r="B36" t="s">
-        <v>885</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E36">
         <v>60</v>
@@ -15191,7 +15191,7 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -15199,33 +15199,33 @@
         <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E37">
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G37" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B38" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C38" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -15234,73 +15234,73 @@
         <v>20</v>
       </c>
       <c r="F38" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G38" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B39" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D39" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E39">
         <v>5</v>
       </c>
       <c r="F39" t="s">
+        <v>859</v>
+      </c>
+      <c r="G39" t="s">
         <v>860</v>
-      </c>
-      <c r="G39" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C40" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D40" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F40">
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B41" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C41" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D41" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F41">
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -15308,7 +15308,7 @@
         <v>156</v>
       </c>
       <c r="B42" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -15320,7 +15320,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -15328,7 +15328,7 @@
         <v>172</v>
       </c>
       <c r="B43" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C43" t="s">
         <v>12</v>
@@ -15340,41 +15340,41 @@
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B44" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
       </c>
       <c r="D44" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E44">
         <v>30</v>
       </c>
       <c r="F44" t="s">
+        <v>859</v>
+      </c>
+      <c r="G44" t="s">
         <v>860</v>
-      </c>
-      <c r="G44" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B45" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C45" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D45" t="s">
         <v>13</v>
@@ -15386,7 +15386,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -15394,10 +15394,10 @@
         <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C46" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -15409,7 +15409,7 @@
         <v>2</v>
       </c>
       <c r="G46" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -15417,22 +15417,22 @@
         <v>120</v>
       </c>
       <c r="B47" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E47">
         <v>42</v>
       </c>
       <c r="F47" t="s">
+        <v>859</v>
+      </c>
+      <c r="G47" t="s">
         <v>860</v>
-      </c>
-      <c r="G47" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -15440,22 +15440,22 @@
         <v>40</v>
       </c>
       <c r="B48" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E48">
         <v>31</v>
       </c>
       <c r="F48" t="s">
+        <v>859</v>
+      </c>
+      <c r="G48" t="s">
         <v>860</v>
-      </c>
-      <c r="G48" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -15463,22 +15463,22 @@
         <v>247</v>
       </c>
       <c r="B49" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E49">
         <v>31</v>
       </c>
       <c r="F49" t="s">
+        <v>859</v>
+      </c>
+      <c r="G49" t="s">
         <v>860</v>
-      </c>
-      <c r="G49" t="s">
-        <v>861</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F92B88D-B526-48E1-89A8-5AC569A2098D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0460BFF-051A-46B3-8243-6A084974CEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -80,12 +80,25 @@
     <definedName name="Wrexham" localSheetId="5">BD!$P$2:$P$24</definedName>
     <definedName name="WREXHAM">Lista!$R$2:$R$1048576</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="966">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -2980,13 +2993,16 @@
   </si>
   <si>
     <t>PT Joan Garcia</t>
+  </si>
+  <si>
+    <t>Como_1907</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3004,6 +3020,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3397,13 +3419,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D694"/>
+  <dimension ref="A1:D260"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.21875" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -3428,10 +3450,10 @@
         <v>165</v>
       </c>
       <c r="C2" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -3442,10 +3464,10 @@
         <v>359</v>
       </c>
       <c r="C3" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -3456,7 +3478,7 @@
         <v>199</v>
       </c>
       <c r="C4" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -3470,7 +3492,7 @@
         <v>364</v>
       </c>
       <c r="C5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
         <v>2</v>
@@ -3478,13 +3500,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>188</v>
       </c>
       <c r="C6" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D6" s="3">
         <v>1</v>
@@ -3497,10 +3519,10 @@
       <c r="B7" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <v>7</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>2</v>
       </c>
     </row>
@@ -3554,7 +3576,7 @@
         <v>167</v>
       </c>
       <c r="C11" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11" s="3">
         <v>1</v>
@@ -3567,10 +3589,10 @@
       <c r="B12" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="6"/>
+      <c r="C12" s="3">
+        <v>7</v>
+      </c>
+      <c r="D12" s="3"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -3580,7 +3602,7 @@
         <v>156</v>
       </c>
       <c r="C13" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -3594,7 +3616,7 @@
         <v>189</v>
       </c>
       <c r="C14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -3611,7 +3633,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -3633,11 +3655,11 @@
       <c r="B17" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="6">
-        <v>4</v>
+      <c r="C17" s="3">
+        <v>5</v>
       </c>
       <c r="D17" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -3648,13 +3670,15 @@
         <v>357</v>
       </c>
       <c r="C18" s="3">
-        <v>4</v>
-      </c>
-      <c r="D18" s="3"/>
+        <v>5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>125</v>
@@ -3674,7 +3698,7 @@
         <v>368</v>
       </c>
       <c r="C20" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="3">
         <v>3</v>
@@ -3688,10 +3712,10 @@
         <v>175</v>
       </c>
       <c r="C21" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D21" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -3702,7 +3726,7 @@
         <v>380</v>
       </c>
       <c r="C22" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D22" s="3">
         <v>1</v>
@@ -3716,10 +3740,10 @@
         <v>171</v>
       </c>
       <c r="C23" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D23" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -3730,10 +3754,10 @@
         <v>182</v>
       </c>
       <c r="C24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D24" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -3757,10 +3781,10 @@
       <c r="B26" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="3">
         <v>3</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="3">
         <v>2</v>
       </c>
     </row>
@@ -3771,10 +3795,10 @@
       <c r="B27" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="3">
         <v>3</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="3">
         <v>2</v>
       </c>
     </row>
@@ -3786,7 +3810,7 @@
         <v>142</v>
       </c>
       <c r="C28" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -3800,21 +3824,21 @@
         <v>327</v>
       </c>
       <c r="C29" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>172</v>
       </c>
       <c r="C30" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D30" s="3">
         <v>1</v>
@@ -3822,16 +3846,16 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>141</v>
       </c>
       <c r="C31" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D31" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -3896,7 +3920,9 @@
       <c r="C36" s="3">
         <v>2</v>
       </c>
-      <c r="D36" s="3"/>
+      <c r="D36" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
@@ -3905,11 +3931,11 @@
       <c r="B37" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C37" s="6">
-        <v>2</v>
-      </c>
-      <c r="D37" s="6">
-        <v>1</v>
+      <c r="C37" s="3">
+        <v>3</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -3923,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="D38" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -3937,7 +3963,7 @@
         <v>2</v>
       </c>
       <c r="D39" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -3987,10 +4013,10 @@
       <c r="B43" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C43" s="6">
+      <c r="C43" s="3">
         <v>2</v>
       </c>
-      <c r="D43" s="6"/>
+      <c r="D43" s="3"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
@@ -3999,11 +4025,11 @@
       <c r="B44" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C44" s="6">
+      <c r="C44" s="3">
         <v>2</v>
       </c>
-      <c r="D44" s="6">
-        <v>1</v>
+      <c r="D44" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4029,7 +4055,7 @@
         <v>2</v>
       </c>
       <c r="D46" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -4067,7 +4093,7 @@
       <c r="B49" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C49" s="6">
+      <c r="C49" s="3">
         <v>2</v>
       </c>
       <c r="D49" s="3">
@@ -4082,10 +4108,10 @@
         <v>168</v>
       </c>
       <c r="C50" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -4108,7 +4134,7 @@
         <v>162</v>
       </c>
       <c r="C52" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D52" s="3">
         <v>1</v>
@@ -4197,7 +4223,7 @@
       <c r="B59" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C59" s="6">
+      <c r="C59" s="3">
         <v>1</v>
       </c>
       <c r="D59" s="3"/>
@@ -4216,21 +4242,21 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>299</v>
       </c>
       <c r="C61" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>363</v>
@@ -4303,10 +4329,10 @@
       <c r="B67" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C67" s="6">
-        <v>1</v>
-      </c>
-      <c r="D67" s="6">
+      <c r="C67" s="3">
+        <v>2</v>
+      </c>
+      <c r="D67" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4317,22 +4343,22 @@
       <c r="B68" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="C68" s="6">
-        <v>1</v>
-      </c>
-      <c r="D68" s="6"/>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C69" s="6">
-        <v>1</v>
-      </c>
-      <c r="D69" s="6"/>
+      <c r="C69" s="3">
+        <v>1</v>
+      </c>
+      <c r="D69" s="3"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
@@ -4341,10 +4367,10 @@
       <c r="B70" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C70" s="6">
-        <v>1</v>
-      </c>
-      <c r="D70" s="6"/>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
@@ -4353,10 +4379,10 @@
       <c r="B71" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C71" s="6">
-        <v>1</v>
-      </c>
-      <c r="D71" s="6">
+      <c r="C71" s="3">
+        <v>1</v>
+      </c>
+      <c r="D71" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4367,10 +4393,10 @@
       <c r="B72" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C72" s="6">
-        <v>1</v>
-      </c>
-      <c r="D72" s="6"/>
+      <c r="C72" s="3">
+        <v>1</v>
+      </c>
+      <c r="D72" s="3"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
@@ -4379,10 +4405,10 @@
       <c r="B73" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C73" s="6">
-        <v>1</v>
-      </c>
-      <c r="D73" s="6">
+      <c r="C73" s="3">
+        <v>1</v>
+      </c>
+      <c r="D73" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4393,10 +4419,10 @@
       <c r="B74" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C74" s="6">
-        <v>1</v>
-      </c>
-      <c r="D74" s="6"/>
+      <c r="C74" s="3">
+        <v>1</v>
+      </c>
+      <c r="D74" s="3"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
@@ -4405,10 +4431,10 @@
       <c r="B75" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C75" s="6">
-        <v>1</v>
-      </c>
-      <c r="D75" s="6"/>
+      <c r="C75" s="3">
+        <v>1</v>
+      </c>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
@@ -4417,10 +4443,10 @@
       <c r="B76" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C76" s="6">
-        <v>1</v>
-      </c>
-      <c r="D76" s="6"/>
+      <c r="C76" s="3">
+        <v>1</v>
+      </c>
+      <c r="D76" s="3"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
@@ -4429,10 +4455,10 @@
       <c r="B77" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C77" s="6">
-        <v>1</v>
-      </c>
-      <c r="D77" s="6">
+      <c r="C77" s="3">
+        <v>1</v>
+      </c>
+      <c r="D77" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4444,23 +4470,23 @@
         <v>332</v>
       </c>
       <c r="C78" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="6">
-        <v>1</v>
-      </c>
-      <c r="D79" s="6">
+      <c r="C79" s="3">
+        <v>2</v>
+      </c>
+      <c r="D79" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4485,10 +4511,10 @@
       <c r="B81" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C81" s="6">
-        <v>1</v>
-      </c>
-      <c r="D81" s="6">
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4500,7 +4526,7 @@
         <v>103</v>
       </c>
       <c r="C82" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D82" s="3">
         <v>1</v>
@@ -4540,9 +4566,11 @@
         <v>159</v>
       </c>
       <c r="C85" s="3">
-        <v>1</v>
-      </c>
-      <c r="D85" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
@@ -4632,7 +4660,7 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>315</v>
@@ -4644,7 +4672,7 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>45</v>
@@ -4685,10 +4713,10 @@
       <c r="B97" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="C97" s="6">
-        <v>1</v>
-      </c>
-      <c r="D97" s="6">
+      <c r="C97" s="3">
+        <v>1</v>
+      </c>
+      <c r="D97" s="3">
         <v>3</v>
       </c>
     </row>
@@ -4699,10 +4727,10 @@
       <c r="B98" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="C98" s="6">
-        <v>1</v>
-      </c>
-      <c r="D98" s="6">
+      <c r="C98" s="3">
+        <v>1</v>
+      </c>
+      <c r="D98" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4737,7 +4765,9 @@
       <c r="B101" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="C101" s="3"/>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
       <c r="D101" s="3">
         <v>4</v>
       </c>
@@ -4797,7 +4827,9 @@
       <c r="B106" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C106" s="3"/>
+      <c r="C106" s="3">
+        <v>1</v>
+      </c>
       <c r="D106" s="3">
         <v>2</v>
       </c>
@@ -4821,8 +4853,10 @@
       <c r="B108" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6">
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3">
         <v>1</v>
       </c>
     </row>
@@ -4888,7 +4922,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>109</v>
@@ -4931,7 +4965,7 @@
       </c>
       <c r="C117" s="3"/>
       <c r="D117" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
@@ -4965,7 +4999,7 @@
       <c r="B120" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="3"/>
       <c r="D120" s="3">
         <v>2</v>
       </c>
@@ -4984,7 +5018,7 @@
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>379</v>
@@ -5091,106 +5125,208 @@
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
+      <c r="A131" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B131" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
+      <c r="D131" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
+      <c r="A132" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B132" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C132" s="3">
+        <v>1</v>
+      </c>
       <c r="D132" s="3"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
+      <c r="A133" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B133" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
+      <c r="D133" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
+      <c r="A134" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B134" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="C134" s="3"/>
-      <c r="D134" s="3"/>
+      <c r="D134" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
+      <c r="A135" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B135" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="C135" s="3"/>
-      <c r="D135" s="3"/>
+      <c r="D135" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
+      <c r="A136" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="C136" s="3"/>
-      <c r="D136" s="3"/>
+      <c r="D136" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
-      <c r="C137" s="3"/>
+      <c r="A137" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C137" s="3">
+        <v>1</v>
+      </c>
       <c r="D137" s="3"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
+      <c r="A138" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="C138" s="3"/>
-      <c r="D138" s="3"/>
+      <c r="D138" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
+      <c r="A139" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="C139" s="3"/>
-      <c r="D139" s="3"/>
+      <c r="D139" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
+      <c r="A140" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
+      <c r="D140" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
-      <c r="C141" s="3"/>
+      <c r="A141" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="C141" s="3">
+        <v>1</v>
+      </c>
       <c r="D141" s="3"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
-      <c r="C142" s="3"/>
+      <c r="A142" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" s="3">
+        <v>1</v>
+      </c>
       <c r="D142" s="3"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
-      <c r="C143" s="3"/>
+      <c r="A143" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C143" s="3">
+        <v>1</v>
+      </c>
       <c r="D143" s="3"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
+      <c r="A144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="C144" s="3"/>
-      <c r="D144" s="3"/>
+      <c r="D144" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
-      <c r="C145" s="6"/>
+      <c r="A145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C145" s="3">
+        <v>1</v>
+      </c>
       <c r="D145" s="3"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
-      <c r="C146" s="6"/>
+      <c r="A146" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C146" s="3">
+        <v>1</v>
+      </c>
       <c r="D146" s="3"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
+      <c r="A147" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B147" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
@@ -5292,7 +5428,7 @@
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
-      <c r="D164" s="6"/>
+      <c r="D164" s="3"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3"/>
@@ -5370,37 +5506,37 @@
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
-      <c r="D177" s="6"/>
+      <c r="D177" s="3"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
-      <c r="D178" s="6"/>
+      <c r="D178" s="3"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
-      <c r="C179" s="6"/>
+      <c r="C179" s="3"/>
       <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
-      <c r="D182" s="6"/>
+      <c r="D182" s="3"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
@@ -5411,20 +5547,20 @@
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
@@ -5441,8 +5577,8 @@
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>
@@ -5501,26 +5637,26 @@
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" s="3"/>
@@ -5585,162 +5721,162 @@
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
-      <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
-      <c r="C220" s="6"/>
-      <c r="D220" s="6"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
-      <c r="C221" s="6"/>
-      <c r="D221" s="6"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
-      <c r="C222" s="6"/>
-      <c r="D222" s="6"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
-      <c r="C223" s="6"/>
-      <c r="D223" s="6"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
-      <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
-      <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
-      <c r="C226" s="6"/>
-      <c r="D226" s="6"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
-      <c r="C227" s="6"/>
-      <c r="D227" s="6"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
-      <c r="C228" s="6"/>
-      <c r="D228" s="6"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
-      <c r="C229" s="6"/>
-      <c r="D229" s="6"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
-      <c r="C230" s="6"/>
-      <c r="D230" s="6"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
-      <c r="C231" s="6"/>
-      <c r="D231" s="6"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
-      <c r="C232" s="6"/>
-      <c r="D232" s="6"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
-      <c r="C233" s="6"/>
-      <c r="D233" s="6"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="6"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
-      <c r="C235" s="6"/>
-      <c r="D235" s="6"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
-      <c r="C236" s="6"/>
-      <c r="D236" s="6"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
-      <c r="C237" s="6"/>
-      <c r="D237" s="6"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="B238" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C238" s="6"/>
-      <c r="D238" s="6">
+      <c r="C238" s="3"/>
+      <c r="D238" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5751,8 +5887,8 @@
       <c r="B239" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C239" s="6"/>
-      <c r="D239" s="6">
+      <c r="C239" s="3"/>
+      <c r="D239" s="3">
         <v>2</v>
       </c>
     </row>
@@ -5763,8 +5899,10 @@
       <c r="B240" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C240" s="6"/>
-      <c r="D240" s="6">
+      <c r="C240" s="3">
+        <v>1</v>
+      </c>
+      <c r="D240" s="3">
         <v>2</v>
       </c>
     </row>
@@ -5775,8 +5913,8 @@
       <c r="B241" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="C241" s="6"/>
-      <c r="D241" s="6">
+      <c r="C241" s="3"/>
+      <c r="D241" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5787,9 +5925,11 @@
       <c r="B242" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="C242" s="6"/>
-      <c r="D242" s="6">
-        <v>1</v>
+      <c r="C242" s="3">
+        <v>1</v>
+      </c>
+      <c r="D242" s="3">
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
@@ -5799,8 +5939,8 @@
       <c r="B243" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6">
+      <c r="C243" s="3"/>
+      <c r="D243" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5811,8 +5951,8 @@
       <c r="B244" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="C244" s="6"/>
-      <c r="D244" s="6">
+      <c r="C244" s="3"/>
+      <c r="D244" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5823,8 +5963,8 @@
       <c r="B245" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C245" s="6"/>
-      <c r="D245" s="6">
+      <c r="C245" s="3"/>
+      <c r="D245" s="3">
         <v>2</v>
       </c>
     </row>
@@ -5835,1830 +5975,94 @@
       <c r="B246" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C246" s="6"/>
-      <c r="D246" s="6">
+      <c r="C246" s="3"/>
+      <c r="D246" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
-      <c r="C247" s="6"/>
-      <c r="D247" s="6"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
-      <c r="C248" s="6"/>
-      <c r="D248" s="6"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
-      <c r="C249" s="6"/>
-      <c r="D249" s="6"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
-      <c r="C250" s="6"/>
-      <c r="D250" s="6"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
-      <c r="C251" s="6"/>
-      <c r="D251" s="6"/>
+      <c r="C251" s="3"/>
+      <c r="D251" s="3"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
-      <c r="C252" s="6"/>
-      <c r="D252" s="6"/>
+      <c r="C252" s="3"/>
+      <c r="D252" s="3"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
-      <c r="C253" s="6"/>
-      <c r="D253" s="6"/>
+      <c r="C253" s="3"/>
+      <c r="D253" s="3"/>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
-      <c r="C254" s="6"/>
-      <c r="D254" s="6"/>
+      <c r="C254" s="3"/>
+      <c r="D254" s="3"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
-      <c r="C255" s="6"/>
-      <c r="D255" s="6"/>
+      <c r="C255" s="3"/>
+      <c r="D255" s="3"/>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
-      <c r="C256" s="6"/>
-      <c r="D256" s="6"/>
+      <c r="C256" s="3"/>
+      <c r="D256" s="3"/>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
-      <c r="C257" s="6"/>
-      <c r="D257" s="6"/>
+      <c r="C257" s="3"/>
+      <c r="D257" s="3"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
-      <c r="C258" s="6"/>
-      <c r="D258" s="6"/>
+      <c r="C258" s="3"/>
+      <c r="D258" s="3"/>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
-      <c r="C259" s="6"/>
-      <c r="D259" s="6"/>
+      <c r="C259" s="3"/>
+      <c r="D259" s="3"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
-      <c r="C260" s="6"/>
-      <c r="D260" s="6"/>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A261" s="1"/>
-      <c r="B261" s="1"/>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A262" s="1"/>
-      <c r="B262" s="1"/>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A263" s="1"/>
-      <c r="B263" s="1"/>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A264" s="1"/>
-      <c r="B264" s="1"/>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A265" s="1"/>
-      <c r="B265" s="1"/>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A266" s="1"/>
-      <c r="B266" s="1"/>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A267" s="1"/>
-      <c r="B267" s="1"/>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A268" s="1"/>
-      <c r="B268" s="1"/>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A269" s="1"/>
-      <c r="B269" s="1"/>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A270" s="1"/>
-      <c r="B270" s="1"/>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A271" s="1"/>
-      <c r="B271" s="1"/>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273" s="1"/>
-      <c r="B273" s="1"/>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274" s="1"/>
-      <c r="B274" s="1"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275" s="1"/>
-      <c r="B275" s="1"/>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276" s="1"/>
-      <c r="B276" s="1"/>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278" s="1"/>
-      <c r="B278" s="1"/>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279" s="1"/>
-      <c r="B279" s="1"/>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280" s="1"/>
-      <c r="B280" s="1"/>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281" s="1"/>
-      <c r="B281" s="1"/>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282" s="1"/>
-      <c r="B282" s="1"/>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283" s="1"/>
-      <c r="B283" s="1"/>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284" s="1"/>
-      <c r="B284" s="1"/>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285" s="1"/>
-      <c r="B285" s="1"/>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286" s="1"/>
-      <c r="B286" s="1"/>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287" s="1"/>
-      <c r="B287" s="1"/>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288" s="1"/>
-      <c r="B288" s="1"/>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289" s="1"/>
-      <c r="B289" s="1"/>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290" s="1"/>
-      <c r="B290" s="1"/>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291" s="1"/>
-      <c r="B291" s="1"/>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292" s="1"/>
-      <c r="B292" s="1"/>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293" s="1"/>
-      <c r="B293" s="1"/>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295" s="1"/>
-      <c r="B295" s="1"/>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296" s="1"/>
-      <c r="B296" s="1"/>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A298" s="1"/>
-      <c r="B298" s="1"/>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A299" s="1"/>
-      <c r="B299" s="1"/>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A300" s="1"/>
-      <c r="B300" s="1"/>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A301" s="1"/>
-      <c r="B301" s="1"/>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A302" s="1"/>
-      <c r="B302" s="1"/>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A303" s="1"/>
-      <c r="B303" s="1"/>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A304" s="1"/>
-      <c r="B304" s="1"/>
-    </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A305" s="1"/>
-      <c r="B305" s="1"/>
-    </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A306" s="1"/>
-      <c r="B306" s="1"/>
-    </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A307" s="1"/>
-      <c r="B307" s="1"/>
-    </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A308" s="1"/>
-      <c r="B308" s="1"/>
-    </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A309" s="1"/>
-      <c r="B309" s="1"/>
-    </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A310" s="1"/>
-      <c r="B310" s="1"/>
-    </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A311" s="1"/>
-      <c r="B311" s="1"/>
-    </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A312" s="1"/>
-      <c r="B312" s="1"/>
-    </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A313" s="1"/>
-      <c r="B313" s="1"/>
-    </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A314" s="1"/>
-      <c r="B314" s="1"/>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A315" s="1"/>
-      <c r="B315" s="1"/>
-    </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A316" s="1"/>
-      <c r="B316" s="1"/>
-    </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A317" s="1"/>
-      <c r="B317" s="1"/>
-    </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A318" s="1"/>
-      <c r="B318" s="1"/>
-    </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A319" s="1"/>
-      <c r="B319" s="1"/>
-    </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A320" s="1"/>
-      <c r="B320" s="1"/>
-    </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A321" s="1"/>
-      <c r="B321" s="1"/>
-    </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A322" s="1"/>
-      <c r="B322" s="1"/>
-    </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
-    </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A324" s="1"/>
-      <c r="B324" s="1"/>
-    </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A325" s="1"/>
-      <c r="B325" s="1"/>
-    </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A326" s="1"/>
-      <c r="B326" s="1"/>
-    </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A327" s="1"/>
-      <c r="B327" s="1"/>
-    </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A328" s="1"/>
-      <c r="B328" s="1"/>
-    </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
-    </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
-    </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
-    </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A332" s="1"/>
-      <c r="B332" s="1"/>
-    </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
-    </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A334" s="1"/>
-      <c r="B334" s="1"/>
-    </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A335" s="1"/>
-      <c r="B335" s="1"/>
-    </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A336" s="1"/>
-      <c r="B336" s="1"/>
-    </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A337" s="1"/>
-      <c r="B337" s="1"/>
-    </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A338" s="1"/>
-      <c r="B338" s="1"/>
-    </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A339" s="1"/>
-      <c r="B339" s="1"/>
-    </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A340" s="1"/>
-      <c r="B340" s="1"/>
-    </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A341" s="1"/>
-      <c r="B341" s="1"/>
-    </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A342" s="1"/>
-      <c r="B342" s="1"/>
-    </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A343" s="1"/>
-      <c r="B343" s="1"/>
-    </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A344" s="1"/>
-      <c r="B344" s="1"/>
-    </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A345" s="1"/>
-      <c r="B345" s="1"/>
-    </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A346" s="1"/>
-      <c r="B346" s="1"/>
-    </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A347" s="1"/>
-      <c r="B347" s="1"/>
-    </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A348" s="1"/>
-      <c r="B348" s="1"/>
-    </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A349" s="1"/>
-      <c r="B349" s="1"/>
-    </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A350" s="1"/>
-      <c r="B350" s="1"/>
-    </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A351" s="1"/>
-      <c r="B351" s="1"/>
-    </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A352" s="1"/>
-      <c r="B352" s="1"/>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353" s="1"/>
-      <c r="B353" s="1"/>
-    </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A354" s="1"/>
-      <c r="B354" s="1"/>
-    </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A355" s="1"/>
-      <c r="B355" s="1"/>
-    </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A356" s="1"/>
-      <c r="B356" s="1"/>
-    </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A357" s="1"/>
-      <c r="B357" s="1"/>
-    </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A358" s="1"/>
-      <c r="B358" s="1"/>
-    </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A359" s="1"/>
-      <c r="B359" s="1"/>
-    </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A360" s="1"/>
-      <c r="B360" s="1"/>
-    </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A361" s="1"/>
-      <c r="B361" s="1"/>
-    </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A362" s="1"/>
-      <c r="B362" s="1"/>
-    </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A363" s="1"/>
-      <c r="B363" s="1"/>
-    </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A364" s="1"/>
-      <c r="B364" s="1"/>
-    </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
-    </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A366" s="1"/>
-      <c r="B366" s="1"/>
-    </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A367" s="1"/>
-      <c r="B367" s="1"/>
-    </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A368" s="1"/>
-      <c r="B368" s="1"/>
-    </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A369" s="1"/>
-      <c r="B369" s="1"/>
-    </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A370" s="1"/>
-      <c r="B370" s="1"/>
-    </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
-    </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
-    </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
-    </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
-    </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
-    </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A376" s="1"/>
-      <c r="B376" s="1"/>
-    </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A377" s="1"/>
-      <c r="B377" s="1"/>
-    </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A378" s="1"/>
-      <c r="B378" s="1"/>
-    </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A379" s="1"/>
-      <c r="B379" s="1"/>
-    </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A380" s="1"/>
-      <c r="B380" s="1"/>
-    </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A381" s="1"/>
-      <c r="B381" s="1"/>
-    </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A382" s="1"/>
-      <c r="B382" s="1"/>
-    </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A383" s="1"/>
-      <c r="B383" s="1"/>
-    </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A384" s="1"/>
-      <c r="B384" s="1"/>
-    </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A385" s="1"/>
-      <c r="B385" s="1"/>
-    </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A386" s="1"/>
-      <c r="B386" s="1"/>
-    </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A387" s="1"/>
-      <c r="B387" s="1"/>
-    </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A388" s="1"/>
-      <c r="B388" s="1"/>
-    </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A389" s="1"/>
-      <c r="B389" s="1"/>
-    </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A390" s="1"/>
-      <c r="B390" s="1"/>
-    </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A391" s="1"/>
-      <c r="B391" s="1"/>
-    </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A392" s="1"/>
-      <c r="B392" s="1"/>
-    </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A393" s="1"/>
-      <c r="B393" s="1"/>
-    </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A394" s="1"/>
-      <c r="B394" s="1"/>
-    </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A395" s="1"/>
-      <c r="B395" s="1"/>
-    </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A396" s="1"/>
-      <c r="B396" s="1"/>
-    </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A397" s="1"/>
-      <c r="B397" s="1"/>
-    </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A398" s="1"/>
-      <c r="B398" s="1"/>
-    </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A399" s="1"/>
-      <c r="B399" s="1"/>
-    </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A400" s="1"/>
-      <c r="B400" s="1"/>
-    </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A401" s="1"/>
-      <c r="B401" s="1"/>
-    </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A402" s="1"/>
-      <c r="B402" s="1"/>
-    </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A403" s="1"/>
-      <c r="B403" s="1"/>
-    </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A404" s="1"/>
-      <c r="B404" s="1"/>
-    </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A405" s="1"/>
-      <c r="B405" s="1"/>
-    </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A406" s="1"/>
-      <c r="B406" s="1"/>
-    </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A407" s="1"/>
-      <c r="B407" s="1"/>
-    </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A408" s="1"/>
-      <c r="B408" s="1"/>
-    </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A409" s="1"/>
-      <c r="B409" s="1"/>
-    </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A410" s="1"/>
-      <c r="B410" s="1"/>
-    </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A411" s="1"/>
-      <c r="B411" s="1"/>
-    </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A412" s="1"/>
-      <c r="B412" s="1"/>
-    </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A413" s="1"/>
-      <c r="B413" s="1"/>
-    </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A414" s="1"/>
-      <c r="B414" s="1"/>
-    </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A415" s="1"/>
-      <c r="B415" s="1"/>
-    </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A416" s="1"/>
-      <c r="B416" s="1"/>
-    </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A417" s="1"/>
-      <c r="B417" s="1"/>
-    </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A418" s="1"/>
-      <c r="B418" s="1"/>
-    </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A419" s="1"/>
-      <c r="B419" s="1"/>
-    </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A420" s="1"/>
-      <c r="B420" s="1"/>
-    </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A421" s="1"/>
-      <c r="B421" s="1"/>
-    </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A422" s="1"/>
-      <c r="B422" s="1"/>
-    </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A423" s="1"/>
-      <c r="B423" s="1"/>
-    </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A424" s="1"/>
-      <c r="B424" s="1"/>
-    </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A425" s="1"/>
-      <c r="B425" s="1"/>
-    </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A426" s="1"/>
-      <c r="B426" s="1"/>
-    </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A427" s="1"/>
-      <c r="B427" s="1"/>
-    </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A428" s="1"/>
-      <c r="B428" s="1"/>
-    </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A429" s="1"/>
-      <c r="B429" s="1"/>
-    </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A430" s="1"/>
-      <c r="B430" s="1"/>
-    </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A431" s="1"/>
-      <c r="B431" s="1"/>
-    </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A432" s="1"/>
-      <c r="B432" s="1"/>
-    </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A433" s="1"/>
-      <c r="B433" s="1"/>
-    </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A434" s="1"/>
-      <c r="B434" s="1"/>
-    </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A435" s="1"/>
-      <c r="B435" s="1"/>
-    </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A436" s="1"/>
-      <c r="B436" s="1"/>
-    </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A437" s="1"/>
-      <c r="B437" s="1"/>
-    </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A438" s="1"/>
-      <c r="B438" s="1"/>
-    </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A439" s="1"/>
-      <c r="B439" s="1"/>
-    </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A440" s="1"/>
-      <c r="B440" s="1"/>
-    </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A441" s="1"/>
-      <c r="B441" s="1"/>
-    </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A442" s="1"/>
-      <c r="B442" s="1"/>
-    </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A443" s="1"/>
-      <c r="B443" s="1"/>
-    </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A444" s="1"/>
-      <c r="B444" s="1"/>
-    </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A445" s="1"/>
-      <c r="B445" s="1"/>
-    </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A446" s="1"/>
-      <c r="B446" s="1"/>
-    </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A447" s="1"/>
-      <c r="B447" s="1"/>
-    </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A448" s="1"/>
-      <c r="B448" s="1"/>
-    </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A449" s="1"/>
-      <c r="B449" s="1"/>
-    </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A450" s="1"/>
-      <c r="B450" s="1"/>
-    </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A451" s="1"/>
-      <c r="B451" s="1"/>
-    </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A452" s="1"/>
-      <c r="B452" s="1"/>
-    </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A453" s="1"/>
-      <c r="B453" s="1"/>
-    </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A454" s="1"/>
-      <c r="B454" s="1"/>
-    </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A455" s="1"/>
-      <c r="B455" s="1"/>
-    </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A456" s="1"/>
-      <c r="B456" s="1"/>
-    </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A457" s="1"/>
-      <c r="B457" s="1"/>
-    </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A458" s="1"/>
-      <c r="B458" s="1"/>
-    </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A459" s="1"/>
-      <c r="B459" s="1"/>
-    </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A460" s="1"/>
-      <c r="B460" s="1"/>
-    </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A461" s="1"/>
-      <c r="B461" s="1"/>
-    </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A462" s="1"/>
-      <c r="B462" s="1"/>
-    </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A463" s="1"/>
-      <c r="B463" s="1"/>
-    </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A464" s="1"/>
-      <c r="B464" s="1"/>
-    </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A465" s="1"/>
-      <c r="B465" s="1"/>
-    </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A466" s="1"/>
-      <c r="B466" s="1"/>
-    </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A467" s="1"/>
-      <c r="B467" s="1"/>
-    </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A468" s="1"/>
-      <c r="B468" s="1"/>
-    </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A469" s="1"/>
-      <c r="B469" s="1"/>
-    </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A470" s="1"/>
-      <c r="B470" s="1"/>
-    </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A471" s="1"/>
-      <c r="B471" s="1"/>
-    </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A472" s="1"/>
-      <c r="B472" s="1"/>
-    </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
-    </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A474" s="1"/>
-      <c r="B474" s="1"/>
-    </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A475" s="1"/>
-      <c r="B475" s="1"/>
-    </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A476" s="1"/>
-      <c r="B476" s="1"/>
-    </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A477" s="1"/>
-      <c r="B477" s="1"/>
-    </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A478" s="1"/>
-      <c r="B478" s="1"/>
-    </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A479" s="1"/>
-      <c r="B479" s="1"/>
-    </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A480" s="1"/>
-      <c r="B480" s="1"/>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A481" s="1"/>
-      <c r="B481" s="1"/>
-    </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A482" s="1"/>
-      <c r="B482" s="1"/>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A483" s="1"/>
-      <c r="B483" s="1"/>
-    </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A484" s="1"/>
-      <c r="B484" s="1"/>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A485" s="1"/>
-      <c r="B485" s="1"/>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A486" s="1"/>
-      <c r="B486" s="1"/>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A487" s="1"/>
-      <c r="B487" s="1"/>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A488" s="1"/>
-      <c r="B488" s="1"/>
-    </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A489" s="1"/>
-      <c r="B489" s="1"/>
-    </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A490" s="1"/>
-      <c r="B490" s="1"/>
-    </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A491" s="1"/>
-      <c r="B491" s="1"/>
-    </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A492" s="1"/>
-      <c r="B492" s="1"/>
-    </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A493" s="1"/>
-      <c r="B493" s="1"/>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A494" s="1"/>
-      <c r="B494" s="1"/>
-    </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A495" s="1"/>
-      <c r="B495" s="1"/>
-    </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A496" s="1"/>
-      <c r="B496" s="1"/>
-    </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A497" s="1"/>
-      <c r="B497" s="1"/>
-    </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A498" s="1"/>
-      <c r="B498" s="1"/>
-    </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A499" s="1"/>
-      <c r="B499" s="1"/>
-    </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A500" s="1"/>
-      <c r="B500" s="1"/>
-    </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A501" s="1"/>
-      <c r="B501" s="1"/>
-    </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A502" s="1"/>
-      <c r="B502" s="1"/>
-    </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A503" s="1"/>
-      <c r="B503" s="1"/>
-    </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A504" s="1"/>
-      <c r="B504" s="1"/>
-    </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A505" s="1"/>
-      <c r="B505" s="1"/>
-    </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A506" s="1"/>
-      <c r="B506" s="1"/>
-    </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A507" s="1"/>
-      <c r="B507" s="1"/>
-    </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A508" s="1"/>
-      <c r="B508" s="1"/>
-    </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A509" s="1"/>
-      <c r="B509" s="1"/>
-    </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A510" s="1"/>
-      <c r="B510" s="1"/>
-    </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A511" s="1"/>
-      <c r="B511" s="1"/>
-    </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A512" s="1"/>
-      <c r="B512" s="1"/>
-    </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A513" s="1"/>
-      <c r="B513" s="1"/>
-    </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A514" s="1"/>
-      <c r="B514" s="1"/>
-    </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A515" s="1"/>
-      <c r="B515" s="1"/>
-    </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A516" s="1"/>
-      <c r="B516" s="1"/>
-    </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A517" s="1"/>
-      <c r="B517" s="1"/>
-    </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A518" s="1"/>
-      <c r="B518" s="1"/>
-    </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A519" s="1"/>
-      <c r="B519" s="1"/>
-    </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A520" s="1"/>
-      <c r="B520" s="1"/>
-    </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A521" s="1"/>
-      <c r="B521" s="1"/>
-    </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A522" s="1"/>
-      <c r="B522" s="1"/>
-    </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A523" s="1"/>
-      <c r="B523" s="1"/>
-    </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A524" s="1"/>
-      <c r="B524" s="1"/>
-    </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A525" s="1"/>
-      <c r="B525" s="1"/>
-    </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A526" s="1"/>
-      <c r="B526" s="1"/>
-    </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A527" s="1"/>
-      <c r="B527" s="1"/>
-    </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A528" s="1"/>
-      <c r="B528" s="1"/>
-    </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A529" s="1"/>
-      <c r="B529" s="1"/>
-    </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A530" s="1"/>
-      <c r="B530" s="1"/>
-    </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A531" s="1"/>
-      <c r="B531" s="1"/>
-    </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A532" s="1"/>
-      <c r="B532" s="1"/>
-    </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A533" s="1"/>
-      <c r="B533" s="1"/>
-    </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A534" s="1"/>
-      <c r="B534" s="1"/>
-    </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A535" s="1"/>
-      <c r="B535" s="1"/>
-    </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A536" s="1"/>
-      <c r="B536" s="1"/>
-    </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A537" s="1"/>
-      <c r="B537" s="1"/>
-    </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A538" s="1"/>
-      <c r="B538" s="1"/>
-    </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A539" s="1"/>
-      <c r="B539" s="1"/>
-    </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A540" s="1"/>
-      <c r="B540" s="1"/>
-    </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A541" s="1"/>
-      <c r="B541" s="1"/>
-    </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A542" s="1"/>
-      <c r="B542" s="1"/>
-    </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A543" s="1"/>
-      <c r="B543" s="1"/>
-    </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A544" s="1"/>
-      <c r="B544" s="1"/>
-    </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A545" s="1"/>
-      <c r="B545" s="1"/>
-    </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A546" s="1"/>
-      <c r="B546" s="1"/>
-    </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A547" s="1"/>
-      <c r="B547" s="1"/>
-    </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A548" s="1"/>
-      <c r="B548" s="1"/>
-    </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A549" s="1"/>
-      <c r="B549" s="1"/>
-    </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A550" s="1"/>
-      <c r="B550" s="1"/>
-    </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A551" s="1"/>
-      <c r="B551" s="1"/>
-    </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A552" s="1"/>
-      <c r="B552" s="1"/>
-    </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A553" s="1"/>
-      <c r="B553" s="1"/>
-    </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A554" s="1"/>
-      <c r="B554" s="1"/>
-    </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A555" s="1"/>
-      <c r="B555" s="1"/>
-    </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A556" s="1"/>
-      <c r="B556" s="1"/>
-    </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A557" s="1"/>
-      <c r="B557" s="1"/>
-    </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A558" s="1"/>
-      <c r="B558" s="1"/>
-    </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A559" s="1"/>
-      <c r="B559" s="1"/>
-    </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A560" s="1"/>
-      <c r="B560" s="1"/>
-    </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A561" s="1"/>
-      <c r="B561" s="1"/>
-    </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A562" s="1"/>
-      <c r="B562" s="1"/>
-    </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A563" s="1"/>
-      <c r="B563" s="1"/>
-    </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A564" s="1"/>
-      <c r="B564" s="1"/>
-    </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A565" s="1"/>
-      <c r="B565" s="1"/>
-    </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A566" s="1"/>
-      <c r="B566" s="1"/>
-    </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A567" s="1"/>
-      <c r="B567" s="1"/>
-    </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A568" s="1"/>
-      <c r="B568" s="1"/>
-    </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A569" s="1"/>
-      <c r="B569" s="1"/>
-    </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A570" s="1"/>
-      <c r="B570" s="1"/>
-    </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A571" s="1"/>
-      <c r="B571" s="1"/>
-    </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A572" s="1"/>
-      <c r="B572" s="1"/>
-    </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A573" s="1"/>
-      <c r="B573" s="1"/>
-    </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A574" s="1"/>
-      <c r="B574" s="1"/>
-    </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A575" s="1"/>
-      <c r="B575" s="1"/>
-    </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A576" s="1"/>
-      <c r="B576" s="1"/>
-    </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A577" s="1"/>
-      <c r="B577" s="1"/>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A578" s="1"/>
-      <c r="B578" s="1"/>
-    </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A579" s="1"/>
-      <c r="B579" s="1"/>
-    </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A580" s="1"/>
-      <c r="B580" s="1"/>
-    </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A581" s="1"/>
-      <c r="B581" s="1"/>
-    </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A582" s="1"/>
-      <c r="B582" s="1"/>
-    </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A583" s="1"/>
-      <c r="B583" s="1"/>
-    </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A584" s="1"/>
-      <c r="B584" s="1"/>
-    </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A585" s="1"/>
-      <c r="B585" s="1"/>
-    </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A586" s="1"/>
-      <c r="B586" s="1"/>
-    </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A587" s="1"/>
-      <c r="B587" s="1"/>
-    </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A588" s="1"/>
-      <c r="B588" s="1"/>
-    </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A589" s="1"/>
-      <c r="B589" s="1"/>
-    </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A590" s="1"/>
-      <c r="B590" s="1"/>
-    </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A591" s="1"/>
-      <c r="B591" s="1"/>
-    </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A592" s="1"/>
-      <c r="B592" s="1"/>
-    </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A593" s="1"/>
-      <c r="B593" s="1"/>
-    </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A594" s="1"/>
-      <c r="B594" s="1"/>
-    </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A595" s="1"/>
-      <c r="B595" s="1"/>
-    </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A596" s="1"/>
-      <c r="B596" s="1"/>
-    </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A597" s="1"/>
-      <c r="B597" s="1"/>
-    </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A598" s="1"/>
-      <c r="B598" s="1"/>
-    </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A599" s="1"/>
-      <c r="B599" s="1"/>
-    </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A600" s="1"/>
-      <c r="B600" s="1"/>
-    </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A601" s="1"/>
-      <c r="B601" s="1"/>
-    </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A602" s="1"/>
-      <c r="B602" s="1"/>
-    </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A603" s="1"/>
-      <c r="B603" s="1"/>
-    </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A604" s="1"/>
-      <c r="B604" s="1"/>
-    </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A605" s="1"/>
-      <c r="B605" s="1"/>
-    </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A606" s="1"/>
-      <c r="B606" s="1"/>
-    </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A607" s="1"/>
-      <c r="B607" s="1"/>
-    </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A608" s="1"/>
-      <c r="B608" s="1"/>
-    </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A609" s="1"/>
-      <c r="B609" s="1"/>
-    </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A610" s="1"/>
-      <c r="B610" s="1"/>
-    </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A611" s="1"/>
-      <c r="B611" s="1"/>
-    </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A612" s="1"/>
-      <c r="B612" s="1"/>
-    </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A613" s="1"/>
-      <c r="B613" s="1"/>
-    </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A614" s="1"/>
-      <c r="B614" s="1"/>
-    </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A615" s="1"/>
-      <c r="B615" s="1"/>
-    </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A616" s="1"/>
-      <c r="B616" s="1"/>
-    </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A617" s="1"/>
-      <c r="B617" s="1"/>
-    </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A618" s="1"/>
-      <c r="B618" s="1"/>
-    </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A619" s="1"/>
-      <c r="B619" s="1"/>
-    </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A620" s="1"/>
-      <c r="B620" s="1"/>
-    </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A621" s="1"/>
-      <c r="B621" s="1"/>
-    </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A622" s="1"/>
-      <c r="B622" s="1"/>
-    </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A623" s="1"/>
-      <c r="B623" s="1"/>
-    </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A624" s="1"/>
-      <c r="B624" s="1"/>
-    </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A625" s="1"/>
-      <c r="B625" s="1"/>
-    </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A626" s="1"/>
-      <c r="B626" s="1"/>
-    </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A627" s="1"/>
-      <c r="B627" s="1"/>
-    </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A628" s="1"/>
-      <c r="B628" s="1"/>
-    </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A629" s="1"/>
-      <c r="B629" s="1"/>
-    </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A630" s="1"/>
-      <c r="B630" s="1"/>
-    </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A631" s="1"/>
-      <c r="B631" s="1"/>
-    </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
-    </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A633" s="1"/>
-      <c r="B633" s="1"/>
-    </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A634" s="1"/>
-      <c r="B634" s="1"/>
-    </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A635" s="1"/>
-      <c r="B635" s="1"/>
-    </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A636" s="1"/>
-      <c r="B636" s="1"/>
-    </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A637" s="1"/>
-      <c r="B637" s="1"/>
-    </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A638" s="1"/>
-      <c r="B638" s="1"/>
-    </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A639" s="1"/>
-      <c r="B639" s="1"/>
-    </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A640" s="1"/>
-      <c r="B640" s="1"/>
-    </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A641" s="1"/>
-      <c r="B641" s="1"/>
-    </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A642" s="1"/>
-      <c r="B642" s="1"/>
-    </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A643" s="1"/>
-      <c r="B643" s="1"/>
-    </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A644" s="1"/>
-      <c r="B644" s="1"/>
-    </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A645" s="1"/>
-      <c r="B645" s="1"/>
-    </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A646" s="1"/>
-      <c r="B646" s="1"/>
-    </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A647" s="1"/>
-      <c r="B647" s="1"/>
-    </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A648" s="1"/>
-      <c r="B648" s="1"/>
-    </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A649" s="1"/>
-      <c r="B649" s="1"/>
-    </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A650" s="1"/>
-      <c r="B650" s="1"/>
-    </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A651" s="1"/>
-      <c r="B651" s="1"/>
-    </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A652" s="1"/>
-      <c r="B652" s="1"/>
-    </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A653" s="1"/>
-      <c r="B653" s="1"/>
-    </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A654" s="1"/>
-      <c r="B654" s="1"/>
-    </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A655" s="1"/>
-      <c r="B655" s="1"/>
-    </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A656" s="1"/>
-      <c r="B656" s="1"/>
-    </row>
-    <row r="657" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A657" s="1"/>
-      <c r="B657" s="1"/>
-    </row>
-    <row r="658" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
-    </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A659" s="1"/>
-      <c r="B659" s="1"/>
-    </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A660" s="1"/>
-      <c r="B660" s="1"/>
-    </row>
-    <row r="661" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A661" s="1"/>
-      <c r="B661" s="1"/>
-    </row>
-    <row r="662" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A662" s="1"/>
-      <c r="B662" s="1"/>
-    </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A663" s="1"/>
-      <c r="B663" s="1"/>
-    </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A664" s="1"/>
-      <c r="B664" s="1"/>
-    </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A665" s="1"/>
-      <c r="B665" s="1"/>
-    </row>
-    <row r="666" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A666" s="1"/>
-      <c r="B666" s="1"/>
-    </row>
-    <row r="667" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A667" s="1"/>
-      <c r="B667" s="1"/>
-    </row>
-    <row r="668" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A668" s="1"/>
-      <c r="B668" s="1"/>
-    </row>
-    <row r="669" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A669" s="1"/>
-      <c r="B669" s="1"/>
-    </row>
-    <row r="670" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A670" s="1"/>
-      <c r="B670" s="1"/>
-    </row>
-    <row r="671" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A671" s="1"/>
-      <c r="B671" s="1"/>
-    </row>
-    <row r="672" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A672" s="1"/>
-      <c r="B672" s="1"/>
-    </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A673" s="1"/>
-      <c r="B673" s="1"/>
-    </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A674" s="1"/>
-      <c r="B674" s="1"/>
-    </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A675" s="1"/>
-      <c r="B675" s="1"/>
-    </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A676" s="1"/>
-      <c r="B676" s="1"/>
-    </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A677" s="1"/>
-      <c r="B677" s="1"/>
-    </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A678" s="1"/>
-      <c r="B678" s="1"/>
-    </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A679" s="1"/>
-      <c r="B679" s="1"/>
-    </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A680" s="1"/>
-      <c r="B680" s="1"/>
-    </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A681" s="1"/>
-      <c r="B681" s="1"/>
-    </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A682" s="1"/>
-      <c r="B682" s="1"/>
-    </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A683" s="1"/>
-      <c r="B683" s="1"/>
-    </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
-    </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A685" s="1"/>
-      <c r="B685" s="1"/>
-    </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A686" s="1"/>
-      <c r="B686" s="1"/>
-    </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A687" s="1"/>
-      <c r="B687" s="1"/>
-    </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A688" s="1"/>
-      <c r="B688" s="1"/>
-    </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A689" s="1"/>
-      <c r="B689" s="1"/>
-    </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A690" s="1"/>
-      <c r="B690" s="1"/>
-    </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A691" s="1"/>
-      <c r="B691" s="1"/>
-    </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A692" s="1"/>
-      <c r="B692" s="1"/>
-    </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A693" s="1"/>
-      <c r="B693" s="1"/>
-    </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A694" s="1"/>
-      <c r="B694" s="1"/>
+      <c r="C260" s="3"/>
+      <c r="D260" s="3"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D246" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -7666,7 +6070,26 @@
       <sortCondition descending="1" ref="C1:C246"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6F97E1D4-95A1-4D1B-B3C9-F10707C25085}">
+          <x14:formula1>
+            <xm:f>BD!$A$1:$Q$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>A131:A238 A2 A6 A19 A30:A31 A61:A62 A69 A79 A93:A94 A114 A122</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{648B5F03-60F3-4B0E-AC3D-96CE1E8ACD30}">
+          <x14:formula1>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A131, BD!$A$1:$Q$1, 0))</xm:f>
+          </x14:formula1>
+          <xm:sqref>B131:B237</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -11308,7 +9731,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>13</v>
+        <v>965</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0460BFF-051A-46B3-8243-6A084974CEDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617352F3-642D-46BD-95A9-7764B61B8C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$96</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="968">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -2992,10 +2992,16 @@
     <t>Logos Equipos/borussia.webp</t>
   </si>
   <si>
-    <t>PT Joan Garcia</t>
-  </si>
-  <si>
     <t>Como_1907</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Carlos Espi</t>
+  </si>
+  <si>
+    <t>DC Carlos Espi</t>
   </si>
 </sst>
 </file>
@@ -3419,7 +3425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:E260"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -3472,13 +3478,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>964</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C4" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3">
         <v>1</v>
@@ -3486,69 +3492,69 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>364</v>
+        <v>199</v>
       </c>
       <c r="C5" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>965</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>188</v>
+        <v>364</v>
       </c>
       <c r="C6" s="3">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>368</v>
       </c>
       <c r="C7" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C8" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C9" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="3">
         <v>1</v>
@@ -3556,84 +3562,86 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="C10" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="C12" s="3">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D12" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C13" s="3">
         <v>6</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="C14" s="3">
         <v>6</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>341</v>
+        <v>378</v>
       </c>
       <c r="C15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -3641,78 +3649,80 @@
         <v>12</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="C16" s="3">
-        <v>5</v>
-      </c>
-      <c r="D16" s="3"/>
+        <v>6</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C17" s="3">
         <v>6</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C17" s="3">
-        <v>5</v>
-      </c>
       <c r="D17" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>357</v>
+        <v>118</v>
       </c>
       <c r="C18" s="3">
         <v>5</v>
       </c>
       <c r="D18" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="C19" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C20" s="3">
+        <v>5</v>
+      </c>
+      <c r="D20" s="3">
         <v>2</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C20" s="3">
-        <v>6</v>
-      </c>
-      <c r="D20" s="3">
-        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C21" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D21" s="3">
         <v>2</v>
@@ -3720,69 +3730,67 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>380</v>
+        <v>327</v>
       </c>
       <c r="C22" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D22" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>171</v>
+        <v>357</v>
       </c>
       <c r="C23" s="3">
         <v>5</v>
       </c>
       <c r="D23" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C24" s="3">
-        <v>4</v>
-      </c>
-      <c r="D24" s="3">
         <v>5</v>
       </c>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>344</v>
+        <v>182</v>
       </c>
       <c r="C25" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D25" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>3</v>
+        <v>964</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>369</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="3">
         <v>2</v>
@@ -3790,16 +3798,16 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>3</v>
+        <v>964</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>321</v>
+        <v>125</v>
       </c>
       <c r="C27" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -3818,107 +3826,111 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C29" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>965</v>
+        <v>14</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C30" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>965</v>
+        <v>4</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>141</v>
+        <v>163</v>
       </c>
       <c r="C31" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D31" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>12</v>
+        <v>964</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>330</v>
+        <v>299</v>
       </c>
       <c r="C32" s="3">
         <v>3</v>
       </c>
       <c r="D32" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>163</v>
+        <v>369</v>
       </c>
       <c r="C33" s="3">
         <v>3</v>
       </c>
       <c r="D33" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>211</v>
+        <v>321</v>
       </c>
       <c r="C34" s="3">
         <v>3</v>
       </c>
-      <c r="D34" s="3"/>
+      <c r="D34" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="C35" s="3">
+        <v>3</v>
+      </c>
+      <c r="D35" s="3">
         <v>2</v>
       </c>
-      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>150</v>
+        <v>344</v>
       </c>
       <c r="C36" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -3926,130 +3938,134 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>173</v>
+        <v>330</v>
       </c>
       <c r="C37" s="3">
         <v>3</v>
       </c>
       <c r="D37" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>6</v>
+        <v>964</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>181</v>
+        <v>379</v>
       </c>
       <c r="C38" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D38" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="C39" s="3">
-        <v>2</v>
-      </c>
-      <c r="D39" s="3">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="D39" s="3"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="C40" s="3">
         <v>2</v>
       </c>
       <c r="D40" s="3">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>185</v>
+        <v>332</v>
       </c>
       <c r="C41" s="3">
         <v>2</v>
       </c>
       <c r="D41" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="C42" s="3">
         <v>2</v>
       </c>
-      <c r="D42" s="3"/>
+      <c r="D42" s="3">
+        <v>5</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>386</v>
+        <v>8</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>387</v>
+        <v>183</v>
       </c>
       <c r="C43" s="3">
         <v>2</v>
       </c>
-      <c r="D43" s="3"/>
+      <c r="D43" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="C44" s="3">
         <v>2</v>
       </c>
       <c r="D44" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="C45" s="3">
         <v>2</v>
       </c>
-      <c r="D45" s="3"/>
+      <c r="D45" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>340</v>
+        <v>126</v>
       </c>
       <c r="C46" s="3">
         <v>2</v>
@@ -4060,10 +4076,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>144</v>
+        <v>340</v>
       </c>
       <c r="C47" s="3">
         <v>2</v>
@@ -4074,24 +4090,24 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>388</v>
+        <v>144</v>
       </c>
       <c r="C48" s="3">
         <v>2</v>
       </c>
       <c r="D48" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C49" s="3">
         <v>2</v>
@@ -4102,36 +4118,38 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>168</v>
+        <v>185</v>
       </c>
       <c r="C50" s="3">
         <v>2</v>
       </c>
       <c r="D50" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>14</v>
+        <v>386</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>94</v>
+        <v>388</v>
       </c>
       <c r="C51" s="3">
-        <v>1</v>
-      </c>
-      <c r="D51" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D51" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="C52" s="3">
         <v>2</v>
@@ -4142,49 +4160,55 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="C53" s="3">
-        <v>1</v>
-      </c>
-      <c r="D53" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>170</v>
+        <v>326</v>
       </c>
       <c r="C54" s="3">
-        <v>1</v>
-      </c>
-      <c r="D54" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D54" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>8</v>
+        <v>964</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>247</v>
+        <v>157</v>
       </c>
       <c r="C55" s="3">
-        <v>1</v>
-      </c>
-      <c r="D55" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D55" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="C56" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" s="3">
         <v>1</v>
@@ -4192,13 +4216,13 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>371</v>
+        <v>159</v>
       </c>
       <c r="C57" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -4209,201 +4233,207 @@
         <v>5</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C58" s="3">
-        <v>1</v>
-      </c>
-      <c r="D58" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D58" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>3</v>
+        <v>964</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="C59" s="3">
-        <v>1</v>
-      </c>
-      <c r="D59" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D59" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>389</v>
+        <v>166</v>
       </c>
       <c r="C60" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D60" s="3"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>965</v>
+        <v>12</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>299</v>
+        <v>44</v>
       </c>
       <c r="C61" s="3">
-        <v>3</v>
-      </c>
-      <c r="D61" s="3">
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>965</v>
+        <v>386</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="C62" s="3">
-        <v>1</v>
-      </c>
-      <c r="D62" s="3">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>311</v>
+        <v>161</v>
       </c>
       <c r="C63" s="3">
-        <v>1</v>
-      </c>
-      <c r="D63" s="3">
         <v>2</v>
       </c>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>10</v>
+        <v>928</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>360</v>
+        <v>941</v>
       </c>
       <c r="C64" s="3">
-        <v>1</v>
-      </c>
-      <c r="D64" s="3">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="C65" s="3">
         <v>1</v>
       </c>
       <c r="D65" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3">
         <v>4</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="C66" s="3">
-        <v>1</v>
-      </c>
-      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>8</v>
+        <v>386</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>326</v>
+        <v>392</v>
       </c>
       <c r="C67" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D67" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>350</v>
+        <v>311</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
       </c>
-      <c r="D68" s="3"/>
+      <c r="D68" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>965</v>
+        <v>6</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>45</v>
+        <v>308</v>
       </c>
       <c r="C69" s="3">
         <v>1</v>
       </c>
-      <c r="D69" s="3"/>
+      <c r="D69" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1</v>
+      </c>
+      <c r="D70" s="3">
         <v>2</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C70" s="3">
-        <v>1</v>
-      </c>
-      <c r="D70" s="3"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>86</v>
+        <v>283</v>
       </c>
       <c r="C71" s="3">
         <v>1</v>
       </c>
       <c r="D71" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>92</v>
+        <v>241</v>
       </c>
       <c r="C72" s="3">
         <v>1</v>
       </c>
-      <c r="D72" s="3"/>
+      <c r="D72" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="C73" s="3">
         <v>1</v>
@@ -4414,46 +4444,52 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>105</v>
+        <v>360</v>
       </c>
       <c r="C74" s="3">
         <v>1</v>
       </c>
-      <c r="D74" s="3"/>
+      <c r="D74" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>123</v>
+        <v>346</v>
       </c>
       <c r="C75" s="3">
         <v>1</v>
       </c>
-      <c r="D75" s="3"/>
+      <c r="D75" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>242</v>
+        <v>86</v>
       </c>
       <c r="C76" s="3">
         <v>1</v>
       </c>
-      <c r="D76" s="3"/>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="C77" s="3">
         <v>1</v>
@@ -4464,27 +4500,27 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>332</v>
+        <v>136</v>
       </c>
       <c r="C78" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>965</v>
+        <v>12</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="C79" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79" s="3">
         <v>1</v>
@@ -4492,214 +4528,215 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C80" s="3">
+        <v>1</v>
+      </c>
+      <c r="D80" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C81" s="3">
+        <v>1</v>
+      </c>
+      <c r="D81" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C82" s="3">
+        <v>1</v>
+      </c>
+      <c r="D82" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C83" s="3">
+        <v>1</v>
+      </c>
+      <c r="D83" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C84" s="3">
+        <v>1</v>
+      </c>
+      <c r="D84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="3">
+        <v>1</v>
+      </c>
+      <c r="D85" s="3"/>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C86" s="3">
+        <v>1</v>
+      </c>
+      <c r="D86" s="3"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="3">
+        <v>1</v>
+      </c>
+      <c r="D87" s="3"/>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
+      <c r="D88" s="3"/>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89" s="3">
+        <v>1</v>
+      </c>
+      <c r="D89" s="3"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="C90" s="3">
+        <v>1</v>
+      </c>
+      <c r="D90" s="3"/>
+      <c r="E90" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1</v>
+      </c>
+      <c r="D91" s="3"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C92" s="3">
+        <v>1</v>
+      </c>
+      <c r="D92" s="3"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C93" s="3">
+        <v>1</v>
+      </c>
+      <c r="D93" s="3"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C94" s="3">
+        <v>1</v>
+      </c>
+      <c r="D94" s="3"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C80" s="3">
-        <v>1</v>
-      </c>
-      <c r="D80" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C81" s="3">
-        <v>1</v>
-      </c>
-      <c r="D81" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C82" s="3">
-        <v>2</v>
-      </c>
-      <c r="D82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="C83" s="3">
-        <v>1</v>
-      </c>
-      <c r="D83" s="3"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C84" s="3">
-        <v>1</v>
-      </c>
-      <c r="D84" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C85" s="3">
-        <v>2</v>
-      </c>
-      <c r="D85" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C86" s="3">
-        <v>1</v>
-      </c>
-      <c r="D86" s="3"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C87" s="3">
-        <v>1</v>
-      </c>
-      <c r="D87" s="3"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="3" t="s">
+      <c r="B95" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C95" s="3">
+        <v>1</v>
+      </c>
+      <c r="D95" s="3"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="C88" s="3">
-        <v>1</v>
-      </c>
-      <c r="D88" s="3"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="C89" s="3">
-        <v>1</v>
-      </c>
-      <c r="D89" s="3"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="C90" s="3">
-        <v>1</v>
-      </c>
-      <c r="D90" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C91" s="3">
-        <v>1</v>
-      </c>
-      <c r="D91" s="3"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="C92" s="3">
-        <v>1</v>
-      </c>
-      <c r="D92" s="3"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C93" s="3">
-        <v>1</v>
-      </c>
-      <c r="D93" s="3"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C94" s="3">
-        <v>1</v>
-      </c>
-      <c r="D94" s="3"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C95" s="3">
-        <v>1</v>
-      </c>
-      <c r="D95" s="3"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="3" t="s">
-        <v>386</v>
-      </c>
       <c r="B96" s="3" t="s">
-        <v>391</v>
+        <v>105</v>
       </c>
       <c r="C96" s="3">
         <v>1</v>
@@ -4708,380 +4745,370 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>386</v>
+        <v>11</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>392</v>
+        <v>123</v>
       </c>
       <c r="C97" s="3">
         <v>1</v>
       </c>
-      <c r="D97" s="3">
-        <v>3</v>
-      </c>
+      <c r="D97" s="3"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>285</v>
+        <v>242</v>
       </c>
       <c r="C98" s="3">
         <v>1</v>
       </c>
-      <c r="D98" s="3">
-        <v>1</v>
-      </c>
+      <c r="D98" s="3"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C99" s="3"/>
-      <c r="D99" s="3">
-        <v>4</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1</v>
+      </c>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3">
-        <v>2</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
       <c r="C101" s="3">
         <v>1</v>
       </c>
-      <c r="D101" s="3">
-        <v>4</v>
-      </c>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3">
-        <v>2</v>
-      </c>
+        <v>343</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3">
-        <v>3</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="C103" s="3">
+        <v>1</v>
+      </c>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3">
-        <v>2</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
-        <v>10</v>
+        <v>386</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3">
-        <v>2</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="C105" s="3">
+        <v>1</v>
+      </c>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>6</v>
+        <v>964</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="C106" s="3">
         <v>1</v>
       </c>
-      <c r="D106" s="3">
-        <v>2</v>
-      </c>
+      <c r="D106" s="3"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>11</v>
+        <v>964</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="D107" s="3">
-        <v>2</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C107" s="3">
+        <v>1</v>
+      </c>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>241</v>
+        <v>146</v>
       </c>
       <c r="C108" s="3">
         <v>1</v>
       </c>
-      <c r="D108" s="3">
-        <v>1</v>
-      </c>
+      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" s="3" t="s">
-        <v>8</v>
+        <v>386</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3">
-        <v>2</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1</v>
+      </c>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" s="3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3">
-        <v>2</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1</v>
+      </c>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" s="3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C111" s="3"/>
-      <c r="D111" s="3">
-        <v>1</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="C111" s="3">
+        <v>1</v>
+      </c>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" s="3" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="C112" s="3"/>
-      <c r="D112" s="3">
-        <v>2</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1</v>
+      </c>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="C113" s="3"/>
-      <c r="D113" s="3">
-        <v>1</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C113" s="3">
+        <v>1</v>
+      </c>
+      <c r="D113" s="3"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" s="3" t="s">
-        <v>965</v>
+        <v>11</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C114" s="3"/>
-      <c r="D114" s="3">
-        <v>1</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1</v>
+      </c>
+      <c r="D114" s="3"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" s="3" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C115" s="3"/>
-      <c r="D115" s="3">
-        <v>3</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1</v>
+      </c>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3">
-        <v>1</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1</v>
+      </c>
+      <c r="D116" s="3"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C117" s="3"/>
-      <c r="D117" s="3">
-        <v>2</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C117" s="3">
+        <v>1</v>
+      </c>
+      <c r="D117" s="3"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" s="3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3">
-        <v>4</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1</v>
+      </c>
+      <c r="D118" s="3"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" s="3" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>290</v>
+        <v>124</v>
       </c>
       <c r="C119" s="3"/>
       <c r="D119" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" s="3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>328</v>
+        <v>116</v>
       </c>
       <c r="C120" s="3"/>
       <c r="D120" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" s="3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="C121" s="3"/>
       <c r="D121" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" s="3" t="s">
-        <v>965</v>
+        <v>14</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>379</v>
+        <v>46</v>
       </c>
       <c r="C122" s="3"/>
       <c r="D122" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" s="3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>84</v>
+        <v>198</v>
       </c>
       <c r="C123" s="3"/>
       <c r="D123" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" s="3" t="s">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>193</v>
+        <v>158</v>
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" s="3" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>263</v>
+        <v>369</v>
       </c>
       <c r="C125" s="3"/>
       <c r="D125" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" s="3" t="s">
-        <v>386</v>
+        <v>11</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>394</v>
+        <v>250</v>
       </c>
       <c r="C127" s="3"/>
       <c r="D127" s="3">
@@ -5093,7 +5120,7 @@
         <v>8</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>88</v>
+        <v>279</v>
       </c>
       <c r="C128" s="3"/>
       <c r="D128" s="3">
@@ -5102,94 +5129,94 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>100</v>
+        <v>263</v>
       </c>
       <c r="C129" s="3"/>
       <c r="D129" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>275</v>
+        <v>131</v>
       </c>
       <c r="C130" s="3"/>
       <c r="D130" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" s="3" t="s">
-        <v>965</v>
+        <v>2</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>77</v>
+        <v>304</v>
       </c>
       <c r="C131" s="3"/>
       <c r="D131" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" s="3" t="s">
-        <v>965</v>
+        <v>10</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C132" s="3">
-        <v>1</v>
-      </c>
-      <c r="D132" s="3"/>
+        <v>328</v>
+      </c>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" s="3" t="s">
-        <v>2</v>
+        <v>386</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>193</v>
+        <v>394</v>
       </c>
       <c r="C133" s="3"/>
       <c r="D133" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="C134" s="3"/>
       <c r="D134" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>8</v>
+        <v>964</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>294</v>
+        <v>236</v>
       </c>
       <c r="C135" s="3"/>
       <c r="D135" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" s="3" t="s">
-        <v>965</v>
+        <v>7</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>236</v>
+        <v>87</v>
       </c>
       <c r="C136" s="3"/>
       <c r="D136" s="3">
@@ -5198,34 +5225,34 @@
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" s="3" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="C137" s="3">
-        <v>1</v>
-      </c>
-      <c r="D137" s="3"/>
+        <v>158</v>
+      </c>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>1</v>
+        <v>964</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>319</v>
+        <v>109</v>
       </c>
       <c r="C138" s="3"/>
       <c r="D138" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" s="3" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>205</v>
+        <v>393</v>
       </c>
       <c r="C139" s="3"/>
       <c r="D139" s="3">
@@ -5234,10 +5261,10 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" s="3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>96</v>
+        <v>121</v>
       </c>
       <c r="C140" s="3"/>
       <c r="D140" s="3">
@@ -5246,46 +5273,46 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" s="3" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="C141" s="3">
-        <v>1</v>
-      </c>
-      <c r="D141" s="3"/>
+        <v>290</v>
+      </c>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C142" s="3">
-        <v>1</v>
-      </c>
-      <c r="D142" s="3"/>
+        <v>273</v>
+      </c>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" s="3" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C143" s="3">
-        <v>1</v>
-      </c>
-      <c r="D143" s="3"/>
+        <v>84</v>
+      </c>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="C144" s="3"/>
       <c r="D144" s="3">
@@ -5294,34 +5321,34 @@
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C145" s="3">
-        <v>1</v>
-      </c>
-      <c r="D145" s="3"/>
+        <v>263</v>
+      </c>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" s="3" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C146" s="3">
-        <v>1</v>
-      </c>
-      <c r="D146" s="3"/>
+        <v>76</v>
+      </c>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" s="3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>256</v>
+        <v>100</v>
       </c>
       <c r="C147" s="3"/>
       <c r="D147" s="3">
@@ -5329,130 +5356,256 @@
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
+      <c r="A148" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B148" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="C148" s="3"/>
-      <c r="D148" s="3"/>
+      <c r="D148" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
+      <c r="A149" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B149" s="3" t="s">
+        <v>77</v>
+      </c>
       <c r="C149" s="3"/>
-      <c r="D149" s="3"/>
+      <c r="D149" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
+      <c r="A150" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B150" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="C150" s="3"/>
-      <c r="D150" s="3"/>
+      <c r="D150" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
+      <c r="A151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B151" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
+      <c r="D151" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
+      <c r="A152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" s="3" t="s">
+        <v>294</v>
+      </c>
       <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
+      <c r="D152" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
+      <c r="A153" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B153" s="3" t="s">
+        <v>319</v>
+      </c>
       <c r="C153" s="3"/>
-      <c r="D153" s="3"/>
+      <c r="D153" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
+      <c r="A154" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B154" s="3" t="s">
+        <v>205</v>
+      </c>
       <c r="C154" s="3"/>
-      <c r="D154" s="3"/>
+      <c r="D154" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
+      <c r="A155" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="C155" s="3"/>
-      <c r="D155" s="3"/>
+      <c r="D155" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
+      <c r="A156" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="C156" s="3"/>
-      <c r="D156" s="3"/>
+      <c r="D156" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
+      <c r="A157" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B157" s="3" t="s">
+        <v>256</v>
+      </c>
       <c r="C157" s="3"/>
-      <c r="D157" s="3"/>
+      <c r="D157" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
+      <c r="A158" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B158" s="3" t="s">
+        <v>93</v>
+      </c>
       <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
+      <c r="D158" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
+      <c r="A159" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B159" s="3" t="s">
+        <v>288</v>
+      </c>
       <c r="C159" s="3"/>
-      <c r="D159" s="3"/>
+      <c r="D159" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
+      <c r="A160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B160" s="3" t="s">
+        <v>155</v>
+      </c>
       <c r="C160" s="3"/>
-      <c r="D160" s="3"/>
+      <c r="D160" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
+      <c r="A161" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="C161" s="3"/>
-      <c r="D161" s="3"/>
+      <c r="D161" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
+      <c r="A162" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="C162" s="3"/>
-      <c r="D162" s="3"/>
+      <c r="D162" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
+      <c r="A163" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B163" s="3" t="s">
+        <v>331</v>
+      </c>
       <c r="C163" s="3"/>
-      <c r="D163" s="3"/>
+      <c r="D163" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
+      <c r="A164" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="C164" s="3"/>
-      <c r="D164" s="3"/>
+      <c r="D164" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
+      <c r="A165" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B165" s="3" t="s">
+        <v>942</v>
+      </c>
       <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
+      <c r="D165" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
+      <c r="A166" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B166" s="3" t="s">
+        <v>933</v>
+      </c>
       <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
+      <c r="D166" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
+      <c r="A167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B167" s="3" t="s">
+        <v>114</v>
+      </c>
       <c r="C167" s="3"/>
-      <c r="D167" s="3"/>
+      <c r="D167" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
+      <c r="A168" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B168" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="C168" s="3"/>
-      <c r="D168" s="3"/>
+      <c r="D168" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" s="3"/>
@@ -5869,116 +6022,58 @@
       <c r="D237" s="3"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="B238" s="3" t="s">
-        <v>93</v>
-      </c>
+      <c r="A238" s="3"/>
+      <c r="B238" s="3"/>
       <c r="C238" s="3"/>
-      <c r="D238" s="3">
-        <v>1</v>
-      </c>
+      <c r="D238" s="3"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B239" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="A239" s="3"/>
+      <c r="B239" s="3"/>
       <c r="C239" s="3"/>
-      <c r="D239" s="3">
-        <v>2</v>
-      </c>
+      <c r="D239" s="3"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B240" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="C240" s="3">
-        <v>1</v>
-      </c>
-      <c r="D240" s="3">
-        <v>2</v>
-      </c>
+      <c r="A240" s="3"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B241" s="3" t="s">
-        <v>288</v>
-      </c>
+      <c r="A241" s="3"/>
+      <c r="B241" s="3"/>
       <c r="C241" s="3"/>
-      <c r="D241" s="3">
-        <v>1</v>
-      </c>
+      <c r="D241" s="3"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B242" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="C242" s="3">
-        <v>1</v>
-      </c>
-      <c r="D242" s="3">
-        <v>2</v>
-      </c>
+      <c r="A242" s="3"/>
+      <c r="B242" s="3"/>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B243" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
       <c r="C243" s="3"/>
-      <c r="D243" s="3">
-        <v>1</v>
-      </c>
+      <c r="D243" s="3"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B244" s="3" t="s">
-        <v>358</v>
-      </c>
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
       <c r="C244" s="3"/>
-      <c r="D244" s="3">
-        <v>1</v>
-      </c>
+      <c r="D244" s="3"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B245" s="3" t="s">
-        <v>158</v>
-      </c>
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
       <c r="C245" s="3"/>
-      <c r="D245" s="3">
-        <v>2</v>
-      </c>
+      <c r="D245" s="3"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B246" s="3" t="s">
-        <v>40</v>
-      </c>
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
       <c r="C246" s="3"/>
-      <c r="D246" s="3">
-        <v>1</v>
-      </c>
+      <c r="D246" s="3"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" s="3"/>
@@ -6079,13 +6174,13 @@
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A131:A238 A2 A6 A19 A30:A31 A61:A62 A69 A79 A93:A94 A114 A122</xm:sqref>
+          <xm:sqref>A122 A2 A6 A19 A30:A31 A61:A62 A69 A79 A93:A94 A114 A131:A168 A170:A260 A169</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{648B5F03-60F3-4B0E-AC3D-96CE1E8ACD30}">
           <x14:formula1>
             <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A131, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B237</xm:sqref>
+          <xm:sqref>B131:B168 B170:B260 B169</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6610,10 +6705,10 @@
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -6631,1506 +6726,2158 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="3">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="A3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="3">
+        <v>7</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
+      <c r="A4" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="3">
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5" s="3">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="A6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C7" s="3">
+        <v>4</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" s="3">
+        <v>4</v>
+      </c>
+      <c r="D8" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="3">
+        <v>3</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" s="3">
+        <v>3</v>
+      </c>
+      <c r="D10" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="3">
+        <v>3</v>
+      </c>
+      <c r="D11" s="3"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
+      <c r="A13" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3</v>
+      </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="A15" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3</v>
+      </c>
+      <c r="D16" s="3"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
+      <c r="A17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" s="3">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="A18" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="3">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="A19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="3">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C20" s="3">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="A21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="3">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
+      <c r="A22" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
+      <c r="A23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C23" s="3">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="A24" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
+      <c r="A25" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C25" s="3">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="A26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="3">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
+      <c r="A27" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C27" s="3">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
+      <c r="A28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C28" s="3">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
+      <c r="A29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="3">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
+      <c r="A30" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
+      <c r="A31" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
+      <c r="A32" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+      <c r="A33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="C33" s="3">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
+      <c r="A34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="3">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="6"/>
+      <c r="A35" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C35" s="3">
+        <v>1</v>
+      </c>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="6"/>
-      <c r="B36" s="6"/>
-      <c r="C36" s="6"/>
-      <c r="D36" s="6"/>
+      <c r="A36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C36" s="3">
+        <v>1</v>
+      </c>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
+      <c r="A37" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="3">
+        <v>1</v>
+      </c>
+      <c r="D37" s="3"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
+      <c r="A38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C38" s="3">
+        <v>1</v>
+      </c>
+      <c r="D38" s="3"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
+      <c r="A39" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1</v>
+      </c>
+      <c r="D39" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="A40" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C40" s="3">
+        <v>1</v>
+      </c>
+      <c r="D40" s="3"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
+      <c r="A41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" s="3">
+        <v>1</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C42" s="3">
+        <v>1</v>
+      </c>
+      <c r="D42" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="A43" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C43" s="3">
+        <v>1</v>
+      </c>
+      <c r="D43" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
+      <c r="A44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="3">
+        <v>1</v>
+      </c>
+      <c r="D44" s="3"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
-      <c r="D45" s="6"/>
+      <c r="A45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="3">
+        <v>1</v>
+      </c>
+      <c r="D45" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
+      <c r="A46" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>943</v>
+      </c>
+      <c r="C46" s="3">
+        <v>1</v>
+      </c>
+      <c r="D46" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
+      <c r="A47" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="C47" s="3">
+        <v>1</v>
+      </c>
+      <c r="D47" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
+      <c r="A48" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C48" s="3">
+        <v>1</v>
+      </c>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="6"/>
+      <c r="A49" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C49" s="3">
+        <v>1</v>
+      </c>
+      <c r="D49" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
-      <c r="D50" s="6"/>
+      <c r="A50" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="3">
+        <v>1</v>
+      </c>
+      <c r="D50" s="3"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
-      <c r="D51" s="6"/>
+      <c r="A51" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" s="3">
+        <v>1</v>
+      </c>
+      <c r="D51" s="3"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
-      <c r="D52" s="6"/>
+      <c r="A52" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C52" s="3">
+        <v>1</v>
+      </c>
+      <c r="D52" s="3"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
+      <c r="A53" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="3">
+        <v>1</v>
+      </c>
+      <c r="D53" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
+      <c r="A54" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C54" s="3">
+        <v>1</v>
+      </c>
+      <c r="D54" s="3"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
+      <c r="A55" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="3">
+        <v>1</v>
+      </c>
+      <c r="D55" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
+      <c r="A56" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C56" s="3">
+        <v>1</v>
+      </c>
+      <c r="D56" s="3"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
+      <c r="A57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C57" s="3">
+        <v>1</v>
+      </c>
+      <c r="D57" s="3"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
+      <c r="A58" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C58" s="3">
+        <v>1</v>
+      </c>
+      <c r="D58" s="3"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
+      <c r="A59" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C59" s="3">
+        <v>1</v>
+      </c>
+      <c r="D59" s="3"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
+      <c r="A60" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>942</v>
+      </c>
+      <c r="C60" s="3">
+        <v>1</v>
+      </c>
+      <c r="D60" s="3"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
+      <c r="A61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="C61" s="3">
+        <v>1</v>
+      </c>
+      <c r="D61" s="3"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
+      <c r="A62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="C62" s="3">
+        <v>1</v>
+      </c>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
+      <c r="A63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63" s="3">
+        <v>1</v>
+      </c>
+      <c r="D63" s="3"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
+      <c r="A64" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1</v>
+      </c>
+      <c r="D64" s="3"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
+      <c r="A65" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1</v>
+      </c>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
+      <c r="A66" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1</v>
+      </c>
+      <c r="D66" s="3"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
+      <c r="A67" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C67" s="3">
+        <v>1</v>
+      </c>
+      <c r="D67" s="3"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
+      <c r="A68" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>934</v>
+      </c>
+      <c r="C68" s="3">
+        <v>1</v>
+      </c>
+      <c r="D68" s="3"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
-      <c r="C69" s="6"/>
-      <c r="D69" s="6"/>
+      <c r="A69" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="C69" s="3"/>
+      <c r="D69" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
+      <c r="A70" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C70" s="3"/>
+      <c r="D70" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
+      <c r="A71" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C71" s="3"/>
+      <c r="D71" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
+      <c r="A72" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" s="3"/>
+      <c r="D72" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
-      <c r="C73" s="6"/>
-      <c r="D73" s="6"/>
+      <c r="A73" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
-      <c r="C74" s="6"/>
-      <c r="D74" s="6"/>
+      <c r="A74" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C74" s="3"/>
+      <c r="D74" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
+      <c r="A75" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>929</v>
+      </c>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6"/>
-      <c r="D76" s="6"/>
+      <c r="A76" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C76" s="3"/>
+      <c r="D76" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="6"/>
-      <c r="D77" s="6"/>
+      <c r="A77" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3">
+        <v>3</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="6"/>
+      <c r="A78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C78" s="3"/>
+      <c r="D78" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
-      <c r="C79" s="6"/>
-      <c r="D79" s="6"/>
+      <c r="A79" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C79" s="3"/>
+      <c r="D79" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
-      <c r="C80" s="6"/>
-      <c r="D80" s="6"/>
+      <c r="A80" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C80" s="3"/>
+      <c r="D80" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
-      <c r="C81" s="6"/>
-      <c r="D81" s="6"/>
+      <c r="A81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C81" s="3"/>
+      <c r="D81" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="6"/>
+      <c r="A82" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
-      <c r="C83" s="6"/>
-      <c r="D83" s="6"/>
+      <c r="A83" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C83" s="3"/>
+      <c r="D83" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
-      <c r="C84" s="6"/>
-      <c r="D84" s="6"/>
+      <c r="A84" s="3" t="s">
+        <v>964</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C84" s="3"/>
+      <c r="D84" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
-      <c r="C85" s="6"/>
-      <c r="D85" s="6"/>
+      <c r="A85" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>932</v>
+      </c>
+      <c r="C85" s="3"/>
+      <c r="D85" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
-      <c r="C86" s="6"/>
-      <c r="D86" s="6"/>
+      <c r="A86" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86" s="3"/>
+      <c r="D86" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
+      <c r="A87" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>935</v>
+      </c>
+      <c r="C87" s="3"/>
+      <c r="D87" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="6"/>
+      <c r="A88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C88" s="3"/>
+      <c r="D88" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
+      <c r="A89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C89" s="3"/>
+      <c r="D89" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
-      <c r="C90" s="6"/>
-      <c r="D90" s="6"/>
+      <c r="A90" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C90" s="3"/>
+      <c r="D90" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
-      <c r="C91" s="6"/>
-      <c r="D91" s="6"/>
+      <c r="A91" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="C91" s="3"/>
+      <c r="D91" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
+      <c r="A92" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C92" s="3"/>
+      <c r="D92" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
-      <c r="C93" s="6"/>
-      <c r="D93" s="6"/>
+      <c r="A93" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C93" s="3"/>
+      <c r="D93" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
-      <c r="C94" s="6"/>
-      <c r="D94" s="6"/>
+      <c r="A94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
-      <c r="C95" s="6"/>
-      <c r="D95" s="6"/>
+      <c r="A95" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
-      <c r="C96" s="6"/>
-      <c r="D96" s="6"/>
+      <c r="A96" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C96" s="3"/>
+      <c r="D96" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
-      <c r="C97" s="6"/>
-      <c r="D97" s="6"/>
+      <c r="A97" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C97" s="3"/>
+      <c r="D97" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
-      <c r="C98" s="6"/>
-      <c r="D98" s="6"/>
+      <c r="A98" s="3"/>
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
-      <c r="C99" s="6"/>
-      <c r="D99" s="6"/>
+      <c r="A99" s="3"/>
+      <c r="B99" s="3"/>
+      <c r="C99" s="3"/>
+      <c r="D99" s="3"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
+      <c r="A100" s="3"/>
+      <c r="B100" s="3"/>
+      <c r="C100" s="3"/>
+      <c r="D100" s="3"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="6"/>
+      <c r="A101" s="3"/>
+      <c r="B101" s="3"/>
+      <c r="C101" s="3"/>
+      <c r="D101" s="3"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
-      <c r="C102" s="6"/>
-      <c r="D102" s="6"/>
+      <c r="A102" s="3"/>
+      <c r="B102" s="3"/>
+      <c r="C102" s="3"/>
+      <c r="D102" s="3"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
+      <c r="A103" s="3"/>
+      <c r="B103" s="3"/>
+      <c r="C103" s="3"/>
+      <c r="D103" s="3"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
-      <c r="C104" s="6"/>
-      <c r="D104" s="6"/>
+      <c r="A104" s="3"/>
+      <c r="B104" s="3"/>
+      <c r="C104" s="3"/>
+      <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="6"/>
+      <c r="A105" s="3"/>
+      <c r="B105" s="3"/>
+      <c r="C105" s="3"/>
+      <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
+      <c r="A106" s="3"/>
+      <c r="B106" s="3"/>
+      <c r="C106" s="3"/>
+      <c r="D106" s="3"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="6"/>
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
-      <c r="C108" s="6"/>
-      <c r="D108" s="6"/>
+      <c r="A108" s="3"/>
+      <c r="B108" s="3"/>
+      <c r="C108" s="3"/>
+      <c r="D108" s="3"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
-      <c r="C109" s="6"/>
-      <c r="D109" s="6"/>
+      <c r="A109" s="3"/>
+      <c r="B109" s="3"/>
+      <c r="C109" s="3"/>
+      <c r="D109" s="3"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
-      <c r="C110" s="6"/>
-      <c r="D110" s="6"/>
+      <c r="A110" s="3"/>
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="6"/>
+      <c r="A111" s="3"/>
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
+      <c r="A112" s="3"/>
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="3"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
-      <c r="C113" s="6"/>
-      <c r="D113" s="6"/>
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
-      <c r="C114" s="6"/>
-      <c r="D114" s="6"/>
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
-      <c r="C115" s="6"/>
-      <c r="D115" s="6"/>
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
-      <c r="C116" s="6"/>
-      <c r="D116" s="6"/>
+      <c r="A116" s="3"/>
+      <c r="B116" s="3"/>
+      <c r="C116" s="3"/>
+      <c r="D116" s="3"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
-      <c r="C117" s="6"/>
-      <c r="D117" s="6"/>
+      <c r="A117" s="3"/>
+      <c r="B117" s="3"/>
+      <c r="C117" s="3"/>
+      <c r="D117" s="3"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
+      <c r="A118" s="3"/>
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
-      <c r="C119" s="6"/>
-      <c r="D119" s="6"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
+      <c r="A120" s="3"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6"/>
+      <c r="A121" s="3"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
-      <c r="C122" s="6"/>
-      <c r="D122" s="6"/>
+      <c r="A122" s="3"/>
+      <c r="B122" s="3"/>
+      <c r="C122" s="3"/>
+      <c r="D122" s="3"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
-      <c r="C123" s="6"/>
-      <c r="D123" s="6"/>
+      <c r="A123" s="3"/>
+      <c r="B123" s="3"/>
+      <c r="C123" s="3"/>
+      <c r="D123" s="3"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
-      <c r="C124" s="6"/>
-      <c r="D124" s="6"/>
+      <c r="A124" s="3"/>
+      <c r="B124" s="3"/>
+      <c r="C124" s="3"/>
+      <c r="D124" s="3"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
-      <c r="C125" s="6"/>
-      <c r="D125" s="6"/>
+      <c r="A125" s="3"/>
+      <c r="B125" s="3"/>
+      <c r="C125" s="3"/>
+      <c r="D125" s="3"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
-      <c r="C126" s="6"/>
-      <c r="D126" s="6"/>
+      <c r="A126" s="3"/>
+      <c r="B126" s="3"/>
+      <c r="C126" s="3"/>
+      <c r="D126" s="3"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
-      <c r="C127" s="6"/>
-      <c r="D127" s="6"/>
+      <c r="A127" s="3"/>
+      <c r="B127" s="3"/>
+      <c r="C127" s="3"/>
+      <c r="D127" s="3"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
+      <c r="A128" s="3"/>
+      <c r="B128" s="3"/>
+      <c r="C128" s="3"/>
+      <c r="D128" s="3"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
-      <c r="C129" s="6"/>
-      <c r="D129" s="6"/>
+      <c r="A129" s="3"/>
+      <c r="B129" s="3"/>
+      <c r="C129" s="3"/>
+      <c r="D129" s="3"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
-      <c r="C130" s="6"/>
-      <c r="D130" s="6"/>
+      <c r="A130" s="3"/>
+      <c r="B130" s="3"/>
+      <c r="C130" s="3"/>
+      <c r="D130" s="3"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
-      <c r="D131" s="6"/>
+      <c r="A131" s="3"/>
+      <c r="B131" s="3"/>
+      <c r="C131" s="3"/>
+      <c r="D131" s="3"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
-      <c r="C132" s="6"/>
-      <c r="D132" s="6"/>
+      <c r="A132" s="3"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
-      <c r="C133" s="6"/>
-      <c r="D133" s="6"/>
+      <c r="A133" s="3"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
-      <c r="D134" s="6"/>
+      <c r="A134" s="3"/>
+      <c r="B134" s="3"/>
+      <c r="C134" s="3"/>
+      <c r="D134" s="3"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
-      <c r="D135" s="6"/>
+      <c r="A135" s="3"/>
+      <c r="B135" s="3"/>
+      <c r="C135" s="3"/>
+      <c r="D135" s="3"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="6"/>
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
-      <c r="D138" s="6"/>
+      <c r="A138" s="3"/>
+      <c r="B138" s="3"/>
+      <c r="C138" s="3"/>
+      <c r="D138" s="3"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
+      <c r="A139" s="3"/>
+      <c r="B139" s="3"/>
+      <c r="C139" s="3"/>
+      <c r="D139" s="3"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="6"/>
-      <c r="D140" s="6"/>
+      <c r="A140" s="3"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="6"/>
-      <c r="D141" s="6"/>
+      <c r="A141" s="3"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
-      <c r="C142" s="6"/>
-      <c r="D142" s="6"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
-      <c r="D143" s="6"/>
+      <c r="A143" s="3"/>
+      <c r="B143" s="3"/>
+      <c r="C143" s="3"/>
+      <c r="D143" s="3"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
-      <c r="D144" s="6"/>
+      <c r="A144" s="3"/>
+      <c r="B144" s="3"/>
+      <c r="C144" s="3"/>
+      <c r="D144" s="3"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
-      <c r="D145" s="6"/>
+      <c r="A145" s="3"/>
+      <c r="B145" s="3"/>
+      <c r="C145" s="3"/>
+      <c r="D145" s="3"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
-      <c r="D146" s="6"/>
+      <c r="A146" s="3"/>
+      <c r="B146" s="3"/>
+      <c r="C146" s="3"/>
+      <c r="D146" s="3"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
-      <c r="D147" s="6"/>
+      <c r="A147" s="3"/>
+      <c r="B147" s="3"/>
+      <c r="C147" s="3"/>
+      <c r="D147" s="3"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
-      <c r="C148" s="6"/>
-      <c r="D148" s="6"/>
+      <c r="A148" s="3"/>
+      <c r="B148" s="3"/>
+      <c r="C148" s="3"/>
+      <c r="D148" s="3"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
-      <c r="C149" s="6"/>
-      <c r="D149" s="6"/>
+      <c r="A149" s="3"/>
+      <c r="B149" s="3"/>
+      <c r="C149" s="3"/>
+      <c r="D149" s="3"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
-      <c r="C150" s="6"/>
-      <c r="D150" s="6"/>
+      <c r="A150" s="3"/>
+      <c r="B150" s="3"/>
+      <c r="C150" s="3"/>
+      <c r="D150" s="3"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
-      <c r="C151" s="6"/>
-      <c r="D151" s="6"/>
+      <c r="A151" s="3"/>
+      <c r="B151" s="3"/>
+      <c r="C151" s="3"/>
+      <c r="D151" s="3"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="6"/>
-      <c r="D152" s="6"/>
+      <c r="A152" s="3"/>
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="6"/>
-      <c r="D153" s="6"/>
+      <c r="A153" s="3"/>
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
-      <c r="C154" s="6"/>
-      <c r="D154" s="6"/>
+      <c r="A154" s="3"/>
+      <c r="B154" s="3"/>
+      <c r="C154" s="3"/>
+      <c r="D154" s="3"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
-      <c r="C155" s="6"/>
-      <c r="D155" s="6"/>
+      <c r="A155" s="3"/>
+      <c r="B155" s="3"/>
+      <c r="C155" s="3"/>
+      <c r="D155" s="3"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
-      <c r="C156" s="6"/>
-      <c r="D156" s="6"/>
+      <c r="A156" s="3"/>
+      <c r="B156" s="3"/>
+      <c r="C156" s="3"/>
+      <c r="D156" s="3"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
-      <c r="C157" s="6"/>
-      <c r="D157" s="6"/>
+      <c r="A157" s="3"/>
+      <c r="B157" s="3"/>
+      <c r="C157" s="3"/>
+      <c r="D157" s="3"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
-      <c r="C158" s="6"/>
-      <c r="D158" s="6"/>
+      <c r="A158" s="3"/>
+      <c r="B158" s="3"/>
+      <c r="C158" s="3"/>
+      <c r="D158" s="3"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
-      <c r="C159" s="6"/>
-      <c r="D159" s="6"/>
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
-      <c r="D160" s="6"/>
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
-      <c r="C161" s="6"/>
-      <c r="D161" s="6"/>
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
+      <c r="C161" s="3"/>
+      <c r="D161" s="3"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
-      <c r="C162" s="6"/>
-      <c r="D162" s="6"/>
+      <c r="A162" s="3"/>
+      <c r="B162" s="3"/>
+      <c r="C162" s="3"/>
+      <c r="D162" s="3"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
-      <c r="C163" s="6"/>
-      <c r="D163" s="6"/>
+      <c r="A163" s="3"/>
+      <c r="B163" s="3"/>
+      <c r="C163" s="3"/>
+      <c r="D163" s="3"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
-      <c r="C164" s="6"/>
-      <c r="D164" s="6"/>
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3"/>
+      <c r="D164" s="3"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
-      <c r="C165" s="6"/>
-      <c r="D165" s="6"/>
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3"/>
+      <c r="D165" s="3"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
-      <c r="C166" s="6"/>
-      <c r="D166" s="6"/>
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A167" s="6"/>
-      <c r="B167" s="6"/>
-      <c r="C167" s="6"/>
-      <c r="D167" s="6"/>
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A168" s="6"/>
-      <c r="B168" s="6"/>
-      <c r="C168" s="6"/>
-      <c r="D168" s="6"/>
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
+      <c r="C168" s="3"/>
+      <c r="D168" s="3"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="6"/>
-      <c r="B169" s="6"/>
-      <c r="C169" s="6"/>
-      <c r="D169" s="6"/>
+      <c r="A169" s="3"/>
+      <c r="B169" s="3"/>
+      <c r="C169" s="3"/>
+      <c r="D169" s="3"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="6"/>
-      <c r="B170" s="6"/>
-      <c r="C170" s="6"/>
-      <c r="D170" s="6"/>
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3"/>
+      <c r="D170" s="3"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="6"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="6"/>
-      <c r="D171" s="6"/>
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3"/>
+      <c r="D171" s="3"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="6"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="6"/>
-      <c r="D172" s="6"/>
+      <c r="A172" s="3"/>
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="6"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="6"/>
-      <c r="D173" s="6"/>
+      <c r="A173" s="3"/>
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="6"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="6"/>
-      <c r="D174" s="6"/>
+      <c r="A174" s="3"/>
+      <c r="B174" s="3"/>
+      <c r="C174" s="3"/>
+      <c r="D174" s="3"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="6"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="6"/>
-      <c r="D175" s="6"/>
+      <c r="A175" s="3"/>
+      <c r="B175" s="3"/>
+      <c r="C175" s="3"/>
+      <c r="D175" s="3"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="6"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="6"/>
-      <c r="D176" s="6"/>
+      <c r="A176" s="3"/>
+      <c r="B176" s="3"/>
+      <c r="C176" s="3"/>
+      <c r="D176" s="3"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="6"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="6"/>
-      <c r="D177" s="6"/>
+      <c r="A177" s="3"/>
+      <c r="B177" s="3"/>
+      <c r="C177" s="3"/>
+      <c r="D177" s="3"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="6"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="6"/>
-      <c r="D178" s="6"/>
+      <c r="A178" s="3"/>
+      <c r="B178" s="3"/>
+      <c r="C178" s="3"/>
+      <c r="D178" s="3"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="6"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="6"/>
-      <c r="D179" s="6"/>
+      <c r="A179" s="3"/>
+      <c r="B179" s="3"/>
+      <c r="C179" s="3"/>
+      <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="6"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
+      <c r="A180" s="3"/>
+      <c r="B180" s="3"/>
+      <c r="C180" s="3"/>
+      <c r="D180" s="3"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="6"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="6"/>
-      <c r="D181" s="6"/>
+      <c r="A181" s="3"/>
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="6"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="6"/>
-      <c r="D182" s="6"/>
+      <c r="A182" s="3"/>
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="6"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="6"/>
-      <c r="D183" s="6"/>
+      <c r="A183" s="3"/>
+      <c r="B183" s="3"/>
+      <c r="C183" s="3"/>
+      <c r="D183" s="3"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="6"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="6"/>
-      <c r="D184" s="6"/>
+      <c r="A184" s="3"/>
+      <c r="B184" s="3"/>
+      <c r="C184" s="3"/>
+      <c r="D184" s="3"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="6"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="6"/>
-      <c r="D185" s="6"/>
+      <c r="A185" s="3"/>
+      <c r="B185" s="3"/>
+      <c r="C185" s="3"/>
+      <c r="D185" s="3"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="6"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="6"/>
-      <c r="D186" s="6"/>
+      <c r="A186" s="3"/>
+      <c r="B186" s="3"/>
+      <c r="C186" s="3"/>
+      <c r="D186" s="3"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="6"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="6"/>
-      <c r="D187" s="6"/>
+      <c r="A187" s="3"/>
+      <c r="B187" s="3"/>
+      <c r="C187" s="3"/>
+      <c r="D187" s="3"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="6"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="6"/>
-      <c r="D188" s="6"/>
+      <c r="A188" s="3"/>
+      <c r="B188" s="3"/>
+      <c r="C188" s="3"/>
+      <c r="D188" s="3"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="6"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="6"/>
-      <c r="D189" s="6"/>
+      <c r="A189" s="3"/>
+      <c r="B189" s="3"/>
+      <c r="C189" s="3"/>
+      <c r="D189" s="3"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="6"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="6"/>
-      <c r="D190" s="6"/>
+      <c r="A190" s="3"/>
+      <c r="B190" s="3"/>
+      <c r="C190" s="3"/>
+      <c r="D190" s="3"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="6"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="6"/>
-      <c r="D191" s="6"/>
+      <c r="A191" s="3"/>
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="6"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="6"/>
-      <c r="D192" s="6"/>
+      <c r="A192" s="3"/>
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="6"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="6"/>
-      <c r="D193" s="6"/>
+      <c r="A193" s="3"/>
+      <c r="B193" s="3"/>
+      <c r="C193" s="3"/>
+      <c r="D193" s="3"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="6"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="6"/>
-      <c r="D194" s="6"/>
+      <c r="A194" s="3"/>
+      <c r="B194" s="3"/>
+      <c r="C194" s="3"/>
+      <c r="D194" s="3"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A195" s="6"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="6"/>
-      <c r="D195" s="6"/>
+      <c r="A195" s="3"/>
+      <c r="B195" s="3"/>
+      <c r="C195" s="3"/>
+      <c r="D195" s="3"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A196" s="6"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="6"/>
-      <c r="D196" s="6"/>
+      <c r="A196" s="3"/>
+      <c r="B196" s="3"/>
+      <c r="C196" s="3"/>
+      <c r="D196" s="3"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A197" s="6"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="6"/>
-      <c r="D197" s="6"/>
+      <c r="A197" s="3"/>
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A198" s="6"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="6"/>
-      <c r="D198" s="6"/>
+      <c r="A198" s="3"/>
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A199" s="6"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="6"/>
-      <c r="D199" s="6"/>
+      <c r="A199" s="3"/>
+      <c r="B199" s="3"/>
+      <c r="C199" s="3"/>
+      <c r="D199" s="3"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A200" s="6"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="6"/>
-      <c r="D200" s="6"/>
+      <c r="A200" s="3"/>
+      <c r="B200" s="3"/>
+      <c r="C200" s="3"/>
+      <c r="D200" s="3"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A201" s="6"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="6"/>
-      <c r="D201" s="6"/>
+      <c r="A201" s="3"/>
+      <c r="B201" s="3"/>
+      <c r="C201" s="3"/>
+      <c r="D201" s="3"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A202" s="6"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="6"/>
-      <c r="D202" s="6"/>
+      <c r="A202" s="3"/>
+      <c r="B202" s="3"/>
+      <c r="C202" s="3"/>
+      <c r="D202" s="3"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A203" s="6"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="6"/>
-      <c r="D203" s="6"/>
+      <c r="A203" s="3"/>
+      <c r="B203" s="3"/>
+      <c r="C203" s="3"/>
+      <c r="D203" s="3"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A204" s="6"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="6"/>
-      <c r="D204" s="6"/>
+      <c r="A204" s="3"/>
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A205" s="6"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="6"/>
-      <c r="D205" s="6"/>
+      <c r="A205" s="3"/>
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A206" s="6"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="6"/>
-      <c r="D206" s="6"/>
+      <c r="A206" s="3"/>
+      <c r="B206" s="3"/>
+      <c r="C206" s="3"/>
+      <c r="D206" s="3"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A207" s="6"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="6"/>
-      <c r="D207" s="6"/>
+      <c r="A207" s="3"/>
+      <c r="B207" s="3"/>
+      <c r="C207" s="3"/>
+      <c r="D207" s="3"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A208" s="6"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="6"/>
-      <c r="D208" s="6"/>
+      <c r="A208" s="3"/>
+      <c r="B208" s="3"/>
+      <c r="C208" s="3"/>
+      <c r="D208" s="3"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A209" s="6"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="6"/>
-      <c r="D209" s="6"/>
+      <c r="A209" s="3"/>
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A210" s="6"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="6"/>
-      <c r="D210" s="6"/>
+      <c r="A210" s="3"/>
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A211" s="6"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="6"/>
-      <c r="D211" s="6"/>
+      <c r="A211" s="3"/>
+      <c r="B211" s="3"/>
+      <c r="C211" s="3"/>
+      <c r="D211" s="3"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A212" s="6"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="6"/>
-      <c r="D212" s="6"/>
+      <c r="A212" s="3"/>
+      <c r="B212" s="3"/>
+      <c r="C212" s="3"/>
+      <c r="D212" s="3"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A213" s="6"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="6"/>
-      <c r="D213" s="6"/>
+      <c r="A213" s="3"/>
+      <c r="B213" s="3"/>
+      <c r="C213" s="3"/>
+      <c r="D213" s="3"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A214" s="6"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="6"/>
-      <c r="D214" s="6"/>
+      <c r="A214" s="3"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A215" s="6"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="6"/>
-      <c r="D215" s="6"/>
+      <c r="A215" s="3"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A216" s="6"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="6"/>
-      <c r="D216" s="6"/>
+      <c r="A216" s="3"/>
+      <c r="B216" s="3"/>
+      <c r="C216" s="3"/>
+      <c r="D216" s="3"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A217" s="6"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="6"/>
-      <c r="D217" s="6"/>
+      <c r="A217" s="3"/>
+      <c r="B217" s="3"/>
+      <c r="C217" s="3"/>
+      <c r="D217" s="3"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A218" s="6"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="6"/>
-      <c r="D218" s="6"/>
+      <c r="A218" s="3"/>
+      <c r="B218" s="3"/>
+      <c r="C218" s="3"/>
+      <c r="D218" s="3"/>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A219" s="6"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="6"/>
-      <c r="D219" s="6"/>
+      <c r="A219" s="3"/>
+      <c r="B219" s="3"/>
+      <c r="C219" s="3"/>
+      <c r="D219" s="3"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A220" s="6"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="6"/>
-      <c r="D220" s="6"/>
+      <c r="A220" s="3"/>
+      <c r="B220" s="3"/>
+      <c r="C220" s="3"/>
+      <c r="D220" s="3"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A221" s="6"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="6"/>
-      <c r="D221" s="6"/>
+      <c r="A221" s="3"/>
+      <c r="B221" s="3"/>
+      <c r="C221" s="3"/>
+      <c r="D221" s="3"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A222" s="6"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="6"/>
-      <c r="D222" s="6"/>
+      <c r="A222" s="3"/>
+      <c r="B222" s="3"/>
+      <c r="C222" s="3"/>
+      <c r="D222" s="3"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A223" s="6"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="6"/>
-      <c r="D223" s="6"/>
+      <c r="A223" s="3"/>
+      <c r="B223" s="3"/>
+      <c r="C223" s="3"/>
+      <c r="D223" s="3"/>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A224" s="6"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
+      <c r="A224" s="3"/>
+      <c r="B224" s="3"/>
+      <c r="C224" s="3"/>
+      <c r="D224" s="3"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A225" s="6"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="6"/>
-      <c r="D225" s="6"/>
+      <c r="A225" s="3"/>
+      <c r="B225" s="3"/>
+      <c r="C225" s="3"/>
+      <c r="D225" s="3"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A226" s="6"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="6"/>
-      <c r="D226" s="6"/>
+      <c r="A226" s="3"/>
+      <c r="B226" s="3"/>
+      <c r="C226" s="3"/>
+      <c r="D226" s="3"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A227" s="6"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="6"/>
-      <c r="D227" s="6"/>
+      <c r="A227" s="3"/>
+      <c r="B227" s="3"/>
+      <c r="C227" s="3"/>
+      <c r="D227" s="3"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A228" s="6"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="6"/>
-      <c r="D228" s="6"/>
+      <c r="A228" s="3"/>
+      <c r="B228" s="3"/>
+      <c r="C228" s="3"/>
+      <c r="D228" s="3"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A229" s="6"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="6"/>
-      <c r="D229" s="6"/>
+      <c r="A229" s="3"/>
+      <c r="B229" s="3"/>
+      <c r="C229" s="3"/>
+      <c r="D229" s="3"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A230" s="6"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="6"/>
-      <c r="D230" s="6"/>
+      <c r="A230" s="3"/>
+      <c r="B230" s="3"/>
+      <c r="C230" s="3"/>
+      <c r="D230" s="3"/>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A231" s="6"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="6"/>
-      <c r="D231" s="6"/>
+      <c r="A231" s="3"/>
+      <c r="B231" s="3"/>
+      <c r="C231" s="3"/>
+      <c r="D231" s="3"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A232" s="6"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="6"/>
-      <c r="D232" s="6"/>
+      <c r="A232" s="3"/>
+      <c r="B232" s="3"/>
+      <c r="C232" s="3"/>
+      <c r="D232" s="3"/>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A233" s="6"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="6"/>
-      <c r="D233" s="6"/>
+      <c r="A233" s="3"/>
+      <c r="B233" s="3"/>
+      <c r="C233" s="3"/>
+      <c r="D233" s="3"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A234" s="6"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="6"/>
+      <c r="A234" s="3"/>
+      <c r="B234" s="3"/>
+      <c r="C234" s="3"/>
+      <c r="D234" s="3"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A235" s="6"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="6"/>
-      <c r="D235" s="6"/>
+      <c r="A235" s="3"/>
+      <c r="B235" s="3"/>
+      <c r="C235" s="3"/>
+      <c r="D235" s="3"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A236" s="6"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="6"/>
-      <c r="D236" s="6"/>
+      <c r="A236" s="3"/>
+      <c r="B236" s="3"/>
+      <c r="C236" s="3"/>
+      <c r="D236" s="3"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A237" s="6"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="6"/>
-      <c r="D237" s="6"/>
+      <c r="A237" s="3"/>
+      <c r="B237" s="3"/>
+      <c r="C237" s="3"/>
+      <c r="D237" s="3"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A238" s="6"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="6"/>
-      <c r="D238" s="6"/>
+      <c r="A238" s="3"/>
+      <c r="B238" s="3"/>
+      <c r="C238" s="3"/>
+      <c r="D238" s="3"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A239" s="6"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="6"/>
-      <c r="D239" s="6"/>
+      <c r="A239" s="3"/>
+      <c r="B239" s="3"/>
+      <c r="C239" s="3"/>
+      <c r="D239" s="3"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A240" s="6"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="6"/>
-      <c r="D240" s="6"/>
+      <c r="A240" s="3"/>
+      <c r="B240" s="3"/>
+      <c r="C240" s="3"/>
+      <c r="D240" s="3"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A241" s="6"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="6"/>
-      <c r="D241" s="6"/>
+      <c r="A241" s="3"/>
+      <c r="B241" s="3"/>
+      <c r="C241" s="3"/>
+      <c r="D241" s="3"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A242" s="6"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="6"/>
-      <c r="D242" s="6"/>
+      <c r="A242" s="3"/>
+      <c r="B242" s="3"/>
+      <c r="C242" s="3"/>
+      <c r="D242" s="3"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A243" s="6"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="6"/>
-      <c r="D243" s="6"/>
+      <c r="A243" s="3"/>
+      <c r="B243" s="3"/>
+      <c r="C243" s="3"/>
+      <c r="D243" s="3"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A244" s="6"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="6"/>
-      <c r="D244" s="6"/>
+      <c r="A244" s="3"/>
+      <c r="B244" s="3"/>
+      <c r="C244" s="3"/>
+      <c r="D244" s="3"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A245" s="6"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="6"/>
-      <c r="D245" s="6"/>
+      <c r="A245" s="3"/>
+      <c r="B245" s="3"/>
+      <c r="C245" s="3"/>
+      <c r="D245" s="3"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A246" s="6"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="6"/>
-      <c r="D246" s="6"/>
+      <c r="A246" s="3"/>
+      <c r="B246" s="3"/>
+      <c r="C246" s="3"/>
+      <c r="D246" s="3"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A247" s="6"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="6"/>
-      <c r="D247" s="6"/>
+      <c r="A247" s="3"/>
+      <c r="B247" s="3"/>
+      <c r="C247" s="3"/>
+      <c r="D247" s="3"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A248" s="6"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="6"/>
-      <c r="D248" s="6"/>
+      <c r="A248" s="3"/>
+      <c r="B248" s="3"/>
+      <c r="C248" s="3"/>
+      <c r="D248" s="3"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A249" s="6"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="6"/>
-      <c r="D249" s="6"/>
+      <c r="A249" s="3"/>
+      <c r="B249" s="3"/>
+      <c r="C249" s="3"/>
+      <c r="D249" s="3"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A250" s="6"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="6"/>
-      <c r="D250" s="6"/>
+      <c r="A250" s="3"/>
+      <c r="B250" s="3"/>
+      <c r="C250" s="3"/>
+      <c r="D250" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
-      <sortCondition descending="1" ref="D1"/>
+  <autoFilter ref="A1:D96" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D97">
+      <sortCondition descending="1" ref="C1:C96"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6DDBBF46-B864-4C5A-B837-66C2569C6E93}">
+          <x14:formula1>
+            <xm:f>BD!$A$1:$Q$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A250</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EDDCD597-0F56-4149-B25F-6A7DA2647F45}">
+          <x14:formula1>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A2, BD!$A$1:$Q$1, 0))</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B250</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -9731,7 +10478,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -10649,7 +11396,7 @@
         <v>945</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>873</v>
+        <v>966</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -11969,7 +12716,7 @@
         <v>921</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>964</v>
+        <v>967</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>698</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{617352F3-642D-46BD-95A9-7764B61B8C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0250245F-A251-43BE-B942-5B1DED4C907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="968">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -3832,10 +3832,10 @@
         <v>355</v>
       </c>
       <c r="C29" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D29" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -3916,10 +3916,10 @@
         <v>133</v>
       </c>
       <c r="C35" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D35" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -3930,7 +3930,7 @@
         <v>344</v>
       </c>
       <c r="C36" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D36" s="3">
         <v>1</v>
@@ -4040,10 +4040,10 @@
         <v>164</v>
       </c>
       <c r="C44" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D44" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4124,7 +4124,7 @@
         <v>185</v>
       </c>
       <c r="C50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50" s="3">
         <v>1</v>
@@ -4312,9 +4312,11 @@
         <v>941</v>
       </c>
       <c r="C64" s="3">
-        <v>2</v>
-      </c>
-      <c r="D64" s="3"/>
+        <v>3</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
@@ -4324,7 +4326,7 @@
         <v>314</v>
       </c>
       <c r="C65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65" s="3">
         <v>4</v>
@@ -4590,7 +4592,7 @@
         <v>966</v>
       </c>
       <c r="C84" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D84" s="3">
         <v>1</v>
@@ -4616,7 +4618,7 @@
         <v>186</v>
       </c>
       <c r="C86" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D86" s="3"/>
     </row>
@@ -4630,7 +4632,9 @@
       <c r="C87" s="3">
         <v>1</v>
       </c>
-      <c r="D87" s="3"/>
+      <c r="D87" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
@@ -4789,7 +4793,9 @@
       <c r="C100" s="3">
         <v>1</v>
       </c>
-      <c r="D100" s="3"/>
+      <c r="D100" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
@@ -4991,7 +4997,7 @@
         <v>160</v>
       </c>
       <c r="C117" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117" s="3"/>
     </row>
@@ -5100,7 +5106,7 @@
       </c>
       <c r="C126" s="3"/>
       <c r="D126" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
@@ -5172,7 +5178,7 @@
       </c>
       <c r="C132" s="3"/>
       <c r="D132" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.3">
@@ -5340,7 +5346,7 @@
       </c>
       <c r="C146" s="3"/>
       <c r="D146" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.3">
@@ -5508,7 +5514,7 @@
       </c>
       <c r="C160" s="3"/>
       <c r="D160" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
@@ -5604,127 +5610,253 @@
       </c>
       <c r="C168" s="3"/>
       <c r="D168" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
-      <c r="C169" s="3"/>
+      <c r="A169" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169" s="3">
+        <v>2</v>
+      </c>
       <c r="D169" s="3"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
+      <c r="A170" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" s="3" t="s">
+        <v>238</v>
+      </c>
       <c r="C170" s="3"/>
-      <c r="D170" s="3"/>
+      <c r="D170" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
+      <c r="A171" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C171" s="3">
+        <v>1</v>
+      </c>
       <c r="D171" s="3"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
+      <c r="A172" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C172" s="3">
+        <v>2</v>
+      </c>
+      <c r="D172" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
-      <c r="C173" s="3"/>
-      <c r="D173" s="3"/>
+      <c r="A173" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C173" s="3">
+        <v>1</v>
+      </c>
+      <c r="D173" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
-      <c r="C174" s="3"/>
+      <c r="A174" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B174" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C174" s="3">
+        <v>1</v>
+      </c>
       <c r="D174" s="3"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
-      <c r="C175" s="3"/>
+      <c r="A175" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B175" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C175" s="3">
+        <v>1</v>
+      </c>
       <c r="D175" s="3"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
+      <c r="A176" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B176" s="3" t="s">
+        <v>281</v>
+      </c>
       <c r="C176" s="3"/>
-      <c r="D176" s="3"/>
+      <c r="D176" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
+      <c r="A177" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B177" s="3" t="s">
+        <v>303</v>
+      </c>
       <c r="C177" s="3"/>
-      <c r="D177" s="3"/>
+      <c r="D177" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
+      <c r="A178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="C178" s="3"/>
-      <c r="D178" s="3"/>
+      <c r="D178" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
-      <c r="C179" s="3"/>
+      <c r="A179" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B179" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C179" s="3">
+        <v>3</v>
+      </c>
       <c r="D179" s="3"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
+      <c r="A180" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B180" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C180" s="3">
+        <v>1</v>
+      </c>
+      <c r="D180" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
+      <c r="A181" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B181" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="C181" s="3">
+        <v>2</v>
+      </c>
       <c r="D181" s="3"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
+      <c r="A182" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B182" s="3" t="s">
+        <v>101</v>
+      </c>
       <c r="C182" s="3"/>
-      <c r="D182" s="3"/>
+      <c r="D182" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
-      <c r="C183" s="3"/>
+      <c r="A183" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B183" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C183" s="3">
+        <v>1</v>
+      </c>
       <c r="D183" s="3"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
+      <c r="A184" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B184" s="3" t="s">
+        <v>149</v>
+      </c>
       <c r="C184" s="3"/>
-      <c r="D184" s="3"/>
+      <c r="D184" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
-      <c r="C185" s="3"/>
+      <c r="A185" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C185" s="3">
+        <v>1</v>
+      </c>
       <c r="D185" s="3"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
-      <c r="C186" s="3"/>
+      <c r="A186" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B186" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="C186" s="3">
+        <v>1</v>
+      </c>
       <c r="D186" s="3"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
+      <c r="A187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187" s="3" t="s">
+        <v>282</v>
+      </c>
       <c r="C187" s="3"/>
-      <c r="D187" s="3"/>
+      <c r="D187" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
-      <c r="C188" s="3"/>
+      <c r="A188" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C188" s="3">
+        <v>1</v>
+      </c>
       <c r="D188" s="3"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
@@ -6702,6 +6834,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6725,7 +6858,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -6737,7 +6870,7 @@
       </c>
       <c r="D2" s="3"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -6745,13 +6878,13 @@
         <v>168</v>
       </c>
       <c r="C3" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D3" s="3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>964</v>
       </c>
@@ -6765,7 +6898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
@@ -6777,7 +6910,7 @@
       </c>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>2</v>
       </c>
@@ -6791,7 +6924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -6805,7 +6938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
@@ -6816,10 +6949,10 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
@@ -6833,7 +6966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>14</v>
       </c>
@@ -6847,7 +6980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>964</v>
       </c>
@@ -6859,7 +6992,7 @@
       </c>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>1</v>
       </c>
@@ -6873,7 +7006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>928</v>
       </c>
@@ -6885,7 +7018,7 @@
       </c>
       <c r="D13" s="3"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
@@ -6893,11 +7026,11 @@
         <v>171</v>
       </c>
       <c r="C14" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D14" s="3"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>928</v>
       </c>
@@ -6911,7 +7044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
@@ -6923,7 +7056,7 @@
       </c>
       <c r="D16" s="3"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>2</v>
       </c>
@@ -6937,7 +7070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>2</v>
       </c>
@@ -6951,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>14</v>
       </c>
@@ -6965,7 +7098,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
@@ -6979,7 +7112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>4</v>
       </c>
@@ -6993,7 +7126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>964</v>
       </c>
@@ -7007,7 +7140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>10</v>
       </c>
@@ -7021,7 +7154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>964</v>
       </c>
@@ -7035,7 +7168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>964</v>
       </c>
@@ -7047,7 +7180,7 @@
       </c>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>1</v>
       </c>
@@ -7059,7 +7192,7 @@
       </c>
       <c r="D26" s="3"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>928</v>
       </c>
@@ -7071,7 +7204,7 @@
       </c>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>0</v>
       </c>
@@ -7083,7 +7216,7 @@
       </c>
       <c r="D28" s="3"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>14</v>
       </c>
@@ -7095,7 +7228,7 @@
       </c>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>14</v>
       </c>
@@ -7107,7 +7240,7 @@
       </c>
       <c r="D30" s="3"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>4</v>
       </c>
@@ -7118,10 +7251,10 @@
         <v>1</v>
       </c>
       <c r="D31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>9</v>
       </c>
@@ -7135,7 +7268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>4</v>
       </c>
@@ -7147,7 +7280,7 @@
       </c>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>10</v>
       </c>
@@ -7159,7 +7292,7 @@
       </c>
       <c r="D34" s="3"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>10</v>
       </c>
@@ -7167,11 +7300,13 @@
         <v>360</v>
       </c>
       <c r="C35" s="3">
-        <v>1</v>
-      </c>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>12</v>
       </c>
@@ -7183,7 +7318,7 @@
       </c>
       <c r="D36" s="3"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>0</v>
       </c>
@@ -7195,7 +7330,7 @@
       </c>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>11</v>
       </c>
@@ -7207,7 +7342,7 @@
       </c>
       <c r="D38" s="3"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>11</v>
       </c>
@@ -7215,13 +7350,13 @@
         <v>186</v>
       </c>
       <c r="C39" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>0</v>
       </c>
@@ -7233,7 +7368,7 @@
       </c>
       <c r="D40" s="3"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>2</v>
       </c>
@@ -7247,7 +7382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>6</v>
       </c>
@@ -7261,7 +7396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>6</v>
       </c>
@@ -7275,7 +7410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>8</v>
       </c>
@@ -7287,7 +7422,7 @@
       </c>
       <c r="D44" s="3"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
@@ -7301,7 +7436,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>928</v>
       </c>
@@ -7315,7 +7450,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>928</v>
       </c>
@@ -7329,7 +7464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>1</v>
       </c>
@@ -7341,7 +7476,7 @@
       </c>
       <c r="D48" s="3"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>2</v>
       </c>
@@ -7355,7 +7490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>14</v>
       </c>
@@ -7367,7 +7502,7 @@
       </c>
       <c r="D50" s="3"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>14</v>
       </c>
@@ -7379,7 +7514,7 @@
       </c>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>7</v>
       </c>
@@ -7391,7 +7526,7 @@
       </c>
       <c r="D52" s="3"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
         <v>7</v>
       </c>
@@ -7405,7 +7540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
         <v>1</v>
       </c>
@@ -7417,7 +7552,7 @@
       </c>
       <c r="D54" s="3"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>964</v>
       </c>
@@ -7431,7 +7566,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>964</v>
       </c>
@@ -7443,7 +7578,7 @@
       </c>
       <c r="D56" s="3"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>2</v>
       </c>
@@ -7455,7 +7590,7 @@
       </c>
       <c r="D57" s="3"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>14</v>
       </c>
@@ -7467,7 +7602,7 @@
       </c>
       <c r="D58" s="3"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>7</v>
       </c>
@@ -7479,7 +7614,7 @@
       </c>
       <c r="D59" s="3"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>928</v>
       </c>
@@ -7491,7 +7626,7 @@
       </c>
       <c r="D60" s="3"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>12</v>
       </c>
@@ -7501,9 +7636,11 @@
       <c r="C61" s="3">
         <v>1</v>
       </c>
-      <c r="D61" s="3"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D61" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>12</v>
       </c>
@@ -7515,7 +7652,7 @@
       </c>
       <c r="D62" s="3"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>11</v>
       </c>
@@ -7523,11 +7660,13 @@
         <v>170</v>
       </c>
       <c r="C63" s="3">
-        <v>1</v>
-      </c>
-      <c r="D63" s="3"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>8</v>
       </c>
@@ -7539,7 +7678,7 @@
       </c>
       <c r="D64" s="3"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>8</v>
       </c>
@@ -7551,7 +7690,7 @@
       </c>
       <c r="D65" s="3"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>2</v>
       </c>
@@ -7563,7 +7702,7 @@
       </c>
       <c r="D66" s="3"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>1</v>
       </c>
@@ -7575,7 +7714,7 @@
       </c>
       <c r="D67" s="3"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
         <v>928</v>
       </c>
@@ -7587,7 +7726,7 @@
       </c>
       <c r="D68" s="3"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
         <v>9</v>
       </c>
@@ -7599,7 +7738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
         <v>4</v>
       </c>
@@ -7611,7 +7750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
         <v>10</v>
       </c>
@@ -7623,7 +7762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
         <v>14</v>
       </c>
@@ -7635,7 +7774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
         <v>964</v>
       </c>
@@ -7647,7 +7786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
         <v>1</v>
       </c>
@@ -7659,7 +7798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
         <v>928</v>
       </c>
@@ -7671,7 +7810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
         <v>6</v>
       </c>
@@ -7683,7 +7822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
         <v>7</v>
       </c>
@@ -7695,7 +7834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
         <v>12</v>
       </c>
@@ -7707,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
         <v>964</v>
       </c>
@@ -7719,7 +7858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
         <v>2</v>
       </c>
@@ -7731,7 +7870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
         <v>8</v>
       </c>
@@ -7743,7 +7882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
         <v>4</v>
       </c>
@@ -7752,10 +7891,10 @@
       </c>
       <c r="C82" s="3"/>
       <c r="D82" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
         <v>964</v>
       </c>
@@ -7767,7 +7906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>964</v>
       </c>
@@ -7779,7 +7918,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
         <v>928</v>
       </c>
@@ -7791,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
         <v>7</v>
       </c>
@@ -7803,7 +7942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
         <v>928</v>
       </c>
@@ -7815,31 +7954,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="C88" s="3"/>
+      <c r="C88" s="3">
+        <v>1</v>
+      </c>
       <c r="D88" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C89" s="3"/>
+      <c r="C89" s="3">
+        <v>6</v>
+      </c>
       <c r="D89" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
         <v>0</v>
       </c>
@@ -7851,7 +7994,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
         <v>0</v>
       </c>
@@ -7863,7 +8006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
         <v>8</v>
       </c>
@@ -7875,7 +8018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
         <v>14</v>
       </c>
@@ -7887,7 +8030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
         <v>8</v>
       </c>
@@ -7899,7 +8042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
         <v>6</v>
       </c>
@@ -7911,7 +8054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
         <v>1</v>
       </c>
@@ -7923,7 +8066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
         <v>7</v>
       </c>
@@ -7935,95 +8078,195 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>280</v>
+      </c>
       <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
-      <c r="C99" s="3"/>
+      <c r="D98" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" s="3">
+        <v>1</v>
+      </c>
       <c r="D99" s="3"/>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
-      <c r="C100" s="3"/>
-      <c r="D100" s="3"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
-      <c r="C101" s="3"/>
-      <c r="D101" s="3"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C100" s="3">
+        <v>1</v>
+      </c>
+      <c r="D100" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C101" s="3">
+        <v>1</v>
+      </c>
+      <c r="D101" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C102" s="3">
+        <v>1</v>
+      </c>
+      <c r="D102" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>346</v>
+      </c>
       <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
+      <c r="D103" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B104" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1</v>
+      </c>
       <c r="D104" s="3"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
+      <c r="A105" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="3">
+        <v>5</v>
+      </c>
       <c r="D105" s="3"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
+      <c r="A106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" s="3" t="s">
+        <v>79</v>
+      </c>
       <c r="C106" s="3"/>
-      <c r="D106" s="3"/>
+      <c r="D106" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
-      <c r="C107" s="3"/>
+      <c r="A107" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C107" s="3">
+        <v>1</v>
+      </c>
       <c r="D107" s="3"/>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
-      <c r="C108" s="3"/>
-      <c r="D108" s="3"/>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1</v>
+      </c>
+      <c r="D108" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B109" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1</v>
+      </c>
       <c r="D109" s="3"/>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B110" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C110" s="3">
+        <v>2</v>
+      </c>
+      <c r="D110" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
+      <c r="A111" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>254</v>
+      </c>
       <c r="C111" s="3"/>
-      <c r="D111" s="3"/>
+      <c r="D111" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
+      <c r="A112" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>95</v>
+      </c>
       <c r="C112" s="3"/>
-      <c r="D112" s="3"/>
+      <c r="D112" s="3">
+        <v>2</v>
+      </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" s="3"/>
@@ -8854,7 +9097,12 @@
       <c r="D250" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D96" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="A1:D112" xr:uid="{00000000-0009-0000-0000-000003000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Borussia_Dortmund"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D97">
       <sortCondition descending="1" ref="C1:C96"/>
     </sortState>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0250245F-A251-43BE-B942-5B1DED4C907C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82585704-B76D-4A8C-A14A-C40E5CE159E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="968">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -3916,7 +3916,7 @@
         <v>133</v>
       </c>
       <c r="C35" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="3">
         <v>4</v>
@@ -4043,7 +4043,7 @@
         <v>6</v>
       </c>
       <c r="D44" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -4312,7 +4312,7 @@
         <v>941</v>
       </c>
       <c r="C64" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D64" s="3">
         <v>1</v>
@@ -5572,7 +5572,9 @@
       <c r="B165" s="3" t="s">
         <v>942</v>
       </c>
-      <c r="C165" s="3"/>
+      <c r="C165" s="3">
+        <v>1</v>
+      </c>
       <c r="D165" s="3">
         <v>1</v>
       </c>
@@ -5831,9 +5833,11 @@
         <v>940</v>
       </c>
       <c r="C186" s="3">
-        <v>1</v>
-      </c>
-      <c r="D186" s="3"/>
+        <v>2</v>
+      </c>
+      <c r="D186" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" s="3" t="s">
@@ -5860,10 +5864,16 @@
       <c r="D188" s="3"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
+      <c r="A189" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="B189" s="3" t="s">
+        <v>943</v>
+      </c>
       <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
+      <c r="D189" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" s="3"/>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82585704-B76D-4A8C-A14A-C40E5CE159E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D6320-9531-420A-A25E-683CDE7D6816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1020">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -3002,6 +3002,162 @@
   </si>
   <si>
     <t>DC Carlos Espi</t>
+  </si>
+  <si>
+    <t>Club_America</t>
+  </si>
+  <si>
+    <t>Yann Sommer</t>
+  </si>
+  <si>
+    <t>Luke Shaw</t>
+  </si>
+  <si>
+    <t>Alessandro Deiola</t>
+  </si>
+  <si>
+    <t>Amir Rrahmani</t>
+  </si>
+  <si>
+    <t>Joshua Kimmich</t>
+  </si>
+  <si>
+    <t>Sergio Busquets</t>
+  </si>
+  <si>
+    <t>Seko Fofana</t>
+  </si>
+  <si>
+    <t>Lee Jae-sung</t>
+  </si>
+  <si>
+    <t>Rodrigo Garro</t>
+  </si>
+  <si>
+    <t>Gerard Moreno</t>
+  </si>
+  <si>
+    <t>Alessandro Del Piero</t>
+  </si>
+  <si>
+    <t>Lucas Perri</t>
+  </si>
+  <si>
+    <t>Sebastián Cáceres</t>
+  </si>
+  <si>
+    <t>Miguel Layún</t>
+  </si>
+  <si>
+    <t>Lucas Digne</t>
+  </si>
+  <si>
+    <t>Ross Barkley</t>
+  </si>
+  <si>
+    <t>Yacine Adli</t>
+  </si>
+  <si>
+    <t>Álvaro Fidalgo</t>
+  </si>
+  <si>
+    <t>Tommaso Baldanzi</t>
+  </si>
+  <si>
+    <t>Olivier Giroud</t>
+  </si>
+  <si>
+    <t>Florian Thauvin</t>
+  </si>
+  <si>
+    <t>Ciro Immobile</t>
+  </si>
+  <si>
+    <t>Gabriel Barbosa</t>
+  </si>
+  <si>
+    <t>Club America</t>
+  </si>
+  <si>
+    <t>PT Yann Sommer</t>
+  </si>
+  <si>
+    <t>LI Luke Shaw</t>
+  </si>
+  <si>
+    <t>MC Alessandro Deiola</t>
+  </si>
+  <si>
+    <t>CT Amir Rrahmani</t>
+  </si>
+  <si>
+    <t>MCD Joshua Kimmich</t>
+  </si>
+  <si>
+    <t>MCD Sergio Busquets</t>
+  </si>
+  <si>
+    <t>MC Seko Fofana</t>
+  </si>
+  <si>
+    <t>MP Lee Jae-sung</t>
+  </si>
+  <si>
+    <t>MP Rodrigo Garro</t>
+  </si>
+  <si>
+    <t>DC Gerard Moreno</t>
+  </si>
+  <si>
+    <t>DC Alessandro Del Piero</t>
+  </si>
+  <si>
+    <t>PT Lucas Perri</t>
+  </si>
+  <si>
+    <t>CT Sebastián Cáceres</t>
+  </si>
+  <si>
+    <t>LD Miguel Layún</t>
+  </si>
+  <si>
+    <t>LI Lucas Digne</t>
+  </si>
+  <si>
+    <t>MC Ross Barkley</t>
+  </si>
+  <si>
+    <t>MC Yacine Adli</t>
+  </si>
+  <si>
+    <t>MC Álvaro Fidalgo</t>
+  </si>
+  <si>
+    <t>MP Tommaso Baldanzi</t>
+  </si>
+  <si>
+    <t>DC Olivier Giroud</t>
+  </si>
+  <si>
+    <t>ED Florian Thauvin</t>
+  </si>
+  <si>
+    <t>DC Ciro Immobile</t>
+  </si>
+  <si>
+    <t>DC Gabriel Barbosa</t>
+  </si>
+  <si>
+    <t>AME</t>
+  </si>
+  <si>
+    <t>Estadio Banorte</t>
+  </si>
+  <si>
+    <t>Jose Diaz</t>
+  </si>
+  <si>
+    <t>Logos Equipos/clubamerica.png</t>
   </si>
 </sst>
 </file>
@@ -3072,7 +3228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3091,6 +3247,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10670,29 +10829,30 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:Q24"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -10744,8 +10904,11 @@
       <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R1" s="8" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
@@ -10797,8 +10960,11 @@
       <c r="Q2" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R2" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>32</v>
       </c>
@@ -10850,8 +11016,11 @@
       <c r="Q3" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R3" s="3" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>48</v>
       </c>
@@ -10903,8 +11072,11 @@
       <c r="Q4" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R4" s="3" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>64</v>
       </c>
@@ -10956,8 +11128,11 @@
       <c r="Q5" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R5" s="3" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>80</v>
       </c>
@@ -11009,8 +11184,11 @@
       <c r="Q6" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R6" s="3" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>96</v>
       </c>
@@ -11062,8 +11240,11 @@
       <c r="Q7" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R7" s="3" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>112</v>
       </c>
@@ -11115,8 +11296,11 @@
       <c r="Q8" s="3" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R8" s="3" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>128</v>
       </c>
@@ -11168,8 +11352,11 @@
       <c r="Q9" s="3" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R9" s="3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>144</v>
       </c>
@@ -11221,8 +11408,11 @@
       <c r="Q10" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R10" s="3" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>159</v>
       </c>
@@ -11274,8 +11464,11 @@
       <c r="Q11" s="3" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R11" s="3" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>175</v>
       </c>
@@ -11327,8 +11520,11 @@
       <c r="Q12" s="3" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R12" s="3" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>191</v>
       </c>
@@ -11380,8 +11576,11 @@
       <c r="Q13" s="3" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R13" s="3" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>207</v>
       </c>
@@ -11433,8 +11632,11 @@
       <c r="Q14" s="3" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R14" s="3" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>223</v>
       </c>
@@ -11486,8 +11688,11 @@
       <c r="Q15" s="3" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R15" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>239</v>
       </c>
@@ -11539,8 +11744,11 @@
       <c r="Q16" s="3" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R16" s="3" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="5" t="s">
         <v>255</v>
       </c>
@@ -11592,8 +11800,11 @@
       <c r="Q17" s="3" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R17" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>271</v>
       </c>
@@ -11645,8 +11856,11 @@
       <c r="Q18" s="3" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R18" s="3" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
         <v>287</v>
       </c>
@@ -11698,8 +11912,11 @@
       <c r="Q19" s="3" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R19" s="3" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
         <v>302</v>
       </c>
@@ -11751,8 +11968,11 @@
       <c r="Q20" s="3" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R20" s="3" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
         <v>318</v>
       </c>
@@ -11804,8 +12024,11 @@
       <c r="Q21" s="3" t="s">
         <v>333</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R21" s="3" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
         <v>334</v>
       </c>
@@ -11857,8 +12080,11 @@
       <c r="Q22" s="3" t="s">
         <v>349</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R22" s="3" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
         <v>350</v>
       </c>
@@ -11910,8 +12136,11 @@
       <c r="Q23" s="3" t="s">
         <v>365</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="R23" s="3" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>366</v>
       </c>
@@ -11962,6 +12191,9 @@
       </c>
       <c r="Q24" s="3" t="s">
         <v>381</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>991</v>
       </c>
     </row>
   </sheetData>
@@ -12046,7 +12278,9 @@
       <c r="Q1" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="R1" s="3"/>
+      <c r="R1" s="3" t="s">
+        <v>992</v>
+      </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -12100,7 +12334,9 @@
       <c r="Q2" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="R2" s="3"/>
+      <c r="R2" s="3" t="s">
+        <v>993</v>
+      </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
@@ -12154,7 +12390,9 @@
       <c r="Q3" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="R3" s="3"/>
+      <c r="R3" s="3" t="s">
+        <v>994</v>
+      </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
@@ -12208,7 +12446,9 @@
       <c r="Q4" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="R4" s="3"/>
+      <c r="R4" s="3" t="s">
+        <v>995</v>
+      </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
@@ -12262,7 +12502,9 @@
       <c r="Q5" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="R5" s="3"/>
+      <c r="R5" s="3" t="s">
+        <v>996</v>
+      </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
@@ -12316,7 +12558,9 @@
       <c r="Q6" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="R6" s="3"/>
+      <c r="R6" s="3" t="s">
+        <v>997</v>
+      </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
@@ -12370,7 +12614,9 @@
       <c r="Q7" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="R7" s="3"/>
+      <c r="R7" s="3" t="s">
+        <v>998</v>
+      </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
@@ -12424,7 +12670,9 @@
       <c r="Q8" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="R8" s="3"/>
+      <c r="R8" s="3" t="s">
+        <v>999</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -12478,7 +12726,9 @@
       <c r="Q9" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="R9" s="3"/>
+      <c r="R9" s="3" t="s">
+        <v>1000</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
@@ -12532,7 +12782,9 @@
       <c r="Q10" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="R10" s="3"/>
+      <c r="R10" s="3" t="s">
+        <v>1001</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
@@ -12586,7 +12838,9 @@
       <c r="Q11" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="R11" s="3"/>
+      <c r="R11" s="3" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
@@ -12640,7 +12894,9 @@
       <c r="Q12" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="R12" s="3"/>
+      <c r="R12" s="3" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -12694,7 +12950,9 @@
       <c r="Q13" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="R13" s="3"/>
+      <c r="R13" s="3" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -12748,7 +13006,9 @@
       <c r="Q14" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="R14" s="3"/>
+      <c r="R14" s="3" t="s">
+        <v>1005</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -12802,7 +13062,9 @@
       <c r="Q15" s="3" t="s">
         <v>648</v>
       </c>
-      <c r="R15" s="3"/>
+      <c r="R15" s="3" t="s">
+        <v>1006</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -12856,7 +13118,9 @@
       <c r="Q16" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="R16" s="3"/>
+      <c r="R16" s="3" t="s">
+        <v>1007</v>
+      </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
@@ -12910,7 +13174,9 @@
       <c r="Q17" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="R17" s="3"/>
+      <c r="R17" s="3" t="s">
+        <v>1008</v>
+      </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
@@ -12964,7 +13230,9 @@
       <c r="Q18" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="R18" s="3"/>
+      <c r="R18" s="3" t="s">
+        <v>1009</v>
+      </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
@@ -13018,7 +13286,9 @@
       <c r="Q19" s="3" t="s">
         <v>711</v>
       </c>
-      <c r="R19" s="3"/>
+      <c r="R19" s="3" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
@@ -13072,7 +13342,9 @@
       <c r="Q20" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="R20" s="3"/>
+      <c r="R20" s="3" t="s">
+        <v>1011</v>
+      </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
@@ -13126,7 +13398,9 @@
       <c r="Q21" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="R21" s="3"/>
+      <c r="R21" s="3" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
@@ -13180,7 +13454,9 @@
       <c r="Q22" s="3" t="s">
         <v>759</v>
       </c>
-      <c r="R22" s="3"/>
+      <c r="R22" s="3" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
@@ -13234,7 +13510,9 @@
       <c r="Q23" s="3" t="s">
         <v>775</v>
       </c>
-      <c r="R23" s="3"/>
+      <c r="R23" s="3" t="s">
+        <v>1014</v>
+      </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
@@ -13288,7 +13566,9 @@
       <c r="Q24" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="R24" s="3"/>
+      <c r="R24" s="3" t="s">
+        <v>1015</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13297,7 +13577,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
@@ -13772,6 +14052,29 @@
       </c>
       <c r="G18" t="s">
         <v>963</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>992</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E19">
+        <v>100000000</v>
+      </c>
+      <c r="F19" s="7">
+        <v>300000000</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1019</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C71D6320-9531-420A-A25E-683CDE7D6816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAADCB2-DFAC-47E8-A1F9-E0AF56EDCEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1018">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -2749,9 +2749,6 @@
     <t>Estevao</t>
   </si>
   <si>
-    <t>Xavi Simons</t>
-  </si>
-  <si>
     <t>Prestamo</t>
   </si>
   <si>
@@ -2812,39 +2809,15 @@
     <t>II Álex Baena</t>
   </si>
   <si>
-    <t>SD Sebastian Szymański</t>
-  </si>
-  <si>
-    <t>PT Guglielmo Vicario</t>
-  </si>
-  <si>
-    <t>LI Alex Sandro</t>
-  </si>
-  <si>
     <t>LI Ferland Mendy</t>
   </si>
   <si>
-    <t>LD Dani Carvajal</t>
-  </si>
-  <si>
     <t>CT Dayot Upamecano</t>
   </si>
   <si>
-    <t>ID Juan Cuadrado</t>
-  </si>
-  <si>
-    <t>MP Takumi Minamino</t>
-  </si>
-  <si>
     <t>ED Ismaïla Sarr</t>
   </si>
   <si>
-    <t>DC Randal Kolo Muani</t>
-  </si>
-  <si>
-    <t>MC Teboho Mokoena</t>
-  </si>
-  <si>
     <t>MC Kodai Sano</t>
   </si>
   <si>
@@ -2860,27 +2833,12 @@
     <t>MP Lucas Paquetá</t>
   </si>
   <si>
-    <t>CT Gianluca Mancini</t>
-  </si>
-  <si>
-    <t>MCD Bryan Cristante</t>
-  </si>
-  <si>
-    <t>MCD Samuele Ricci</t>
-  </si>
-  <si>
-    <t>LI David Møller Wolfe</t>
-  </si>
-  <si>
     <t>CT Renato Veiga</t>
   </si>
   <si>
     <t>LD Nahuel Molina</t>
   </si>
   <si>
-    <t>PT Rui Silva</t>
-  </si>
-  <si>
     <t>Urawa Red Diamonds</t>
   </si>
   <si>
@@ -3158,6 +3116,42 @@
   </si>
   <si>
     <t>Logos Equipos/clubamerica.png</t>
+  </si>
+  <si>
+    <t>PT Ørjan Nyland</t>
+  </si>
+  <si>
+    <t>CT Odilon Kossounou</t>
+  </si>
+  <si>
+    <t>MP Eliesse Ben Seghir</t>
+  </si>
+  <si>
+    <t>MC Pape Matar Sarr</t>
+  </si>
+  <si>
+    <t>EI Jérémie Boga</t>
+  </si>
+  <si>
+    <t>CT Evan Ndicka</t>
+  </si>
+  <si>
+    <t>LD Juan Cuadrado</t>
+  </si>
+  <si>
+    <t>MC Senny Mayulu</t>
+  </si>
+  <si>
+    <t>MP Sebastian Szymański</t>
+  </si>
+  <si>
+    <t>LI Jorrel Hato</t>
+  </si>
+  <si>
+    <t>Trent Alexander Arnold</t>
+  </si>
+  <si>
+    <t>Mercado de mitad de temporada</t>
   </si>
 </sst>
 </file>
@@ -3228,7 +3222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3247,9 +3241,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3637,7 +3628,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -3847,7 +3838,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>141</v>
@@ -3943,7 +3934,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>172</v>
@@ -3957,7 +3948,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>125</v>
@@ -4027,7 +4018,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>299</v>
@@ -4111,7 +4102,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>379</v>
@@ -4347,7 +4338,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>157</v>
@@ -4403,7 +4394,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>363</v>
@@ -4465,10 +4456,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C64" s="3">
         <v>4</v>
@@ -4731,7 +4722,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>347</v>
@@ -4748,7 +4739,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4831,7 +4822,7 @@
       </c>
       <c r="D90" s="3"/>
       <c r="E90" t="s">
-        <v>965</v>
+        <v>951</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -4860,7 +4851,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>45</v>
@@ -5018,7 +5009,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>315</v>
@@ -5030,7 +5021,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>45</v>
@@ -5366,7 +5357,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>236</v>
@@ -5402,7 +5393,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>109</v>
@@ -5534,7 +5525,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>77</v>
@@ -5642,7 +5633,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>93</v>
@@ -5702,7 +5693,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>331</v>
@@ -5726,10 +5717,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="B165" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="B165" s="3" t="s">
-        <v>942</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5740,10 +5731,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3">
@@ -5986,10 +5977,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="C186" s="3">
         <v>2</v>
@@ -6024,10 +6015,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6496,18 +6487,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B1" t="s">
         <v>891</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>892</v>
-      </c>
-      <c r="C1" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B2" t="s">
         <v>808</v>
@@ -6518,10 +6509,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>893</v>
+      </c>
+      <c r="B3" t="s">
         <v>894</v>
-      </c>
-      <c r="B3" t="s">
-        <v>895</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6529,10 +6520,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6540,10 +6531,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B5" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6551,7 +6542,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B6" t="s">
         <v>839</v>
@@ -6562,10 +6553,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>897</v>
+      </c>
+      <c r="B7" t="s">
         <v>898</v>
-      </c>
-      <c r="B7" t="s">
-        <v>899</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6573,10 +6564,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B8" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6584,7 +6575,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B9" t="s">
         <v>839</v>
@@ -6595,7 +6586,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B10" t="s">
         <v>808</v>
@@ -6606,7 +6597,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B11" t="s">
         <v>818</v>
@@ -6617,10 +6608,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B12" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6628,7 +6619,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B13" t="s">
         <v>839</v>
@@ -6639,7 +6630,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B14" t="s">
         <v>818</v>
@@ -7055,7 +7046,7 @@
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -7151,7 +7142,7 @@
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>172</v>
@@ -7166,7 +7157,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -7177,10 +7168,10 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -7201,10 +7192,10 @@
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -7297,7 +7288,7 @@
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>141</v>
@@ -7325,7 +7316,7 @@
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>157</v>
@@ -7339,7 +7330,7 @@
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>379</v>
@@ -7363,10 +7354,10 @@
     </row>
     <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
@@ -7607,10 +7598,10 @@
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -7621,10 +7612,10 @@
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>937</v>
+        <v>923</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -7723,7 +7714,7 @@
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>125</v>
@@ -7737,7 +7728,7 @@
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>347</v>
@@ -7785,10 +7776,10 @@
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>928</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>942</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -7885,10 +7876,10 @@
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -7945,7 +7936,7 @@
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>315</v>
@@ -7969,10 +7960,10 @@
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -8017,7 +8008,7 @@
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
@@ -8065,7 +8056,7 @@
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>109</v>
@@ -8077,7 +8068,7 @@
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>363</v>
@@ -8089,10 +8080,10 @@
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>932</v>
+        <v>918</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -8113,10 +8104,10 @@
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3">
@@ -10857,7 +10848,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>928</v>
+        <v>914</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -10896,7 +10887,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>964</v>
+        <v>950</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -10904,8 +10895,8 @@
       <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="8" t="s">
-        <v>968</v>
+      <c r="R1" s="3" t="s">
+        <v>954</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10913,7 +10904,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>929</v>
+        <v>915</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -10961,7 +10952,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>969</v>
+        <v>955</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -10969,7 +10960,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>930</v>
+        <v>916</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -11017,7 +11008,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>970</v>
+        <v>956</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -11025,7 +11016,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>931</v>
+        <v>917</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -11073,7 +11064,7 @@
         <v>63</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>971</v>
+        <v>957</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -11081,7 +11072,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>932</v>
+        <v>918</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -11129,7 +11120,7 @@
         <v>79</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>972</v>
+        <v>958</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -11137,7 +11128,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -11185,7 +11176,7 @@
         <v>95</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>973</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -11193,7 +11184,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>933</v>
+        <v>919</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -11241,7 +11232,7 @@
         <v>111</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>974</v>
+        <v>960</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -11249,7 +11240,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -11297,7 +11288,7 @@
         <v>127</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>975</v>
+        <v>961</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -11305,7 +11296,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>935</v>
+        <v>921</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -11353,7 +11344,7 @@
         <v>143</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>976</v>
+        <v>962</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -11361,10 +11352,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>936</v>
+        <v>922</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -11409,7 +11400,7 @@
         <v>145</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>977</v>
+        <v>963</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -11417,7 +11408,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>937</v>
+        <v>923</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -11465,7 +11456,7 @@
         <v>174</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>978</v>
+        <v>964</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -11473,7 +11464,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>938</v>
+        <v>924</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -11521,7 +11512,7 @@
         <v>190</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>979</v>
+        <v>965</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -11529,7 +11520,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>939</v>
+        <v>925</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -11577,7 +11568,7 @@
         <v>206</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>980</v>
+        <v>966</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -11585,7 +11576,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>940</v>
+        <v>926</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -11633,7 +11624,7 @@
         <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>981</v>
+        <v>967</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -11641,7 +11632,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>941</v>
+        <v>927</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -11689,7 +11680,7 @@
         <v>238</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>982</v>
+        <v>968</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11697,7 +11688,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>942</v>
+        <v>928</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -11745,7 +11736,7 @@
         <v>254</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>983</v>
+        <v>969</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11753,7 +11744,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>943</v>
+        <v>929</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -11801,7 +11792,7 @@
         <v>270</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>984</v>
+        <v>970</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11809,7 +11800,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>944</v>
+        <v>930</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -11857,7 +11848,7 @@
         <v>286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>985</v>
+        <v>971</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -11865,10 +11856,10 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>945</v>
+        <v>931</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>966</v>
+        <v>952</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -11913,7 +11904,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>986</v>
+        <v>972</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -11921,7 +11912,7 @@
         <v>302</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>946</v>
+        <v>932</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>303</v>
@@ -11969,7 +11960,7 @@
         <v>317</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -11977,7 +11968,7 @@
         <v>318</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>947</v>
+        <v>933</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>319</v>
@@ -12025,7 +12016,7 @@
         <v>333</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>988</v>
+        <v>974</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -12033,7 +12024,7 @@
         <v>334</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>948</v>
+        <v>934</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>335</v>
@@ -12081,7 +12072,7 @@
         <v>349</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>989</v>
+        <v>975</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -12137,7 +12128,7 @@
         <v>365</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>990</v>
+        <v>976</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -12145,7 +12136,7 @@
         <v>366</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>949</v>
+        <v>935</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>367</v>
@@ -12193,7 +12184,7 @@
         <v>381</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>991</v>
+        <v>977</v>
       </c>
     </row>
   </sheetData>
@@ -12206,23 +12197,23 @@
   <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="22.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="40" width="11.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12230,8 +12221,8 @@
       <c r="A1" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B1" t="s">
-        <v>927</v>
+      <c r="B1" s="1" t="s">
+        <v>913</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>419</v>
@@ -12279,7 +12270,7 @@
         <v>425</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -12287,7 +12278,7 @@
         <v>426</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>904</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>427</v>
@@ -12335,7 +12326,7 @@
         <v>441</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>993</v>
+        <v>979</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -12343,7 +12334,7 @@
         <v>442</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>905</v>
+        <v>503</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>443</v>
@@ -12391,7 +12382,7 @@
         <v>457</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>994</v>
+        <v>980</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -12399,7 +12390,7 @@
         <v>458</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>459</v>
@@ -12447,7 +12438,7 @@
         <v>473</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>995</v>
+        <v>981</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -12455,7 +12446,7 @@
         <v>474</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>907</v>
+        <v>1007</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>475</v>
@@ -12503,7 +12494,7 @@
         <v>489</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>996</v>
+        <v>982</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -12511,7 +12502,7 @@
         <v>490</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>491</v>
@@ -12559,7 +12550,7 @@
         <v>505</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>997</v>
+        <v>983</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -12567,7 +12558,7 @@
         <v>506</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>909</v>
+        <v>1008</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>507</v>
@@ -12615,7 +12606,7 @@
         <v>521</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>998</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -12623,7 +12614,7 @@
         <v>522</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>910</v>
+        <v>1009</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>523</v>
@@ -12671,7 +12662,7 @@
         <v>537</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>999</v>
+        <v>985</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -12679,7 +12670,7 @@
         <v>538</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>539</v>
@@ -12727,7 +12718,7 @@
         <v>553</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>1000</v>
+        <v>986</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -12735,10 +12726,10 @@
         <v>554</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>556</v>
@@ -12783,7 +12774,7 @@
         <v>555</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>1001</v>
+        <v>987</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -12791,7 +12782,7 @@
         <v>569</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>913</v>
+        <v>1010</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>570</v>
@@ -12839,7 +12830,7 @@
         <v>584</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>1002</v>
+        <v>988</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -12847,7 +12838,7 @@
         <v>585</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>914</v>
+        <v>602</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>586</v>
@@ -12895,7 +12886,7 @@
         <v>600</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>1003</v>
+        <v>989</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -12903,7 +12894,7 @@
         <v>601</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>602</v>
@@ -12951,7 +12942,7 @@
         <v>616</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>1004</v>
+        <v>990</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -12959,7 +12950,7 @@
         <v>617</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>916</v>
+        <v>909</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>618</v>
@@ -13007,7 +12998,7 @@
         <v>632</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>1005</v>
+        <v>991</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -13015,7 +13006,7 @@
         <v>633</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>917</v>
+        <v>1011</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>634</v>
@@ -13063,7 +13054,7 @@
         <v>648</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>1006</v>
+        <v>992</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -13071,7 +13062,7 @@
         <v>649</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>918</v>
+        <v>910</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>650</v>
@@ -13119,7 +13110,7 @@
         <v>664</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>1007</v>
+        <v>993</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -13127,7 +13118,7 @@
         <v>665</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>919</v>
+        <v>1012</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>666</v>
@@ -13175,7 +13166,7 @@
         <v>680</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>1008</v>
+        <v>994</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -13183,7 +13174,7 @@
         <v>681</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>920</v>
+        <v>1013</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>682</v>
@@ -13231,7 +13222,7 @@
         <v>696</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>1009</v>
+        <v>995</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -13239,10 +13230,10 @@
         <v>697</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>921</v>
+        <v>906</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>967</v>
+        <v>953</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>698</v>
@@ -13287,7 +13278,7 @@
         <v>711</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>1010</v>
+        <v>996</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -13295,7 +13286,7 @@
         <v>712</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>922</v>
+        <v>1014</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>713</v>
@@ -13343,7 +13334,7 @@
         <v>727</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>1011</v>
+        <v>997</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -13351,7 +13342,7 @@
         <v>728</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>923</v>
+        <v>1015</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>729</v>
@@ -13399,7 +13390,7 @@
         <v>743</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>1012</v>
+        <v>998</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -13407,7 +13398,7 @@
         <v>744</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>924</v>
+        <v>761</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>745</v>
@@ -13455,7 +13446,7 @@
         <v>759</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>1013</v>
+        <v>999</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -13463,7 +13454,7 @@
         <v>760</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>761</v>
@@ -13511,7 +13502,7 @@
         <v>775</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>1014</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -13519,7 +13510,7 @@
         <v>776</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>926</v>
+        <v>912</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>777</v>
@@ -13567,7 +13558,7 @@
         <v>791</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>1015</v>
+        <v>1001</v>
       </c>
     </row>
   </sheetData>
@@ -13672,7 +13663,7 @@
         <v>402</v>
       </c>
       <c r="B4" t="s">
-        <v>952</v>
+        <v>938</v>
       </c>
       <c r="C4" t="s">
         <v>807</v>
@@ -13724,7 +13715,7 @@
         <v>403</v>
       </c>
       <c r="B6" t="s">
-        <v>953</v>
+        <v>939</v>
       </c>
       <c r="C6" t="s">
         <v>800</v>
@@ -13776,7 +13767,7 @@
         <v>415</v>
       </c>
       <c r="B8" t="s">
-        <v>954</v>
+        <v>940</v>
       </c>
       <c r="C8" t="s">
         <v>820</v>
@@ -13886,7 +13877,7 @@
         <v>835</v>
       </c>
       <c r="D12" t="s">
-        <v>958</v>
+        <v>944</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13935,10 +13926,10 @@
         <v>841</v>
       </c>
       <c r="C14" t="s">
-        <v>955</v>
+        <v>941</v>
       </c>
       <c r="D14" t="s">
-        <v>959</v>
+        <v>945</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13955,25 +13946,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>927</v>
+        <v>913</v>
       </c>
       <c r="B15" t="s">
-        <v>950</v>
+        <v>936</v>
       </c>
       <c r="C15" t="s">
-        <v>956</v>
+        <v>942</v>
       </c>
       <c r="D15" t="s">
-        <v>960</v>
+        <v>946</v>
       </c>
       <c r="E15">
         <v>100000000</v>
       </c>
       <c r="F15" s="7">
-        <v>300000000</v>
+        <v>137000000</v>
       </c>
       <c r="G15" t="s">
-        <v>962</v>
+        <v>948</v>
       </c>
       <c r="H15">
         <v>13</v>
@@ -14036,13 +14027,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>951</v>
+        <v>937</v>
       </c>
       <c r="C18" t="s">
-        <v>957</v>
+        <v>943</v>
       </c>
       <c r="D18" t="s">
-        <v>961</v>
+        <v>947</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14051,21 +14042,21 @@
         <v>300000000</v>
       </c>
       <c r="G18" t="s">
-        <v>963</v>
+        <v>949</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>992</v>
+        <v>978</v>
       </c>
       <c r="B19" t="s">
-        <v>1016</v>
+        <v>1002</v>
       </c>
       <c r="C19" t="s">
-        <v>1017</v>
+        <v>1003</v>
       </c>
       <c r="D19" t="s">
-        <v>1018</v>
+        <v>1004</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -14074,7 +14065,7 @@
         <v>300000000</v>
       </c>
       <c r="G19" t="s">
-        <v>1019</v>
+        <v>1005</v>
       </c>
     </row>
   </sheetData>
@@ -14904,39 +14895,39 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>883</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>884</v>
+        <v>865</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="E36">
-        <v>60</v>
-      </c>
-      <c r="F36">
-        <v>2</v>
+        <v>20</v>
+      </c>
+      <c r="F36" t="s">
+        <v>859</v>
       </c>
       <c r="G36" t="s">
-        <v>885</v>
+        <v>866</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>885</v>
       </c>
       <c r="B37" t="s">
         <v>865</v>
       </c>
       <c r="C37" t="s">
+        <v>421</v>
+      </c>
+      <c r="D37" t="s">
         <v>13</v>
-      </c>
-      <c r="D37" t="s">
-        <v>421</v>
       </c>
       <c r="E37">
         <v>20</v>
@@ -14953,125 +14944,125 @@
         <v>886</v>
       </c>
       <c r="B38" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="C38" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="D38" t="s">
-        <v>13</v>
+        <v>880</v>
       </c>
       <c r="E38">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F38" t="s">
         <v>859</v>
       </c>
       <c r="G38" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>887</v>
+        <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="C39" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D39" t="s">
         <v>880</v>
       </c>
-      <c r="E39">
-        <v>5</v>
-      </c>
-      <c r="F39" t="s">
-        <v>859</v>
+      <c r="F39">
+        <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>329</v>
+        <v>887</v>
       </c>
       <c r="B40" t="s">
+        <v>883</v>
+      </c>
+      <c r="C40" t="s">
+        <v>880</v>
+      </c>
+      <c r="D40" t="s">
+        <v>407</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
         <v>884</v>
-      </c>
-      <c r="C40" t="s">
-        <v>407</v>
-      </c>
-      <c r="D40" t="s">
-        <v>880</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>888</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
+        <v>883</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
         <v>884</v>
-      </c>
-      <c r="C41" t="s">
-        <v>880</v>
-      </c>
-      <c r="D41" t="s">
-        <v>407</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="B42" t="s">
+        <v>883</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
         <v>884</v>
-      </c>
-      <c r="C42" t="s">
-        <v>13</v>
-      </c>
-      <c r="D42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>172</v>
+        <v>888</v>
       </c>
       <c r="B43" t="s">
-        <v>884</v>
+        <v>858</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43">
-        <v>1</v>
+        <v>409</v>
+      </c>
+      <c r="E43">
+        <v>30</v>
+      </c>
+      <c r="F43" t="s">
+        <v>859</v>
       </c>
       <c r="G43" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -15079,30 +15070,30 @@
         <v>889</v>
       </c>
       <c r="B44" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="C44" t="s">
+        <v>422</v>
+      </c>
+      <c r="D44" t="s">
         <v>13</v>
       </c>
-      <c r="D44" t="s">
-        <v>409</v>
-      </c>
       <c r="E44">
-        <v>30</v>
-      </c>
-      <c r="F44" t="s">
-        <v>859</v>
+        <v>40</v>
+      </c>
+      <c r="F44">
+        <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>890</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C45" t="s">
         <v>422</v>
@@ -15111,41 +15102,41 @@
         <v>13</v>
       </c>
       <c r="E45">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F45">
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>884</v>
+        <v>858</v>
       </c>
       <c r="C46" t="s">
-        <v>422</v>
+        <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>13</v>
+        <v>423</v>
       </c>
       <c r="E46">
-        <v>15</v>
-      </c>
-      <c r="F46">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="F46" t="s">
+        <v>859</v>
       </c>
       <c r="G46" t="s">
-        <v>885</v>
+        <v>860</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="B47" t="s">
         <v>858</v>
@@ -15157,7 +15148,7 @@
         <v>423</v>
       </c>
       <c r="E47">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F47" t="s">
         <v>859</v>
@@ -15168,7 +15159,7 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>247</v>
       </c>
       <c r="B48" t="s">
         <v>858</v>
@@ -15191,25 +15182,25 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>247</v>
+        <v>1016</v>
       </c>
       <c r="B49" t="s">
-        <v>858</v>
+        <v>883</v>
       </c>
       <c r="C49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>423</v>
+        <v>913</v>
       </c>
       <c r="E49">
-        <v>31</v>
-      </c>
-      <c r="F49" t="s">
-        <v>859</v>
+        <v>0</v>
+      </c>
+      <c r="F49">
+        <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>860</v>
+        <v>1017</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAADCB2-DFAC-47E8-A1F9-E0AF56EDCEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D1F93E-A30F-49F7-9307-C494E963F5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="Campeones" sheetId="10" r:id="rId10"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$246</definedName>
@@ -13608,418 +13609,418 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>411</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>799</v>
+        <v>837</v>
       </c>
       <c r="C2" t="s">
-        <v>800</v>
+        <v>838</v>
       </c>
       <c r="D2" t="s">
-        <v>801</v>
+        <v>839</v>
       </c>
       <c r="E2">
         <v>100000000</v>
       </c>
       <c r="F2" s="7">
-        <v>1400000000</v>
+        <v>2690000000</v>
       </c>
       <c r="G2" t="s">
-        <v>802</v>
+        <v>840</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>422</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>803</v>
+        <v>834</v>
       </c>
       <c r="C3" t="s">
-        <v>804</v>
+        <v>835</v>
       </c>
       <c r="D3" t="s">
-        <v>805</v>
+        <v>944</v>
       </c>
       <c r="E3">
         <v>100000000</v>
       </c>
       <c r="F3" s="7">
-        <v>68000000</v>
+        <v>300000000</v>
       </c>
       <c r="G3" t="s">
-        <v>806</v>
+        <v>836</v>
       </c>
       <c r="H3">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>402</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>938</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>807</v>
+        <v>831</v>
       </c>
       <c r="D4" t="s">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="E4">
         <v>100000000</v>
       </c>
       <c r="F4" s="7">
-        <v>2575000000</v>
+        <v>1000000000</v>
       </c>
       <c r="G4" t="s">
-        <v>809</v>
+        <v>833</v>
       </c>
       <c r="H4">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>810</v>
+        <v>938</v>
       </c>
       <c r="C5" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="D5" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="E5">
         <v>100000000</v>
       </c>
       <c r="F5" s="7">
-        <v>300000000</v>
+        <v>2575000000</v>
       </c>
       <c r="G5" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="H5">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>939</v>
+        <v>823</v>
       </c>
       <c r="C6" t="s">
-        <v>800</v>
+        <v>824</v>
       </c>
       <c r="D6" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="E6">
         <v>100000000</v>
       </c>
       <c r="F6" s="7">
-        <v>566000000</v>
+        <v>815000000</v>
       </c>
       <c r="G6" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="C7" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="D7" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="E7">
         <v>100000000</v>
       </c>
       <c r="F7" s="7">
-        <v>2152000000</v>
+        <v>300000000</v>
       </c>
       <c r="G7" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="B8" t="s">
-        <v>940</v>
+        <v>816</v>
       </c>
       <c r="C8" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D8" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="E8">
         <v>100000000</v>
       </c>
       <c r="F8" s="7">
-        <v>299000000</v>
+        <v>2152000000</v>
       </c>
       <c r="G8" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="H8">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B9" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="C9" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="D9" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="E9">
         <v>100000000</v>
       </c>
       <c r="F9" s="7">
-        <v>815000000</v>
+        <v>68000000</v>
       </c>
       <c r="G9" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="C10" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="D10" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="E10">
         <v>100000000</v>
       </c>
       <c r="F10" s="7">
-        <v>358000000</v>
+        <v>300000000</v>
       </c>
       <c r="G10" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="H10">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>827</v>
       </c>
       <c r="C11" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D11" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="E11">
         <v>100000000</v>
       </c>
       <c r="F11" s="7">
-        <v>1000000000</v>
+        <v>358000000</v>
       </c>
       <c r="G11" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="H11">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>834</v>
+        <v>799</v>
       </c>
       <c r="C12" t="s">
-        <v>835</v>
+        <v>800</v>
       </c>
       <c r="D12" t="s">
-        <v>944</v>
+        <v>801</v>
       </c>
       <c r="E12">
         <v>100000000</v>
       </c>
       <c r="F12" s="7">
-        <v>300000000</v>
+        <v>1400000000</v>
       </c>
       <c r="G12" t="s">
-        <v>836</v>
+        <v>802</v>
       </c>
       <c r="H12">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>837</v>
+        <v>940</v>
       </c>
       <c r="C13" t="s">
-        <v>838</v>
+        <v>820</v>
       </c>
       <c r="D13" t="s">
-        <v>839</v>
+        <v>821</v>
       </c>
       <c r="E13">
         <v>100000000</v>
       </c>
       <c r="F13" s="7">
-        <v>2690000000</v>
+        <v>299000000</v>
       </c>
       <c r="G13" t="s">
-        <v>840</v>
+        <v>822</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>419</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C14" t="s">
-        <v>941</v>
+        <v>844</v>
       </c>
       <c r="D14" t="s">
-        <v>945</v>
+        <v>845</v>
       </c>
       <c r="E14">
         <v>100000000</v>
       </c>
       <c r="F14" s="7">
-        <v>450000000</v>
+        <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="H14">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>913</v>
+        <v>419</v>
       </c>
       <c r="B15" t="s">
-        <v>936</v>
+        <v>841</v>
       </c>
       <c r="C15" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D15" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E15">
         <v>100000000</v>
       </c>
       <c r="F15" s="7">
-        <v>137000000</v>
+        <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>948</v>
+        <v>842</v>
       </c>
       <c r="H15">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>9</v>
+        <v>913</v>
       </c>
       <c r="B16" t="s">
-        <v>843</v>
+        <v>936</v>
       </c>
       <c r="C16" t="s">
-        <v>844</v>
+        <v>942</v>
       </c>
       <c r="D16" t="s">
-        <v>845</v>
+        <v>946</v>
       </c>
       <c r="E16">
         <v>100000000</v>
       </c>
       <c r="F16" s="7">
-        <v>300000000</v>
+        <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>846</v>
+        <v>948</v>
       </c>
       <c r="H16">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="B17" t="s">
-        <v>847</v>
+        <v>939</v>
       </c>
       <c r="C17" t="s">
-        <v>848</v>
+        <v>800</v>
       </c>
       <c r="D17" t="s">
-        <v>849</v>
+        <v>814</v>
       </c>
       <c r="E17">
         <v>100000000</v>
       </c>
       <c r="F17" s="7">
-        <v>300000000</v>
+        <v>566000000</v>
       </c>
       <c r="G17" t="s">
-        <v>850</v>
+        <v>815</v>
       </c>
       <c r="H17">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -14044,6 +14045,9 @@
       <c r="G18" t="s">
         <v>949</v>
       </c>
+      <c r="H18">
+        <v>17</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -14069,6 +14073,11 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H19" xr:uid="{00000000-0001-0000-0700-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H19">
+      <sortCondition ref="H1:H19"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D1F93E-A30F-49F7-9307-C494E963F5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9086B66-B188-4FB8-AD65-D50DCC4B694E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="CopaEstelar" sheetId="3" r:id="rId3"/>
     <sheet name="Registro Champions" sheetId="4" r:id="rId4"/>
     <sheet name="RegistroEstelar" sheetId="5" r:id="rId5"/>
-    <sheet name="BD" sheetId="6" r:id="rId6"/>
-    <sheet name="Lista" sheetId="7" r:id="rId7"/>
+    <sheet name="Lista" sheetId="7" r:id="rId6"/>
+    <sheet name="BD" sheetId="6" r:id="rId7"/>
     <sheet name="Clubes" sheetId="8" r:id="rId8"/>
     <sheet name="Mercado" sheetId="9" r:id="rId9"/>
     <sheet name="Campeones" sheetId="10" r:id="rId10"/>
@@ -33,52 +33,52 @@
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
-    <definedName name="Arsenal" localSheetId="5">BD!$J$2:$J$24</definedName>
+    <definedName name="Arsenal" localSheetId="6">BD!$J$2:$J$24</definedName>
     <definedName name="Arsenal">Lista!$K$2:$K$1048576</definedName>
     <definedName name="AstonVilla">Lista!$I$2:$I$1048576</definedName>
     <definedName name="Bayer_Munich">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Bayern_Leverkusen" localSheetId="5">BD!$E$2:$E$24</definedName>
+    <definedName name="Bayern_Leverkusen" localSheetId="6">BD!$E$2:$E$24</definedName>
     <definedName name="Bayern_Leverkusen">Lista!$F$2:$F$1048576</definedName>
     <definedName name="Bayern_Munich">BD!$N$2:$N$24</definedName>
-    <definedName name="Boca_Juniors" localSheetId="5">BD!$G$2:$G$24</definedName>
+    <definedName name="Boca_Juniors" localSheetId="6">BD!$G$2:$G$24</definedName>
     <definedName name="Boca_Juniors">Lista!$H$2:$H$1048576</definedName>
     <definedName name="BocaJuniors">Lista!$H$2:$H$1048576</definedName>
-    <definedName name="Como_1907" localSheetId="5">BD!$K$2:$K$24</definedName>
+    <definedName name="Como_1907" localSheetId="6">BD!$K$2:$K$24</definedName>
     <definedName name="COMO_1907">Lista!$L$2:$L$1048576</definedName>
     <definedName name="Como1907">Lista!$M$2:$M$1048576</definedName>
-    <definedName name="FC_Barcelona" localSheetId="5">BD!$C$2:$C$24</definedName>
+    <definedName name="FC_Barcelona" localSheetId="6">BD!$C$2:$C$24</definedName>
     <definedName name="FC_Barcelona">Lista!$C$2:$C$1048576</definedName>
     <definedName name="FcBarcelona">Lista!$C$2:$C$1048576</definedName>
-    <definedName name="Galatasaray" localSheetId="5">BD!$H$2:$H$24</definedName>
+    <definedName name="Galatasaray" localSheetId="6">BD!$H$2:$H$24</definedName>
     <definedName name="GALATASARAY">Lista!$I$2:$I$1048576</definedName>
-    <definedName name="Hellas_Verona" localSheetId="5">BD!$M$2:$M$24</definedName>
+    <definedName name="Hellas_Verona" localSheetId="6">BD!$M$2:$M$24</definedName>
     <definedName name="Hellas_Verona">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Inter_de_Milan" localSheetId="5">BD!$A$2:$A$24</definedName>
+    <definedName name="Inter_de_Milan" localSheetId="6">BD!$A$2:$A$24</definedName>
     <definedName name="Inter_de_Milan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="InterMilan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="Leverkusen">Lista!$F$2:$F$1048576</definedName>
-    <definedName name="Manchester_United" localSheetId="5">BD!$O$2:$O$24</definedName>
+    <definedName name="Manchester_United" localSheetId="6">BD!$O$2:$O$24</definedName>
     <definedName name="Manchester_United">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Melbourne_City" localSheetId="5">BD!#REF!</definedName>
+    <definedName name="Melbourne_City" localSheetId="6">BD!#REF!</definedName>
     <definedName name="Melbourne_City">Lista!$Q$2:$Q$1048576</definedName>
     <definedName name="PARIS_SAINT___GERMAIN">Lista!$J$2:$J$1048576</definedName>
-    <definedName name="PSG" localSheetId="5">BD!$I$2:$I$23</definedName>
+    <definedName name="PSG" localSheetId="6">BD!$I$2:$I$23</definedName>
     <definedName name="PSG">Lista!$K$2:$K$1048576</definedName>
-    <definedName name="RB_Leipzig" localSheetId="5">BD!$F$2:$F$24</definedName>
+    <definedName name="RB_Leipzig" localSheetId="6">BD!$F$2:$F$24</definedName>
     <definedName name="RB_LEIPZIG">Lista!$G$2:$G$1048576</definedName>
     <definedName name="RBLeipzig">Lista!$G$2:$G$1048576</definedName>
-    <definedName name="Real_Madrid" localSheetId="5">BD!$B$2:$B$24</definedName>
+    <definedName name="Real_Madrid" localSheetId="6">BD!$B$2:$B$24</definedName>
     <definedName name="Real_Madrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="RealMadrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="Sparta">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Terengganu_FC" localSheetId="5">BD!#REF!</definedName>
+    <definedName name="Terengganu_FC" localSheetId="6">BD!#REF!</definedName>
     <definedName name="Terengganu_FC">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Terrengganu">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Tottenham">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Tottenham_Hotspur" localSheetId="5">BD!$L$2:$L$24</definedName>
+    <definedName name="Tottenham_Hotspur" localSheetId="6">BD!$L$2:$L$24</definedName>
     <definedName name="Tottenham_Hotspur">Lista!$M$2:$M$1048576</definedName>
     <definedName name="United">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Wrexham" localSheetId="5">BD!$P$2:$P$24</definedName>
+    <definedName name="Wrexham" localSheetId="6">BD!$P$2:$P$24</definedName>
     <definedName name="WREXHAM">Lista!$R$2:$R$1048576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1016">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -1421,9 +1421,6 @@
     <t>PT Diogo Costa</t>
   </si>
   <si>
-    <t>PT Anatoliy Trubin</t>
-  </si>
-  <si>
     <t>DC Romelu Lukaku</t>
   </si>
   <si>
@@ -1451,9 +1448,6 @@
     <t>LI Joško Gvardiol</t>
   </si>
   <si>
-    <t>ID Denzel Dumfries</t>
-  </si>
-  <si>
     <t>CT Victor Nelsson</t>
   </si>
   <si>
@@ -1490,9 +1484,6 @@
     <t>CT Marquinhos</t>
   </si>
   <si>
-    <t>CT Fabinho</t>
-  </si>
-  <si>
     <t>CT Dan Burn</t>
   </si>
   <si>
@@ -1586,9 +1577,6 @@
     <t>LD Raoul Bellanova</t>
   </si>
   <si>
-    <t>LD John Stones</t>
-  </si>
-  <si>
     <t>LD Aaron Wan-Bissaka</t>
   </si>
   <si>
@@ -1682,9 +1670,6 @@
     <t>MC Paul Scholes</t>
   </si>
   <si>
-    <t>MP Michael Olise</t>
-  </si>
-  <si>
     <t>EI Vinícius Júnior</t>
   </si>
   <si>
@@ -1697,9 +1682,6 @@
     <t>MC Martin Ødegaard</t>
   </si>
   <si>
-    <t>MCD Warren Zaïre-Emery</t>
-  </si>
-  <si>
     <t>MC Joelinton</t>
   </si>
   <si>
@@ -1745,9 +1727,6 @@
     <t>MC İlkay Gündoğan</t>
   </si>
   <si>
-    <t>MC Arda Güler</t>
-  </si>
-  <si>
     <t>EI Marco Reus</t>
   </si>
   <si>
@@ -1793,9 +1772,6 @@
     <t>DC Liam Delap</t>
   </si>
   <si>
-    <t>EI Savinho</t>
-  </si>
-  <si>
     <t>ED Lionel Messi</t>
   </si>
   <si>
@@ -1814,18 +1790,12 @@
     <t>DC Ruud van Nistelrooy</t>
   </si>
   <si>
-    <t>ED Leroy Sané</t>
-  </si>
-  <si>
     <t>DC João Pedro</t>
   </si>
   <si>
     <t>DC Alexander Isak</t>
   </si>
   <si>
-    <t>SD Antoine Griezmann</t>
-  </si>
-  <si>
     <t>DC Omar Marmoush</t>
   </si>
   <si>
@@ -1838,9 +1808,6 @@
     <t>ED Lee Kang-in</t>
   </si>
   <si>
-    <t>ED Bernardo Silva</t>
-  </si>
-  <si>
     <t>DC Erling Haaland</t>
   </si>
   <si>
@@ -1856,9 +1823,6 @@
     <t>DC Ivan Toney</t>
   </si>
   <si>
-    <t>DC Ousmane Dembélé</t>
-  </si>
-  <si>
     <t>DC Diego Forlán</t>
   </si>
   <si>
@@ -1871,18 +1835,12 @@
     <t>DC Semih Kılıçsoy</t>
   </si>
   <si>
-    <t>DC Wayne Rooney</t>
-  </si>
-  <si>
     <t>MP Estêvão</t>
   </si>
   <si>
     <t>DC Harry Kane</t>
   </si>
   <si>
-    <t>EI Raphinha</t>
-  </si>
-  <si>
     <t>DC Alexander Sørloth</t>
   </si>
   <si>
@@ -1904,9 +1862,6 @@
     <t>EI Thorgan Hazard</t>
   </si>
   <si>
-    <t>PT Jan Oblak</t>
-  </si>
-  <si>
     <t>ED Antony</t>
   </si>
   <si>
@@ -1928,15 +1883,9 @@
     <t>LI Ian Maatsen</t>
   </si>
   <si>
-    <t>DC Mateo Retegui</t>
-  </si>
-  <si>
     <t>PT Aaron Ramsdale</t>
   </si>
   <si>
-    <t>PT David de Gea</t>
-  </si>
-  <si>
     <t>PT Unai Simón</t>
   </si>
   <si>
@@ -1952,9 +1901,6 @@
     <t>MCD Amadou Onana</t>
   </si>
   <si>
-    <t>CT Gleison Bremer</t>
-  </si>
-  <si>
     <t>PT Vítor Baía</t>
   </si>
   <si>
@@ -1991,24 +1937,15 @@
     <t>CT Manuel Akanji</t>
   </si>
   <si>
-    <t>CT Maxence Lacroix</t>
-  </si>
-  <si>
     <t>CT Malick Thiaw</t>
   </si>
   <si>
     <t>MP Ismael Saibari</t>
   </si>
   <si>
-    <t>CT Federico Gatti</t>
-  </si>
-  <si>
     <t>PT Bart Verbruggen</t>
   </si>
   <si>
-    <t>MCD Ryan Gravenberch</t>
-  </si>
-  <si>
     <t>CT Cristhian Mosquera</t>
   </si>
   <si>
@@ -2039,9 +1976,6 @@
     <t>LI Gerard Martín</t>
   </si>
   <si>
-    <t>II Andrea Cambiaso</t>
-  </si>
-  <si>
     <t>CT Nathan Collins</t>
   </si>
   <si>
@@ -2078,9 +2012,6 @@
     <t>CT Piero Hincapié</t>
   </si>
   <si>
-    <t>MCD Rúben Neves</t>
-  </si>
-  <si>
     <t>MCD Elliot Anderson</t>
   </si>
   <si>
@@ -2090,9 +2021,6 @@
     <t>LD Kyle Walker</t>
   </si>
   <si>
-    <t>MC Toni Kroos</t>
-  </si>
-  <si>
     <t>MC Leon Goretzka</t>
   </si>
   <si>
@@ -2111,9 +2039,6 @@
     <t>ID Yeremy Pino</t>
   </si>
   <si>
-    <t>MC Declan Rice</t>
-  </si>
-  <si>
     <t>CT Giorgio Scalvini</t>
   </si>
   <si>
@@ -2126,9 +2051,6 @@
     <t>CT Alex Freeman</t>
   </si>
   <si>
-    <t>MCD Marcelo Brozović</t>
-  </si>
-  <si>
     <t>MC Ayyoub Bouaddi</t>
   </si>
   <si>
@@ -2159,9 +2081,6 @@
     <t>EI Harvey Barnes</t>
   </si>
   <si>
-    <t>MP Bruno Fernandes</t>
-  </si>
-  <si>
     <t>CT Archie Gray</t>
   </si>
   <si>
@@ -2192,9 +2111,6 @@
     <t>ID Diogo Dalot</t>
   </si>
   <si>
-    <t>MC Martín Zubimendi</t>
-  </si>
-  <si>
     <t>II Conor Gallagher</t>
   </si>
   <si>
@@ -2219,9 +2135,6 @@
     <t>MC Fabián Ruiz</t>
   </si>
   <si>
-    <t>MP Brahim Díaz</t>
-  </si>
-  <si>
     <t>II Rodrygo</t>
   </si>
   <si>
@@ -2231,15 +2144,9 @@
     <t>MP Johan Manzambi</t>
   </si>
   <si>
-    <t>MP Raheem Sterling</t>
-  </si>
-  <si>
     <t>CT Raúl Asencio</t>
   </si>
   <si>
-    <t>MC Eduardo Camavinga</t>
-  </si>
-  <si>
     <t>ED Matías Soulé</t>
   </si>
   <si>
@@ -2267,18 +2174,12 @@
     <t>MP Nicolò Zaniolo</t>
   </si>
   <si>
-    <t>MP Christopher Nkunku</t>
-  </si>
-  <si>
     <t>ID Mason Greenwood</t>
   </si>
   <si>
     <t>MP Tijjani Reijnders</t>
   </si>
   <si>
-    <t>MP Karim Adeyemi</t>
-  </si>
-  <si>
     <t>ID Takefusa Kubo</t>
   </si>
   <si>
@@ -2300,9 +2201,6 @@
     <t>MP Rodrigo Mora</t>
   </si>
   <si>
-    <t>SD João Félix</t>
-  </si>
-  <si>
     <t>MP Kevin De Bruyne</t>
   </si>
   <si>
@@ -2333,9 +2231,6 @@
     <t>EI Christos Tzolis</t>
   </si>
   <si>
-    <t>DC Francesco Pio Esposito</t>
-  </si>
-  <si>
     <t>CT Marc Guéhi</t>
   </si>
   <si>
@@ -2345,12 +2240,6 @@
     <t>MP Fermín López</t>
   </si>
   <si>
-    <t>MCD André-Frank Zambo Anguissa</t>
-  </si>
-  <si>
-    <t>DC Morgan Rogers</t>
-  </si>
-  <si>
     <t>MP Dejan Kulusevski</t>
   </si>
   <si>
@@ -2363,9 +2252,6 @@
     <t>ED Francisco Trincão</t>
   </si>
   <si>
-    <t>DC Julián Álvarez</t>
-  </si>
-  <si>
     <t>EI Yan Diomande</t>
   </si>
   <si>
@@ -2825,9 +2711,6 @@
     <t>DC Darwin Núñez</t>
   </si>
   <si>
-    <t>EI Eden Hazard</t>
-  </si>
-  <si>
     <t>ED Jhon Arias</t>
   </si>
   <si>
@@ -3131,9 +3014,6 @@
     <t>MC Pape Matar Sarr</t>
   </si>
   <si>
-    <t>EI Jérémie Boga</t>
-  </si>
-  <si>
     <t>CT Evan Ndicka</t>
   </si>
   <si>
@@ -3153,6 +3033,120 @@
   </si>
   <si>
     <t>Mercado de mitad de temporada</t>
+  </si>
+  <si>
+    <t>Julian Alvarez</t>
+  </si>
+  <si>
+    <t>EI Eden Hazard (C)</t>
+  </si>
+  <si>
+    <t>MCD Youri Tielemans</t>
+  </si>
+  <si>
+    <t>MP Nico Paz</t>
+  </si>
+  <si>
+    <t>ED Lionel Messi (P)</t>
+  </si>
+  <si>
+    <t>EI Ousmane Dembélé (P)</t>
+  </si>
+  <si>
+    <t>MC Warren Zaïre-Emery</t>
+  </si>
+  <si>
+    <t>MP James Maddison</t>
+  </si>
+  <si>
+    <t>MP Arda Güler (P)</t>
+  </si>
+  <si>
+    <t>ED James Rodríguez</t>
+  </si>
+  <si>
+    <t>II Savinho</t>
+  </si>
+  <si>
+    <t>LI Micky van de Ven (P)</t>
+  </si>
+  <si>
+    <t>MP Morgan Rogers</t>
+  </si>
+  <si>
+    <t>ED Raphinha</t>
+  </si>
+  <si>
+    <t>PT Anatolii Trubin</t>
+  </si>
+  <si>
+    <t>LI Maxi Araújo</t>
+  </si>
+  <si>
+    <t>DC Jonathan David</t>
+  </si>
+  <si>
+    <t>MCD Fabinho</t>
+  </si>
+  <si>
+    <t>LD Cafu</t>
+  </si>
+  <si>
+    <t>CT John Stones</t>
+  </si>
+  <si>
+    <t>MC Ryan Gravenberch</t>
+  </si>
+  <si>
+    <t>MCD Declan Rice</t>
+  </si>
+  <si>
+    <t>MC Bruno Fernandes</t>
+  </si>
+  <si>
+    <t>ED Michael Olise</t>
+  </si>
+  <si>
+    <t>EI João Félix</t>
+  </si>
+  <si>
+    <t>DC Antoine Griezmann</t>
+  </si>
+  <si>
+    <t>MCD Martín Zubimendi</t>
+  </si>
+  <si>
+    <t>LD Giovanni Di Lorenzo</t>
+  </si>
+  <si>
+    <t>CT Takehiro Tomiyasu</t>
+  </si>
+  <si>
+    <t>ED Karim Adeyemi</t>
+  </si>
+  <si>
+    <t>DC Nick Woltemade</t>
+  </si>
+  <si>
+    <t>DC Julián Álvarez (P)</t>
+  </si>
+  <si>
+    <t>PT Marco Carnesecchi</t>
+  </si>
+  <si>
+    <t>CT Davinson Sánchez</t>
+  </si>
+  <si>
+    <t>CT Jarell Quansah</t>
+  </si>
+  <si>
+    <t>MC Kobbie Mainoo</t>
+  </si>
+  <si>
+    <t>MC Scott McTominay</t>
+  </si>
+  <si>
+    <t>DC Pio Esposito</t>
   </si>
 </sst>
 </file>
@@ -3188,12 +3182,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -3223,7 +3229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3242,6 +3248,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3629,7 +3647,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -3839,7 +3857,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>141</v>
@@ -3935,7 +3953,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>172</v>
@@ -3949,7 +3967,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>125</v>
@@ -4019,7 +4037,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>299</v>
@@ -4103,7 +4121,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>379</v>
@@ -4339,7 +4357,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>157</v>
@@ -4395,7 +4413,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>363</v>
@@ -4457,10 +4475,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="C64" s="3">
         <v>4</v>
@@ -4723,7 +4741,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>347</v>
@@ -4740,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>952</v>
+        <v>913</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4823,7 +4841,7 @@
       </c>
       <c r="D90" s="3"/>
       <c r="E90" t="s">
-        <v>951</v>
+        <v>912</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -4852,7 +4870,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>45</v>
@@ -5010,7 +5028,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>315</v>
@@ -5022,7 +5040,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>45</v>
@@ -5358,7 +5376,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>236</v>
@@ -5394,7 +5412,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>109</v>
@@ -5526,7 +5544,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>77</v>
@@ -5634,7 +5652,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>93</v>
@@ -5694,7 +5712,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>331</v>
@@ -5718,10 +5736,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5732,10 +5750,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>919</v>
+        <v>880</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3">
@@ -5978,10 +5996,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>926</v>
+        <v>887</v>
       </c>
       <c r="C186" s="3">
         <v>2</v>
@@ -6016,10 +6034,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>929</v>
+        <v>890</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6488,21 +6506,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>890</v>
+        <v>852</v>
       </c>
       <c r="B1" t="s">
-        <v>891</v>
+        <v>853</v>
       </c>
       <c r="C1" t="s">
-        <v>892</v>
+        <v>854</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="B2" t="s">
-        <v>808</v>
+        <v>770</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6510,10 +6528,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="B3" t="s">
-        <v>894</v>
+        <v>856</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6521,10 +6539,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="B4" t="s">
-        <v>895</v>
+        <v>857</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6532,10 +6550,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="B5" t="s">
-        <v>896</v>
+        <v>858</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6543,10 +6561,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>893</v>
+        <v>855</v>
       </c>
       <c r="B6" t="s">
-        <v>839</v>
+        <v>801</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6554,10 +6572,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="B7" t="s">
-        <v>898</v>
+        <v>860</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6565,10 +6583,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="B8" t="s">
-        <v>899</v>
+        <v>861</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6576,10 +6594,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="B9" t="s">
-        <v>839</v>
+        <v>801</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6587,10 +6605,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="B10" t="s">
-        <v>808</v>
+        <v>770</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6598,10 +6616,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>897</v>
+        <v>859</v>
       </c>
       <c r="B11" t="s">
-        <v>818</v>
+        <v>780</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6609,10 +6627,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="B12" t="s">
-        <v>896</v>
+        <v>858</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6620,10 +6638,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="B13" t="s">
-        <v>839</v>
+        <v>801</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6631,10 +6649,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>900</v>
+        <v>862</v>
       </c>
       <c r="B14" t="s">
-        <v>818</v>
+        <v>780</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7047,7 +7065,7 @@
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -7143,7 +7161,7 @@
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>172</v>
@@ -7158,7 +7176,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>952</v>
+        <v>913</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -7169,10 +7187,10 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>926</v>
+        <v>887</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -7193,10 +7211,10 @@
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -7289,7 +7307,7 @@
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>141</v>
@@ -7317,7 +7335,7 @@
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>157</v>
@@ -7331,7 +7349,7 @@
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>379</v>
@@ -7355,10 +7373,10 @@
     </row>
     <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
@@ -7599,10 +7617,10 @@
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>929</v>
+        <v>890</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -7613,10 +7631,10 @@
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>923</v>
+        <v>884</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -7715,7 +7733,7 @@
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>125</v>
@@ -7729,7 +7747,7 @@
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>347</v>
@@ -7777,10 +7795,10 @@
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -7877,10 +7895,10 @@
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>920</v>
+        <v>881</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -7937,7 +7955,7 @@
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>315</v>
@@ -7961,10 +7979,10 @@
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>915</v>
+        <v>876</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -8009,7 +8027,7 @@
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
@@ -8057,7 +8075,7 @@
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>109</v>
@@ -8069,7 +8087,7 @@
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>363</v>
@@ -8081,10 +8099,10 @@
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>918</v>
+        <v>879</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -8105,10 +8123,10 @@
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>921</v>
+        <v>882</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3">
@@ -10820,6 +10838,1381 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:AN24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="23.44140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.5546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.21875" style="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.88671875" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="40" width="11.5546875" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>874</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>430</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>436</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="O2" s="8" t="s">
+        <v>439</v>
+      </c>
+      <c r="P2" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="O3" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="P3" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>456</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>459</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>465</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="O4" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="P4" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>474</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>475</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>477</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>478</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>481</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="8" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>491</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>996</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>492</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="O6" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="P6" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>504</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="O7" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>617</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="O9" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>479</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="O10" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>751</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>997</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="O11" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>507</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>578</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="O12" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>869</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>588</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>998</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="O13" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>870</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>999</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>606</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="O15" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>871</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="O16" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
+        <v>641</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>644</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="O17" s="8" t="s">
+        <v>667</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>658</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="O18" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>868</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>680</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>719</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>693</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>697</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>701</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="O22" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>720</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>872</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>731</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>732</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="P23" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>873</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>739</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>740</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>741</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>742</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>744</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>745</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>748</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>749</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>1008</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>962</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -10849,7 +12242,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>914</v>
+        <v>875</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -10888,7 +12281,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>950</v>
+        <v>911</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -10897,7 +12290,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>954</v>
+        <v>915</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10905,7 +12298,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>915</v>
+        <v>876</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -10953,7 +12346,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>955</v>
+        <v>916</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -10961,7 +12354,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>916</v>
+        <v>877</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -11009,7 +12402,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>956</v>
+        <v>917</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -11017,7 +12410,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>917</v>
+        <v>878</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -11065,7 +12458,7 @@
         <v>63</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>957</v>
+        <v>918</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -11073,7 +12466,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>918</v>
+        <v>879</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -11121,7 +12514,7 @@
         <v>79</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>958</v>
+        <v>919</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -11129,7 +12522,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>886</v>
+        <v>848</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -11177,7 +12570,7 @@
         <v>95</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>959</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -11185,7 +12578,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>919</v>
+        <v>880</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -11233,7 +12626,7 @@
         <v>111</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>960</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -11241,7 +12634,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>920</v>
+        <v>881</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -11289,7 +12682,7 @@
         <v>127</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>961</v>
+        <v>922</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -11297,7 +12690,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>921</v>
+        <v>882</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -11345,7 +12738,7 @@
         <v>143</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>962</v>
+        <v>923</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -11353,10 +12746,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>922</v>
+        <v>883</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>901</v>
+        <v>863</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -11401,7 +12794,7 @@
         <v>145</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>963</v>
+        <v>924</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -11409,7 +12802,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>923</v>
+        <v>884</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -11457,7 +12850,7 @@
         <v>174</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>964</v>
+        <v>925</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -11465,7 +12858,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>924</v>
+        <v>885</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -11513,7 +12906,7 @@
         <v>190</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>965</v>
+        <v>926</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -11521,7 +12914,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>925</v>
+        <v>886</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -11569,7 +12962,7 @@
         <v>206</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>966</v>
+        <v>927</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -11577,7 +12970,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>926</v>
+        <v>887</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -11625,7 +13018,7 @@
         <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>967</v>
+        <v>928</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -11633,7 +13026,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>927</v>
+        <v>888</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -11681,7 +13074,7 @@
         <v>238</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>968</v>
+        <v>929</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11689,7 +13082,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>928</v>
+        <v>889</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -11737,7 +13130,7 @@
         <v>254</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>969</v>
+        <v>930</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11745,7 +13138,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>929</v>
+        <v>890</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -11793,7 +13186,7 @@
         <v>270</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>970</v>
+        <v>931</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11801,7 +13194,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>930</v>
+        <v>891</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -11849,7 +13242,7 @@
         <v>286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>971</v>
+        <v>932</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -11857,10 +13250,10 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>931</v>
+        <v>892</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>952</v>
+        <v>913</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -11905,7 +13298,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>972</v>
+        <v>933</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -11913,7 +13306,7 @@
         <v>302</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>932</v>
+        <v>893</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>303</v>
@@ -11961,7 +13354,7 @@
         <v>317</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>973</v>
+        <v>934</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -11969,7 +13362,7 @@
         <v>318</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>933</v>
+        <v>894</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>319</v>
@@ -12017,7 +13410,7 @@
         <v>333</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>974</v>
+        <v>935</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -12025,7 +13418,7 @@
         <v>334</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>934</v>
+        <v>895</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>335</v>
@@ -12073,7 +13466,7 @@
         <v>349</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>975</v>
+        <v>936</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -12129,7 +13522,7 @@
         <v>365</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>976</v>
+        <v>937</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -12137,7 +13530,7 @@
         <v>366</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>935</v>
+        <v>896</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>367</v>
@@ -12185,1381 +13578,7 @@
         <v>381</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>977</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:AN24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="40" width="11.5546875" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>913</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>904</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>903</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>509</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>510</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>512</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>513</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>515</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>516</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>517</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>518</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>519</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>520</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>521</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>522</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>523</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>525</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>526</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>530</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>532</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>533</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>534</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>537</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>538</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>905</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>539</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>540</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>545</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>554</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>908</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>902</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>562</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>563</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>564</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>555</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>577</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>579</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>581</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>584</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>585</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>586</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>587</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>589</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>591</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>593</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>597</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>598</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>599</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>601</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>907</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>602</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>603</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>606</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>607</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>609</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>612</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>613</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>614</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>615</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>909</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>619</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>620</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>622</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>624</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>625</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>626</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>627</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>628</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>629</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>630</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>633</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>634</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>635</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>639</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>640</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>641</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>643</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>646</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>647</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>648</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>910</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>655</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>656</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>657</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>660</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>661</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>668</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>669</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>672</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>673</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>674</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>675</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>676</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>680</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>681</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>682</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>683</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>684</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>685</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>686</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>693</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>694</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>695</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>696</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>697</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>906</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>953</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>699</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>700</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>707</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>708</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>709</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>710</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>712</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>713</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>714</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>715</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>716</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>717</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>719</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>721</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>722</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>723</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>724</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>725</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>728</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>729</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>730</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>736</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>740</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>741</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>744</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>755</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>757</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>759</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>911</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>761</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>771</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>773</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="3" t="s">
-        <v>776</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>912</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>777</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>778</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>779</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>780</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>781</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>783</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>784</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>785</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>786</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>787</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>788</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>789</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>790</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>1001</v>
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -13586,25 +13605,25 @@
         <v>382</v>
       </c>
       <c r="B1" t="s">
-        <v>792</v>
+        <v>754</v>
       </c>
       <c r="C1" t="s">
-        <v>793</v>
+        <v>755</v>
       </c>
       <c r="D1" t="s">
-        <v>794</v>
+        <v>756</v>
       </c>
       <c r="E1" t="s">
-        <v>795</v>
+        <v>757</v>
       </c>
       <c r="F1" t="s">
-        <v>796</v>
+        <v>758</v>
       </c>
       <c r="G1" t="s">
-        <v>797</v>
+        <v>759</v>
       </c>
       <c r="H1" t="s">
-        <v>798</v>
+        <v>760</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -13612,22 +13631,22 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>837</v>
+        <v>799</v>
       </c>
       <c r="C2" t="s">
-        <v>838</v>
+        <v>800</v>
       </c>
       <c r="D2" t="s">
-        <v>839</v>
+        <v>801</v>
       </c>
       <c r="E2">
         <v>100000000</v>
       </c>
       <c r="F2" s="7">
-        <v>2690000000</v>
+        <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>840</v>
+        <v>802</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -13638,22 +13657,22 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>834</v>
+        <v>796</v>
       </c>
       <c r="C3" t="s">
-        <v>835</v>
+        <v>797</v>
       </c>
       <c r="D3" t="s">
-        <v>944</v>
+        <v>905</v>
       </c>
       <c r="E3">
         <v>100000000</v>
       </c>
       <c r="F3" s="7">
-        <v>300000000</v>
+        <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>836</v>
+        <v>798</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -13667,19 +13686,19 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>831</v>
+        <v>793</v>
       </c>
       <c r="D4" t="s">
-        <v>832</v>
+        <v>794</v>
       </c>
       <c r="E4">
         <v>100000000</v>
       </c>
       <c r="F4" s="7">
-        <v>1000000000</v>
+        <v>8100000000</v>
       </c>
       <c r="G4" t="s">
-        <v>833</v>
+        <v>795</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -13690,22 +13709,22 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>938</v>
+        <v>899</v>
       </c>
       <c r="C5" t="s">
-        <v>807</v>
+        <v>769</v>
       </c>
       <c r="D5" t="s">
-        <v>808</v>
+        <v>770</v>
       </c>
       <c r="E5">
         <v>100000000</v>
       </c>
       <c r="F5" s="7">
-        <v>2575000000</v>
+        <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>809</v>
+        <v>771</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -13716,22 +13735,22 @@
         <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>823</v>
+        <v>785</v>
       </c>
       <c r="C6" t="s">
-        <v>824</v>
+        <v>786</v>
       </c>
       <c r="D6" t="s">
-        <v>825</v>
+        <v>787</v>
       </c>
       <c r="E6">
         <v>100000000</v>
       </c>
       <c r="F6" s="7">
-        <v>815000000</v>
+        <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -13742,22 +13761,22 @@
         <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>810</v>
+        <v>772</v>
       </c>
       <c r="C7" t="s">
-        <v>811</v>
+        <v>773</v>
       </c>
       <c r="D7" t="s">
-        <v>812</v>
+        <v>774</v>
       </c>
       <c r="E7">
         <v>100000000</v>
       </c>
       <c r="F7" s="7">
-        <v>300000000</v>
+        <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>813</v>
+        <v>775</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -13768,22 +13787,22 @@
         <v>407</v>
       </c>
       <c r="B8" t="s">
-        <v>816</v>
+        <v>778</v>
       </c>
       <c r="C8" t="s">
-        <v>817</v>
+        <v>779</v>
       </c>
       <c r="D8" t="s">
-        <v>818</v>
+        <v>780</v>
       </c>
       <c r="E8">
         <v>100000000</v>
       </c>
       <c r="F8" s="7">
-        <v>2152000000</v>
+        <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>819</v>
+        <v>781</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -13794,22 +13813,22 @@
         <v>422</v>
       </c>
       <c r="B9" t="s">
-        <v>803</v>
+        <v>765</v>
       </c>
       <c r="C9" t="s">
-        <v>804</v>
+        <v>766</v>
       </c>
       <c r="D9" t="s">
-        <v>805</v>
+        <v>767</v>
       </c>
       <c r="E9">
         <v>100000000</v>
       </c>
       <c r="F9" s="7">
-        <v>68000000</v>
+        <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>806</v>
+        <v>768</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -13820,22 +13839,22 @@
         <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>847</v>
+        <v>809</v>
       </c>
       <c r="C10" t="s">
-        <v>848</v>
+        <v>810</v>
       </c>
       <c r="D10" t="s">
-        <v>849</v>
+        <v>811</v>
       </c>
       <c r="E10">
         <v>100000000</v>
       </c>
       <c r="F10" s="7">
-        <v>300000000</v>
+        <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>850</v>
+        <v>812</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -13846,22 +13865,22 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>827</v>
+        <v>789</v>
       </c>
       <c r="C11" t="s">
-        <v>828</v>
+        <v>790</v>
       </c>
       <c r="D11" t="s">
-        <v>829</v>
+        <v>791</v>
       </c>
       <c r="E11">
         <v>100000000</v>
       </c>
       <c r="F11" s="7">
-        <v>358000000</v>
+        <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>830</v>
+        <v>792</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -13872,22 +13891,22 @@
         <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>799</v>
+        <v>761</v>
       </c>
       <c r="C12" t="s">
-        <v>800</v>
+        <v>762</v>
       </c>
       <c r="D12" t="s">
-        <v>801</v>
+        <v>763</v>
       </c>
       <c r="E12">
         <v>100000000</v>
       </c>
       <c r="F12" s="7">
-        <v>1400000000</v>
+        <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>802</v>
+        <v>764</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -13898,22 +13917,22 @@
         <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>940</v>
+        <v>901</v>
       </c>
       <c r="C13" t="s">
-        <v>820</v>
+        <v>782</v>
       </c>
       <c r="D13" t="s">
-        <v>821</v>
+        <v>783</v>
       </c>
       <c r="E13">
         <v>100000000</v>
       </c>
       <c r="F13" s="7">
-        <v>299000000</v>
+        <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>822</v>
+        <v>784</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -13924,13 +13943,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>843</v>
+        <v>805</v>
       </c>
       <c r="C14" t="s">
-        <v>844</v>
+        <v>806</v>
       </c>
       <c r="D14" t="s">
-        <v>845</v>
+        <v>807</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13939,7 +13958,7 @@
         <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>846</v>
+        <v>808</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -13950,13 +13969,13 @@
         <v>419</v>
       </c>
       <c r="B15" t="s">
-        <v>841</v>
+        <v>803</v>
       </c>
       <c r="C15" t="s">
-        <v>941</v>
+        <v>902</v>
       </c>
       <c r="D15" t="s">
-        <v>945</v>
+        <v>906</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13965,7 +13984,7 @@
         <v>450000000</v>
       </c>
       <c r="G15" t="s">
-        <v>842</v>
+        <v>804</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -13973,16 +13992,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>913</v>
+        <v>874</v>
       </c>
       <c r="B16" t="s">
-        <v>936</v>
+        <v>897</v>
       </c>
       <c r="C16" t="s">
-        <v>942</v>
+        <v>903</v>
       </c>
       <c r="D16" t="s">
-        <v>946</v>
+        <v>907</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -13991,7 +14010,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>948</v>
+        <v>909</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -14002,22 +14021,22 @@
         <v>403</v>
       </c>
       <c r="B17" t="s">
-        <v>939</v>
+        <v>900</v>
       </c>
       <c r="C17" t="s">
-        <v>800</v>
+        <v>762</v>
       </c>
       <c r="D17" t="s">
-        <v>814</v>
+        <v>776</v>
       </c>
       <c r="E17">
         <v>100000000</v>
       </c>
       <c r="F17" s="7">
-        <v>566000000</v>
+        <v>440000000</v>
       </c>
       <c r="G17" t="s">
-        <v>815</v>
+        <v>777</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -14028,22 +14047,22 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>937</v>
+        <v>898</v>
       </c>
       <c r="C18" t="s">
-        <v>943</v>
+        <v>904</v>
       </c>
       <c r="D18" t="s">
-        <v>947</v>
+        <v>908</v>
       </c>
       <c r="E18">
         <v>100000000</v>
       </c>
       <c r="F18" s="7">
-        <v>300000000</v>
+        <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>949</v>
+        <v>910</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14051,25 +14070,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>978</v>
+        <v>939</v>
       </c>
       <c r="B19" t="s">
-        <v>1002</v>
+        <v>963</v>
       </c>
       <c r="C19" t="s">
-        <v>1003</v>
+        <v>964</v>
       </c>
       <c r="D19" t="s">
-        <v>1004</v>
+        <v>965</v>
       </c>
       <c r="E19">
         <v>100000000</v>
       </c>
       <c r="F19" s="7">
-        <v>300000000</v>
+        <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>1005</v>
+        <v>966</v>
       </c>
     </row>
   </sheetData>
@@ -14084,7 +14103,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -14102,30 +14121,30 @@
         <v>383</v>
       </c>
       <c r="B1" t="s">
-        <v>851</v>
+        <v>813</v>
       </c>
       <c r="C1" t="s">
-        <v>852</v>
+        <v>814</v>
       </c>
       <c r="D1" t="s">
-        <v>853</v>
+        <v>815</v>
       </c>
       <c r="E1" t="s">
-        <v>854</v>
+        <v>816</v>
       </c>
       <c r="F1" t="s">
-        <v>855</v>
+        <v>817</v>
       </c>
       <c r="G1" t="s">
-        <v>856</v>
+        <v>818</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>857</v>
+        <v>819</v>
       </c>
       <c r="B2" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C2" t="s">
         <v>411</v>
@@ -14137,10 +14156,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G2" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -14148,7 +14167,7 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C3" t="s">
         <v>411</v>
@@ -14160,10 +14179,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G3" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -14171,7 +14190,7 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C4" t="s">
         <v>411</v>
@@ -14183,10 +14202,10 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G4" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -14194,30 +14213,30 @@
         <v>394</v>
       </c>
       <c r="B5" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C5" t="s">
         <v>411</v>
       </c>
       <c r="D5" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G5" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>862</v>
+        <v>824</v>
       </c>
       <c r="B6" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C6" t="s">
         <v>411</v>
@@ -14229,18 +14248,18 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G6" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>863</v>
+        <v>825</v>
       </c>
       <c r="B7" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C7" t="s">
         <v>411</v>
@@ -14252,18 +14271,18 @@
         <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G7" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>864</v>
+        <v>826</v>
       </c>
       <c r="B8" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C8" t="s">
         <v>420</v>
@@ -14275,18 +14294,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G8" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>867</v>
+        <v>829</v>
       </c>
       <c r="B9" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C9" t="s">
         <v>411</v>
@@ -14298,33 +14317,33 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G9" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>868</v>
+        <v>830</v>
       </c>
       <c r="B10" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C10" t="s">
         <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="E10">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G10" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -14332,33 +14351,33 @@
         <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C11" t="s">
         <v>411</v>
       </c>
       <c r="D11" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G11" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>870</v>
+        <v>832</v>
       </c>
       <c r="B12" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C12" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -14367,10 +14386,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G12" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -14378,10 +14397,10 @@
         <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C13" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="D13" t="s">
         <v>406</v>
@@ -14390,21 +14409,21 @@
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G13" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>871</v>
+        <v>833</v>
       </c>
       <c r="B14" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C14" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="D14" t="s">
         <v>409</v>
@@ -14413,41 +14432,41 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G14" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>872</v>
+        <v>834</v>
       </c>
       <c r="B15" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C15" t="s">
         <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>861</v>
+        <v>823</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G15" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>873</v>
+        <v>835</v>
       </c>
       <c r="B16" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -14459,18 +14478,18 @@
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G16" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>874</v>
+        <v>836</v>
       </c>
       <c r="B17" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -14482,18 +14501,18 @@
         <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G17" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>875</v>
+        <v>837</v>
       </c>
       <c r="B18" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C18" t="s">
         <v>406</v>
@@ -14505,10 +14524,10 @@
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G18" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -14516,10 +14535,10 @@
         <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C19" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="D19" t="s">
         <v>420</v>
@@ -14528,21 +14547,21 @@
         <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G19" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>877</v>
+        <v>839</v>
       </c>
       <c r="B20" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C20" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="D20" t="s">
         <v>420</v>
@@ -14551,10 +14570,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G20" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -14562,68 +14581,68 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C21" t="s">
         <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G21" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>878</v>
+        <v>840</v>
       </c>
       <c r="B22" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C22" t="s">
         <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="E22">
         <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G22" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>879</v>
+        <v>841</v>
       </c>
       <c r="B23" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C23" t="s">
         <v>407</v>
       </c>
       <c r="D23" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G23" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -14631,10 +14650,10 @@
         <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C24" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="D24" t="s">
         <v>407</v>
@@ -14643,10 +14662,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G24" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -14654,22 +14673,22 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C25" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="D25" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G25" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -14677,22 +14696,22 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C26" t="s">
-        <v>876</v>
+        <v>838</v>
       </c>
       <c r="D26" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G26" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -14700,7 +14719,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -14712,10 +14731,10 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G27" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -14723,7 +14742,7 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -14735,18 +14754,18 @@
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G28" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>881</v>
+        <v>843</v>
       </c>
       <c r="B29" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C29" t="s">
         <v>421</v>
@@ -14758,10 +14777,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G29" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -14769,7 +14788,7 @@
         <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -14781,10 +14800,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G30" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -14792,7 +14811,7 @@
         <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C31" t="s">
         <v>420</v>
@@ -14804,10 +14823,10 @@
         <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G31" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -14815,7 +14834,7 @@
         <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>869</v>
+        <v>831</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -14827,10 +14846,10 @@
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G32" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -14838,7 +14857,7 @@
         <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C33" t="s">
         <v>422</v>
@@ -14850,10 +14869,10 @@
         <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G33" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -14861,7 +14880,7 @@
         <v>332</v>
       </c>
       <c r="B34" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C34" t="s">
         <v>422</v>
@@ -14873,18 +14892,18 @@
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G34" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>882</v>
+        <v>844</v>
       </c>
       <c r="B35" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -14896,10 +14915,10 @@
         <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G35" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -14907,7 +14926,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -14919,18 +14938,18 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G36" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>885</v>
+        <v>847</v>
       </c>
       <c r="B37" t="s">
-        <v>865</v>
+        <v>827</v>
       </c>
       <c r="C37" t="s">
         <v>421</v>
@@ -14942,33 +14961,33 @@
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G37" t="s">
-        <v>866</v>
+        <v>828</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>886</v>
+        <v>848</v>
       </c>
       <c r="B38" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C38" t="s">
         <v>409</v>
       </c>
       <c r="D38" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G38" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -14976,30 +14995,30 @@
         <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C39" t="s">
         <v>407</v>
       </c>
       <c r="D39" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>887</v>
+        <v>849</v>
       </c>
       <c r="B40" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C40" t="s">
-        <v>880</v>
+        <v>842</v>
       </c>
       <c r="D40" t="s">
         <v>407</v>
@@ -15008,7 +15027,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -15016,7 +15035,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -15028,7 +15047,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -15036,7 +15055,7 @@
         <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -15048,15 +15067,15 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>888</v>
+        <v>850</v>
       </c>
       <c r="B43" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -15068,18 +15087,18 @@
         <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G43" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>889</v>
+        <v>851</v>
       </c>
       <c r="B44" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C44" t="s">
         <v>422</v>
@@ -15094,7 +15113,7 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -15102,7 +15121,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C45" t="s">
         <v>422</v>
@@ -15117,7 +15136,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>884</v>
+        <v>846</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -15125,7 +15144,7 @@
         <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -15137,10 +15156,10 @@
         <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G46" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -15148,7 +15167,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -15160,10 +15179,10 @@
         <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G47" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -15171,7 +15190,7 @@
         <v>247</v>
       </c>
       <c r="B48" t="s">
-        <v>858</v>
+        <v>820</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -15183,24 +15202,24 @@
         <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>859</v>
+        <v>821</v>
       </c>
       <c r="G48" t="s">
-        <v>860</v>
+        <v>822</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1016</v>
+        <v>976</v>
       </c>
       <c r="B49" t="s">
-        <v>883</v>
+        <v>845</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>913</v>
+        <v>874</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -15209,7 +15228,53 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>1017</v>
+        <v>977</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>978</v>
+      </c>
+      <c r="B50" t="s">
+        <v>845</v>
+      </c>
+      <c r="C50" t="s">
+        <v>407</v>
+      </c>
+      <c r="D50" t="s">
+        <v>411</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>2</v>
+      </c>
+      <c r="G50" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>826</v>
+      </c>
+      <c r="B51" t="s">
+        <v>845</v>
+      </c>
+      <c r="C51" t="s">
+        <v>411</v>
+      </c>
+      <c r="D51" t="s">
+        <v>407</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>2</v>
+      </c>
+      <c r="G51" t="s">
+        <v>977</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9086B66-B188-4FB8-AD65-D50DCC4B694E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC06AB8-96F4-462B-ACFD-218D285D6934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1019">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -1382,9 +1382,6 @@
     <t>PT Emiliano Martínez</t>
   </si>
   <si>
-    <t>LD Jeremie Frimpong</t>
-  </si>
-  <si>
     <t>PT Alisson Becker</t>
   </si>
   <si>
@@ -1427,9 +1424,6 @@
     <t>CT Alessandro Bastoni</t>
   </si>
   <si>
-    <t>CT Jonathan Tah</t>
-  </si>
-  <si>
     <t>CT Gabriel Magalhães</t>
   </si>
   <si>
@@ -1472,9 +1466,6 @@
     <t>CT David Alaba</t>
   </si>
   <si>
-    <t>CT Micky van de Ven</t>
-  </si>
-  <si>
     <t>LD Jules Koundé</t>
   </si>
   <si>
@@ -1565,9 +1556,6 @@
     <t>LI Alejandro Grimaldo</t>
   </si>
   <si>
-    <t>MP Malik Tillman</t>
-  </si>
-  <si>
     <t>CT Robin Le Normand</t>
   </si>
   <si>
@@ -1658,9 +1646,6 @@
     <t>MC Lamine Camara</t>
   </si>
   <si>
-    <t>EI Mattia Zaccagni</t>
-  </si>
-  <si>
     <t>LD Malo Gusto</t>
   </si>
   <si>
@@ -1787,9 +1772,6 @@
     <t>EI Anthony Gordon</t>
   </si>
   <si>
-    <t>DC Ruud van Nistelrooy</t>
-  </si>
-  <si>
     <t>DC João Pedro</t>
   </si>
   <si>
@@ -1823,9 +1805,6 @@
     <t>DC Ivan Toney</t>
   </si>
   <si>
-    <t>DC Diego Forlán</t>
-  </si>
-  <si>
     <t>MC Rodrigo De Paul</t>
   </si>
   <si>
@@ -1901,9 +1880,6 @@
     <t>MCD Amadou Onana</t>
   </si>
   <si>
-    <t>PT Vítor Baía</t>
-  </si>
-  <si>
     <t>PT Keylor Navas</t>
   </si>
   <si>
@@ -1943,9 +1919,6 @@
     <t>MP Ismael Saibari</t>
   </si>
   <si>
-    <t>PT Bart Verbruggen</t>
-  </si>
-  <si>
     <t>CT Cristhian Mosquera</t>
   </si>
   <si>
@@ -1985,9 +1958,6 @@
     <t>CT Willian Pacho</t>
   </si>
   <si>
-    <t>LI Pervis Estupiñán</t>
-  </si>
-  <si>
     <t>MP Cole Palmer</t>
   </si>
   <si>
@@ -2120,9 +2090,6 @@
     <t>ED Serge Gnabry</t>
   </si>
   <si>
-    <t>EI Rafael Leão</t>
-  </si>
-  <si>
     <t>MC Bruno Guimarães</t>
   </si>
   <si>
@@ -2147,9 +2114,6 @@
     <t>CT Raúl Asencio</t>
   </si>
   <si>
-    <t>ED Matías Soulé</t>
-  </si>
-  <si>
     <t>ED Donyell Malen</t>
   </si>
   <si>
@@ -2189,9 +2153,6 @@
     <t>MP Rayan Cherki</t>
   </si>
   <si>
-    <t>ED Giuliano Simeone</t>
-  </si>
-  <si>
     <t>MCD Casemiro</t>
   </si>
   <si>
@@ -2231,9 +2192,6 @@
     <t>EI Christos Tzolis</t>
   </si>
   <si>
-    <t>CT Marc Guéhi</t>
-  </si>
-  <si>
     <t>CT Rúben Dias</t>
   </si>
   <si>
@@ -2318,9 +2276,6 @@
     <t>DC Mikel Oyarzabal</t>
   </si>
   <si>
-    <t>CT Éder Militão</t>
-  </si>
-  <si>
     <t>DC Sergio Agüero</t>
   </si>
   <si>
@@ -2843,9 +2798,6 @@
     <t>Carlos Espi</t>
   </si>
   <si>
-    <t>DC Carlos Espi</t>
-  </si>
-  <si>
     <t>Club_America</t>
   </si>
   <si>
@@ -3147,6 +3099,63 @@
   </si>
   <si>
     <t>DC Pio Esposito</t>
+  </si>
+  <si>
+    <t>PT Manuel Neuer</t>
+  </si>
+  <si>
+    <t>CT Murilo</t>
+  </si>
+  <si>
+    <t>CT Juan Pablo Freytes</t>
+  </si>
+  <si>
+    <t>CT Daniel Ballard</t>
+  </si>
+  <si>
+    <t>LD Pedro Porro</t>
+  </si>
+  <si>
+    <t>MCD Mario Lemina</t>
+  </si>
+  <si>
+    <t>MC Eduardo Camavinga</t>
+  </si>
+  <si>
+    <t>MP João Mário</t>
+  </si>
+  <si>
+    <t>MP Kaká</t>
+  </si>
+  <si>
+    <t>DC Mauro Icardi</t>
+  </si>
+  <si>
+    <t>DC Rafael Leão</t>
+  </si>
+  <si>
+    <t>ID Giuliano Simeone</t>
+  </si>
+  <si>
+    <t>ED Leroy Sané</t>
+  </si>
+  <si>
+    <t>II Koki Ando</t>
+  </si>
+  <si>
+    <t>DC Carlos Espí</t>
+  </si>
+  <si>
+    <t>II Nicola Zalewski</t>
+  </si>
+  <si>
+    <t>ED Ángel Di María</t>
+  </si>
+  <si>
+    <t>EI Mykhailo Mudryk</t>
+  </si>
+  <si>
+    <t>EI Jadon Sancho</t>
   </si>
 </sst>
 </file>
@@ -3647,7 +3656,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -3857,7 +3866,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>141</v>
@@ -3953,7 +3962,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>172</v>
@@ -3967,7 +3976,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>125</v>
@@ -4037,7 +4046,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>299</v>
@@ -4121,7 +4130,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>379</v>
@@ -4357,7 +4366,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>157</v>
@@ -4413,7 +4422,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>363</v>
@@ -4475,10 +4484,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="C64" s="3">
         <v>4</v>
@@ -4741,7 +4750,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>347</v>
@@ -4758,7 +4767,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4841,7 +4850,7 @@
       </c>
       <c r="D90" s="3"/>
       <c r="E90" t="s">
-        <v>912</v>
+        <v>897</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -4870,7 +4879,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>45</v>
@@ -5028,7 +5037,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>315</v>
@@ -5040,7 +5049,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>45</v>
@@ -5376,7 +5385,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>236</v>
@@ -5412,7 +5421,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>109</v>
@@ -5544,7 +5553,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>77</v>
@@ -5652,7 +5661,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>93</v>
@@ -5712,7 +5721,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>331</v>
@@ -5736,10 +5745,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5750,10 +5759,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3">
@@ -5996,10 +6005,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="C186" s="3">
         <v>2</v>
@@ -6034,10 +6043,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B189" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="B189" s="3" t="s">
-        <v>890</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6506,21 +6515,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="B1" t="s">
-        <v>853</v>
+        <v>838</v>
       </c>
       <c r="C1" t="s">
-        <v>854</v>
+        <v>839</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B2" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6528,10 +6537,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B3" t="s">
-        <v>856</v>
+        <v>841</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6539,10 +6548,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B4" t="s">
-        <v>857</v>
+        <v>842</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6550,10 +6559,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B5" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6561,10 +6570,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>855</v>
+        <v>840</v>
       </c>
       <c r="B6" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6572,10 +6581,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="B7" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6583,10 +6592,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="B8" t="s">
-        <v>861</v>
+        <v>846</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6594,10 +6603,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="B9" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6605,10 +6614,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="B10" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6616,10 +6625,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="B11" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6627,10 +6636,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="B12" t="s">
-        <v>858</v>
+        <v>843</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6638,10 +6647,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="B13" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6649,10 +6658,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>862</v>
+        <v>847</v>
       </c>
       <c r="B14" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7065,7 +7074,7 @@
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -7161,7 +7170,7 @@
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>172</v>
@@ -7176,7 +7185,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -7187,10 +7196,10 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -7211,10 +7220,10 @@
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -7307,7 +7316,7 @@
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>141</v>
@@ -7335,7 +7344,7 @@
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>157</v>
@@ -7349,7 +7358,7 @@
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>379</v>
@@ -7373,10 +7382,10 @@
     </row>
     <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
@@ -7617,10 +7626,10 @@
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>875</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>890</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -7631,10 +7640,10 @@
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -7733,7 +7742,7 @@
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>125</v>
@@ -7747,7 +7756,7 @@
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>347</v>
@@ -7795,10 +7804,10 @@
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -7895,10 +7904,10 @@
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -7955,7 +7964,7 @@
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>315</v>
@@ -7979,10 +7988,10 @@
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -8027,7 +8036,7 @@
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
@@ -8075,7 +8084,7 @@
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>109</v>
@@ -8087,7 +8096,7 @@
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>363</v>
@@ -8099,10 +8108,10 @@
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -8123,10 +8132,10 @@
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3">
@@ -10844,8 +10853,7 @@
   <cols>
     <col min="1" max="1" width="23.44140625" style="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.88671875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="20.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.88671875" style="9" bestFit="1" customWidth="1"/>
@@ -10868,9 +10876,9 @@
         <v>411</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>874</v>
-      </c>
-      <c r="C1" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>419</v>
       </c>
       <c r="D1" s="8" t="s">
@@ -10916,7 +10924,7 @@
         <v>425</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10924,1287 +10932,1287 @@
         <v>426</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>967</v>
-      </c>
-      <c r="C2" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="8" t="s">
         <v>435</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="8" t="s">
         <v>438</v>
       </c>
-      <c r="O2" s="8" t="s">
+      <c r="P2" s="8" t="s">
+        <v>976</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>992</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>440</v>
-      </c>
       <c r="R2" s="3" t="s">
-        <v>940</v>
+        <v>924</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>495</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>441</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>499</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="8" t="s">
         <v>442</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="F3" s="8" t="s">
         <v>443</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="G3" s="8" t="s">
+        <v>584</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>445</v>
       </c>
-      <c r="G3" s="8" t="s">
-        <v>591</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="L3" s="8" t="s">
         <v>448</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="M3" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="O3" s="8" t="s">
         <v>451</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>450</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="N3" s="3" t="s">
+      <c r="P3" s="8" t="s">
         <v>452</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="Q3" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="P3" s="8" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>455</v>
-      </c>
       <c r="R3" s="3" t="s">
-        <v>941</v>
+        <v>925</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>851</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>866</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="F4" s="8" t="s">
         <v>457</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="G4" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>458</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="I4" s="8" t="s">
         <v>459</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="J4" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>446</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="K4" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="L4" s="8" t="s">
         <v>462</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="M4" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="L4" s="8" t="s">
+      <c r="O4" s="8" t="s">
         <v>465</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="Q4" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>468</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>469</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>470</v>
-      </c>
       <c r="R4" s="3" t="s">
-        <v>942</v>
+        <v>926</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>470</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>471</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>968</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="8" t="s">
         <v>472</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="G5" s="8" t="s">
+        <v>979</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="I5" s="8" t="s">
         <v>475</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>995</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="J5" s="8" t="s">
+        <v>596</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="L5" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="J5" s="8" t="s">
-        <v>604</v>
-      </c>
-      <c r="K5" s="3" t="s">
+      <c r="M5" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="N5" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>481</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="Q5" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="O5" s="8" t="s">
-        <v>484</v>
-      </c>
-      <c r="P5" s="8" t="s">
-        <v>485</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>486</v>
-      </c>
       <c r="R5" s="3" t="s">
-        <v>943</v>
+        <v>927</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>850</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>485</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>486</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>487</v>
       </c>
-      <c r="B6" s="8" t="s">
-        <v>865</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="G6" s="8" t="s">
+        <v>980</v>
+      </c>
+      <c r="H6" s="8" t="s">
         <v>488</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="I6" s="8" t="s">
         <v>489</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="J6" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="K6" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>996</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="L6" s="8" t="s">
         <v>492</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="M6" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="J6" s="8" t="s">
+      <c r="N6" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="L6" s="8" t="s">
+      <c r="O6" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="P6" s="8" t="s">
         <v>496</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="Q6" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>1005</v>
-      </c>
-      <c r="P6" s="8" t="s">
-        <v>500</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>501</v>
-      </c>
       <c r="R6" s="3" t="s">
-        <v>944</v>
+        <v>928</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>501</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>969</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="G7" s="8" t="s">
+        <v>473</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>476</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="K7" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="L7" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="M7" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="N7" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="O7" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="P7" s="8" t="s">
         <v>512</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="Q7" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>514</v>
-      </c>
-      <c r="O7" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="P7" s="8" t="s">
-        <v>516</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>517</v>
-      </c>
       <c r="R7" s="3" t="s">
-        <v>945</v>
+        <v>929</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>514</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>970</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="I8" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="J8" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="K8" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="L8" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="M8" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>617</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="N8" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="J8" s="8" t="s">
+      <c r="O8" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="P8" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="Q8" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="L8" s="8" t="s">
-        <v>980</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>528</v>
-      </c>
-      <c r="O8" s="8" t="s">
-        <v>637</v>
-      </c>
-      <c r="P8" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>531</v>
-      </c>
       <c r="R8" s="3" t="s">
-        <v>946</v>
+        <v>930</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>867</v>
-      </c>
-      <c r="C9" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>531</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="I9" s="8" t="s">
         <v>534</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="J9" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="K9" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>632</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="L9" s="8" t="s">
+        <v>965</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="O9" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="J9" s="8" t="s">
+      <c r="P9" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="Q9" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="L9" s="8" t="s">
-        <v>981</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>543</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>544</v>
-      </c>
-      <c r="P9" s="8" t="s">
-        <v>545</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>546</v>
-      </c>
       <c r="R9" s="3" t="s">
-        <v>947</v>
+        <v>931</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>979</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>864</v>
+        <v>963</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1008</v>
       </c>
       <c r="D10" s="8" t="s">
+        <v>544</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>476</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="I10" s="8" t="s">
         <v>549</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="J10" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="K10" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>479</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="L10" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="N10" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="O10" s="8" t="s">
         <v>554</v>
       </c>
-      <c r="J10" s="8" t="s">
+      <c r="P10" s="8" t="s">
         <v>555</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>556</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>982</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>558</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="P10" s="8" t="s">
-        <v>560</v>
-      </c>
       <c r="Q10" s="3" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>948</v>
+        <v>932</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
+        <v>556</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>981</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="J11" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>751</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>989</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="L11" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="M11" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="N11" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>997</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="O11" s="8" t="s">
         <v>565</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="P11" s="8" t="s">
         <v>566</v>
       </c>
-      <c r="J11" s="8" t="s">
+      <c r="Q11" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>983</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>569</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>570</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>571</v>
-      </c>
-      <c r="P11" s="8" t="s">
-        <v>572</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>573</v>
-      </c>
       <c r="R11" s="3" t="s">
-        <v>949</v>
+        <v>933</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>1009</v>
+        <v>993</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>587</v>
-      </c>
-      <c r="C12" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>570</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="L12" s="8" t="s">
         <v>574</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="M12" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="N12" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="O12" s="8" t="s">
         <v>577</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>507</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="P12" s="8" t="s">
         <v>578</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="Q12" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="J12" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>580</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>584</v>
-      </c>
-      <c r="P12" s="8" t="s">
-        <v>585</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>586</v>
-      </c>
       <c r="R12" s="3" t="s">
-        <v>950</v>
+        <v>934</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>1010</v>
+        <v>994</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>869</v>
-      </c>
-      <c r="C13" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>581</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>582</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>583</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="L13" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="M13" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="N13" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="O13" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>998</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="P13" s="8" t="s">
+        <v>591</v>
+      </c>
+      <c r="Q13" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="I13" s="8" t="s">
-        <v>593</v>
-      </c>
-      <c r="J13" s="8" t="s">
-        <v>864</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>594</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>596</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>595</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>597</v>
-      </c>
-      <c r="P13" s="8" t="s">
-        <v>598</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>599</v>
-      </c>
       <c r="R13" s="3" t="s">
-        <v>951</v>
+        <v>935</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>1011</v>
+        <v>995</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>870</v>
-      </c>
-      <c r="C14" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>594</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>598</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>599</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="L14" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="M14" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="N14" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>999</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="O14" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="Q14" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="I14" s="9" t="s">
-        <v>606</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>607</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>608</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>609</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>610</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>611</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>1006</v>
-      </c>
-      <c r="P14" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>613</v>
-      </c>
       <c r="R14" s="3" t="s">
-        <v>952</v>
+        <v>936</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>1012</v>
+        <v>996</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="C15" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>607</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="M15" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>990</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="N15" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="O15" s="8" t="s">
+        <v>629</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="G15" s="8" t="s">
-        <v>1000</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>618</v>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>619</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>620</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>621</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>622</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>623</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>624</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="P15" s="8" t="s">
-        <v>625</v>
-      </c>
       <c r="Q15" s="3" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>953</v>
+        <v>937</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>975</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>621</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>623</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>625</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>871</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="D16" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="O16" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>977</v>
+      </c>
+      <c r="Q16" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>633</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>634</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>635</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>636</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>984</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>637</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>638</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>652</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>993</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>640</v>
-      </c>
       <c r="R16" s="3" t="s">
-        <v>954</v>
+        <v>938</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>636</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>972</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>642</v>
-      </c>
-      <c r="D17" s="8" t="s">
+      <c r="O17" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="P17" s="8" t="s">
         <v>643</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="Q17" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>727</v>
-      </c>
-      <c r="H17" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="J17" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>649</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>664</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>650</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>651</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>667</v>
-      </c>
-      <c r="P17" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>654</v>
-      </c>
       <c r="R17" s="3" t="s">
-        <v>955</v>
+        <v>939</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>652</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>969</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B18" s="8" t="s">
-        <v>973</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="N18" s="3" t="s">
         <v>656</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>657</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="O18" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="P18" s="8" t="s">
         <v>658</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="Q18" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="G18" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>661</v>
-      </c>
-      <c r="J18" s="8" t="s">
-        <v>662</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>985</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>665</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>666</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="P18" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>669</v>
-      </c>
       <c r="R18" s="3" t="s">
-        <v>956</v>
+        <v>940</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>1013</v>
+        <v>997</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>868</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>914</v>
+        <v>853</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1015</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>660</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>662</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="O19" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="P19" s="8" t="s">
+        <v>978</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>670</v>
       </c>
-      <c r="E19" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>672</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>1002</v>
-      </c>
-      <c r="H19" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>675</v>
-      </c>
-      <c r="J19" s="8" t="s">
-        <v>676</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>677</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>986</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>680</v>
-      </c>
-      <c r="P19" s="8" t="s">
-        <v>994</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>681</v>
-      </c>
       <c r="R19" s="3" t="s">
-        <v>957</v>
+        <v>941</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>1014</v>
+        <v>998</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>974</v>
-      </c>
-      <c r="C20" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>676</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>677</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="P20" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="Q20" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>683</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="G20" s="8" t="s">
-        <v>1003</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>687</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>688</v>
-      </c>
-      <c r="J20" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>690</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>987</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>692</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>719</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>694</v>
-      </c>
       <c r="R20" s="3" t="s">
-        <v>958</v>
+        <v>942</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>684</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>695</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>975</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>696</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>697</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>698</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>700</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>701</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>704</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>705</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>706</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>1007</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>708</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>709</v>
-      </c>
       <c r="R21" s="3" t="s">
-        <v>959</v>
+        <v>943</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>1015</v>
+        <v>999</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>723</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1016</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>711</v>
+        <v>697</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>712</v>
+        <v>698</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>1004</v>
+        <v>988</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>715</v>
+        <v>701</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>716</v>
+        <v>702</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>988</v>
+        <v>972</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>717</v>
+        <v>703</v>
       </c>
       <c r="N22" s="3" t="s">
-        <v>718</v>
+        <v>704</v>
       </c>
       <c r="O22" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="Q22" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="P22" s="8" t="s">
-        <v>720</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>721</v>
-      </c>
       <c r="R22" s="3" t="s">
-        <v>960</v>
+        <v>944</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>711</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>728</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>716</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="O23" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="P23" s="8" t="s">
         <v>722</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>872</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>723</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>725</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>726</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="J23" s="8" t="s">
-        <v>730</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>733</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>735</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>736</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>737</v>
-      </c>
       <c r="R23" s="3" t="s">
-        <v>961</v>
+        <v>945</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>731</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>733</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>734</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>735</v>
+      </c>
+      <c r="O24" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q24" s="3" t="s">
         <v>738</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>873</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>739</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>741</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>742</v>
-      </c>
-      <c r="G24" s="8" t="s">
-        <v>673</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>744</v>
-      </c>
-      <c r="I24" s="8" t="s">
-        <v>745</v>
-      </c>
-      <c r="J24" s="8" t="s">
-        <v>746</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>748</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>749</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>750</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>1008</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>752</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>753</v>
-      </c>
       <c r="R24" s="3" t="s">
-        <v>962</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -12242,7 +12250,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>875</v>
+        <v>860</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -12281,7 +12289,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>911</v>
+        <v>896</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -12290,7 +12298,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>915</v>
+        <v>899</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -12298,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>876</v>
+        <v>861</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -12346,7 +12354,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>916</v>
+        <v>900</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -12354,7 +12362,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>877</v>
+        <v>862</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -12402,7 +12410,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>917</v>
+        <v>901</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -12410,7 +12418,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>878</v>
+        <v>863</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -12458,7 +12466,7 @@
         <v>63</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>918</v>
+        <v>902</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -12466,7 +12474,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>879</v>
+        <v>864</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -12514,7 +12522,7 @@
         <v>79</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>919</v>
+        <v>903</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -12522,7 +12530,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -12570,7 +12578,7 @@
         <v>95</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>920</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -12578,7 +12586,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>880</v>
+        <v>865</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -12626,7 +12634,7 @@
         <v>111</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -12634,7 +12642,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -12682,7 +12690,7 @@
         <v>127</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>922</v>
+        <v>906</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -12690,7 +12698,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>882</v>
+        <v>867</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -12738,7 +12746,7 @@
         <v>143</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>923</v>
+        <v>907</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -12746,10 +12754,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>883</v>
+        <v>868</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>863</v>
+        <v>848</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -12794,7 +12802,7 @@
         <v>145</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>924</v>
+        <v>908</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -12802,7 +12810,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>884</v>
+        <v>869</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -12850,7 +12858,7 @@
         <v>174</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>925</v>
+        <v>909</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -12858,7 +12866,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>885</v>
+        <v>870</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -12906,7 +12914,7 @@
         <v>190</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>926</v>
+        <v>910</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -12914,7 +12922,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>886</v>
+        <v>871</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -12962,7 +12970,7 @@
         <v>206</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>927</v>
+        <v>911</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -12970,7 +12978,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>887</v>
+        <v>872</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -13018,7 +13026,7 @@
         <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>928</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -13026,7 +13034,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>888</v>
+        <v>873</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -13074,7 +13082,7 @@
         <v>238</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>929</v>
+        <v>913</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -13082,7 +13090,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>889</v>
+        <v>874</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -13130,7 +13138,7 @@
         <v>254</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>930</v>
+        <v>914</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -13138,7 +13146,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>890</v>
+        <v>875</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -13186,7 +13194,7 @@
         <v>270</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>931</v>
+        <v>915</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -13194,7 +13202,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>891</v>
+        <v>876</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -13242,7 +13250,7 @@
         <v>286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>932</v>
+        <v>916</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -13250,10 +13258,10 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>892</v>
+        <v>877</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>913</v>
+        <v>898</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -13298,7 +13306,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>933</v>
+        <v>917</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -13306,7 +13314,7 @@
         <v>302</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>893</v>
+        <v>878</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>303</v>
@@ -13354,7 +13362,7 @@
         <v>317</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>934</v>
+        <v>918</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -13362,7 +13370,7 @@
         <v>318</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>894</v>
+        <v>879</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>319</v>
@@ -13410,7 +13418,7 @@
         <v>333</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>935</v>
+        <v>919</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -13418,7 +13426,7 @@
         <v>334</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>335</v>
@@ -13466,7 +13474,7 @@
         <v>349</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>936</v>
+        <v>920</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -13522,7 +13530,7 @@
         <v>365</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>937</v>
+        <v>921</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -13530,7 +13538,7 @@
         <v>366</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>896</v>
+        <v>881</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>367</v>
@@ -13578,7 +13586,7 @@
         <v>381</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>938</v>
+        <v>922</v>
       </c>
     </row>
   </sheetData>
@@ -13605,25 +13613,25 @@
         <v>382</v>
       </c>
       <c r="B1" t="s">
-        <v>754</v>
+        <v>739</v>
       </c>
       <c r="C1" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="D1" t="s">
-        <v>756</v>
+        <v>741</v>
       </c>
       <c r="E1" t="s">
-        <v>757</v>
+        <v>742</v>
       </c>
       <c r="F1" t="s">
-        <v>758</v>
+        <v>743</v>
       </c>
       <c r="G1" t="s">
-        <v>759</v>
+        <v>744</v>
       </c>
       <c r="H1" t="s">
-        <v>760</v>
+        <v>745</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -13631,13 +13639,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>799</v>
+        <v>784</v>
       </c>
       <c r="C2" t="s">
-        <v>800</v>
+        <v>785</v>
       </c>
       <c r="D2" t="s">
-        <v>801</v>
+        <v>786</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -13646,7 +13654,7 @@
         <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -13657,13 +13665,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>796</v>
+        <v>781</v>
       </c>
       <c r="C3" t="s">
-        <v>797</v>
+        <v>782</v>
       </c>
       <c r="D3" t="s">
-        <v>905</v>
+        <v>890</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13672,7 +13680,7 @@
         <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>798</v>
+        <v>783</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -13686,10 +13694,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>793</v>
+        <v>778</v>
       </c>
       <c r="D4" t="s">
-        <v>794</v>
+        <v>779</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13698,7 +13706,7 @@
         <v>8100000000</v>
       </c>
       <c r="G4" t="s">
-        <v>795</v>
+        <v>780</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -13709,13 +13717,13 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>899</v>
+        <v>884</v>
       </c>
       <c r="C5" t="s">
-        <v>769</v>
+        <v>754</v>
       </c>
       <c r="D5" t="s">
-        <v>770</v>
+        <v>755</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13724,7 +13732,7 @@
         <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -13735,13 +13743,13 @@
         <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>785</v>
+        <v>770</v>
       </c>
       <c r="C6" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="D6" t="s">
-        <v>787</v>
+        <v>772</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13750,7 +13758,7 @@
         <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>788</v>
+        <v>773</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -13761,13 +13769,13 @@
         <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>772</v>
+        <v>757</v>
       </c>
       <c r="C7" t="s">
-        <v>773</v>
+        <v>758</v>
       </c>
       <c r="D7" t="s">
-        <v>774</v>
+        <v>759</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13776,7 +13784,7 @@
         <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -13787,13 +13795,13 @@
         <v>407</v>
       </c>
       <c r="B8" t="s">
-        <v>778</v>
+        <v>763</v>
       </c>
       <c r="C8" t="s">
-        <v>779</v>
+        <v>764</v>
       </c>
       <c r="D8" t="s">
-        <v>780</v>
+        <v>765</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13802,7 +13810,7 @@
         <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>781</v>
+        <v>766</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -13813,13 +13821,13 @@
         <v>422</v>
       </c>
       <c r="B9" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="C9" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
       <c r="D9" t="s">
-        <v>767</v>
+        <v>752</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13828,7 +13836,7 @@
         <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>768</v>
+        <v>753</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -13839,13 +13847,13 @@
         <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>809</v>
+        <v>794</v>
       </c>
       <c r="C10" t="s">
-        <v>810</v>
+        <v>795</v>
       </c>
       <c r="D10" t="s">
-        <v>811</v>
+        <v>796</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13854,7 +13862,7 @@
         <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>812</v>
+        <v>797</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -13865,13 +13873,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>789</v>
+        <v>774</v>
       </c>
       <c r="C11" t="s">
-        <v>790</v>
+        <v>775</v>
       </c>
       <c r="D11" t="s">
-        <v>791</v>
+        <v>776</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13880,7 +13888,7 @@
         <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>792</v>
+        <v>777</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -13891,13 +13899,13 @@
         <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>761</v>
+        <v>746</v>
       </c>
       <c r="C12" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="D12" t="s">
-        <v>763</v>
+        <v>748</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13906,7 +13914,7 @@
         <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>764</v>
+        <v>749</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -13917,13 +13925,13 @@
         <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>901</v>
+        <v>886</v>
       </c>
       <c r="C13" t="s">
-        <v>782</v>
+        <v>767</v>
       </c>
       <c r="D13" t="s">
-        <v>783</v>
+        <v>768</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13932,7 +13940,7 @@
         <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>784</v>
+        <v>769</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -13943,13 +13951,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>805</v>
+        <v>790</v>
       </c>
       <c r="C14" t="s">
-        <v>806</v>
+        <v>791</v>
       </c>
       <c r="D14" t="s">
-        <v>807</v>
+        <v>792</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13958,7 +13966,7 @@
         <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>808</v>
+        <v>793</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -13969,22 +13977,22 @@
         <v>419</v>
       </c>
       <c r="B15" t="s">
-        <v>803</v>
+        <v>788</v>
       </c>
       <c r="C15" t="s">
-        <v>902</v>
+        <v>887</v>
       </c>
       <c r="D15" t="s">
-        <v>906</v>
+        <v>891</v>
       </c>
       <c r="E15">
         <v>100000000</v>
       </c>
       <c r="F15" s="7">
-        <v>450000000</v>
+        <v>357000000</v>
       </c>
       <c r="G15" t="s">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -13992,16 +14000,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="B16" t="s">
-        <v>897</v>
+        <v>882</v>
       </c>
       <c r="C16" t="s">
-        <v>903</v>
+        <v>888</v>
       </c>
       <c r="D16" t="s">
-        <v>907</v>
+        <v>892</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -14010,7 +14018,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>909</v>
+        <v>894</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -14021,13 +14029,13 @@
         <v>403</v>
       </c>
       <c r="B17" t="s">
-        <v>900</v>
+        <v>885</v>
       </c>
       <c r="C17" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="D17" t="s">
-        <v>776</v>
+        <v>761</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -14036,7 +14044,7 @@
         <v>440000000</v>
       </c>
       <c r="G17" t="s">
-        <v>777</v>
+        <v>762</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -14047,13 +14055,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>898</v>
+        <v>883</v>
       </c>
       <c r="C18" t="s">
-        <v>904</v>
+        <v>889</v>
       </c>
       <c r="D18" t="s">
-        <v>908</v>
+        <v>893</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14062,7 +14070,7 @@
         <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>910</v>
+        <v>895</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14070,16 +14078,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>939</v>
+        <v>923</v>
       </c>
       <c r="B19" t="s">
-        <v>963</v>
+        <v>947</v>
       </c>
       <c r="C19" t="s">
-        <v>964</v>
+        <v>948</v>
       </c>
       <c r="D19" t="s">
-        <v>965</v>
+        <v>949</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -14088,7 +14096,7 @@
         <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>966</v>
+        <v>950</v>
       </c>
     </row>
   </sheetData>
@@ -14121,30 +14129,30 @@
         <v>383</v>
       </c>
       <c r="B1" t="s">
-        <v>813</v>
+        <v>798</v>
       </c>
       <c r="C1" t="s">
-        <v>814</v>
+        <v>799</v>
       </c>
       <c r="D1" t="s">
-        <v>815</v>
+        <v>800</v>
       </c>
       <c r="E1" t="s">
-        <v>816</v>
+        <v>801</v>
       </c>
       <c r="F1" t="s">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="G1" t="s">
-        <v>818</v>
+        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>819</v>
+        <v>804</v>
       </c>
       <c r="B2" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C2" t="s">
         <v>411</v>
@@ -14156,10 +14164,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G2" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -14167,7 +14175,7 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C3" t="s">
         <v>411</v>
@@ -14179,10 +14187,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G3" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -14190,7 +14198,7 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C4" t="s">
         <v>411</v>
@@ -14202,10 +14210,10 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G4" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -14213,30 +14221,30 @@
         <v>394</v>
       </c>
       <c r="B5" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C5" t="s">
         <v>411</v>
       </c>
       <c r="D5" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G5" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="B6" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C6" t="s">
         <v>411</v>
@@ -14248,18 +14256,18 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G6" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>825</v>
+        <v>810</v>
       </c>
       <c r="B7" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C7" t="s">
         <v>411</v>
@@ -14271,18 +14279,18 @@
         <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G7" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="B8" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C8" t="s">
         <v>420</v>
@@ -14294,18 +14302,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G8" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>829</v>
+        <v>814</v>
       </c>
       <c r="B9" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C9" t="s">
         <v>411</v>
@@ -14317,33 +14325,33 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G9" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>830</v>
+        <v>815</v>
       </c>
       <c r="B10" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C10" t="s">
         <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="E10">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G10" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -14351,33 +14359,33 @@
         <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C11" t="s">
         <v>411</v>
       </c>
       <c r="D11" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G11" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>832</v>
+        <v>817</v>
       </c>
       <c r="B12" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C12" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -14386,10 +14394,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G12" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -14397,10 +14405,10 @@
         <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C13" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D13" t="s">
         <v>406</v>
@@ -14409,21 +14417,21 @@
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G13" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>833</v>
+        <v>818</v>
       </c>
       <c r="B14" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C14" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="D14" t="s">
         <v>409</v>
@@ -14432,41 +14440,41 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G14" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>834</v>
+        <v>819</v>
       </c>
       <c r="B15" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C15" t="s">
         <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>823</v>
+        <v>808</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G15" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>835</v>
+        <v>820</v>
       </c>
       <c r="B16" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -14478,18 +14486,18 @@
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G16" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>836</v>
+        <v>821</v>
       </c>
       <c r="B17" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -14501,18 +14509,18 @@
         <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G17" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>837</v>
+        <v>822</v>
       </c>
       <c r="B18" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C18" t="s">
         <v>406</v>
@@ -14524,10 +14532,10 @@
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G18" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -14535,10 +14543,10 @@
         <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C19" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="D19" t="s">
         <v>420</v>
@@ -14547,21 +14555,21 @@
         <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G19" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="B20" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C20" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="D20" t="s">
         <v>420</v>
@@ -14570,10 +14578,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G20" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -14581,68 +14589,68 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C21" t="s">
         <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G21" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>840</v>
+        <v>825</v>
       </c>
       <c r="B22" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C22" t="s">
         <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E22">
         <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G22" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>841</v>
+        <v>826</v>
       </c>
       <c r="B23" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C23" t="s">
         <v>407</v>
       </c>
       <c r="D23" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G23" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -14650,10 +14658,10 @@
         <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C24" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="D24" t="s">
         <v>407</v>
@@ -14662,10 +14670,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G24" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -14673,22 +14681,22 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
+        <v>812</v>
+      </c>
+      <c r="C25" t="s">
         <v>827</v>
       </c>
-      <c r="C25" t="s">
-        <v>842</v>
-      </c>
       <c r="D25" t="s">
-        <v>838</v>
+        <v>823</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G25" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -14696,22 +14704,22 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
+        <v>812</v>
+      </c>
+      <c r="C26" t="s">
+        <v>823</v>
+      </c>
+      <c r="D26" t="s">
         <v>827</v>
-      </c>
-      <c r="C26" t="s">
-        <v>838</v>
-      </c>
-      <c r="D26" t="s">
-        <v>842</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G26" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -14719,7 +14727,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -14731,10 +14739,10 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G27" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -14742,7 +14750,7 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -14754,18 +14762,18 @@
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G28" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>843</v>
+        <v>828</v>
       </c>
       <c r="B29" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C29" t="s">
         <v>421</v>
@@ -14777,10 +14785,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G29" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -14788,7 +14796,7 @@
         <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -14800,10 +14808,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G30" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -14811,7 +14819,7 @@
         <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C31" t="s">
         <v>420</v>
@@ -14823,10 +14831,10 @@
         <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G31" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -14834,7 +14842,7 @@
         <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>831</v>
+        <v>816</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -14846,10 +14854,10 @@
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G32" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -14857,7 +14865,7 @@
         <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C33" t="s">
         <v>422</v>
@@ -14869,10 +14877,10 @@
         <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G33" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -14880,7 +14888,7 @@
         <v>332</v>
       </c>
       <c r="B34" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C34" t="s">
         <v>422</v>
@@ -14892,18 +14900,18 @@
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G34" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>844</v>
+        <v>829</v>
       </c>
       <c r="B35" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -14915,10 +14923,10 @@
         <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G35" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -14926,7 +14934,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -14938,18 +14946,18 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G36" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>847</v>
+        <v>832</v>
       </c>
       <c r="B37" t="s">
-        <v>827</v>
+        <v>812</v>
       </c>
       <c r="C37" t="s">
         <v>421</v>
@@ -14961,33 +14969,33 @@
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G37" t="s">
-        <v>828</v>
+        <v>813</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>848</v>
+        <v>833</v>
       </c>
       <c r="B38" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C38" t="s">
         <v>409</v>
       </c>
       <c r="D38" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G38" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -14995,30 +15003,30 @@
         <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C39" t="s">
         <v>407</v>
       </c>
       <c r="D39" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="F39">
         <v>1</v>
       </c>
       <c r="G39" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>849</v>
+        <v>834</v>
       </c>
       <c r="B40" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C40" t="s">
-        <v>842</v>
+        <v>827</v>
       </c>
       <c r="D40" t="s">
         <v>407</v>
@@ -15027,7 +15035,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -15035,7 +15043,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -15047,7 +15055,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -15055,7 +15063,7 @@
         <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -15067,15 +15075,15 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>850</v>
+        <v>835</v>
       </c>
       <c r="B43" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -15087,18 +15095,18 @@
         <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G43" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="B44" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C44" t="s">
         <v>422</v>
@@ -15113,7 +15121,7 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -15121,7 +15129,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C45" t="s">
         <v>422</v>
@@ -15136,7 +15144,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>846</v>
+        <v>831</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -15144,7 +15152,7 @@
         <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -15156,10 +15164,10 @@
         <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G46" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -15167,7 +15175,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -15179,10 +15187,10 @@
         <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G47" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -15190,7 +15198,7 @@
         <v>247</v>
       </c>
       <c r="B48" t="s">
-        <v>820</v>
+        <v>805</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -15202,24 +15210,24 @@
         <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>821</v>
+        <v>806</v>
       </c>
       <c r="G48" t="s">
-        <v>822</v>
+        <v>807</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>976</v>
+        <v>960</v>
       </c>
       <c r="B49" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>874</v>
+        <v>859</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -15228,15 +15236,15 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>978</v>
+        <v>962</v>
       </c>
       <c r="B50" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C50" t="s">
         <v>407</v>
@@ -15251,15 +15259,15 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>826</v>
+        <v>811</v>
       </c>
       <c r="B51" t="s">
-        <v>845</v>
+        <v>830</v>
       </c>
       <c r="C51" t="s">
         <v>411</v>
@@ -15274,7 +15282,7 @@
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>977</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC06AB8-96F4-462B-ACFD-218D285D6934}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977BF75B-3A92-44A9-AEF0-0CE8C369F7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1020">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -1910,9 +1910,6 @@
     <t>CT Pau Torres</t>
   </si>
   <si>
-    <t>CT Manuel Akanji</t>
-  </si>
-  <si>
     <t>CT Malick Thiaw</t>
   </si>
   <si>
@@ -2141,9 +2138,6 @@
     <t>ID Mason Greenwood</t>
   </si>
   <si>
-    <t>MP Tijjani Reijnders</t>
-  </si>
-  <si>
     <t>ID Takefusa Kubo</t>
   </si>
   <si>
@@ -2180,9 +2174,6 @@
     <t>ID Phil Foden</t>
   </si>
   <si>
-    <t>ID Ritsu Doan</t>
-  </si>
-  <si>
     <t>ED Riyad Mahrez</t>
   </si>
   <si>
@@ -2261,9 +2252,6 @@
     <t>DC Karim Benzema</t>
   </si>
   <si>
-    <t>DC Christian Pulišić</t>
-  </si>
-  <si>
     <t>EI Cody Gakpo</t>
   </si>
   <si>
@@ -3156,6 +3144,21 @@
   </si>
   <si>
     <t>EI Jadon Sancho</t>
+  </si>
+  <si>
+    <t>MP Xavi Simons</t>
+  </si>
+  <si>
+    <t>PT Joan García</t>
+  </si>
+  <si>
+    <t>CT Marc Guéhi</t>
+  </si>
+  <si>
+    <t>ID Ritsu Dōan</t>
+  </si>
+  <si>
+    <t>DC Christian Pulisic</t>
   </si>
 </sst>
 </file>
@@ -3656,7 +3659,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -3866,7 +3869,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>141</v>
@@ -3962,7 +3965,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>172</v>
@@ -3976,7 +3979,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>125</v>
@@ -4046,7 +4049,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>299</v>
@@ -4130,7 +4133,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>379</v>
@@ -4366,7 +4369,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>157</v>
@@ -4422,7 +4425,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>363</v>
@@ -4484,10 +4487,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C64" s="3">
         <v>4</v>
@@ -4750,7 +4753,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>347</v>
@@ -4767,7 +4770,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4850,7 +4853,7 @@
       </c>
       <c r="D90" s="3"/>
       <c r="E90" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -4879,7 +4882,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>45</v>
@@ -5037,7 +5040,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>315</v>
@@ -5049,7 +5052,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>45</v>
@@ -5385,7 +5388,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>236</v>
@@ -5421,7 +5424,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>109</v>
@@ -5553,7 +5556,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>77</v>
@@ -5661,7 +5664,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>93</v>
@@ -5721,7 +5724,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>331</v>
@@ -5745,10 +5748,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5759,10 +5762,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3">
@@ -6005,10 +6008,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C186" s="3">
         <v>2</v>
@@ -6043,10 +6046,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6515,21 +6518,21 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="C1" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -6537,10 +6540,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B3" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6548,10 +6551,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B4" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6559,10 +6562,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B5" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6570,10 +6573,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B6" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -6581,10 +6584,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B7" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6592,10 +6595,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B8" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6603,10 +6606,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B9" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -6614,10 +6617,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B10" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -6625,10 +6628,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B11" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -6636,10 +6639,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B12" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6647,10 +6650,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B13" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -6658,10 +6661,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="B14" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -7074,7 +7077,7 @@
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -7170,7 +7173,7 @@
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>172</v>
@@ -7185,7 +7188,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -7196,10 +7199,10 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -7220,10 +7223,10 @@
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -7316,7 +7319,7 @@
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>141</v>
@@ -7344,7 +7347,7 @@
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>157</v>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>379</v>
@@ -7382,10 +7385,10 @@
     </row>
     <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
@@ -7626,10 +7629,10 @@
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -7640,10 +7643,10 @@
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -7742,7 +7745,7 @@
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>125</v>
@@ -7756,7 +7759,7 @@
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>347</v>
@@ -7804,10 +7807,10 @@
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -7904,10 +7907,10 @@
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -7964,7 +7967,7 @@
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>315</v>
@@ -7988,10 +7991,10 @@
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -8036,7 +8039,7 @@
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
@@ -8084,7 +8087,7 @@
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>109</v>
@@ -8096,7 +8099,7 @@
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>363</v>
@@ -8108,10 +8111,10 @@
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>860</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>864</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -8132,10 +8135,10 @@
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3">
@@ -10863,7 +10866,7 @@
     <col min="11" max="11" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -10876,7 +10879,7 @@
         <v>411</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>419</v>
@@ -10911,7 +10914,7 @@
       <c r="M1" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="8" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="8" t="s">
@@ -10924,7 +10927,7 @@
         <v>425</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10932,10 +10935,10 @@
         <v>426</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>427</v>
@@ -10967,20 +10970,20 @@
       <c r="M2" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="N2" s="8" t="s">
         <v>437</v>
       </c>
       <c r="O2" s="8" t="s">
         <v>438</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>439</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -10991,7 +10994,7 @@
         <v>495</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>441</v>
@@ -11023,7 +11026,7 @@
       <c r="M3" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" s="8" t="s">
         <v>450</v>
       </c>
       <c r="O3" s="8" t="s">
@@ -11036,7 +11039,7 @@
         <v>453</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -11044,10 +11047,10 @@
         <v>454</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>455</v>
@@ -11079,7 +11082,7 @@
       <c r="M4" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="N4" s="8" t="s">
         <v>464</v>
       </c>
       <c r="O4" s="8" t="s">
@@ -11092,7 +11095,7 @@
         <v>467</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -11100,10 +11103,10 @@
         <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>470</v>
@@ -11115,7 +11118,7 @@
         <v>472</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>474</v>
@@ -11135,7 +11138,7 @@
       <c r="M5" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="8" t="s">
         <v>480</v>
       </c>
       <c r="O5" s="8" t="s">
@@ -11148,7 +11151,7 @@
         <v>483</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -11156,10 +11159,10 @@
         <v>484</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>485</v>
@@ -11171,7 +11174,7 @@
         <v>487</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>488</v>
@@ -11191,11 +11194,11 @@
       <c r="M6" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="N6" s="3" t="s">
+      <c r="N6" s="8" t="s">
         <v>494</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>496</v>
@@ -11204,7 +11207,7 @@
         <v>497</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -11212,10 +11215,10 @@
         <v>498</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>500</v>
@@ -11247,7 +11250,7 @@
       <c r="M7" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="N7" s="8" t="s">
         <v>510</v>
       </c>
       <c r="O7" s="8" t="s">
@@ -11260,7 +11263,7 @@
         <v>513</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -11268,10 +11271,10 @@
         <v>514</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>515</v>
@@ -11283,7 +11286,7 @@
         <v>517</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>518</v>
@@ -11298,16 +11301,16 @@
         <v>521</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="N8" s="8" t="s">
         <v>523</v>
       </c>
       <c r="O8" s="8" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P8" s="8" t="s">
         <v>525</v>
@@ -11316,7 +11319,7 @@
         <v>526</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -11324,10 +11327,10 @@
         <v>527</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>529</v>
@@ -11339,7 +11342,7 @@
         <v>531</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>533</v>
@@ -11354,13 +11357,13 @@
         <v>536</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>538</v>
+      <c r="N9" s="8" t="s">
+        <v>1015</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>539</v>
@@ -11372,7 +11375,7 @@
         <v>541</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -11380,10 +11383,10 @@
         <v>542</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>544</v>
@@ -11410,12 +11413,12 @@
         <v>551</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="N10" s="3" t="s">
+      <c r="N10" s="8" t="s">
         <v>553</v>
       </c>
       <c r="O10" s="8" t="s">
@@ -11428,7 +11431,7 @@
         <v>543</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -11436,13 +11439,13 @@
         <v>556</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>557</v>
@@ -11451,7 +11454,7 @@
         <v>558</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>559</v>
@@ -11466,12 +11469,12 @@
         <v>562</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="N11" s="3" t="s">
+      <c r="N11" s="8" t="s">
         <v>564</v>
       </c>
       <c r="O11" s="8" t="s">
@@ -11484,18 +11487,18 @@
         <v>567</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>580</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>568</v>
@@ -11516,7 +11519,7 @@
         <v>572</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>573</v>
@@ -11527,7 +11530,7 @@
       <c r="M12" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="N12" s="3" t="s">
+      <c r="N12" s="8" t="s">
         <v>576</v>
       </c>
       <c r="O12" s="8" t="s">
@@ -11540,18 +11543,18 @@
         <v>579</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>581</v>
@@ -11563,7 +11566,7 @@
         <v>583</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>585</v>
@@ -11572,7 +11575,7 @@
         <v>586</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>587</v>
@@ -11583,8 +11586,8 @@
       <c r="M13" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>589</v>
+      <c r="N13" s="8" t="s">
+        <v>1016</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>590</v>
@@ -11596,18 +11599,18 @@
         <v>592</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>593</v>
@@ -11619,7 +11622,7 @@
         <v>595</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>597</v>
@@ -11639,580 +11642,580 @@
       <c r="M14" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="N14" s="8" t="s">
+        <v>1017</v>
+      </c>
+      <c r="O14" s="8" t="s">
+        <v>986</v>
+      </c>
+      <c r="P14" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="O14" s="8" t="s">
-        <v>990</v>
-      </c>
-      <c r="P14" s="8" t="s">
+      <c r="Q14" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>605</v>
-      </c>
       <c r="R14" s="3" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>469</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="E15" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="F15" s="8" t="s">
         <v>606</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>607</v>
-      </c>
       <c r="G15" s="8" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="H15" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="J15" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="K15" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="L15" s="8" t="s">
+      <c r="M15" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="N15" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="N15" s="3" t="s">
+      <c r="O15" s="8" t="s">
+        <v>628</v>
+      </c>
+      <c r="P15" s="8" t="s">
         <v>615</v>
       </c>
-      <c r="O15" s="8" t="s">
-        <v>629</v>
-      </c>
-      <c r="P15" s="8" t="s">
+      <c r="Q15" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>617</v>
-      </c>
       <c r="R15" s="3" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>619</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>620</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>621</v>
-      </c>
       <c r="G16" s="8" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="H16" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="I16" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="I16" s="8" t="s">
+      <c r="J16" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="J16" s="8" t="s">
+      <c r="K16" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="M16" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="L16" s="8" t="s">
-        <v>968</v>
-      </c>
-      <c r="M16" s="3" t="s">
+      <c r="N16" s="8" t="s">
         <v>627</v>
       </c>
-      <c r="N16" s="3" t="s">
-        <v>628</v>
-      </c>
       <c r="O16" s="8" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>632</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>633</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="F17" s="8" t="s">
         <v>634</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="G17" s="8" t="s">
+        <v>710</v>
+      </c>
+      <c r="H17" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="G17" s="8" t="s">
-        <v>713</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="I17" s="8" t="s">
         <v>636</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="J17" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="J17" s="8" t="s">
+      <c r="K17" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="L17" s="8" t="s">
-        <v>654</v>
-      </c>
-      <c r="M17" s="3" t="s">
+      <c r="N17" s="8" t="s">
         <v>640</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>641</v>
-      </c>
       <c r="O17" s="8" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="P17" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="Q17" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>644</v>
-      </c>
       <c r="R17" s="3" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="D18" s="8" t="s">
+        <v>646</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="F18" s="8" t="s">
         <v>648</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>649</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>532</v>
       </c>
       <c r="H18" s="8" t="s">
+        <v>649</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>650</v>
       </c>
-      <c r="I18" s="8" t="s">
+      <c r="J18" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="J18" s="8" t="s">
+      <c r="K18" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>653</v>
-      </c>
       <c r="L18" s="8" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="M18" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="N18" s="8" t="s">
         <v>655</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>656</v>
       </c>
       <c r="O18" s="8" t="s">
         <v>524</v>
       </c>
       <c r="P18" s="8" t="s">
+        <v>657</v>
+      </c>
+      <c r="Q18" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>659</v>
-      </c>
       <c r="R18" s="3" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D19" s="8" t="s">
+        <v>659</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>660</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="F19" s="8" t="s">
         <v>661</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="G19" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="G19" s="8" t="s">
-        <v>986</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="8" t="s">
         <v>663</v>
       </c>
-      <c r="I19" s="8" t="s">
+      <c r="J19" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="8" t="s">
+        <v>966</v>
+      </c>
+      <c r="M19" s="3" t="s">
         <v>666</v>
       </c>
-      <c r="L19" s="8" t="s">
-        <v>970</v>
-      </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="N19" s="3" t="s">
+      <c r="O19" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="O19" s="8" t="s">
+      <c r="P19" s="8" t="s">
+        <v>974</v>
+      </c>
+      <c r="Q19" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="P19" s="8" t="s">
-        <v>978</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>670</v>
-      </c>
       <c r="R19" s="3" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>499</v>
       </c>
       <c r="D20" s="8" t="s">
+        <v>670</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>673</v>
-      </c>
       <c r="G20" s="8" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="H20" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="I20" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="I20" s="8" t="s">
+      <c r="J20" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="J20" s="8" t="s">
+      <c r="K20" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="M20" s="3" t="s">
         <v>678</v>
       </c>
-      <c r="L20" s="8" t="s">
-        <v>971</v>
-      </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="O20" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="P20" s="9" t="s">
         <v>679</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="Q20" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="O20" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="P20" s="9" t="s">
-        <v>681</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>682</v>
-      </c>
       <c r="R20" s="3" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="E21" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="B21" s="8" t="s">
-        <v>959</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>646</v>
-      </c>
-      <c r="D21" s="8" t="s">
+      <c r="F21" s="8" t="s">
         <v>684</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>685</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>686</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>547</v>
       </c>
       <c r="H21" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>686</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="K21" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="J21" s="8" t="s">
+      <c r="L21" s="8" t="s">
         <v>689</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="L21" s="8" t="s">
-        <v>691</v>
-      </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="O21" s="8" t="s">
+        <v>987</v>
+      </c>
+      <c r="P21" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="N21" s="3" t="s">
+      <c r="Q21" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="O21" s="8" t="s">
-        <v>991</v>
-      </c>
-      <c r="P21" s="8" t="s">
-        <v>695</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>696</v>
-      </c>
       <c r="R21" s="3" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="D22" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>695</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>673</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="I22" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="J22" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>988</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="H22" s="8" t="s">
+      <c r="K22" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="I22" s="8" t="s">
+      <c r="L22" s="8" t="s">
+        <v>968</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="J22" s="8" t="s">
+      <c r="N22" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>702</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>972</v>
-      </c>
-      <c r="M22" s="3" t="s">
+      <c r="O22" s="8" t="s">
+        <v>691</v>
+      </c>
+      <c r="P22" s="8" t="s">
         <v>703</v>
       </c>
-      <c r="N22" s="3" t="s">
+      <c r="Q22" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="O22" s="8" t="s">
-        <v>694</v>
-      </c>
-      <c r="P22" s="8" t="s">
-        <v>706</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>707</v>
-      </c>
       <c r="R22" s="3" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>705</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>853</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>708</v>
       </c>
-      <c r="B23" s="8" t="s">
-        <v>857</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="F23" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>724</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>711</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="I23" s="8" t="s">
         <v>712</v>
       </c>
-      <c r="G23" s="8" t="s">
-        <v>728</v>
-      </c>
-      <c r="H23" s="8" t="s">
+      <c r="J23" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="I23" s="8" t="s">
+      <c r="L23" s="8" t="s">
         <v>715</v>
       </c>
-      <c r="J23" s="8" t="s">
+      <c r="M23" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="N23" s="8" t="s">
+        <v>1019</v>
+      </c>
+      <c r="O23" s="8" t="s">
         <v>717</v>
       </c>
-      <c r="L23" s="8" t="s">
+      <c r="P23" s="8" t="s">
         <v>718</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="Q23" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>720</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>721</v>
-      </c>
-      <c r="P23" s="8" t="s">
-        <v>722</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>723</v>
-      </c>
       <c r="R23" s="3" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>528</v>
       </c>
       <c r="H24" s="8" t="s">
+        <v>725</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>728</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>729</v>
       </c>
-      <c r="I24" s="8" t="s">
+      <c r="M24" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="J24" s="8" t="s">
+      <c r="N24" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="L24" s="8" t="s">
+      <c r="O24" s="8" t="s">
+        <v>988</v>
+      </c>
+      <c r="P24" s="8" t="s">
         <v>733</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="Q24" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>992</v>
-      </c>
-      <c r="P24" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>738</v>
-      </c>
       <c r="R24" s="3" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
     </row>
   </sheetData>
@@ -12250,7 +12253,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -12289,7 +12292,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -12298,7 +12301,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -12306,7 +12309,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -12354,7 +12357,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -12362,7 +12365,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -12410,7 +12413,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -12418,7 +12421,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -12466,7 +12469,7 @@
         <v>63</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -12474,7 +12477,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -12522,7 +12525,7 @@
         <v>79</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -12530,7 +12533,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -12578,7 +12581,7 @@
         <v>95</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -12586,7 +12589,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -12634,7 +12637,7 @@
         <v>111</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -12642,7 +12645,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -12690,7 +12693,7 @@
         <v>127</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -12698,7 +12701,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -12746,7 +12749,7 @@
         <v>143</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -12754,10 +12757,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -12802,7 +12805,7 @@
         <v>145</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -12810,7 +12813,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -12858,7 +12861,7 @@
         <v>174</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -12866,7 +12869,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -12914,7 +12917,7 @@
         <v>190</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -12922,7 +12925,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -12970,7 +12973,7 @@
         <v>206</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -12978,7 +12981,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -13026,7 +13029,7 @@
         <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -13034,7 +13037,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -13082,7 +13085,7 @@
         <v>238</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -13090,7 +13093,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -13138,7 +13141,7 @@
         <v>254</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -13146,7 +13149,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -13194,7 +13197,7 @@
         <v>270</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -13202,7 +13205,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -13250,7 +13253,7 @@
         <v>286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -13258,10 +13261,10 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -13306,7 +13309,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -13314,7 +13317,7 @@
         <v>302</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>303</v>
@@ -13362,7 +13365,7 @@
         <v>317</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -13370,7 +13373,7 @@
         <v>318</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>319</v>
@@ -13418,7 +13421,7 @@
         <v>333</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -13426,7 +13429,7 @@
         <v>334</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>335</v>
@@ -13474,7 +13477,7 @@
         <v>349</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -13530,7 +13533,7 @@
         <v>365</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -13538,7 +13541,7 @@
         <v>366</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>367</v>
@@ -13586,7 +13589,7 @@
         <v>381</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
     </row>
   </sheetData>
@@ -13613,25 +13616,25 @@
         <v>382</v>
       </c>
       <c r="B1" t="s">
+        <v>735</v>
+      </c>
+      <c r="C1" t="s">
+        <v>736</v>
+      </c>
+      <c r="D1" t="s">
+        <v>737</v>
+      </c>
+      <c r="E1" t="s">
+        <v>738</v>
+      </c>
+      <c r="F1" t="s">
         <v>739</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>740</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>741</v>
-      </c>
-      <c r="E1" t="s">
-        <v>742</v>
-      </c>
-      <c r="F1" t="s">
-        <v>743</v>
-      </c>
-      <c r="G1" t="s">
-        <v>744</v>
-      </c>
-      <c r="H1" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -13639,13 +13642,13 @@
         <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="E2">
         <v>100000000</v>
@@ -13654,7 +13657,7 @@
         <v>2575000000</v>
       </c>
       <c r="G2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -13665,13 +13668,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C3" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="D3" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13680,7 +13683,7 @@
         <v>211000000</v>
       </c>
       <c r="G3" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="H3">
         <v>2</v>
@@ -13694,10 +13697,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="D4" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="E4">
         <v>100000000</v>
@@ -13706,7 +13709,7 @@
         <v>8100000000</v>
       </c>
       <c r="G4" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="H4">
         <v>3</v>
@@ -13717,13 +13720,13 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C5" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="D5" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E5">
         <v>100000000</v>
@@ -13732,7 +13735,7 @@
         <v>2569000000</v>
       </c>
       <c r="G5" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="H5">
         <v>4</v>
@@ -13743,13 +13746,13 @@
         <v>420</v>
       </c>
       <c r="B6" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C6" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D6" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="E6">
         <v>100000000</v>
@@ -13758,7 +13761,7 @@
         <v>759000000</v>
       </c>
       <c r="G6" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -13769,13 +13772,13 @@
         <v>421</v>
       </c>
       <c r="B7" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C7" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="D7" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="E7">
         <v>100000000</v>
@@ -13784,7 +13787,7 @@
         <v>280000000</v>
       </c>
       <c r="G7" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="H7">
         <v>6</v>
@@ -13795,13 +13798,13 @@
         <v>407</v>
       </c>
       <c r="B8" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C8" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="D8" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="E8">
         <v>100000000</v>
@@ -13810,7 +13813,7 @@
         <v>2154000000</v>
       </c>
       <c r="G8" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="H8">
         <v>7</v>
@@ -13821,13 +13824,13 @@
         <v>422</v>
       </c>
       <c r="B9" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C9" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="D9" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E9">
         <v>100000000</v>
@@ -13836,7 +13839,7 @@
         <v>223000000</v>
       </c>
       <c r="G9" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="H9">
         <v>8</v>
@@ -13847,13 +13850,13 @@
         <v>423</v>
       </c>
       <c r="B10" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C10" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="D10" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="E10">
         <v>100000000</v>
@@ -13862,7 +13865,7 @@
         <v>11000000</v>
       </c>
       <c r="G10" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="H10">
         <v>9</v>
@@ -13873,13 +13876,13 @@
         <v>4</v>
       </c>
       <c r="B11" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C11" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D11" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="E11">
         <v>100000000</v>
@@ -13888,7 +13891,7 @@
         <v>119000000</v>
       </c>
       <c r="G11" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -13899,13 +13902,13 @@
         <v>411</v>
       </c>
       <c r="B12" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C12" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D12" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E12">
         <v>100000000</v>
@@ -13914,7 +13917,7 @@
         <v>2121000000</v>
       </c>
       <c r="G12" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="H12">
         <v>11</v>
@@ -13925,13 +13928,13 @@
         <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="C13" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="D13" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E13">
         <v>100000000</v>
@@ -13940,7 +13943,7 @@
         <v>300000000</v>
       </c>
       <c r="G13" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="H13">
         <v>12</v>
@@ -13951,13 +13954,13 @@
         <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C14" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="D14" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="E14">
         <v>100000000</v>
@@ -13966,7 +13969,7 @@
         <v>300000000</v>
       </c>
       <c r="G14" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="H14">
         <v>13</v>
@@ -13977,13 +13980,13 @@
         <v>419</v>
       </c>
       <c r="B15" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C15" t="s">
+        <v>883</v>
+      </c>
+      <c r="D15" t="s">
         <v>887</v>
-      </c>
-      <c r="D15" t="s">
-        <v>891</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -13992,7 +13995,7 @@
         <v>357000000</v>
       </c>
       <c r="G15" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="H15">
         <v>14</v>
@@ -14000,16 +14003,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="B16" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C16" t="s">
+        <v>884</v>
+      </c>
+      <c r="D16" t="s">
         <v>888</v>
-      </c>
-      <c r="D16" t="s">
-        <v>892</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -14018,7 +14021,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -14029,13 +14032,13 @@
         <v>403</v>
       </c>
       <c r="B17" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="C17" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="D17" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="E17">
         <v>100000000</v>
@@ -14044,7 +14047,7 @@
         <v>440000000</v>
       </c>
       <c r="G17" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="H17">
         <v>16</v>
@@ -14055,13 +14058,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C18" t="s">
+        <v>885</v>
+      </c>
+      <c r="D18" t="s">
         <v>889</v>
-      </c>
-      <c r="D18" t="s">
-        <v>893</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14070,7 +14073,7 @@
         <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14078,16 +14081,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="B19" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C19" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D19" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -14096,7 +14099,7 @@
         <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
     </row>
   </sheetData>
@@ -14129,30 +14132,30 @@
         <v>383</v>
       </c>
       <c r="B1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C1" t="s">
+        <v>795</v>
+      </c>
+      <c r="D1" t="s">
+        <v>796</v>
+      </c>
+      <c r="E1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F1" t="s">
         <v>798</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>799</v>
-      </c>
-      <c r="D1" t="s">
-        <v>800</v>
-      </c>
-      <c r="E1" t="s">
-        <v>801</v>
-      </c>
-      <c r="F1" t="s">
-        <v>802</v>
-      </c>
-      <c r="G1" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="B2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C2" t="s">
         <v>411</v>
@@ -14164,10 +14167,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -14175,7 +14178,7 @@
         <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C3" t="s">
         <v>411</v>
@@ -14187,10 +14190,10 @@
         <v>50</v>
       </c>
       <c r="F3" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G3" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -14198,7 +14201,7 @@
         <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C4" t="s">
         <v>411</v>
@@ -14210,10 +14213,10 @@
         <v>120</v>
       </c>
       <c r="F4" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G4" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -14221,30 +14224,30 @@
         <v>394</v>
       </c>
       <c r="B5" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C5" t="s">
         <v>411</v>
       </c>
       <c r="D5" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E5">
         <v>65</v>
       </c>
       <c r="F5" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G5" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="B6" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C6" t="s">
         <v>411</v>
@@ -14256,18 +14259,18 @@
         <v>90</v>
       </c>
       <c r="F6" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G6" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="B7" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C7" t="s">
         <v>411</v>
@@ -14279,18 +14282,18 @@
         <v>170</v>
       </c>
       <c r="F7" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G7" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B8" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C8" t="s">
         <v>420</v>
@@ -14302,18 +14305,18 @@
         <v>0</v>
       </c>
       <c r="F8" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G8" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="B9" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C9" t="s">
         <v>411</v>
@@ -14325,33 +14328,33 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G9" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="B10" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C10" t="s">
         <v>422</v>
       </c>
       <c r="D10" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E10">
         <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G10" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -14359,33 +14362,33 @@
         <v>394</v>
       </c>
       <c r="B11" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C11" t="s">
         <v>411</v>
       </c>
       <c r="D11" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E11">
         <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G11" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="B12" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C12" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D12" t="s">
         <v>13</v>
@@ -14394,10 +14397,10 @@
         <v>100</v>
       </c>
       <c r="F12" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G12" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -14405,10 +14408,10 @@
         <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C13" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D13" t="s">
         <v>406</v>
@@ -14417,21 +14420,21 @@
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G13" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="B14" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C14" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="D14" t="s">
         <v>409</v>
@@ -14440,41 +14443,41 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G14" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="B15" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C15" t="s">
         <v>409</v>
       </c>
       <c r="D15" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G15" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="B16" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
@@ -14486,18 +14489,18 @@
         <v>75</v>
       </c>
       <c r="F16" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G16" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="B17" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -14509,18 +14512,18 @@
         <v>60</v>
       </c>
       <c r="F17" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G17" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="B18" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C18" t="s">
         <v>406</v>
@@ -14532,10 +14535,10 @@
         <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G18" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -14543,10 +14546,10 @@
         <v>241</v>
       </c>
       <c r="B19" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C19" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="D19" t="s">
         <v>420</v>
@@ -14555,21 +14558,21 @@
         <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G19" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="B20" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C20" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="D20" t="s">
         <v>420</v>
@@ -14578,10 +14581,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G20" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -14589,68 +14592,68 @@
         <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C21" t="s">
         <v>420</v>
       </c>
       <c r="D21" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E21">
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G21" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B22" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C22" t="s">
         <v>422</v>
       </c>
       <c r="D22" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E22">
         <v>136</v>
       </c>
       <c r="F22" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G22" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="B23" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C23" t="s">
         <v>407</v>
       </c>
       <c r="D23" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G23" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -14658,10 +14661,10 @@
         <v>233</v>
       </c>
       <c r="B24" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C24" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="D24" t="s">
         <v>407</v>
@@ -14670,10 +14673,10 @@
         <v>0</v>
       </c>
       <c r="F24" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G24" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -14681,22 +14684,22 @@
         <v>115</v>
       </c>
       <c r="B25" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C25" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D25" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G25" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -14704,22 +14707,22 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C26" t="s">
+        <v>819</v>
+      </c>
+      <c r="D26" t="s">
         <v>823</v>
-      </c>
-      <c r="D26" t="s">
-        <v>827</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
       <c r="F26" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G26" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -14727,7 +14730,7 @@
         <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -14739,10 +14742,10 @@
         <v>50</v>
       </c>
       <c r="F27" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G27" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -14750,7 +14753,7 @@
         <v>199</v>
       </c>
       <c r="B28" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -14762,18 +14765,18 @@
         <v>25</v>
       </c>
       <c r="F28" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G28" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B29" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C29" t="s">
         <v>421</v>
@@ -14785,10 +14788,10 @@
         <v>0</v>
       </c>
       <c r="F29" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G29" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -14796,7 +14799,7 @@
         <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C30" t="s">
         <v>4</v>
@@ -14808,10 +14811,10 @@
         <v>0</v>
       </c>
       <c r="F30" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G30" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -14819,7 +14822,7 @@
         <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C31" t="s">
         <v>420</v>
@@ -14831,10 +14834,10 @@
         <v>80</v>
       </c>
       <c r="F31" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G31" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -14842,7 +14845,7 @@
         <v>134</v>
       </c>
       <c r="B32" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -14854,10 +14857,10 @@
         <v>20</v>
       </c>
       <c r="F32" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G32" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -14865,7 +14868,7 @@
         <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C33" t="s">
         <v>422</v>
@@ -14877,10 +14880,10 @@
         <v>20</v>
       </c>
       <c r="F33" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G33" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -14888,7 +14891,7 @@
         <v>332</v>
       </c>
       <c r="B34" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C34" t="s">
         <v>422</v>
@@ -14900,18 +14903,18 @@
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G34" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="B35" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
@@ -14923,10 +14926,10 @@
         <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G35" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -14934,7 +14937,7 @@
         <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
@@ -14946,18 +14949,18 @@
         <v>20</v>
       </c>
       <c r="F36" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G36" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="B37" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C37" t="s">
         <v>421</v>
@@ -14969,33 +14972,33 @@
         <v>20</v>
       </c>
       <c r="F37" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G37" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="B38" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C38" t="s">
         <v>409</v>
       </c>
       <c r="D38" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="E38">
         <v>5</v>
       </c>
       <c r="F38" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G38" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -15003,30 +15006,30 @@
         <v>329</v>
       </c>
       <c r="B39" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C39" t="s">
         <v>407</v>
       </c>
       <c r="D39" t="s">
+        <v>823</v>
+      </c>
+      <c r="F39">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
         <v>827</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="B40" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C40" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="D40" t="s">
         <v>407</v>
@@ -15035,7 +15038,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -15043,7 +15046,7 @@
         <v>156</v>
       </c>
       <c r="B41" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -15055,7 +15058,7 @@
         <v>1</v>
       </c>
       <c r="G41" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -15063,7 +15066,7 @@
         <v>172</v>
       </c>
       <c r="B42" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C42" t="s">
         <v>12</v>
@@ -15075,15 +15078,15 @@
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="B43" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -15095,18 +15098,18 @@
         <v>30</v>
       </c>
       <c r="F43" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G43" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="B44" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C44" t="s">
         <v>422</v>
@@ -15121,7 +15124,7 @@
         <v>2</v>
       </c>
       <c r="G44" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -15129,7 +15132,7 @@
         <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C45" t="s">
         <v>422</v>
@@ -15144,7 +15147,7 @@
         <v>2</v>
       </c>
       <c r="G45" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -15152,7 +15155,7 @@
         <v>120</v>
       </c>
       <c r="B46" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C46" t="s">
         <v>14</v>
@@ -15164,10 +15167,10 @@
         <v>42</v>
       </c>
       <c r="F46" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G46" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -15175,7 +15178,7 @@
         <v>40</v>
       </c>
       <c r="B47" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -15187,10 +15190,10 @@
         <v>31</v>
       </c>
       <c r="F47" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G47" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -15198,7 +15201,7 @@
         <v>247</v>
       </c>
       <c r="B48" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C48" t="s">
         <v>14</v>
@@ -15210,24 +15213,24 @@
         <v>31</v>
       </c>
       <c r="F48" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="G48" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B49" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -15236,15 +15239,15 @@
         <v>2</v>
       </c>
       <c r="G49" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B50" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C50" t="s">
         <v>407</v>
@@ -15259,15 +15262,15 @@
         <v>2</v>
       </c>
       <c r="G50" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="B51" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="C51" t="s">
         <v>411</v>
@@ -15282,7 +15285,7 @@
         <v>2</v>
       </c>
       <c r="G51" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
     </row>
   </sheetData>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977BF75B-3A92-44A9-AEF0-0CE8C369F7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506E0804-F1FC-4333-865B-F94E8291D793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Mercado!$A$1:$G$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Registro Champions'!$A$1:$D$112</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registro Liga'!$A$1:$D$246</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">RegistroEstelar!$A$1:$D$1</definedName>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="995">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -2501,102 +2501,24 @@
     <t>Detalle</t>
   </si>
   <si>
-    <t>Anatoli Trubin</t>
-  </si>
-  <si>
-    <t>Venta</t>
-  </si>
-  <si>
-    <t>Permanente</t>
-  </si>
-  <si>
-    <t>Traspaso normal</t>
-  </si>
-  <si>
-    <t>Manchester United</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raphinha </t>
-  </si>
-  <si>
-    <t>Dominik Szoboslai</t>
-  </si>
-  <si>
     <t>Ousmane Dembele</t>
   </si>
   <si>
-    <t>Intercambio</t>
-  </si>
-  <si>
-    <t>Intercambio de Jugadores</t>
-  </si>
-  <si>
-    <t>Kylian Mbappe</t>
-  </si>
-  <si>
-    <t>Giuliano Simeone</t>
-  </si>
-  <si>
-    <t>Compra</t>
-  </si>
-  <si>
-    <t>Benjamin Sesko</t>
-  </si>
-  <si>
-    <t>Pedro Neto</t>
-  </si>
-  <si>
-    <t>James Rodriguez</t>
-  </si>
-  <si>
-    <t>Joan Garcia</t>
-  </si>
-  <si>
-    <t>Pedro Porro</t>
-  </si>
-  <si>
-    <t>Dejan Kulusevski</t>
-  </si>
-  <si>
-    <t>Fc Barcelona</t>
-  </si>
-  <si>
-    <t>Jules Kounde</t>
-  </si>
-  <si>
-    <t>Joao Pedro</t>
-  </si>
-  <si>
-    <t>Joao Neves</t>
-  </si>
-  <si>
     <t>Ac Milan</t>
   </si>
   <si>
-    <t>Son Heung Min</t>
-  </si>
-  <si>
-    <t>Estevao</t>
-  </si>
-  <si>
     <t>Prestamo</t>
   </si>
   <si>
     <t>Prestamo de jugadores</t>
   </si>
   <si>
-    <t>Luka Modric</t>
-  </si>
-  <si>
     <t>Dani Carvajal</t>
   </si>
   <si>
     <t>Arda Guler</t>
   </si>
   <si>
-    <t>Oihan Sancet</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dean Huijsen </t>
   </si>
   <si>
@@ -3159,6 +3081,9 @@
   </si>
   <si>
     <t>DC Christian Pulisic</t>
+  </si>
+  <si>
+    <t>Brahim Diaz</t>
   </si>
 </sst>
 </file>
@@ -3659,7 +3584,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -3869,7 +3794,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>141</v>
@@ -3965,7 +3890,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>172</v>
@@ -3979,7 +3904,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>125</v>
@@ -4049,7 +3974,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>299</v>
@@ -4133,7 +4058,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>379</v>
@@ -4369,7 +4294,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>157</v>
@@ -4425,7 +4350,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>363</v>
@@ -4487,10 +4412,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>869</v>
+        <v>843</v>
       </c>
       <c r="C64" s="3">
         <v>4</v>
@@ -4753,7 +4678,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>347</v>
@@ -4770,7 +4695,7 @@
         <v>1</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>894</v>
+        <v>868</v>
       </c>
       <c r="C84" s="3">
         <v>2</v>
@@ -4853,7 +4778,7 @@
       </c>
       <c r="D90" s="3"/>
       <c r="E90" t="s">
-        <v>893</v>
+        <v>867</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.3">
@@ -4882,7 +4807,7 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>45</v>
@@ -5040,7 +4965,7 @@
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>315</v>
@@ -5052,7 +4977,7 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>45</v>
@@ -5388,7 +5313,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>236</v>
@@ -5424,7 +5349,7 @@
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>109</v>
@@ -5556,7 +5481,7 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>77</v>
@@ -5664,7 +5589,7 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>93</v>
@@ -5724,7 +5649,7 @@
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>331</v>
@@ -5748,10 +5673,10 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
       <c r="C165" s="3">
         <v>1</v>
@@ -5762,10 +5687,10 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="C166" s="3"/>
       <c r="D166" s="3">
@@ -6008,10 +5933,10 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>868</v>
+        <v>842</v>
       </c>
       <c r="C186" s="3">
         <v>2</v>
@@ -6046,10 +5971,10 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>871</v>
+        <v>845</v>
       </c>
       <c r="C189" s="3"/>
       <c r="D189" s="3">
@@ -6518,18 +6443,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>833</v>
+        <v>807</v>
       </c>
       <c r="B1" t="s">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="C1" t="s">
-        <v>835</v>
+        <v>809</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>836</v>
+        <v>810</v>
       </c>
       <c r="B2" t="s">
         <v>751</v>
@@ -6540,10 +6465,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>836</v>
+        <v>810</v>
       </c>
       <c r="B3" t="s">
-        <v>837</v>
+        <v>811</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -6551,10 +6476,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>836</v>
+        <v>810</v>
       </c>
       <c r="B4" t="s">
-        <v>838</v>
+        <v>812</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -6562,10 +6487,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>836</v>
+        <v>810</v>
       </c>
       <c r="B5" t="s">
-        <v>839</v>
+        <v>813</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -6573,7 +6498,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>836</v>
+        <v>810</v>
       </c>
       <c r="B6" t="s">
         <v>782</v>
@@ -6584,10 +6509,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="B7" t="s">
-        <v>841</v>
+        <v>815</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6595,10 +6520,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="B8" t="s">
-        <v>842</v>
+        <v>816</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6606,7 +6531,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="B9" t="s">
         <v>782</v>
@@ -6617,7 +6542,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="B10" t="s">
         <v>751</v>
@@ -6628,7 +6553,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>840</v>
+        <v>814</v>
       </c>
       <c r="B11" t="s">
         <v>761</v>
@@ -6639,10 +6564,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>843</v>
+        <v>817</v>
       </c>
       <c r="B12" t="s">
-        <v>839</v>
+        <v>813</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -6650,7 +6575,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>843</v>
+        <v>817</v>
       </c>
       <c r="B13" t="s">
         <v>782</v>
@@ -6661,7 +6586,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>843</v>
+        <v>817</v>
       </c>
       <c r="B14" t="s">
         <v>761</v>
@@ -7077,7 +7002,7 @@
     </row>
     <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>188</v>
@@ -7173,7 +7098,7 @@
     </row>
     <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>172</v>
@@ -7188,7 +7113,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>894</v>
+        <v>868</v>
       </c>
       <c r="C12" s="3">
         <v>3</v>
@@ -7199,10 +7124,10 @@
     </row>
     <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>868</v>
+        <v>842</v>
       </c>
       <c r="C13" s="3">
         <v>3</v>
@@ -7223,10 +7148,10 @@
     </row>
     <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>869</v>
+        <v>843</v>
       </c>
       <c r="C15" s="3">
         <v>3</v>
@@ -7319,7 +7244,7 @@
     </row>
     <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>141</v>
@@ -7347,7 +7272,7 @@
     </row>
     <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>157</v>
@@ -7361,7 +7286,7 @@
     </row>
     <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>379</v>
@@ -7385,10 +7310,10 @@
     </row>
     <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>864</v>
+        <v>838</v>
       </c>
       <c r="C27" s="3">
         <v>2</v>
@@ -7629,10 +7554,10 @@
     </row>
     <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>871</v>
+        <v>845</v>
       </c>
       <c r="C46" s="3">
         <v>1</v>
@@ -7643,10 +7568,10 @@
     </row>
     <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>865</v>
+        <v>839</v>
       </c>
       <c r="C47" s="3">
         <v>1</v>
@@ -7745,7 +7670,7 @@
     </row>
     <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>125</v>
@@ -7759,7 +7684,7 @@
     </row>
     <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>347</v>
@@ -7807,10 +7732,10 @@
     </row>
     <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
       <c r="C60" s="3">
         <v>1</v>
@@ -7907,10 +7832,10 @@
     </row>
     <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>862</v>
+        <v>836</v>
       </c>
       <c r="C68" s="3">
         <v>1</v>
@@ -7967,7 +7892,7 @@
     </row>
     <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>315</v>
@@ -7991,10 +7916,10 @@
     </row>
     <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>857</v>
+        <v>831</v>
       </c>
       <c r="C75" s="3"/>
       <c r="D75" s="3">
@@ -8039,7 +7964,7 @@
     </row>
     <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>331</v>
@@ -8087,7 +8012,7 @@
     </row>
     <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>109</v>
@@ -8099,7 +8024,7 @@
     </row>
     <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>363</v>
@@ -8111,10 +8036,10 @@
     </row>
     <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>860</v>
+        <v>834</v>
       </c>
       <c r="C85" s="3"/>
       <c r="D85" s="3">
@@ -8135,10 +8060,10 @@
     </row>
     <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>863</v>
+        <v>837</v>
       </c>
       <c r="C87" s="3"/>
       <c r="D87" s="3">
@@ -10879,7 +10804,7 @@
         <v>411</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>855</v>
+        <v>829</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>419</v>
@@ -10927,7 +10852,7 @@
         <v>425</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>919</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -10935,10 +10860,10 @@
         <v>426</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>947</v>
+        <v>921</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>996</v>
+        <v>970</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>427</v>
@@ -10977,13 +10902,13 @@
         <v>438</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>972</v>
+        <v>946</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>439</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>920</v>
+        <v>894</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -10994,7 +10919,7 @@
         <v>495</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>997</v>
+        <v>971</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>441</v>
@@ -11039,7 +10964,7 @@
         <v>453</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>921</v>
+        <v>895</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -11047,10 +10972,10 @@
         <v>454</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>847</v>
+        <v>821</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>998</v>
+        <v>972</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>455</v>
@@ -11095,7 +11020,7 @@
         <v>467</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>922</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -11103,10 +11028,10 @@
         <v>468</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>948</v>
+        <v>922</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>999</v>
+        <v>973</v>
       </c>
       <c r="D5" s="8" t="s">
         <v>470</v>
@@ -11118,7 +11043,7 @@
         <v>472</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>975</v>
+        <v>949</v>
       </c>
       <c r="H5" s="8" t="s">
         <v>474</v>
@@ -11151,7 +11076,7 @@
         <v>483</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>923</v>
+        <v>897</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -11159,10 +11084,10 @@
         <v>484</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>846</v>
+        <v>820</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>1000</v>
+        <v>974</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>485</v>
@@ -11174,7 +11099,7 @@
         <v>487</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>976</v>
+        <v>950</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>488</v>
@@ -11198,7 +11123,7 @@
         <v>494</v>
       </c>
       <c r="O6" s="8" t="s">
-        <v>985</v>
+        <v>959</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>496</v>
@@ -11207,7 +11132,7 @@
         <v>497</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>924</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -11215,10 +11140,10 @@
         <v>498</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>949</v>
+        <v>923</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1001</v>
+        <v>975</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>500</v>
@@ -11263,7 +11188,7 @@
         <v>513</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>925</v>
+        <v>899</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -11271,10 +11196,10 @@
         <v>514</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>950</v>
+        <v>924</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1002</v>
+        <v>976</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>515</v>
@@ -11301,7 +11226,7 @@
         <v>521</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>960</v>
+        <v>934</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>522</v>
@@ -11319,7 +11244,7 @@
         <v>526</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>926</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -11327,10 +11252,10 @@
         <v>527</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>848</v>
+        <v>822</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1003</v>
+        <v>977</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>529</v>
@@ -11357,13 +11282,13 @@
         <v>536</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>961</v>
+        <v>935</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>537</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>1015</v>
+        <v>989</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>539</v>
@@ -11375,7 +11300,7 @@
         <v>541</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>927</v>
+        <v>901</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -11383,10 +11308,10 @@
         <v>542</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>959</v>
+        <v>933</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1004</v>
+        <v>978</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>544</v>
@@ -11413,7 +11338,7 @@
         <v>551</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>962</v>
+        <v>936</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>552</v>
@@ -11431,7 +11356,7 @@
         <v>543</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>928</v>
+        <v>902</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -11442,10 +11367,10 @@
         <v>732</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1005</v>
+        <v>979</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>969</v>
+        <v>943</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>557</v>
@@ -11454,7 +11379,7 @@
         <v>558</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>977</v>
+        <v>951</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>559</v>
@@ -11469,7 +11394,7 @@
         <v>562</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>963</v>
+        <v>937</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>563</v>
@@ -11487,18 +11412,18 @@
         <v>567</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>929</v>
+        <v>903</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>989</v>
+        <v>963</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>580</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1006</v>
+        <v>980</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>568</v>
@@ -11543,18 +11468,18 @@
         <v>579</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>930</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="8" t="s">
-        <v>990</v>
+        <v>964</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>850</v>
+        <v>824</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1007</v>
+        <v>981</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>581</v>
@@ -11566,7 +11491,7 @@
         <v>583</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>978</v>
+        <v>952</v>
       </c>
       <c r="H13" s="8" t="s">
         <v>585</v>
@@ -11575,7 +11500,7 @@
         <v>586</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>845</v>
+        <v>819</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>587</v>
@@ -11587,7 +11512,7 @@
         <v>588</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>1016</v>
+        <v>990</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>590</v>
@@ -11599,18 +11524,18 @@
         <v>592</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>931</v>
+        <v>905</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="8" t="s">
-        <v>991</v>
+        <v>965</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>851</v>
+        <v>825</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1008</v>
+        <v>982</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>593</v>
@@ -11622,7 +11547,7 @@
         <v>595</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>979</v>
+        <v>953</v>
       </c>
       <c r="H14" s="8" t="s">
         <v>597</v>
@@ -11643,10 +11568,10 @@
         <v>602</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>1017</v>
+        <v>991</v>
       </c>
       <c r="O14" s="8" t="s">
-        <v>986</v>
+        <v>960</v>
       </c>
       <c r="P14" s="8" t="s">
         <v>603</v>
@@ -11655,21 +11580,21 @@
         <v>604</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>932</v>
+        <v>906</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>992</v>
+        <v>966</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>951</v>
+        <v>925</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>469</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>970</v>
+        <v>944</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>605</v>
@@ -11678,7 +11603,7 @@
         <v>606</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>980</v>
+        <v>954</v>
       </c>
       <c r="H15" s="8" t="s">
         <v>608</v>
@@ -11711,7 +11636,7 @@
         <v>616</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>933</v>
+        <v>907</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -11719,13 +11644,13 @@
         <v>617</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>852</v>
+        <v>826</v>
       </c>
       <c r="C16" s="8" t="s">
         <v>631</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>971</v>
+        <v>945</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>619</v>
@@ -11734,7 +11659,7 @@
         <v>620</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>981</v>
+        <v>955</v>
       </c>
       <c r="H16" s="8" t="s">
         <v>622</v>
@@ -11749,7 +11674,7 @@
         <v>625</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>964</v>
+        <v>938</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>626</v>
@@ -11761,13 +11686,13 @@
         <v>641</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>973</v>
+        <v>947</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>629</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>934</v>
+        <v>908</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -11775,10 +11700,10 @@
         <v>630</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>952</v>
+        <v>926</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1009</v>
+        <v>983</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>632</v>
@@ -11823,7 +11748,7 @@
         <v>643</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>935</v>
+        <v>909</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -11831,10 +11756,10 @@
         <v>644</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>953</v>
+        <v>927</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1010</v>
+        <v>984</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>646</v>
@@ -11861,7 +11786,7 @@
         <v>652</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>965</v>
+        <v>939</v>
       </c>
       <c r="M18" s="3" t="s">
         <v>654</v>
@@ -11879,18 +11804,18 @@
         <v>658</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>936</v>
+        <v>910</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>993</v>
+        <v>967</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>849</v>
+        <v>823</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1011</v>
+        <v>985</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>659</v>
@@ -11902,7 +11827,7 @@
         <v>661</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>982</v>
+        <v>956</v>
       </c>
       <c r="H19" s="8" t="s">
         <v>662</v>
@@ -11917,7 +11842,7 @@
         <v>665</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>966</v>
+        <v>940</v>
       </c>
       <c r="M19" s="3" t="s">
         <v>666</v>
@@ -11929,21 +11854,21 @@
         <v>668</v>
       </c>
       <c r="P19" s="8" t="s">
-        <v>974</v>
+        <v>948</v>
       </c>
       <c r="Q19" s="3" t="s">
         <v>669</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>937</v>
+        <v>911</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>994</v>
+        <v>968</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>954</v>
+        <v>928</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>499</v>
@@ -11958,7 +11883,7 @@
         <v>672</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>983</v>
+        <v>957</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>674</v>
@@ -11973,7 +11898,7 @@
         <v>677</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>967</v>
+        <v>941</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>678</v>
@@ -11991,7 +11916,7 @@
         <v>680</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>938</v>
+        <v>912</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -11999,7 +11924,7 @@
         <v>681</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>955</v>
+        <v>929</v>
       </c>
       <c r="C21" s="8" t="s">
         <v>645</v>
@@ -12035,10 +11960,10 @@
         <v>690</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>1018</v>
+        <v>992</v>
       </c>
       <c r="O21" s="8" t="s">
-        <v>987</v>
+        <v>961</v>
       </c>
       <c r="P21" s="8" t="s">
         <v>692</v>
@@ -12047,18 +11972,18 @@
         <v>693</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>939</v>
+        <v>913</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>995</v>
+        <v>969</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>706</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1012</v>
+        <v>986</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>694</v>
@@ -12067,7 +11992,7 @@
         <v>695</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>984</v>
+        <v>958</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>673</v>
@@ -12085,7 +12010,7 @@
         <v>699</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>968</v>
+        <v>942</v>
       </c>
       <c r="M22" s="3" t="s">
         <v>700</v>
@@ -12103,7 +12028,7 @@
         <v>704</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>940</v>
+        <v>914</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -12111,10 +12036,10 @@
         <v>705</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>853</v>
+        <v>827</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1013</v>
+        <v>987</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>707</v>
@@ -12147,7 +12072,7 @@
         <v>716</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>1019</v>
+        <v>993</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>717</v>
@@ -12159,7 +12084,7 @@
         <v>719</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>941</v>
+        <v>915</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -12167,10 +12092,10 @@
         <v>720</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>854</v>
+        <v>828</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1014</v>
+        <v>988</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>721</v>
@@ -12206,7 +12131,7 @@
         <v>731</v>
       </c>
       <c r="O24" s="8" t="s">
-        <v>988</v>
+        <v>962</v>
       </c>
       <c r="P24" s="8" t="s">
         <v>733</v>
@@ -12215,7 +12140,7 @@
         <v>734</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>942</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -12253,7 +12178,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>856</v>
+        <v>830</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>1</v>
@@ -12292,7 +12217,7 @@
         <v>12</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>892</v>
+        <v>866</v>
       </c>
       <c r="P1" s="3" t="s">
         <v>14</v>
@@ -12301,7 +12226,7 @@
         <v>15</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>895</v>
+        <v>869</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -12309,7 +12234,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>857</v>
+        <v>831</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>17</v>
@@ -12357,7 +12282,7 @@
         <v>31</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>896</v>
+        <v>870</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
@@ -12365,7 +12290,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>858</v>
+        <v>832</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>33</v>
@@ -12413,7 +12338,7 @@
         <v>47</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>897</v>
+        <v>871</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
@@ -12421,7 +12346,7 @@
         <v>48</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>859</v>
+        <v>833</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>49</v>
@@ -12469,7 +12394,7 @@
         <v>63</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>898</v>
+        <v>872</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
@@ -12477,7 +12402,7 @@
         <v>64</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>860</v>
+        <v>834</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>65</v>
@@ -12525,7 +12450,7 @@
         <v>79</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>899</v>
+        <v>873</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
@@ -12533,7 +12458,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>829</v>
+        <v>804</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>81</v>
@@ -12581,7 +12506,7 @@
         <v>95</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>900</v>
+        <v>874</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
@@ -12589,7 +12514,7 @@
         <v>96</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>861</v>
+        <v>835</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>97</v>
@@ -12637,7 +12562,7 @@
         <v>111</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>901</v>
+        <v>875</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
@@ -12645,7 +12570,7 @@
         <v>112</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>862</v>
+        <v>836</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>113</v>
@@ -12693,7 +12618,7 @@
         <v>127</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>902</v>
+        <v>876</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
@@ -12701,7 +12626,7 @@
         <v>128</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>863</v>
+        <v>837</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>129</v>
@@ -12749,7 +12674,7 @@
         <v>143</v>
       </c>
       <c r="R9" s="3" t="s">
-        <v>903</v>
+        <v>877</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
@@ -12757,10 +12682,10 @@
         <v>144</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>864</v>
+        <v>838</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>844</v>
+        <v>818</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>146</v>
@@ -12805,7 +12730,7 @@
         <v>145</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>904</v>
+        <v>878</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
@@ -12813,7 +12738,7 @@
         <v>159</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>865</v>
+        <v>839</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>160</v>
@@ -12861,7 +12786,7 @@
         <v>174</v>
       </c>
       <c r="R11" s="3" t="s">
-        <v>905</v>
+        <v>879</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
@@ -12869,7 +12794,7 @@
         <v>175</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>866</v>
+        <v>840</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>176</v>
@@ -12917,7 +12842,7 @@
         <v>190</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>906</v>
+        <v>880</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
@@ -12925,7 +12850,7 @@
         <v>191</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>867</v>
+        <v>841</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>192</v>
@@ -12973,7 +12898,7 @@
         <v>206</v>
       </c>
       <c r="R13" s="3" t="s">
-        <v>907</v>
+        <v>881</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
@@ -12981,7 +12906,7 @@
         <v>207</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>868</v>
+        <v>842</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>208</v>
@@ -13029,7 +12954,7 @@
         <v>222</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>908</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
@@ -13037,7 +12962,7 @@
         <v>223</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>869</v>
+        <v>843</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>224</v>
@@ -13085,7 +13010,7 @@
         <v>238</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>909</v>
+        <v>883</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.3">
@@ -13093,7 +13018,7 @@
         <v>239</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>870</v>
+        <v>844</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>240</v>
@@ -13141,7 +13066,7 @@
         <v>254</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>910</v>
+        <v>884</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.3">
@@ -13149,7 +13074,7 @@
         <v>255</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>871</v>
+        <v>845</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>256</v>
@@ -13197,7 +13122,7 @@
         <v>270</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>911</v>
+        <v>885</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.3">
@@ -13205,7 +13130,7 @@
         <v>271</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>872</v>
+        <v>846</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>272</v>
@@ -13253,7 +13178,7 @@
         <v>286</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>912</v>
+        <v>886</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.3">
@@ -13261,10 +13186,10 @@
         <v>287</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>873</v>
+        <v>847</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>894</v>
+        <v>868</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>288</v>
@@ -13309,7 +13234,7 @@
         <v>301</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>913</v>
+        <v>887</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.3">
@@ -13317,7 +13242,7 @@
         <v>302</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>874</v>
+        <v>848</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>303</v>
@@ -13365,7 +13290,7 @@
         <v>317</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>914</v>
+        <v>888</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.3">
@@ -13373,7 +13298,7 @@
         <v>318</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>875</v>
+        <v>849</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>319</v>
@@ -13421,7 +13346,7 @@
         <v>333</v>
       </c>
       <c r="R21" s="3" t="s">
-        <v>915</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.3">
@@ -13429,7 +13354,7 @@
         <v>334</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>876</v>
+        <v>850</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>335</v>
@@ -13477,7 +13402,7 @@
         <v>349</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>916</v>
+        <v>890</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.3">
@@ -13533,7 +13458,7 @@
         <v>365</v>
       </c>
       <c r="R23" s="3" t="s">
-        <v>917</v>
+        <v>891</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.3">
@@ -13541,7 +13466,7 @@
         <v>366</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>877</v>
+        <v>851</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>367</v>
@@ -13589,7 +13514,7 @@
         <v>381</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>918</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>
@@ -13674,7 +13599,7 @@
         <v>778</v>
       </c>
       <c r="D3" t="s">
-        <v>886</v>
+        <v>860</v>
       </c>
       <c r="E3">
         <v>100000000</v>
@@ -13720,7 +13645,7 @@
         <v>402</v>
       </c>
       <c r="B5" t="s">
-        <v>880</v>
+        <v>854</v>
       </c>
       <c r="C5" t="s">
         <v>750</v>
@@ -13928,7 +13853,7 @@
         <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>882</v>
+        <v>856</v>
       </c>
       <c r="C13" t="s">
         <v>763</v>
@@ -13983,10 +13908,10 @@
         <v>784</v>
       </c>
       <c r="C15" t="s">
-        <v>883</v>
+        <v>857</v>
       </c>
       <c r="D15" t="s">
-        <v>887</v>
+        <v>861</v>
       </c>
       <c r="E15">
         <v>100000000</v>
@@ -14003,16 +13928,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>855</v>
+        <v>829</v>
       </c>
       <c r="B16" t="s">
-        <v>878</v>
+        <v>852</v>
       </c>
       <c r="C16" t="s">
-        <v>884</v>
+        <v>858</v>
       </c>
       <c r="D16" t="s">
-        <v>888</v>
+        <v>862</v>
       </c>
       <c r="E16">
         <v>100000000</v>
@@ -14021,7 +13946,7 @@
         <v>137000000</v>
       </c>
       <c r="G16" t="s">
-        <v>890</v>
+        <v>864</v>
       </c>
       <c r="H16">
         <v>15</v>
@@ -14032,7 +13957,7 @@
         <v>403</v>
       </c>
       <c r="B17" t="s">
-        <v>881</v>
+        <v>855</v>
       </c>
       <c r="C17" t="s">
         <v>743</v>
@@ -14058,13 +13983,13 @@
         <v>425</v>
       </c>
       <c r="B18" t="s">
-        <v>879</v>
+        <v>853</v>
       </c>
       <c r="C18" t="s">
-        <v>885</v>
+        <v>859</v>
       </c>
       <c r="D18" t="s">
-        <v>889</v>
+        <v>863</v>
       </c>
       <c r="E18">
         <v>100000000</v>
@@ -14073,7 +13998,7 @@
         <v>181000000</v>
       </c>
       <c r="G18" t="s">
-        <v>891</v>
+        <v>865</v>
       </c>
       <c r="H18">
         <v>17</v>
@@ -14081,16 +14006,16 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>893</v>
+      </c>
+      <c r="B19" t="s">
+        <v>917</v>
+      </c>
+      <c r="C19" t="s">
+        <v>918</v>
+      </c>
+      <c r="D19" t="s">
         <v>919</v>
-      </c>
-      <c r="B19" t="s">
-        <v>943</v>
-      </c>
-      <c r="C19" t="s">
-        <v>944</v>
-      </c>
-      <c r="D19" t="s">
-        <v>945</v>
       </c>
       <c r="E19">
         <v>100000000</v>
@@ -14099,7 +14024,7 @@
         <v>210000000</v>
       </c>
       <c r="G19" t="s">
-        <v>946</v>
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -14114,7 +14039,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
@@ -14152,22 +14077,19 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>800</v>
+        <v>329</v>
       </c>
       <c r="B2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D2" t="s">
         <v>801</v>
       </c>
-      <c r="C2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>25</v>
-      </c>
-      <c r="F2" t="s">
-        <v>802</v>
+      <c r="F2">
+        <v>1</v>
       </c>
       <c r="G2" t="s">
         <v>803</v>
@@ -14175,22 +14097,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>221</v>
+        <v>805</v>
       </c>
       <c r="B3" t="s">
+        <v>802</v>
+      </c>
+      <c r="C3" t="s">
         <v>801</v>
       </c>
-      <c r="C3" t="s">
-        <v>411</v>
-      </c>
       <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3">
-        <v>50</v>
-      </c>
-      <c r="F3" t="s">
-        <v>802</v>
+        <v>407</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
       </c>
       <c r="G3" t="s">
         <v>803</v>
@@ -14198,22 +14117,19 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C4" t="s">
-        <v>411</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>120</v>
-      </c>
-      <c r="F4" t="s">
-        <v>802</v>
+        <v>12</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
       </c>
       <c r="G4" t="s">
         <v>803</v>
@@ -14221,22 +14137,19 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>394</v>
+        <v>172</v>
       </c>
       <c r="B5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C5" t="s">
-        <v>411</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
-        <v>804</v>
-      </c>
-      <c r="E5">
-        <v>65</v>
-      </c>
-      <c r="F5" t="s">
-        <v>802</v>
+        <v>13</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
       </c>
       <c r="G5" t="s">
         <v>803</v>
@@ -14244,22 +14157,22 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C6" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D6" t="s">
-        <v>423</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>90</v>
-      </c>
-      <c r="F6" t="s">
-        <v>802</v>
+        <v>40</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
       </c>
       <c r="G6" t="s">
         <v>803</v>
@@ -14267,22 +14180,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>806</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C7" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="D7" t="s">
-        <v>415</v>
+        <v>13</v>
       </c>
       <c r="E7">
-        <v>170</v>
-      </c>
-      <c r="F7" t="s">
-        <v>802</v>
+        <v>15</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
       </c>
       <c r="G7" t="s">
         <v>803</v>
@@ -14290,1006 +14203,144 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>807</v>
+        <v>930</v>
       </c>
       <c r="B8" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C8" t="s">
-        <v>420</v>
+        <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>411</v>
+        <v>829</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" t="s">
-        <v>802</v>
+      <c r="F8">
+        <v>2</v>
       </c>
       <c r="G8" t="s">
-        <v>809</v>
+        <v>931</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>810</v>
+        <v>932</v>
       </c>
       <c r="B9" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C9" t="s">
+        <v>407</v>
+      </c>
+      <c r="D9" t="s">
         <v>411</v>
-      </c>
-      <c r="D9" t="s">
-        <v>420</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" t="s">
-        <v>802</v>
+      <c r="F9">
+        <v>2</v>
       </c>
       <c r="G9" t="s">
-        <v>809</v>
+        <v>931</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>811</v>
+        <v>800</v>
       </c>
       <c r="B10" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C10" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="D10" t="s">
-        <v>804</v>
+        <v>407</v>
       </c>
       <c r="E10">
-        <v>68</v>
-      </c>
-      <c r="F10" t="s">
-        <v>802</v>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
       </c>
       <c r="G10" t="s">
-        <v>803</v>
+        <v>931</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>394</v>
+        <v>250</v>
       </c>
       <c r="B11" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C11" t="s">
-        <v>411</v>
+        <v>801</v>
       </c>
       <c r="D11" t="s">
-        <v>804</v>
+        <v>13</v>
       </c>
       <c r="E11">
-        <v>65</v>
-      </c>
-      <c r="F11" t="s">
-        <v>802</v>
+        <v>50</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
       </c>
       <c r="G11" t="s">
-        <v>803</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>813</v>
+        <v>994</v>
       </c>
       <c r="B12" t="s">
+        <v>802</v>
+      </c>
+      <c r="C12" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" t="s">
         <v>801</v>
       </c>
-      <c r="C12" t="s">
-        <v>804</v>
-      </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
       <c r="E12">
-        <v>100</v>
-      </c>
-      <c r="F12" t="s">
-        <v>802</v>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
       </c>
       <c r="G12" t="s">
-        <v>803</v>
+        <v>931</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s">
+        <v>802</v>
+      </c>
+      <c r="C13" t="s">
         <v>801</v>
       </c>
-      <c r="C13" t="s">
-        <v>804</v>
-      </c>
       <c r="D13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E13">
-        <v>90</v>
-      </c>
-      <c r="F13" t="s">
-        <v>802</v>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>814</v>
-      </c>
-      <c r="B14" t="s">
-        <v>808</v>
-      </c>
-      <c r="C14" t="s">
-        <v>804</v>
-      </c>
-      <c r="D14" t="s">
-        <v>409</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="s">
-        <v>802</v>
-      </c>
-      <c r="G14" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>815</v>
-      </c>
-      <c r="B15" t="s">
-        <v>808</v>
-      </c>
-      <c r="C15" t="s">
-        <v>409</v>
-      </c>
-      <c r="D15" t="s">
-        <v>804</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="s">
-        <v>802</v>
-      </c>
-      <c r="G15" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>816</v>
-      </c>
-      <c r="B16" t="s">
-        <v>812</v>
-      </c>
-      <c r="C16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D16" t="s">
-        <v>406</v>
-      </c>
-      <c r="E16">
-        <v>75</v>
-      </c>
-      <c r="F16" t="s">
-        <v>802</v>
-      </c>
-      <c r="G16" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>817</v>
-      </c>
-      <c r="B17" t="s">
-        <v>812</v>
-      </c>
-      <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17" t="s">
-        <v>406</v>
-      </c>
-      <c r="E17">
-        <v>60</v>
-      </c>
-      <c r="F17" t="s">
-        <v>802</v>
-      </c>
-      <c r="G17" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>818</v>
-      </c>
-      <c r="B18" t="s">
-        <v>801</v>
-      </c>
-      <c r="C18" t="s">
-        <v>406</v>
-      </c>
-      <c r="D18" t="s">
-        <v>422</v>
-      </c>
-      <c r="E18">
-        <v>20</v>
-      </c>
-      <c r="F18" t="s">
-        <v>802</v>
-      </c>
-      <c r="G18" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" t="s">
-        <v>812</v>
-      </c>
-      <c r="C19" t="s">
-        <v>819</v>
-      </c>
-      <c r="D19" t="s">
-        <v>420</v>
-      </c>
-      <c r="E19">
-        <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>802</v>
-      </c>
-      <c r="G19" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>820</v>
-      </c>
-      <c r="B20" t="s">
-        <v>808</v>
-      </c>
-      <c r="C20" t="s">
-        <v>819</v>
-      </c>
-      <c r="D20" t="s">
-        <v>420</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="s">
-        <v>802</v>
-      </c>
-      <c r="G20" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>83</v>
-      </c>
-      <c r="B21" t="s">
-        <v>808</v>
-      </c>
-      <c r="C21" t="s">
-        <v>420</v>
-      </c>
-      <c r="D21" t="s">
-        <v>819</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="s">
-        <v>802</v>
-      </c>
-      <c r="G21" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>821</v>
-      </c>
-      <c r="B22" t="s">
-        <v>812</v>
-      </c>
-      <c r="C22" t="s">
-        <v>422</v>
-      </c>
-      <c r="D22" t="s">
-        <v>819</v>
-      </c>
-      <c r="E22">
-        <v>136</v>
-      </c>
-      <c r="F22" t="s">
-        <v>802</v>
-      </c>
-      <c r="G22" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>822</v>
-      </c>
-      <c r="B23" t="s">
-        <v>808</v>
-      </c>
-      <c r="C23" t="s">
-        <v>407</v>
-      </c>
-      <c r="D23" t="s">
-        <v>819</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-      <c r="F23" t="s">
-        <v>802</v>
-      </c>
-      <c r="G23" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>233</v>
-      </c>
-      <c r="B24" t="s">
-        <v>808</v>
-      </c>
-      <c r="C24" t="s">
-        <v>819</v>
-      </c>
-      <c r="D24" t="s">
-        <v>407</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" t="s">
-        <v>802</v>
-      </c>
-      <c r="G24" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>115</v>
-      </c>
-      <c r="B25" t="s">
-        <v>808</v>
-      </c>
-      <c r="C25" t="s">
-        <v>823</v>
-      </c>
-      <c r="D25" t="s">
-        <v>819</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" t="s">
-        <v>802</v>
-      </c>
-      <c r="G25" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>155</v>
-      </c>
-      <c r="B26" t="s">
-        <v>808</v>
-      </c>
-      <c r="C26" t="s">
-        <v>819</v>
-      </c>
-      <c r="D26" t="s">
-        <v>823</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>802</v>
-      </c>
-      <c r="G26" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B27" t="s">
-        <v>812</v>
-      </c>
-      <c r="C27" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27">
-        <v>50</v>
-      </c>
-      <c r="F27" t="s">
-        <v>802</v>
-      </c>
-      <c r="G27" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>199</v>
-      </c>
-      <c r="B28" t="s">
-        <v>801</v>
-      </c>
-      <c r="C28" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" t="s">
-        <v>423</v>
-      </c>
-      <c r="E28">
-        <v>25</v>
-      </c>
-      <c r="F28" t="s">
-        <v>802</v>
-      </c>
-      <c r="G28" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>824</v>
-      </c>
-      <c r="B29" t="s">
-        <v>808</v>
-      </c>
-      <c r="C29" t="s">
-        <v>421</v>
-      </c>
-      <c r="D29" t="s">
-        <v>4</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29" t="s">
-        <v>802</v>
-      </c>
-      <c r="G29" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
-        <v>164</v>
-      </c>
-      <c r="B30" t="s">
-        <v>808</v>
-      </c>
-      <c r="C30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D30" t="s">
-        <v>421</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-      <c r="F30" t="s">
-        <v>802</v>
-      </c>
-      <c r="G30" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>165</v>
-      </c>
-      <c r="B31" t="s">
-        <v>812</v>
-      </c>
-      <c r="C31" t="s">
-        <v>420</v>
-      </c>
-      <c r="D31" t="s">
-        <v>422</v>
-      </c>
-      <c r="E31">
-        <v>80</v>
-      </c>
-      <c r="F31" t="s">
-        <v>802</v>
-      </c>
-      <c r="G31" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>134</v>
-      </c>
-      <c r="B32" t="s">
-        <v>812</v>
-      </c>
-      <c r="C32" t="s">
-        <v>14</v>
-      </c>
-      <c r="D32" t="s">
-        <v>422</v>
-      </c>
-      <c r="E32">
-        <v>20</v>
-      </c>
-      <c r="F32" t="s">
-        <v>802</v>
-      </c>
-      <c r="G32" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>167</v>
-      </c>
-      <c r="B33" t="s">
-        <v>801</v>
-      </c>
-      <c r="C33" t="s">
-        <v>422</v>
-      </c>
-      <c r="D33" t="s">
-        <v>423</v>
-      </c>
-      <c r="E33">
-        <v>20</v>
-      </c>
-      <c r="F33" t="s">
-        <v>802</v>
-      </c>
-      <c r="G33" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>332</v>
-      </c>
-      <c r="B34" t="s">
-        <v>808</v>
-      </c>
-      <c r="C34" t="s">
-        <v>422</v>
-      </c>
-      <c r="D34" t="s">
-        <v>14</v>
-      </c>
-      <c r="E34">
-        <v>60</v>
-      </c>
-      <c r="F34" t="s">
-        <v>802</v>
-      </c>
-      <c r="G34" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>825</v>
-      </c>
-      <c r="B35" t="s">
-        <v>808</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
-      <c r="D35" t="s">
-        <v>422</v>
-      </c>
-      <c r="E35">
-        <v>60</v>
-      </c>
-      <c r="F35" t="s">
-        <v>802</v>
-      </c>
-      <c r="G35" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" t="s">
-        <v>808</v>
-      </c>
-      <c r="C36" t="s">
-        <v>13</v>
-      </c>
-      <c r="D36" t="s">
-        <v>421</v>
-      </c>
-      <c r="E36">
-        <v>20</v>
-      </c>
-      <c r="F36" t="s">
-        <v>802</v>
-      </c>
-      <c r="G36" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>828</v>
-      </c>
-      <c r="B37" t="s">
-        <v>808</v>
-      </c>
-      <c r="C37" t="s">
-        <v>421</v>
-      </c>
-      <c r="D37" t="s">
-        <v>13</v>
-      </c>
-      <c r="E37">
-        <v>20</v>
-      </c>
-      <c r="F37" t="s">
-        <v>802</v>
-      </c>
-      <c r="G37" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>829</v>
-      </c>
-      <c r="B38" t="s">
-        <v>801</v>
-      </c>
-      <c r="C38" t="s">
-        <v>409</v>
-      </c>
-      <c r="D38" t="s">
-        <v>823</v>
-      </c>
-      <c r="E38">
-        <v>5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>802</v>
-      </c>
-      <c r="G38" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>329</v>
-      </c>
-      <c r="B39" t="s">
-        <v>826</v>
-      </c>
-      <c r="C39" t="s">
-        <v>407</v>
-      </c>
-      <c r="D39" t="s">
-        <v>823</v>
-      </c>
-      <c r="F39">
-        <v>1</v>
-      </c>
-      <c r="G39" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>830</v>
-      </c>
-      <c r="B40" t="s">
-        <v>826</v>
-      </c>
-      <c r="C40" t="s">
-        <v>823</v>
-      </c>
-      <c r="D40" t="s">
-        <v>407</v>
-      </c>
-      <c r="F40">
-        <v>1</v>
-      </c>
-      <c r="G40" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" t="s">
-        <v>156</v>
-      </c>
-      <c r="B41" t="s">
-        <v>826</v>
-      </c>
-      <c r="C41" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" t="s">
-        <v>12</v>
-      </c>
-      <c r="F41">
-        <v>1</v>
-      </c>
-      <c r="G41" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
-        <v>172</v>
-      </c>
-      <c r="B42" t="s">
-        <v>826</v>
-      </c>
-      <c r="C42" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" t="s">
-        <v>13</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>831</v>
-      </c>
-      <c r="B43" t="s">
-        <v>801</v>
-      </c>
-      <c r="C43" t="s">
-        <v>13</v>
-      </c>
-      <c r="D43" t="s">
-        <v>409</v>
-      </c>
-      <c r="E43">
-        <v>30</v>
-      </c>
-      <c r="F43" t="s">
-        <v>802</v>
-      </c>
-      <c r="G43" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>832</v>
-      </c>
-      <c r="B44" t="s">
-        <v>826</v>
-      </c>
-      <c r="C44" t="s">
-        <v>422</v>
-      </c>
-      <c r="D44" t="s">
-        <v>13</v>
-      </c>
-      <c r="E44">
-        <v>40</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" t="s">
-        <v>826</v>
-      </c>
-      <c r="C45" t="s">
-        <v>422</v>
-      </c>
-      <c r="D45" t="s">
-        <v>13</v>
-      </c>
-      <c r="E45">
-        <v>15</v>
-      </c>
-      <c r="F45">
-        <v>2</v>
-      </c>
-      <c r="G45" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>120</v>
-      </c>
-      <c r="B46" t="s">
-        <v>801</v>
-      </c>
-      <c r="C46" t="s">
-        <v>14</v>
-      </c>
-      <c r="D46" t="s">
-        <v>423</v>
-      </c>
-      <c r="E46">
-        <v>42</v>
-      </c>
-      <c r="F46" t="s">
-        <v>802</v>
-      </c>
-      <c r="G46" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" t="s">
-        <v>801</v>
-      </c>
-      <c r="C47" t="s">
-        <v>14</v>
-      </c>
-      <c r="D47" t="s">
-        <v>423</v>
-      </c>
-      <c r="E47">
-        <v>31</v>
-      </c>
-      <c r="F47" t="s">
-        <v>802</v>
-      </c>
-      <c r="G47" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
-        <v>247</v>
-      </c>
-      <c r="B48" t="s">
-        <v>801</v>
-      </c>
-      <c r="C48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" t="s">
-        <v>423</v>
-      </c>
-      <c r="E48">
-        <v>31</v>
-      </c>
-      <c r="F48" t="s">
-        <v>802</v>
-      </c>
-      <c r="G48" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>956</v>
-      </c>
-      <c r="B49" t="s">
-        <v>826</v>
-      </c>
-      <c r="C49" t="s">
-        <v>13</v>
-      </c>
-      <c r="D49" t="s">
-        <v>855</v>
-      </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
-      <c r="F49">
-        <v>2</v>
-      </c>
-      <c r="G49" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>958</v>
-      </c>
-      <c r="B50" t="s">
-        <v>826</v>
-      </c>
-      <c r="C50" t="s">
-        <v>407</v>
-      </c>
-      <c r="D50" t="s">
-        <v>411</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>2</v>
-      </c>
-      <c r="G50" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>807</v>
-      </c>
-      <c r="B51" t="s">
-        <v>826</v>
-      </c>
-      <c r="C51" t="s">
-        <v>411</v>
-      </c>
-      <c r="D51" t="s">
-        <v>407</v>
-      </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51" t="s">
-        <v>957</v>
+        <v>931</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
+  <autoFilter ref="A1:G51" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{506E0804-F1FC-4333-865B-F94E8291D793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E48D3BD-7696-4024-929A-8E0F363EC05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -10788,14 +10788,14 @@
     <col min="8" max="8" width="20.21875" style="9" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="20.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" style="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23.44140625" style="9" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="20.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.88671875" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="21.6640625" style="9" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" style="9" bestFit="1" customWidth="1"/>
     <col min="19" max="40" width="11.5546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10830,7 +10830,7 @@
       <c r="J1" s="8" t="s">
         <v>423</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="8" t="s">
         <v>9</v>
       </c>
       <c r="L1" s="8" t="s">
@@ -10851,7 +10851,7 @@
       <c r="Q1" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="8" t="s">
         <v>893</v>
       </c>
     </row>
@@ -10886,7 +10886,7 @@
       <c r="J2" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="8" t="s">
         <v>434</v>
       </c>
       <c r="L2" s="8" t="s">
@@ -10907,7 +10907,7 @@
       <c r="Q2" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="R2" s="8" t="s">
         <v>894</v>
       </c>
     </row>
@@ -10942,7 +10942,7 @@
       <c r="J3" s="8" t="s">
         <v>449</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="8" t="s">
         <v>447</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -10963,7 +10963,7 @@
       <c r="Q3" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="R3" s="8" t="s">
         <v>895</v>
       </c>
     </row>
@@ -10998,7 +10998,7 @@
       <c r="J4" s="8" t="s">
         <v>460</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="8" t="s">
         <v>461</v>
       </c>
       <c r="L4" s="8" t="s">
@@ -11019,7 +11019,7 @@
       <c r="Q4" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="R4" s="8" t="s">
         <v>896</v>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
       <c r="J5" s="8" t="s">
         <v>596</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="8" t="s">
         <v>477</v>
       </c>
       <c r="L5" s="8" t="s">
@@ -11075,7 +11075,7 @@
       <c r="Q5" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="R5" s="3" t="s">
+      <c r="R5" s="8" t="s">
         <v>897</v>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       <c r="J6" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="8" t="s">
         <v>491</v>
       </c>
       <c r="L6" s="8" t="s">
@@ -11131,7 +11131,7 @@
       <c r="Q6" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="R6" s="3" t="s">
+      <c r="R6" s="8" t="s">
         <v>898</v>
       </c>
     </row>
@@ -11166,7 +11166,7 @@
       <c r="J7" s="8" t="s">
         <v>506</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="K7" s="8" t="s">
         <v>507</v>
       </c>
       <c r="L7" s="8" t="s">
@@ -11187,7 +11187,7 @@
       <c r="Q7" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="R7" s="3" t="s">
+      <c r="R7" s="8" t="s">
         <v>899</v>
       </c>
     </row>
@@ -11222,7 +11222,7 @@
       <c r="J8" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="K8" s="8" t="s">
         <v>521</v>
       </c>
       <c r="L8" s="8" t="s">
@@ -11243,7 +11243,7 @@
       <c r="Q8" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="R8" s="3" t="s">
+      <c r="R8" s="8" t="s">
         <v>900</v>
       </c>
     </row>
@@ -11278,7 +11278,7 @@
       <c r="J9" s="8" t="s">
         <v>535</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="K9" s="8" t="s">
         <v>536</v>
       </c>
       <c r="L9" s="8" t="s">
@@ -11299,7 +11299,7 @@
       <c r="Q9" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="R9" s="8" t="s">
         <v>901</v>
       </c>
     </row>
@@ -11334,7 +11334,7 @@
       <c r="J10" s="8" t="s">
         <v>550</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="8" t="s">
         <v>551</v>
       </c>
       <c r="L10" s="8" t="s">
@@ -11355,7 +11355,7 @@
       <c r="Q10" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="R10" s="8" t="s">
         <v>902</v>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       <c r="J11" s="8" t="s">
         <v>561</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="8" t="s">
         <v>562</v>
       </c>
       <c r="L11" s="8" t="s">
@@ -11411,7 +11411,7 @@
       <c r="Q11" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="R11" s="8" t="s">
         <v>903</v>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       <c r="J12" s="8" t="s">
         <v>618</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="8" t="s">
         <v>573</v>
       </c>
       <c r="L12" s="8" t="s">
@@ -11467,7 +11467,7 @@
       <c r="Q12" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="R12" s="8" t="s">
         <v>904</v>
       </c>
     </row>
@@ -11502,7 +11502,7 @@
       <c r="J13" s="8" t="s">
         <v>819</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="8" t="s">
         <v>587</v>
       </c>
       <c r="L13" s="8" t="s">
@@ -11523,7 +11523,7 @@
       <c r="Q13" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="R13" s="8" t="s">
         <v>905</v>
       </c>
     </row>
@@ -11558,7 +11558,7 @@
       <c r="J14" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K14" s="8" t="s">
         <v>600</v>
       </c>
       <c r="L14" s="8" t="s">
@@ -11579,7 +11579,7 @@
       <c r="Q14" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="8" t="s">
         <v>906</v>
       </c>
     </row>
@@ -11614,7 +11614,7 @@
       <c r="J15" s="8" t="s">
         <v>610</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="K15" s="8" t="s">
         <v>611</v>
       </c>
       <c r="L15" s="8" t="s">
@@ -11635,7 +11635,7 @@
       <c r="Q15" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="R15" s="8" t="s">
         <v>907</v>
       </c>
     </row>
@@ -11670,7 +11670,7 @@
       <c r="J16" s="8" t="s">
         <v>624</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="K16" s="8" t="s">
         <v>625</v>
       </c>
       <c r="L16" s="8" t="s">
@@ -11691,7 +11691,7 @@
       <c r="Q16" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="R16" s="8" t="s">
         <v>908</v>
       </c>
     </row>
@@ -11726,7 +11726,7 @@
       <c r="J17" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K17" s="8" t="s">
         <v>638</v>
       </c>
       <c r="L17" s="8" t="s">
@@ -11747,7 +11747,7 @@
       <c r="Q17" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="R17" s="8" t="s">
         <v>909</v>
       </c>
     </row>
@@ -11782,7 +11782,7 @@
       <c r="J18" s="8" t="s">
         <v>651</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" s="8" t="s">
         <v>652</v>
       </c>
       <c r="L18" s="8" t="s">
@@ -11803,7 +11803,7 @@
       <c r="Q18" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="R18" s="8" t="s">
         <v>910</v>
       </c>
     </row>
@@ -11838,7 +11838,7 @@
       <c r="J19" s="8" t="s">
         <v>664</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="8" t="s">
         <v>665</v>
       </c>
       <c r="L19" s="8" t="s">
@@ -11859,7 +11859,7 @@
       <c r="Q19" s="3" t="s">
         <v>669</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="R19" s="8" t="s">
         <v>911</v>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
       <c r="J20" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="8" t="s">
         <v>677</v>
       </c>
       <c r="L20" s="8" t="s">
@@ -11915,7 +11915,7 @@
       <c r="Q20" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="R20" s="3" t="s">
+      <c r="R20" s="8" t="s">
         <v>912</v>
       </c>
     </row>
@@ -11950,7 +11950,7 @@
       <c r="J21" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="K21" s="8" t="s">
         <v>688</v>
       </c>
       <c r="L21" s="8" t="s">
@@ -11971,7 +11971,7 @@
       <c r="Q21" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="R21" s="3" t="s">
+      <c r="R21" s="8" t="s">
         <v>913</v>
       </c>
     </row>
@@ -12006,7 +12006,7 @@
       <c r="J22" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="K22" s="8" t="s">
         <v>699</v>
       </c>
       <c r="L22" s="8" t="s">
@@ -12027,7 +12027,7 @@
       <c r="Q22" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="R22" s="3" t="s">
+      <c r="R22" s="8" t="s">
         <v>914</v>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       <c r="J23" s="8" t="s">
         <v>713</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="K23" s="8" t="s">
         <v>714</v>
       </c>
       <c r="L23" s="8" t="s">
@@ -12083,7 +12083,7 @@
       <c r="Q23" s="3" t="s">
         <v>719</v>
       </c>
-      <c r="R23" s="3" t="s">
+      <c r="R23" s="8" t="s">
         <v>915</v>
       </c>
     </row>
@@ -12118,7 +12118,7 @@
       <c r="J24" s="8" t="s">
         <v>727</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="K24" s="8" t="s">
         <v>728</v>
       </c>
       <c r="L24" s="8" t="s">
@@ -12139,7 +12139,7 @@
       <c r="Q24" s="3" t="s">
         <v>734</v>
       </c>
-      <c r="R24" s="3" t="s">
+      <c r="R24" s="8" t="s">
         <v>916</v>
       </c>
     </row>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E48D3BD-7696-4024-929A-8E0F363EC05E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4BEA21-A18D-4D21-B18F-148B208640C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -3029,9 +3029,6 @@
     <t>MCD Mario Lemina</t>
   </si>
   <si>
-    <t>MC Eduardo Camavinga</t>
-  </si>
-  <si>
     <t>MP João Mário</t>
   </si>
   <si>
@@ -3053,9 +3050,6 @@
     <t>II Koki Ando</t>
   </si>
   <si>
-    <t>DC Carlos Espí</t>
-  </si>
-  <si>
     <t>II Nicola Zalewski</t>
   </si>
   <si>
@@ -3084,6 +3078,12 @@
   </si>
   <si>
     <t>Brahim Diaz</t>
+  </si>
+  <si>
+    <t>MCD Eduardo Camavinga</t>
+  </si>
+  <si>
+    <t>DC Igor Thiago</t>
   </si>
 </sst>
 </file>
@@ -10919,7 +10919,7 @@
         <v>495</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>441</v>
@@ -10975,7 +10975,7 @@
         <v>821</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>455</v>
@@ -11087,7 +11087,7 @@
         <v>820</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>974</v>
+        <v>469</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>485</v>
@@ -11143,7 +11143,7 @@
         <v>923</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>975</v>
+        <v>993</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>500</v>
@@ -11199,7 +11199,7 @@
         <v>924</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>515</v>
@@ -11255,7 +11255,7 @@
         <v>822</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>529</v>
@@ -11288,7 +11288,7 @@
         <v>537</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="O9" s="8" t="s">
         <v>539</v>
@@ -11311,7 +11311,7 @@
         <v>933</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>978</v>
+        <v>631</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>544</v>
@@ -11423,7 +11423,7 @@
         <v>580</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D12" s="8" t="s">
         <v>568</v>
@@ -11479,7 +11479,7 @@
         <v>824</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>581</v>
@@ -11512,7 +11512,7 @@
         <v>588</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="O13" s="8" t="s">
         <v>590</v>
@@ -11535,7 +11535,7 @@
         <v>825</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>593</v>
@@ -11568,7 +11568,7 @@
         <v>602</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="O14" s="8" t="s">
         <v>960</v>
@@ -11591,7 +11591,7 @@
         <v>925</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>469</v>
+        <v>975</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>944</v>
@@ -11647,7 +11647,7 @@
         <v>826</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>631</v>
+        <v>985</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>945</v>
@@ -11703,7 +11703,7 @@
         <v>926</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>632</v>
@@ -11759,7 +11759,7 @@
         <v>927</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>646</v>
@@ -11815,7 +11815,7 @@
         <v>823</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>659</v>
@@ -11871,7 +11871,7 @@
         <v>928</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>499</v>
+        <v>982</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>670</v>
@@ -11927,7 +11927,7 @@
         <v>929</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>645</v>
+        <v>499</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>682</v>
@@ -11960,7 +11960,7 @@
         <v>690</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="O21" s="8" t="s">
         <v>961</v>
@@ -11983,7 +11983,7 @@
         <v>706</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>986</v>
+        <v>645</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>694</v>
@@ -12039,7 +12039,7 @@
         <v>827</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>987</v>
+        <v>980</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>707</v>
@@ -12072,7 +12072,7 @@
         <v>716</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="O23" s="8" t="s">
         <v>717</v>
@@ -12095,7 +12095,7 @@
         <v>828</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>721</v>
@@ -14295,7 +14295,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="B12" t="s">
         <v>802</v>

--- a/lmi temp 10.xlsx
+++ b/lmi temp 10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alex1\Downloads\LMI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F4BEA21-A18D-4D21-B18F-148B208640C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14558BEA-6D80-4866-8DCA-3F4E01DF980B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registro Liga" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,12 @@
     <sheet name="CopaEstelar" sheetId="3" r:id="rId3"/>
     <sheet name="Registro Champions" sheetId="4" r:id="rId4"/>
     <sheet name="RegistroEstelar" sheetId="5" r:id="rId5"/>
-    <sheet name="Lista" sheetId="7" r:id="rId6"/>
-    <sheet name="BD" sheetId="6" r:id="rId7"/>
+    <sheet name="BD" sheetId="6" r:id="rId6"/>
+    <sheet name="Lista" sheetId="7" r:id="rId7"/>
     <sheet name="Clubes" sheetId="8" r:id="rId8"/>
     <sheet name="Mercado" sheetId="9" r:id="rId9"/>
     <sheet name="Campeones" sheetId="10" r:id="rId10"/>
+    <sheet name="RESPALDO" sheetId="11" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Clubes!$A$1:$H$19</definedName>
@@ -33,52 +34,52 @@
     <definedName name="AC_Milan">BD!$D$2:$D$24</definedName>
     <definedName name="AC_Milán">Lista!$E$2:$E$1048576</definedName>
     <definedName name="AcMilan">Lista!$E$2:$E$1048576</definedName>
-    <definedName name="Arsenal" localSheetId="6">BD!$J$2:$J$24</definedName>
+    <definedName name="Arsenal" localSheetId="5">BD!$J$2:$J$24</definedName>
     <definedName name="Arsenal">Lista!$K$2:$K$1048576</definedName>
     <definedName name="AstonVilla">Lista!$I$2:$I$1048576</definedName>
     <definedName name="Bayer_Munich">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Bayern_Leverkusen" localSheetId="6">BD!$E$2:$E$24</definedName>
+    <definedName name="Bayern_Leverkusen" localSheetId="5">BD!$E$2:$E$24</definedName>
     <definedName name="Bayern_Leverkusen">Lista!$F$2:$F$1048576</definedName>
     <definedName name="Bayern_Munich">BD!$N$2:$N$24</definedName>
-    <definedName name="Boca_Juniors" localSheetId="6">BD!$G$2:$G$24</definedName>
+    <definedName name="Boca_Juniors" localSheetId="5">BD!$G$2:$G$24</definedName>
     <definedName name="Boca_Juniors">Lista!$H$2:$H$1048576</definedName>
     <definedName name="BocaJuniors">Lista!$H$2:$H$1048576</definedName>
-    <definedName name="Como_1907" localSheetId="6">BD!$K$2:$K$24</definedName>
+    <definedName name="Como_1907" localSheetId="5">BD!$K$2:$K$24</definedName>
     <definedName name="COMO_1907">Lista!$L$2:$L$1048576</definedName>
     <definedName name="Como1907">Lista!$M$2:$M$1048576</definedName>
-    <definedName name="FC_Barcelona" localSheetId="6">BD!$C$2:$C$24</definedName>
+    <definedName name="FC_Barcelona" localSheetId="5">BD!$C$2:$C$24</definedName>
     <definedName name="FC_Barcelona">Lista!$C$2:$C$1048576</definedName>
     <definedName name="FcBarcelona">Lista!$C$2:$C$1048576</definedName>
-    <definedName name="Galatasaray" localSheetId="6">BD!$H$2:$H$24</definedName>
+    <definedName name="Galatasaray" localSheetId="5">BD!$H$2:$H$24</definedName>
     <definedName name="GALATASARAY">Lista!$I$2:$I$1048576</definedName>
-    <definedName name="Hellas_Verona" localSheetId="6">BD!$M$2:$M$24</definedName>
+    <definedName name="Hellas_Verona" localSheetId="5">BD!$M$2:$M$24</definedName>
     <definedName name="Hellas_Verona">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Inter_de_Milan" localSheetId="6">BD!$A$2:$A$24</definedName>
+    <definedName name="Inter_de_Milan" localSheetId="5">BD!$A$2:$A$24</definedName>
     <definedName name="Inter_de_Milan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="InterMilan">Lista!$A$2:$A$1048576</definedName>
     <definedName name="Leverkusen">Lista!$F$2:$F$1048576</definedName>
-    <definedName name="Manchester_United" localSheetId="6">BD!$O$2:$O$24</definedName>
+    <definedName name="Manchester_United" localSheetId="5">BD!$O$2:$O$24</definedName>
     <definedName name="Manchester_United">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Melbourne_City" localSheetId="6">BD!#REF!</definedName>
+    <definedName name="Melbourne_City" localSheetId="5">BD!#REF!</definedName>
     <definedName name="Melbourne_City">Lista!$Q$2:$Q$1048576</definedName>
     <definedName name="PARIS_SAINT___GERMAIN">Lista!$J$2:$J$1048576</definedName>
-    <definedName name="PSG" localSheetId="6">BD!$I$2:$I$23</definedName>
+    <definedName name="PSG" localSheetId="5">BD!$I$2:$I$23</definedName>
     <definedName name="PSG">Lista!$K$2:$K$1048576</definedName>
-    <definedName name="RB_Leipzig" localSheetId="6">BD!$F$2:$F$24</definedName>
+    <definedName name="RB_Leipzig" localSheetId="5">BD!$F$2:$F$24</definedName>
     <definedName name="RB_LEIPZIG">Lista!$G$2:$G$1048576</definedName>
     <definedName name="RBLeipzig">Lista!$G$2:$G$1048576</definedName>
-    <definedName name="Real_Madrid" localSheetId="6">BD!$B$2:$B$24</definedName>
+    <definedName name="Real_Madrid" localSheetId="5">BD!$B$2:$B$24</definedName>
     <definedName name="Real_Madrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="RealMadrid">Lista!$B$2:$B$1048576</definedName>
     <definedName name="Sparta">Lista!$P$2:$P$1048576</definedName>
-    <definedName name="Terengganu_FC" localSheetId="6">BD!#REF!</definedName>
+    <definedName name="Terengganu_FC" localSheetId="5">BD!#REF!</definedName>
     <definedName name="Terengganu_FC">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Terrengganu">Lista!$D$2:$D$1048576</definedName>
     <definedName name="Tottenham">Lista!$O$2:$O$1048576</definedName>
-    <definedName name="Tottenham_Hotspur" localSheetId="6">BD!$L$2:$L$24</definedName>
+    <definedName name="Tottenham_Hotspur" localSheetId="5">BD!$L$2:$L$24</definedName>
     <definedName name="Tottenham_Hotspur">Lista!$M$2:$M$1048576</definedName>
     <definedName name="United">Lista!$N$2:$N$1048576</definedName>
-    <definedName name="Wrexham" localSheetId="6">BD!$P$2:$P$24</definedName>
+    <definedName name="Wrexham" localSheetId="5">BD!$P$2:$P$24</definedName>
     <definedName name="WREXHAM">Lista!$R$2:$R$1048576</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -99,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="995">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2233" uniqueCount="1069">
   <si>
     <t>Inter_de_Milan</t>
   </si>
@@ -3084,6 +3085,228 @@
   </si>
   <si>
     <t>DC Igor Thiago</t>
+  </si>
+  <si>
+    <t>Crysencio Summerville</t>
+  </si>
+  <si>
+    <t>Julián Álvarez (P)</t>
+  </si>
+  <si>
+    <t>Marco Carnesecchi</t>
+  </si>
+  <si>
+    <t>Davinson Sánchez</t>
+  </si>
+  <si>
+    <t>Jarell Quansah</t>
+  </si>
+  <si>
+    <t>Kobbie Mainoo</t>
+  </si>
+  <si>
+    <t>Scott McTominay</t>
+  </si>
+  <si>
+    <t>Barış Alper Yılmaz</t>
+  </si>
+  <si>
+    <t>Ørjan Nyland</t>
+  </si>
+  <si>
+    <t>Trent Alexander-Arnold</t>
+  </si>
+  <si>
+    <t>Odilon Kossounou</t>
+  </si>
+  <si>
+    <t>Eliesse Ben Seghir</t>
+  </si>
+  <si>
+    <t>Pape Matar Sarr</t>
+  </si>
+  <si>
+    <t>Evan Ndicka</t>
+  </si>
+  <si>
+    <t>Senny Mayulu</t>
+  </si>
+  <si>
+    <t>Jorrel Hato</t>
+  </si>
+  <si>
+    <t>Manuel Neuer</t>
+  </si>
+  <si>
+    <t>Pedro Porro</t>
+  </si>
+  <si>
+    <t>Murilo</t>
+  </si>
+  <si>
+    <t>Daniel Ballard</t>
+  </si>
+  <si>
+    <t>Kaká</t>
+  </si>
+  <si>
+    <t>João Mário</t>
+  </si>
+  <si>
+    <t>Rafael Leão</t>
+  </si>
+  <si>
+    <t>Juan Pablo Freytes</t>
+  </si>
+  <si>
+    <t>Mario Lemina</t>
+  </si>
+  <si>
+    <t>Mykhailo Mudryk</t>
+  </si>
+  <si>
+    <t>Jadon Sancho</t>
+  </si>
+  <si>
+    <t>Nicola Zalewski</t>
+  </si>
+  <si>
+    <t>Ángel Di María</t>
+  </si>
+  <si>
+    <t>Koki Ando</t>
+  </si>
+  <si>
+    <t>Enzo Fernández</t>
+  </si>
+  <si>
+    <t>Giuliano Simeone</t>
+  </si>
+  <si>
+    <t>Igor Thiago</t>
+  </si>
+  <si>
+    <t>Jules Koundé</t>
+  </si>
+  <si>
+    <t>Micky van de Ven (P)</t>
+  </si>
+  <si>
+    <t>Rúben Dias</t>
+  </si>
+  <si>
+    <t>Jordan Pickford</t>
+  </si>
+  <si>
+    <t>Marc-André ter Stegen</t>
+  </si>
+  <si>
+    <t>Fabinho</t>
+  </si>
+  <si>
+    <t>Cafu</t>
+  </si>
+  <si>
+    <t>José María Giménez</t>
+  </si>
+  <si>
+    <t>Bruno Fernandes</t>
+  </si>
+  <si>
+    <t>João Félix</t>
+  </si>
+  <si>
+    <t>Edinson Cavani</t>
+  </si>
+  <si>
+    <t>Dejan Kulusevski</t>
+  </si>
+  <si>
+    <t>Luis Malagón</t>
+  </si>
+  <si>
+    <t>Lisandro Martínez</t>
+  </si>
+  <si>
+    <t>Ángel Correa</t>
+  </si>
+  <si>
+    <t>Álex Baena</t>
+  </si>
+  <si>
+    <t>Yoshinori Muto</t>
+  </si>
+  <si>
+    <t>Martin Terrier</t>
+  </si>
+  <si>
+    <t>Alejandro Zendejas</t>
+  </si>
+  <si>
+    <t>Youri Tielemans</t>
+  </si>
+  <si>
+    <t>Nico Paz</t>
+  </si>
+  <si>
+    <t>Lionel Messi (P)</t>
+  </si>
+  <si>
+    <t>Ousmane Dembélé (P)</t>
+  </si>
+  <si>
+    <t>Warren Zaïre-Emery</t>
+  </si>
+  <si>
+    <t>James Maddison</t>
+  </si>
+  <si>
+    <t>Arda Güler (P)</t>
+  </si>
+  <si>
+    <t>Uğurcan Çakır</t>
+  </si>
+  <si>
+    <t>Ferdi Kadıoğlu</t>
+  </si>
+  <si>
+    <t>João Palhinha</t>
+  </si>
+  <si>
+    <t>Xavi Simons</t>
+  </si>
+  <si>
+    <t>Joan García</t>
+  </si>
+  <si>
+    <t>Marc Guéhi</t>
+  </si>
+  <si>
+    <t>Ritsu Dōan</t>
+  </si>
+  <si>
+    <t>Christian Pulisic</t>
+  </si>
+  <si>
+    <t>Giovanni Di Lorenzo</t>
+  </si>
+  <si>
+    <t>Kenan Yıldız</t>
+  </si>
+  <si>
+    <t>Nick Woltemade</t>
+  </si>
+  <si>
+    <t>Jakub Kiwior</t>
+  </si>
+  <si>
+    <t>Maxi Araújo</t>
+  </si>
+  <si>
+    <t>Jonathan David</t>
+  </si>
+  <si>
+    <t>Khvicha Kvaratskhelia</t>
   </si>
 </sst>
 </file>
@@ -3955,7 +4178,7 @@
         <v>3</v>
       </c>
       <c r="D30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -4104,7 +4327,7 @@
         <v>332</v>
       </c>
       <c r="C41" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D41" s="3">
         <v>6</v>
@@ -4174,7 +4397,7 @@
         <v>126</v>
       </c>
       <c r="C46" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D46" s="3">
         <v>2</v>
@@ -4673,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.3">
@@ -5055,7 +5278,7 @@
         <v>316</v>
       </c>
       <c r="C113" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D113" s="3"/>
     </row>
@@ -5188,7 +5411,7 @@
       </c>
       <c r="C124" s="3"/>
       <c r="D124" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.3">
@@ -5340,11 +5563,11 @@
         <v>14</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="C137" s="3"/>
       <c r="D137" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.3">
@@ -5982,33 +6205,63 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
+      <c r="A190" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B190" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C190" s="3">
+        <v>1</v>
+      </c>
       <c r="D190" s="3"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
+      <c r="A191" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B191" s="3" t="s">
+        <v>1017</v>
+      </c>
       <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
+      <c r="D191" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
-      <c r="C192" s="3"/>
+      <c r="A192" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B192" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C192" s="3">
+        <v>1</v>
+      </c>
       <c r="D192" s="3"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
+      <c r="A193" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B193" s="3" t="s">
+        <v>1024</v>
+      </c>
       <c r="C193" s="3"/>
-      <c r="D193" s="3"/>
+      <c r="D193" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
-      <c r="C194" s="3"/>
+      <c r="A194" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B194" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C194" s="3">
+        <v>1</v>
+      </c>
       <c r="D194" s="3"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
@@ -6422,13 +6675,13 @@
           <x14:formula1>
             <xm:f>BD!$A$1:$Q$1</xm:f>
           </x14:formula1>
-          <xm:sqref>A122 A2 A6 A19 A30:A31 A61:A62 A69 A79 A93:A94 A114 A131:A168 A170:A260 A169</xm:sqref>
+          <xm:sqref>A122 A2 A6 A19 A30:A31 A61:A62 A69 A79 A93:A94 A114 A169 A170:A260 A131:A132 A134:A168 A133</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{648B5F03-60F3-4B0E-AC3D-96CE1E8ACD30}">
           <x14:formula1>
             <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A131, BD!$A$1:$Q$1, 0))</xm:f>
           </x14:formula1>
-          <xm:sqref>B131:B168 B170:B260 B169</xm:sqref>
+          <xm:sqref>B131:B168 B169 B170:B191 B193:B260 B192</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6597,6 +6850,1380 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E6A380-100E-4864-8D1E-3933CE66BBF3}">
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>832</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>818</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>846</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>849</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>851</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>892</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9250,7 +10877,7 @@
   <dimension ref="A1:D250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.21875" bestFit="1" customWidth="1"/>
@@ -9271,159 +10898,327 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
+      <c r="A2" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C2" s="6">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6"/>
+      <c r="A3" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>1007</v>
+      </c>
       <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
+      <c r="A4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
       <c r="D4" s="6"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>135</v>
+      </c>
       <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
+      <c r="A6" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>843</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
+      <c r="A7" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>845</v>
+      </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
+      <c r="D7" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
+      <c r="A8" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1</v>
+      </c>
       <c r="D8" s="6"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
+      <c r="A9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C9" s="6">
+        <v>1</v>
+      </c>
       <c r="D9" s="6"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="6"/>
+      <c r="A10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>103</v>
+      </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
+      <c r="A11" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>838</v>
+      </c>
+      <c r="C11" s="6">
+        <v>1</v>
+      </c>
       <c r="D11" s="6"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
+      <c r="A12" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>166</v>
+      </c>
       <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="A13" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="6">
+        <v>1</v>
+      </c>
       <c r="D13" s="6"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
+      <c r="A14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>193</v>
+      </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2</v>
+      </c>
       <c r="D15" s="6"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
+      <c r="A16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>318</v>
+      </c>
       <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" s="6">
+        <v>1</v>
+      </c>
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
+      <c r="A18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
+      <c r="A19" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1002</v>
+      </c>
       <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
+      <c r="D19" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
+      <c r="A20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C20" s="6">
+        <v>5</v>
+      </c>
+      <c r="D20" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>154</v>
+      </c>
       <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
+      <c r="D21" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
+      <c r="A22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C22" s="6">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
+      <c r="A23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>42</v>
+      </c>
       <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
+      <c r="A24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="C24" s="6">
+        <v>1</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C25" s="6">
+        <v>1</v>
+      </c>
       <c r="D25" s="6"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="A26" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="A27" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1</v>
+      </c>
       <c r="D27" s="6"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -10771,10 +12566,1402 @@
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{80716056-E58C-44FD-9475-0111955D70C7}">
+          <x14:formula1>
+            <xm:f>BD!$A$1:$Q$1</xm:f>
+          </x14:formula1>
+          <xm:sqref>A2:A250</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4BE0965E-3236-4355-A9BB-A514CCB13701}">
+          <x14:formula1>
+            <xm:f>INDEX(BD!$A$2:$Q$25, 0, MATCH(A2, BD!$A$1:$Q$1, 0))</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B250</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>830</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="R5" s="3" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>838</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>843</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>996</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>997</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>844</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>845</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>841</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>831</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>850</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>892</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:AN24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -12141,1380 +15328,6 @@
       </c>
       <c r="R24" s="8" t="s">
         <v>916</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:R24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>830</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>866</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>831</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>832</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>833</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="R4" s="3" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>834</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="R5" s="3" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>804</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="R6" s="3" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>835</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="R7" s="3" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>836</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>837</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q9" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>880</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>842</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>882</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>843</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="R15" s="3" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>844</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="N16" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="O16" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q16" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="R16" s="3" t="s">
-        <v>884</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>845</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="O17" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="Q17" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>846</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>847</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="N19" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="O19" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q19" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>848</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>849</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="O21" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>850</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>851</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>892</v>
       </c>
     </row>
   </sheetData>
